--- a/data/financeiro.xlsx
+++ b/data/financeiro.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
   <workbookPr codeName="EstaPastaDeTrabalho" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF7D0C2-29ED-47A9-960C-D817B61D9E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65708F8A-302A-4C8D-BA9E-617DD09D7885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -560,7 +560,7 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -580,6 +580,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="16">
     <cellStyle name="Comma" xfId="6" xr:uid="{159D0140-123F-46D6-AE51-0D51B924CA0F}"/>
@@ -2244,10 +2245,6 @@
           <cell r="D7" t="str">
             <v>INCORPORAÇÃO</v>
           </cell>
-          <cell r="E7"/>
-          <cell r="F7"/>
-          <cell r="G7"/>
-          <cell r="H7"/>
           <cell r="I7" t="str">
             <v>01 - INCORPORAÇÃO</v>
           </cell>
@@ -2261,38 +2258,34 @@
             <v>6370000</v>
           </cell>
           <cell r="N7">
-            <v>3968993.2399999993</v>
+            <v>4197678.5799999991</v>
           </cell>
           <cell r="O7">
-            <v>71560.45</v>
+            <v>83164.98000000001</v>
           </cell>
           <cell r="P7">
-            <v>92651.159999999989</v>
+            <v>82233.159999999989</v>
           </cell>
           <cell r="Q7">
             <v>0</v>
           </cell>
           <cell r="R7">
-            <v>4133204.8499999996</v>
+            <v>4363076.72</v>
           </cell>
           <cell r="T7">
-            <v>3576065.7200000007</v>
+            <v>3371401.4500000007</v>
           </cell>
           <cell r="U7">
-            <v>7709270.5700000003</v>
+            <v>7734478.1699999999</v>
           </cell>
           <cell r="V7">
-            <v>-1339270.5700000003</v>
+            <v>-1364478.17</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8" t="str">
             <v xml:space="preserve">REGISTROS, LICENÇAS E DESENVOLVIMENTO	</v>
           </cell>
-          <cell r="E8"/>
-          <cell r="F8"/>
-          <cell r="G8"/>
-          <cell r="H8"/>
           <cell r="I8" t="str">
             <v xml:space="preserve">01.001 - REGISTROS, LICENÇAS E DESENVOLVIMENTO	</v>
           </cell>
@@ -2306,38 +2299,34 @@
             <v>6370000</v>
           </cell>
           <cell r="N8">
-            <v>3968993.2399999993</v>
+            <v>4197678.5799999991</v>
           </cell>
           <cell r="O8">
-            <v>71560.45</v>
+            <v>83164.98000000001</v>
           </cell>
           <cell r="P8">
-            <v>92651.159999999989</v>
+            <v>82233.159999999989</v>
           </cell>
           <cell r="Q8">
             <v>0</v>
           </cell>
           <cell r="R8">
-            <v>4133204.8499999996</v>
+            <v>4363076.72</v>
           </cell>
           <cell r="T8">
-            <v>3576065.7200000007</v>
+            <v>3371401.4500000007</v>
           </cell>
           <cell r="U8">
-            <v>7709270.5700000003</v>
+            <v>7734478.1699999999</v>
           </cell>
           <cell r="V8">
-            <v>-1339270.5700000003</v>
+            <v>-1364478.17</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9" t="str">
             <v>REGISTROS, LICENÇAS E DESENVOLVIMENTO</v>
           </cell>
-          <cell r="E9"/>
-          <cell r="F9"/>
-          <cell r="G9"/>
-          <cell r="H9"/>
           <cell r="I9" t="str">
             <v>01.001.001 - REGISTROS, LICENÇAS E DESENVOLVIMENTO</v>
           </cell>
@@ -2538,10 +2527,6 @@
           <cell r="D13" t="str">
             <v>ACESSORIAS</v>
           </cell>
-          <cell r="E13"/>
-          <cell r="F13"/>
-          <cell r="G13"/>
-          <cell r="H13"/>
           <cell r="I13" t="str">
             <v>01.001.002 - ACESSORIAS</v>
           </cell>
@@ -2555,13 +2540,13 @@
             <v>134000</v>
           </cell>
           <cell r="N13">
-            <v>113612.31999999999</v>
+            <v>117630.31999999999</v>
           </cell>
           <cell r="O13">
             <v>0</v>
           </cell>
           <cell r="P13">
-            <v>16369.16</v>
+            <v>12351.16</v>
           </cell>
           <cell r="Q13">
             <v>0</v>
@@ -2608,13 +2593,13 @@
             <v>100000</v>
           </cell>
           <cell r="N14">
-            <v>99931.839999999997</v>
+            <v>103949.84</v>
           </cell>
           <cell r="O14">
             <v>0</v>
           </cell>
           <cell r="P14">
-            <v>16369.16</v>
+            <v>12351.16</v>
           </cell>
           <cell r="Q14">
             <v>0</v>
@@ -2742,10 +2727,6 @@
           <cell r="D17" t="str">
             <v>TERRENO</v>
           </cell>
-          <cell r="E17"/>
-          <cell r="F17"/>
-          <cell r="G17"/>
-          <cell r="H17"/>
           <cell r="I17" t="str">
             <v>01.001.003 - TERRENO</v>
           </cell>
@@ -2759,7 +2740,7 @@
             <v>150000</v>
           </cell>
           <cell r="N17">
-            <v>229442.61000000002</v>
+            <v>239938.21</v>
           </cell>
           <cell r="O17">
             <v>0</v>
@@ -2771,16 +2752,16 @@
             <v>0</v>
           </cell>
           <cell r="R17">
-            <v>229442.61000000002</v>
+            <v>239938.21</v>
           </cell>
           <cell r="T17">
             <v>0</v>
           </cell>
           <cell r="U17">
-            <v>229442.61000000002</v>
+            <v>239938.21</v>
           </cell>
           <cell r="V17">
-            <v>-79442.610000000015</v>
+            <v>-89938.209999999992</v>
           </cell>
         </row>
         <row r="18">
@@ -2865,7 +2846,7 @@
             <v>150000</v>
           </cell>
           <cell r="N19">
-            <v>206155.11000000002</v>
+            <v>216650.71</v>
           </cell>
           <cell r="O19">
             <v>0</v>
@@ -2877,26 +2858,22 @@
             <v>0</v>
           </cell>
           <cell r="R19">
-            <v>206155.11000000002</v>
+            <v>216650.71</v>
           </cell>
           <cell r="T19">
             <v>0</v>
           </cell>
           <cell r="U19">
-            <v>206155.11000000002</v>
+            <v>216650.71</v>
           </cell>
           <cell r="V19">
-            <v>-56155.110000000015</v>
+            <v>-66650.709999999992</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20" t="str">
             <v>VENDAS</v>
           </cell>
-          <cell r="E20"/>
-          <cell r="F20"/>
-          <cell r="G20"/>
-          <cell r="H20"/>
           <cell r="I20" t="str">
             <v>01.001.004 - VENDAS</v>
           </cell>
@@ -2910,28 +2887,28 @@
             <v>3500000</v>
           </cell>
           <cell r="N20">
-            <v>1567643.69</v>
+            <v>1635432.51</v>
           </cell>
           <cell r="O20">
-            <v>54520</v>
+            <v>54460</v>
           </cell>
           <cell r="P20">
-            <v>3532.2</v>
+            <v>2432.1999999999998</v>
           </cell>
           <cell r="Q20">
             <v>0</v>
           </cell>
           <cell r="R20">
-            <v>1625695.89</v>
+            <v>1692324.71</v>
           </cell>
           <cell r="T20">
-            <v>2244573.0100000002</v>
+            <v>2177944.19</v>
           </cell>
           <cell r="U20">
-            <v>3870268.9000000004</v>
+            <v>3870268.9</v>
           </cell>
           <cell r="V20">
-            <v>-370268.90000000037</v>
+            <v>-370268.89999999991</v>
           </cell>
         </row>
         <row r="21">
@@ -2963,10 +2940,10 @@
             <v>300000</v>
           </cell>
           <cell r="N21">
-            <v>489078.89</v>
+            <v>497578.89</v>
           </cell>
           <cell r="O21">
-            <v>1000</v>
+            <v>960</v>
           </cell>
           <cell r="P21">
             <v>0</v>
@@ -2975,10 +2952,10 @@
             <v>0</v>
           </cell>
           <cell r="R21">
-            <v>490078.89</v>
+            <v>498538.89</v>
           </cell>
           <cell r="T21">
-            <v>110500</v>
+            <v>102040</v>
           </cell>
           <cell r="U21">
             <v>600578.89</v>
@@ -3016,13 +2993,13 @@
             <v>300000</v>
           </cell>
           <cell r="N22">
-            <v>546811.29</v>
+            <v>547931.29</v>
           </cell>
           <cell r="O22">
-            <v>53520</v>
+            <v>53500</v>
           </cell>
           <cell r="P22">
-            <v>3532.2</v>
+            <v>2432.1999999999998</v>
           </cell>
           <cell r="Q22">
             <v>0</v>
@@ -3069,7 +3046,7 @@
             <v>1600000</v>
           </cell>
           <cell r="N23">
-            <v>188371.25</v>
+            <v>233069.19</v>
           </cell>
           <cell r="O23">
             <v>0</v>
@@ -3081,10 +3058,10 @@
             <v>0</v>
           </cell>
           <cell r="R23">
-            <v>188371.25</v>
+            <v>233069.19</v>
           </cell>
           <cell r="T23">
-            <v>652800</v>
+            <v>608102.06000000006</v>
           </cell>
           <cell r="U23">
             <v>841171.25</v>
@@ -3122,7 +3099,7 @@
             <v>1300000</v>
           </cell>
           <cell r="N24">
-            <v>231762.13999999998</v>
+            <v>245233.02</v>
           </cell>
           <cell r="O24">
             <v>0</v>
@@ -3134,10 +3111,10 @@
             <v>0</v>
           </cell>
           <cell r="R24">
-            <v>231762.13999999998</v>
+            <v>245233.02</v>
           </cell>
           <cell r="T24">
-            <v>1068237.8600000001</v>
+            <v>1054766.98</v>
           </cell>
           <cell r="U24">
             <v>1300000</v>
@@ -3203,10 +3180,6 @@
           <cell r="D26" t="str">
             <v>CARTEIRA E RECEBÍVEIS</v>
           </cell>
-          <cell r="E26"/>
-          <cell r="F26"/>
-          <cell r="G26"/>
-          <cell r="H26"/>
           <cell r="I26" t="str">
             <v>01.001.005 - CARTEIRA E RECEBÍVEIS</v>
           </cell>
@@ -3220,28 +3193,28 @@
             <v>627000</v>
           </cell>
           <cell r="N26">
-            <v>233878.2</v>
+            <v>242225.67000000004</v>
           </cell>
           <cell r="O26">
-            <v>17040.45</v>
+            <v>28704.980000000003</v>
           </cell>
           <cell r="P26">
-            <v>72749.799999999988</v>
+            <v>67449.799999999988</v>
           </cell>
           <cell r="Q26">
             <v>0</v>
           </cell>
           <cell r="R26">
-            <v>323668.45</v>
+            <v>338380.45</v>
           </cell>
           <cell r="T26">
             <v>382100.2</v>
           </cell>
           <cell r="U26">
-            <v>705768.65</v>
+            <v>720480.65</v>
           </cell>
           <cell r="V26">
-            <v>-78768.650000000023</v>
+            <v>-93480.650000000023</v>
           </cell>
         </row>
         <row r="27">
@@ -3273,13 +3246,13 @@
             <v>627000</v>
           </cell>
           <cell r="N27">
-            <v>166850</v>
+            <v>172150</v>
           </cell>
           <cell r="O27">
             <v>5300</v>
           </cell>
           <cell r="P27">
-            <v>72749.799999999988</v>
+            <v>67449.799999999988</v>
           </cell>
           <cell r="Q27">
             <v>0</v>
@@ -3326,10 +3299,10 @@
             <v>0</v>
           </cell>
           <cell r="N28">
-            <v>67028.200000000012</v>
+            <v>70075.670000000027</v>
           </cell>
           <cell r="O28">
-            <v>11740.45</v>
+            <v>23404.980000000003</v>
           </cell>
           <cell r="P28">
             <v>0</v>
@@ -3338,26 +3311,22 @@
             <v>0</v>
           </cell>
           <cell r="R28">
-            <v>78768.650000000009</v>
+            <v>93480.650000000023</v>
           </cell>
           <cell r="T28">
             <v>0</v>
           </cell>
           <cell r="U28">
-            <v>78768.650000000009</v>
+            <v>93480.650000000023</v>
           </cell>
           <cell r="V28">
-            <v>-78768.650000000009</v>
+            <v>-93480.650000000023</v>
           </cell>
         </row>
         <row r="29">
           <cell r="D29" t="str">
             <v>CUSTO COM FINANCIAMENTO</v>
           </cell>
-          <cell r="E29"/>
-          <cell r="F29"/>
-          <cell r="G29"/>
-          <cell r="H29"/>
           <cell r="I29" t="str">
             <v>01.001.006 - CUSTO COM FINANCIAMENTO</v>
           </cell>
@@ -3371,7 +3340,7 @@
             <v>990000</v>
           </cell>
           <cell r="N29">
-            <v>1327739.8099999998</v>
+            <v>1463488.65</v>
           </cell>
           <cell r="O29">
             <v>0</v>
@@ -3383,10 +3352,10 @@
             <v>0</v>
           </cell>
           <cell r="R29">
-            <v>1327739.8099999998</v>
+            <v>1463488.65</v>
           </cell>
           <cell r="T29">
-            <v>579028.08000000007</v>
+            <v>443279.24</v>
           </cell>
           <cell r="U29">
             <v>1906767.89</v>
@@ -3424,7 +3393,7 @@
             <v>900000</v>
           </cell>
           <cell r="N30">
-            <v>1297499.8099999998</v>
+            <v>1431808.65</v>
           </cell>
           <cell r="O30">
             <v>0</v>
@@ -3436,10 +3405,10 @@
             <v>0</v>
           </cell>
           <cell r="R30">
-            <v>1297499.8099999998</v>
+            <v>1431808.65</v>
           </cell>
           <cell r="T30">
-            <v>544468.08000000007</v>
+            <v>410159.24</v>
           </cell>
           <cell r="U30">
             <v>1841967.89</v>
@@ -3477,7 +3446,7 @@
             <v>90000</v>
           </cell>
           <cell r="N31">
-            <v>30240</v>
+            <v>31680</v>
           </cell>
           <cell r="O31">
             <v>0</v>
@@ -3489,10 +3458,10 @@
             <v>0</v>
           </cell>
           <cell r="R31">
-            <v>30240</v>
+            <v>31680</v>
           </cell>
           <cell r="T31">
-            <v>34560</v>
+            <v>33120</v>
           </cell>
           <cell r="U31">
             <v>64800</v>
@@ -3505,10 +3474,6 @@
           <cell r="D32" t="str">
             <v>DESPESAS BANCÁRIAS</v>
           </cell>
-          <cell r="E32"/>
-          <cell r="F32"/>
-          <cell r="G32"/>
-          <cell r="H32"/>
           <cell r="I32" t="str">
             <v>01.001.007 - DESPESAS BANCÁRIAS</v>
           </cell>
@@ -3522,7 +3487,7 @@
             <v>27000</v>
           </cell>
           <cell r="N32">
-            <v>71624.949999999168</v>
+            <v>73911.559999999139</v>
           </cell>
           <cell r="O32">
             <v>0</v>
@@ -3534,16 +3499,16 @@
             <v>0</v>
           </cell>
           <cell r="R32">
-            <v>71624.949999999168</v>
+            <v>73911.559999999139</v>
           </cell>
           <cell r="T32">
-            <v>20966.460000000166</v>
+            <v>18679.850000000166</v>
           </cell>
           <cell r="U32">
-            <v>92591.409999999334</v>
+            <v>92591.409999999305</v>
           </cell>
           <cell r="V32">
-            <v>-65591.409999999334</v>
+            <v>-65591.409999999305</v>
           </cell>
         </row>
         <row r="33">
@@ -3628,7 +3593,7 @@
             <v>15000</v>
           </cell>
           <cell r="N34">
-            <v>69534.949999999168</v>
+            <v>71821.559999999139</v>
           </cell>
           <cell r="O34">
             <v>0</v>
@@ -3640,26 +3605,22 @@
             <v>0</v>
           </cell>
           <cell r="R34">
-            <v>69534.949999999168</v>
+            <v>71821.559999999139</v>
           </cell>
           <cell r="T34">
-            <v>11056.460000000166</v>
+            <v>8769.8500000001659</v>
           </cell>
           <cell r="U34">
-            <v>80591.409999999334</v>
+            <v>80591.409999999305</v>
           </cell>
           <cell r="V34">
-            <v>-65591.409999999334</v>
+            <v>-65591.409999999305</v>
           </cell>
         </row>
         <row r="35">
           <cell r="D35" t="str">
             <v>DESPESAS FINAIS E OUTRAS DESPESAS</v>
           </cell>
-          <cell r="E35"/>
-          <cell r="F35"/>
-          <cell r="G35"/>
-          <cell r="H35"/>
           <cell r="I35" t="str">
             <v>01.001.008 - DESPESAS FINAIS E OUTRAS DESPESAS</v>
           </cell>
@@ -3860,10 +3821,6 @@
           <cell r="D39" t="str">
             <v>TAXAS ADMINISTRAÇÃO DE OBRA (BDI 10%)</v>
           </cell>
-          <cell r="E39"/>
-          <cell r="F39"/>
-          <cell r="G39"/>
-          <cell r="H39"/>
           <cell r="I39" t="str">
             <v>02 - TAXAS ADMINISTRAÇÃO DE OBRA (BDI 10%)</v>
           </cell>
@@ -3877,7 +3834,7 @@
             <v>2391066</v>
           </cell>
           <cell r="N39">
-            <v>1657021.3599999999</v>
+            <v>1752027.23</v>
           </cell>
           <cell r="O39">
             <v>0</v>
@@ -3889,26 +3846,22 @@
             <v>0</v>
           </cell>
           <cell r="R39">
-            <v>1657021.3599999999</v>
+            <v>1752027.23</v>
           </cell>
           <cell r="T39">
-            <v>610820.23800000036</v>
+            <v>517344.25500000035</v>
           </cell>
           <cell r="U39">
-            <v>2267841.5980000002</v>
+            <v>2269371.4850000003</v>
           </cell>
           <cell r="V39">
-            <v>123224.40199999977</v>
+            <v>121694.51499999966</v>
           </cell>
         </row>
         <row r="40">
           <cell r="D40" t="str">
             <v>TAXAS ADMINISTRAÇÃO DE OBRA (BDI 10%)</v>
           </cell>
-          <cell r="E40"/>
-          <cell r="F40"/>
-          <cell r="G40"/>
-          <cell r="H40"/>
           <cell r="I40" t="str">
             <v>02.001 - TAXAS ADMINISTRAÇÃO DE OBRA (BDI 10%)</v>
           </cell>
@@ -3922,7 +3875,7 @@
             <v>2391066</v>
           </cell>
           <cell r="N40">
-            <v>1657021.3599999999</v>
+            <v>1752027.23</v>
           </cell>
           <cell r="O40">
             <v>0</v>
@@ -3934,26 +3887,22 @@
             <v>0</v>
           </cell>
           <cell r="R40">
-            <v>1657021.3599999999</v>
+            <v>1752027.23</v>
           </cell>
           <cell r="T40">
-            <v>610820.23800000036</v>
+            <v>517344.25500000035</v>
           </cell>
           <cell r="U40">
-            <v>2267841.5980000002</v>
+            <v>2269371.4850000003</v>
           </cell>
           <cell r="V40">
-            <v>123224.40199999977</v>
+            <v>121694.51499999966</v>
           </cell>
         </row>
         <row r="41">
           <cell r="D41" t="str">
             <v>TAXAS ADMINISTRAÇÃO DE OBRA (BDI 10%)</v>
           </cell>
-          <cell r="E41"/>
-          <cell r="F41"/>
-          <cell r="G41"/>
-          <cell r="H41"/>
           <cell r="I41" t="str">
             <v>02.001.001 - TAXAS ADMINISTRAÇÃO DE OBRA (BDI 10%)</v>
           </cell>
@@ -3967,7 +3916,7 @@
             <v>2391066</v>
           </cell>
           <cell r="N41">
-            <v>1657021.3599999999</v>
+            <v>1752027.23</v>
           </cell>
           <cell r="O41">
             <v>0</v>
@@ -3979,16 +3928,16 @@
             <v>0</v>
           </cell>
           <cell r="R41">
-            <v>1657021.3599999999</v>
+            <v>1752027.23</v>
           </cell>
           <cell r="T41">
-            <v>610820.23800000036</v>
+            <v>517344.25500000035</v>
           </cell>
           <cell r="U41">
-            <v>2267841.5980000002</v>
+            <v>2269371.4850000003</v>
           </cell>
           <cell r="V41">
-            <v>123224.40199999977</v>
+            <v>121694.51499999966</v>
           </cell>
         </row>
         <row r="42">
@@ -4020,7 +3969,7 @@
             <v>2391066</v>
           </cell>
           <cell r="N42">
-            <v>1657021.3599999999</v>
+            <v>1752027.23</v>
           </cell>
           <cell r="O42">
             <v>0</v>
@@ -4032,16 +3981,16 @@
             <v>0</v>
           </cell>
           <cell r="R42">
-            <v>1657021.3599999999</v>
+            <v>1752027.23</v>
           </cell>
           <cell r="T42">
-            <v>610820.23800000036</v>
+            <v>517344.25500000035</v>
           </cell>
           <cell r="U42">
-            <v>2267841.5980000002</v>
+            <v>2269371.4850000003</v>
           </cell>
           <cell r="V42">
-            <v>123224.40199999977</v>
+            <v>121694.51499999966</v>
           </cell>
         </row>
         <row r="43">
@@ -4331,7 +4280,7 @@
             <v>0</v>
           </cell>
           <cell r="N49">
-            <v>970298.36</v>
+            <v>1587120.41</v>
           </cell>
           <cell r="O49">
             <v>0</v>
@@ -4343,16 +4292,16 @@
             <v>0</v>
           </cell>
           <cell r="R49">
-            <v>970298.36</v>
+            <v>1587120.41</v>
           </cell>
           <cell r="T49">
-            <v>-879346.6399999999</v>
+            <v>-1496168.69</v>
           </cell>
           <cell r="U49">
-            <v>90951.720000000088</v>
+            <v>90951.719999999972</v>
           </cell>
           <cell r="V49">
-            <v>-90951.720000000088</v>
+            <v>-90951.719999999972</v>
           </cell>
         </row>
       </sheetData>
@@ -4361,40 +4310,32 @@
       <sheetData sheetId="6"/>
       <sheetData sheetId="7">
         <row r="6">
-          <cell r="D6"/>
-          <cell r="E6"/>
-          <cell r="F6"/>
-          <cell r="G6"/>
-          <cell r="H6"/>
-          <cell r="I6"/>
-          <cell r="J6"/>
-          <cell r="K6"/>
           <cell r="L6">
             <v>23902729.770000003</v>
           </cell>
           <cell r="N6">
-            <v>16477114.23</v>
+            <v>17045781.460000001</v>
           </cell>
           <cell r="O6">
-            <v>691248.3600000001</v>
+            <v>704431.33</v>
           </cell>
           <cell r="P6">
-            <v>1532612.39</v>
+            <v>1530014.1</v>
           </cell>
           <cell r="Q6">
-            <v>129385.90000000001</v>
+            <v>64872.799999999996</v>
           </cell>
           <cell r="R6">
-            <v>18830360.879999999</v>
+            <v>19345099.690000001</v>
           </cell>
           <cell r="T6">
-            <v>3848055.1000000006</v>
+            <v>3348615.1599999997</v>
           </cell>
           <cell r="U6">
-            <v>22678415.98</v>
+            <v>22693714.850000001</v>
           </cell>
           <cell r="V6">
-            <v>1224313.7900000028</v>
+            <v>1209014.9200000018</v>
           </cell>
         </row>
         <row r="7">
@@ -4414,28 +4355,28 @@
             <v>5210747.9000000004</v>
           </cell>
           <cell r="N7">
-            <v>3472763.4400000004</v>
+            <v>3583045.09</v>
           </cell>
           <cell r="O7">
-            <v>90388.14</v>
+            <v>93549.959999999992</v>
           </cell>
           <cell r="P7">
-            <v>393999.49000000005</v>
+            <v>351579.85000000003</v>
           </cell>
           <cell r="Q7">
-            <v>2227.4899999999998</v>
+            <v>2411.5300000000002</v>
           </cell>
           <cell r="R7">
-            <v>3959378.560000001</v>
+            <v>4030586.4299999997</v>
           </cell>
           <cell r="T7">
-            <v>962323.25999999978</v>
+            <v>890347.6799999997</v>
           </cell>
           <cell r="U7">
-            <v>4921701.82</v>
+            <v>4920934.1099999994</v>
           </cell>
           <cell r="V7">
-            <v>289046.08000000007</v>
+            <v>289813.79000000097</v>
           </cell>
         </row>
         <row r="8">
@@ -4455,13 +4396,13 @@
             <v>891749.49</v>
           </cell>
           <cell r="N8">
-            <v>528081.84000000008</v>
+            <v>529117.84000000008</v>
           </cell>
           <cell r="O8">
             <v>1350</v>
           </cell>
           <cell r="P8">
-            <v>13325.9</v>
+            <v>12289.9</v>
           </cell>
           <cell r="Q8">
             <v>0</v>
@@ -5014,13 +4955,13 @@
             <v>524668.59</v>
           </cell>
           <cell r="N19">
-            <v>394603.27</v>
+            <v>395639.27</v>
           </cell>
           <cell r="O19">
             <v>1350</v>
           </cell>
           <cell r="P19">
-            <v>13325.9</v>
+            <v>12289.9</v>
           </cell>
           <cell r="Q19">
             <v>0</v>
@@ -5279,13 +5220,13 @@
             <v>140000</v>
           </cell>
           <cell r="N24">
-            <v>59916.68</v>
+            <v>60916.68</v>
           </cell>
           <cell r="O24">
             <v>0</v>
           </cell>
           <cell r="P24">
-            <v>8550</v>
+            <v>7550</v>
           </cell>
           <cell r="Q24">
             <v>0</v>
@@ -5293,7 +5234,6 @@
           <cell r="R24">
             <v>68466.679999999993</v>
           </cell>
-          <cell r="T24"/>
           <cell r="U24">
             <v>68466.679999999993</v>
           </cell>
@@ -5754,13 +5694,13 @@
             <v>11100</v>
           </cell>
           <cell r="N33">
-            <v>8458</v>
+            <v>8494</v>
           </cell>
           <cell r="O33">
             <v>0</v>
           </cell>
           <cell r="P33">
-            <v>3735.9</v>
+            <v>3699.9</v>
           </cell>
           <cell r="Q33">
             <v>0</v>
@@ -5795,28 +5735,28 @@
             <v>541800</v>
           </cell>
           <cell r="N34">
-            <v>439612.45000000007</v>
+            <v>447658.82000000007</v>
           </cell>
           <cell r="O34">
-            <v>11708.23</v>
+            <v>11472.399999999998</v>
           </cell>
           <cell r="P34">
-            <v>64824.01</v>
+            <v>62490.37</v>
           </cell>
           <cell r="Q34">
-            <v>482.47</v>
+            <v>52.300000000000004</v>
           </cell>
           <cell r="R34">
-            <v>516627.16000000003</v>
+            <v>521673.89000000007</v>
           </cell>
           <cell r="T34">
-            <v>88540.14</v>
+            <v>86517.679999999978</v>
           </cell>
           <cell r="U34">
-            <v>605167.30000000005</v>
+            <v>608191.57000000007</v>
           </cell>
           <cell r="V34">
-            <v>-63367.300000000047</v>
+            <v>-66391.570000000065</v>
           </cell>
         </row>
         <row r="35">
@@ -5836,28 +5776,28 @@
             <v>212000</v>
           </cell>
           <cell r="N35">
-            <v>202108.49</v>
+            <v>203830.85000000003</v>
           </cell>
           <cell r="O35">
-            <v>712</v>
+            <v>0</v>
           </cell>
           <cell r="P35">
-            <v>15864</v>
+            <v>18046</v>
           </cell>
           <cell r="Q35">
-            <v>49.5</v>
+            <v>0</v>
           </cell>
           <cell r="R35">
-            <v>218733.99</v>
+            <v>221876.85000000003</v>
           </cell>
           <cell r="T35">
-            <v>13382.500000000015</v>
+            <v>13202.86</v>
           </cell>
           <cell r="U35">
-            <v>232116.49</v>
+            <v>235079.71000000002</v>
           </cell>
           <cell r="V35">
-            <v>-20116.489999999991</v>
+            <v>-23079.710000000021</v>
           </cell>
         </row>
         <row r="36">
@@ -5889,7 +5829,7 @@
             <v>95000</v>
           </cell>
           <cell r="N36">
-            <v>128144.43000000001</v>
+            <v>128792.79000000001</v>
           </cell>
           <cell r="O36">
             <v>0</v>
@@ -5898,19 +5838,19 @@
             <v>10350</v>
           </cell>
           <cell r="Q36">
-            <v>49.5</v>
+            <v>0</v>
           </cell>
           <cell r="R36">
-            <v>138543.93</v>
+            <v>139142.79</v>
           </cell>
           <cell r="T36">
-            <v>179.64000000001397</v>
+            <v>0</v>
           </cell>
           <cell r="U36">
-            <v>138723.57</v>
+            <v>139142.79</v>
           </cell>
           <cell r="V36">
-            <v>-43723.570000000007</v>
+            <v>-44142.790000000008</v>
           </cell>
         </row>
         <row r="37">
@@ -5995,28 +5935,28 @@
             <v>18000</v>
           </cell>
           <cell r="N38">
-            <v>15384</v>
+            <v>15746</v>
           </cell>
           <cell r="O38">
             <v>0</v>
           </cell>
           <cell r="P38">
-            <v>5514</v>
+            <v>7696</v>
           </cell>
           <cell r="Q38">
             <v>0</v>
           </cell>
           <cell r="R38">
-            <v>20898</v>
+            <v>23442</v>
           </cell>
           <cell r="T38">
             <v>0</v>
           </cell>
           <cell r="U38">
-            <v>20898</v>
+            <v>23442</v>
           </cell>
           <cell r="V38">
-            <v>-2898</v>
+            <v>-5442</v>
           </cell>
         </row>
         <row r="39">
@@ -6260,10 +6200,10 @@
             <v>9000</v>
           </cell>
           <cell r="N43">
-            <v>3973.07</v>
+            <v>4685.07</v>
           </cell>
           <cell r="O43">
-            <v>712</v>
+            <v>0</v>
           </cell>
           <cell r="P43">
             <v>0</v>
@@ -6301,28 +6241,28 @@
             <v>329800</v>
           </cell>
           <cell r="N44">
-            <v>237503.96000000005</v>
+            <v>243827.97000000003</v>
           </cell>
           <cell r="O44">
-            <v>10996.23</v>
+            <v>11472.399999999998</v>
           </cell>
           <cell r="P44">
-            <v>48960.01</v>
+            <v>44444.37</v>
           </cell>
           <cell r="Q44">
-            <v>432.97</v>
+            <v>52.300000000000004</v>
           </cell>
           <cell r="R44">
-            <v>297893.17000000004</v>
+            <v>299797.04000000004</v>
           </cell>
           <cell r="T44">
-            <v>75157.639999999985</v>
+            <v>73314.819999999978</v>
           </cell>
           <cell r="U44">
-            <v>373050.81000000006</v>
+            <v>373111.86</v>
           </cell>
           <cell r="V44">
-            <v>-43250.810000000056</v>
+            <v>-43311.859999999986</v>
           </cell>
         </row>
         <row r="45">
@@ -6354,10 +6294,10 @@
             <v>18000</v>
           </cell>
           <cell r="N45">
-            <v>12243.62</v>
+            <v>13314.78</v>
           </cell>
           <cell r="O45">
-            <v>2571.16</v>
+            <v>1500</v>
           </cell>
           <cell r="P45">
             <v>0</v>
@@ -6407,10 +6347,10 @@
             <v>72000</v>
           </cell>
           <cell r="N46">
-            <v>31656.73</v>
+            <v>34202.479999999996</v>
           </cell>
           <cell r="O46">
-            <v>6000</v>
+            <v>5000</v>
           </cell>
           <cell r="P46">
             <v>0</v>
@@ -6419,10 +6359,10 @@
             <v>0</v>
           </cell>
           <cell r="R46">
-            <v>37656.729999999996</v>
+            <v>39202.479999999996</v>
           </cell>
           <cell r="T46">
-            <v>14290.940000000002</v>
+            <v>12745.190000000002</v>
           </cell>
           <cell r="U46">
             <v>51947.67</v>
@@ -6460,10 +6400,10 @@
             <v>10800</v>
           </cell>
           <cell r="N47">
-            <v>3969.429999999998</v>
+            <v>4089.4199999999978</v>
           </cell>
           <cell r="O47">
-            <v>870.09999999999991</v>
+            <v>750.1099999999999</v>
           </cell>
           <cell r="P47">
             <v>0</v>
@@ -6513,22 +6453,22 @@
             <v>7200</v>
           </cell>
           <cell r="N48">
-            <v>9839.9000000000015</v>
+            <v>10144.950000000003</v>
           </cell>
           <cell r="O48">
-            <v>175.7</v>
+            <v>292.24</v>
           </cell>
           <cell r="P48">
             <v>0</v>
           </cell>
           <cell r="Q48">
-            <v>409.35</v>
+            <v>52.300000000000004</v>
           </cell>
           <cell r="R48">
-            <v>10424.950000000003</v>
+            <v>10489.490000000002</v>
           </cell>
           <cell r="T48">
-            <v>4414.9499999999989</v>
+            <v>4350.41</v>
           </cell>
           <cell r="U48">
             <v>14839.900000000001</v>
@@ -6566,22 +6506,22 @@
             <v>7200</v>
           </cell>
           <cell r="N49">
-            <v>9791.4199999999983</v>
+            <v>9563.5899999999983</v>
           </cell>
           <cell r="O49">
-            <v>55.22</v>
+            <v>128</v>
           </cell>
           <cell r="P49">
             <v>0</v>
           </cell>
           <cell r="Q49">
-            <v>23.62</v>
+            <v>0</v>
           </cell>
           <cell r="R49">
-            <v>9870.2599999999984</v>
+            <v>9691.5899999999983</v>
           </cell>
           <cell r="T49">
-            <v>4779.4599999999991</v>
+            <v>4958.1299999999992</v>
           </cell>
           <cell r="U49">
             <v>14649.719999999998</v>
@@ -6619,13 +6559,13 @@
             <v>21600</v>
           </cell>
           <cell r="N50">
-            <v>31880.16</v>
+            <v>31960.16</v>
           </cell>
           <cell r="O50">
-            <v>0</v>
+            <v>2492</v>
           </cell>
           <cell r="P50">
-            <v>22536</v>
+            <v>19964</v>
           </cell>
           <cell r="Q50">
             <v>0</v>
@@ -6672,10 +6612,10 @@
             <v>36000</v>
           </cell>
           <cell r="N51">
-            <v>23354.760000000002</v>
+            <v>23429.81</v>
           </cell>
           <cell r="O51">
-            <v>14</v>
+            <v>0</v>
           </cell>
           <cell r="P51">
             <v>0</v>
@@ -6684,16 +6624,16 @@
             <v>0</v>
           </cell>
           <cell r="R51">
-            <v>23368.760000000002</v>
+            <v>23429.81</v>
           </cell>
           <cell r="T51">
             <v>0</v>
           </cell>
           <cell r="U51">
-            <v>23368.760000000002</v>
+            <v>23429.81</v>
           </cell>
           <cell r="V51">
-            <v>12631.239999999998</v>
+            <v>12570.189999999999</v>
           </cell>
         </row>
         <row r="52">
@@ -6937,7 +6877,7 @@
             <v>10000</v>
           </cell>
           <cell r="N56">
-            <v>388.84000000000003</v>
+            <v>885.8900000000001</v>
           </cell>
           <cell r="O56">
             <v>0</v>
@@ -6949,10 +6889,10 @@
             <v>0</v>
           </cell>
           <cell r="R56">
-            <v>388.84000000000003</v>
+            <v>885.8900000000001</v>
           </cell>
           <cell r="T56">
-            <v>9611.16</v>
+            <v>9114.11</v>
           </cell>
           <cell r="U56">
             <v>10000</v>
@@ -7043,22 +6983,22 @@
             <v>58800</v>
           </cell>
           <cell r="N58">
-            <v>52652.860000000037</v>
+            <v>53962.91000000004</v>
           </cell>
           <cell r="O58">
             <v>1310.05</v>
           </cell>
           <cell r="P58">
-            <v>18378.3</v>
+            <v>16982.400000000001</v>
           </cell>
           <cell r="Q58">
             <v>0</v>
           </cell>
           <cell r="R58">
-            <v>72341.210000000036</v>
+            <v>72255.360000000044</v>
           </cell>
           <cell r="T58">
-            <v>2925.109999999986</v>
+            <v>3010.9599999999773</v>
           </cell>
           <cell r="U58">
             <v>75266.320000000022</v>
@@ -7149,13 +7089,13 @@
             <v>24000</v>
           </cell>
           <cell r="N60">
-            <v>41877.039999999972</v>
+            <v>42424.77999999997</v>
           </cell>
           <cell r="O60">
             <v>0</v>
           </cell>
           <cell r="P60">
-            <v>8045.71</v>
+            <v>7497.97</v>
           </cell>
           <cell r="Q60">
             <v>0</v>
@@ -7190,28 +7130,28 @@
             <v>921807.4</v>
           </cell>
           <cell r="N61">
-            <v>610345.14</v>
+            <v>627501.06000000006</v>
           </cell>
           <cell r="O61">
-            <v>11391.74</v>
+            <v>16747.489999999998</v>
           </cell>
           <cell r="P61">
-            <v>147870</v>
+            <v>139270</v>
           </cell>
           <cell r="Q61">
-            <v>1745.02</v>
+            <v>2359.23</v>
           </cell>
           <cell r="R61">
-            <v>771351.9</v>
+            <v>785877.78</v>
           </cell>
           <cell r="T61">
-            <v>87542.99</v>
+            <v>79675.130000000019</v>
           </cell>
           <cell r="U61">
-            <v>858894.89</v>
+            <v>865552.91</v>
           </cell>
           <cell r="V61">
-            <v>62912.510000000009</v>
+            <v>56254.489999999991</v>
           </cell>
         </row>
         <row r="62">
@@ -7231,28 +7171,28 @@
             <v>683792.8</v>
           </cell>
           <cell r="N62">
-            <v>376617.16000000003</v>
+            <v>390649.28</v>
           </cell>
           <cell r="O62">
-            <v>9215.4599999999991</v>
+            <v>16211.68</v>
           </cell>
           <cell r="P62">
-            <v>147870</v>
+            <v>139270</v>
           </cell>
           <cell r="Q62">
             <v>0</v>
           </cell>
           <cell r="R62">
-            <v>533702.62000000011</v>
+            <v>546130.96</v>
           </cell>
           <cell r="T62">
-            <v>154182.12</v>
+            <v>149325.36000000002</v>
           </cell>
           <cell r="U62">
-            <v>687884.74000000011</v>
+            <v>695456.32</v>
           </cell>
           <cell r="V62">
-            <v>-4091.9400000000605</v>
+            <v>-11663.519999999902</v>
           </cell>
         </row>
         <row r="63">
@@ -7284,7 +7224,7 @@
             <v>16100</v>
           </cell>
           <cell r="N63">
-            <v>17600</v>
+            <v>22000</v>
           </cell>
           <cell r="O63">
             <v>2200</v>
@@ -7296,16 +7236,16 @@
             <v>0</v>
           </cell>
           <cell r="R63">
-            <v>19800</v>
+            <v>24200</v>
           </cell>
           <cell r="T63">
             <v>0</v>
           </cell>
           <cell r="U63">
-            <v>19800</v>
+            <v>24200</v>
           </cell>
           <cell r="V63">
-            <v>-3700</v>
+            <v>-8100</v>
           </cell>
         </row>
         <row r="64">
@@ -7390,28 +7330,28 @@
             <v>114000</v>
           </cell>
           <cell r="N65">
-            <v>13032.2</v>
+            <v>18106.280000000002</v>
           </cell>
           <cell r="O65">
-            <v>4768.5</v>
+            <v>3336</v>
           </cell>
           <cell r="P65">
-            <v>95579.51</v>
+            <v>91978.559999999998</v>
           </cell>
           <cell r="Q65">
             <v>0</v>
           </cell>
           <cell r="R65">
-            <v>113380.20999999999</v>
+            <v>113420.84</v>
           </cell>
           <cell r="T65">
             <v>0</v>
           </cell>
           <cell r="U65">
-            <v>113380.20999999999</v>
+            <v>113420.84</v>
           </cell>
           <cell r="V65">
-            <v>619.79000000000815</v>
+            <v>579.16000000000349</v>
           </cell>
         </row>
         <row r="66">
@@ -7446,25 +7386,25 @@
             <v>12405.93</v>
           </cell>
           <cell r="O66">
-            <v>0</v>
+            <v>3300</v>
           </cell>
           <cell r="P66">
-            <v>4900.51</v>
+            <v>1601.46</v>
           </cell>
           <cell r="Q66">
             <v>0</v>
           </cell>
           <cell r="R66">
-            <v>17306.440000000002</v>
+            <v>17307.39</v>
           </cell>
           <cell r="T66">
             <v>0</v>
           </cell>
           <cell r="U66">
-            <v>17306.440000000002</v>
+            <v>17307.39</v>
           </cell>
           <cell r="V66">
-            <v>-4306.4400000000023</v>
+            <v>-4307.3899999999994</v>
           </cell>
         </row>
         <row r="67">
@@ -7605,7 +7545,7 @@
             <v>267</v>
           </cell>
           <cell r="O69">
-            <v>0</v>
+            <v>110</v>
           </cell>
           <cell r="P69">
             <v>0</v>
@@ -7614,10 +7554,10 @@
             <v>0</v>
           </cell>
           <cell r="R69">
-            <v>267</v>
+            <v>377</v>
           </cell>
           <cell r="T69">
-            <v>401</v>
+            <v>291</v>
           </cell>
           <cell r="U69">
             <v>668</v>
@@ -7761,22 +7701,22 @@
             <v>352000</v>
           </cell>
           <cell r="N72">
-            <v>163416.95000000001</v>
+            <v>165624.99</v>
           </cell>
           <cell r="O72">
-            <v>226.96</v>
+            <v>4465.68</v>
           </cell>
           <cell r="P72">
-            <v>42500</v>
+            <v>40800</v>
           </cell>
           <cell r="Q72">
             <v>0</v>
           </cell>
           <cell r="R72">
-            <v>206143.91</v>
+            <v>210890.66999999998</v>
           </cell>
           <cell r="T72">
-            <v>145856.09</v>
+            <v>141109.33000000002</v>
           </cell>
           <cell r="U72">
             <v>352000</v>
@@ -8132,10 +8072,10 @@
             <v>20000</v>
           </cell>
           <cell r="N79">
-            <v>36197.68</v>
+            <v>36347.68</v>
           </cell>
           <cell r="O79">
-            <v>0</v>
+            <v>350</v>
           </cell>
           <cell r="P79">
             <v>0</v>
@@ -8144,16 +8084,16 @@
             <v>0</v>
           </cell>
           <cell r="R79">
-            <v>36197.68</v>
+            <v>36697.68</v>
           </cell>
           <cell r="T79">
             <v>0</v>
           </cell>
           <cell r="U79">
-            <v>36197.68</v>
+            <v>36697.68</v>
           </cell>
           <cell r="V79">
-            <v>-16197.68</v>
+            <v>-16697.68</v>
           </cell>
         </row>
         <row r="80">
@@ -8185,10 +8125,10 @@
             <v>30000</v>
           </cell>
           <cell r="N80">
-            <v>66134.709999999992</v>
+            <v>68334.709999999992</v>
           </cell>
           <cell r="O80">
-            <v>2020</v>
+            <v>2450</v>
           </cell>
           <cell r="P80">
             <v>0</v>
@@ -8197,16 +8137,16 @@
             <v>0</v>
           </cell>
           <cell r="R80">
-            <v>68154.709999999992</v>
+            <v>70784.709999999992</v>
           </cell>
           <cell r="T80">
             <v>0</v>
           </cell>
           <cell r="U80">
-            <v>68154.709999999992</v>
+            <v>70784.709999999992</v>
           </cell>
           <cell r="V80">
-            <v>-38154.709999999992</v>
+            <v>-40784.709999999992</v>
           </cell>
         </row>
         <row r="81">
@@ -8756,28 +8696,28 @@
             <v>30000</v>
           </cell>
           <cell r="N91">
-            <v>68840.409999999989</v>
+            <v>70155.169999999984</v>
           </cell>
           <cell r="O91">
-            <v>391.28</v>
+            <v>131.80000000000001</v>
           </cell>
           <cell r="P91">
             <v>0</v>
           </cell>
           <cell r="Q91">
-            <v>997.98</v>
+            <v>82.5</v>
           </cell>
           <cell r="R91">
-            <v>70229.669999999984</v>
+            <v>70369.469999999987</v>
           </cell>
           <cell r="T91">
-            <v>-49160.768999999986</v>
+            <v>-49258.628999999986</v>
           </cell>
           <cell r="U91">
-            <v>21068.900999999998</v>
+            <v>21110.841</v>
           </cell>
           <cell r="V91">
-            <v>8931.099000000002</v>
+            <v>8889.1589999999997</v>
           </cell>
         </row>
         <row r="92">
@@ -8809,28 +8749,28 @@
             <v>30000</v>
           </cell>
           <cell r="N92">
-            <v>68840.409999999989</v>
+            <v>70155.169999999984</v>
           </cell>
           <cell r="O92">
-            <v>391.28</v>
+            <v>131.80000000000001</v>
           </cell>
           <cell r="P92">
             <v>0</v>
           </cell>
           <cell r="Q92">
-            <v>997.98</v>
+            <v>82.5</v>
           </cell>
           <cell r="R92">
-            <v>70229.669999999984</v>
+            <v>70369.469999999987</v>
           </cell>
           <cell r="T92">
-            <v>-49160.768999999986</v>
+            <v>-49258.628999999986</v>
           </cell>
           <cell r="U92">
-            <v>21068.900999999998</v>
+            <v>21110.841</v>
           </cell>
           <cell r="V92">
-            <v>8931.099000000002</v>
+            <v>8889.1589999999997</v>
           </cell>
         </row>
         <row r="93">
@@ -8850,28 +8790,28 @@
             <v>208014.59999999998</v>
           </cell>
           <cell r="N93">
-            <v>164887.57</v>
+            <v>166696.61000000002</v>
           </cell>
           <cell r="O93">
-            <v>1785</v>
+            <v>404.01</v>
           </cell>
           <cell r="P93">
             <v>0</v>
           </cell>
           <cell r="Q93">
-            <v>747.04</v>
+            <v>2276.73</v>
           </cell>
           <cell r="R93">
-            <v>167419.61000000002</v>
+            <v>169377.35000000003</v>
           </cell>
           <cell r="T93">
-            <v>-17478.361000000001</v>
+            <v>-20391.601000000006</v>
           </cell>
           <cell r="U93">
-            <v>149941.24900000001</v>
+            <v>148985.74900000004</v>
           </cell>
           <cell r="V93">
-            <v>58073.350999999966</v>
+            <v>59028.850999999937</v>
           </cell>
         </row>
         <row r="94">
@@ -9062,10 +9002,10 @@
             <v>10000</v>
           </cell>
           <cell r="N97">
-            <v>21689.93</v>
+            <v>23054.93</v>
           </cell>
           <cell r="O97">
-            <v>1365</v>
+            <v>0</v>
           </cell>
           <cell r="P97">
             <v>0</v>
@@ -9077,13 +9017,13 @@
             <v>23054.93</v>
           </cell>
           <cell r="T97">
-            <v>-15182.950999999999</v>
+            <v>-16138.450999999999</v>
           </cell>
           <cell r="U97">
-            <v>7871.9790000000012</v>
+            <v>6916.4790000000012</v>
           </cell>
           <cell r="V97">
-            <v>2128.0209999999988</v>
+            <v>3083.5209999999988</v>
           </cell>
         </row>
         <row r="98">
@@ -9221,22 +9161,22 @@
             <v>73158.62</v>
           </cell>
           <cell r="N100">
-            <v>64809.549999999996</v>
+            <v>64833.59</v>
           </cell>
           <cell r="O100">
-            <v>0</v>
+            <v>404.01</v>
           </cell>
           <cell r="P100">
             <v>0</v>
           </cell>
           <cell r="Q100">
-            <v>747.04</v>
+            <v>2276.73</v>
           </cell>
           <cell r="R100">
-            <v>65556.59</v>
+            <v>67514.33</v>
           </cell>
           <cell r="T100">
-            <v>7602.0299999999988</v>
+            <v>5644.2899999999936</v>
           </cell>
           <cell r="U100">
             <v>73158.62</v>
@@ -9274,10 +9214,10 @@
             <v>19365.52</v>
           </cell>
           <cell r="N101">
-            <v>35149.47</v>
+            <v>35569.47</v>
           </cell>
           <cell r="O101">
-            <v>420</v>
+            <v>0</v>
           </cell>
           <cell r="P101">
             <v>0</v>
@@ -9527,28 +9467,28 @@
             <v>86500</v>
           </cell>
           <cell r="N106">
-            <v>89087.17</v>
+            <v>99537.17</v>
           </cell>
           <cell r="O106">
-            <v>10450</v>
+            <v>5500</v>
           </cell>
           <cell r="P106">
-            <v>41600</v>
+            <v>25650</v>
           </cell>
           <cell r="Q106">
             <v>0</v>
           </cell>
           <cell r="R106">
-            <v>141137.16999999998</v>
+            <v>130687.17</v>
           </cell>
           <cell r="T106">
             <v>8382.36</v>
           </cell>
           <cell r="U106">
-            <v>149519.52999999997</v>
+            <v>139069.53</v>
           </cell>
           <cell r="V106">
-            <v>-63019.52999999997</v>
+            <v>-52569.53</v>
           </cell>
         </row>
         <row r="107">
@@ -9568,28 +9508,28 @@
             <v>76500</v>
           </cell>
           <cell r="N107">
-            <v>88887.17</v>
+            <v>99337.17</v>
           </cell>
           <cell r="O107">
-            <v>10450</v>
+            <v>5500</v>
           </cell>
           <cell r="P107">
-            <v>41600</v>
+            <v>25650</v>
           </cell>
           <cell r="Q107">
             <v>0</v>
           </cell>
           <cell r="R107">
-            <v>140937.16999999998</v>
+            <v>130487.17</v>
           </cell>
           <cell r="T107">
             <v>-1417.6399999999994</v>
           </cell>
           <cell r="U107">
-            <v>139519.52999999997</v>
+            <v>129069.53</v>
           </cell>
           <cell r="V107">
-            <v>-63019.52999999997</v>
+            <v>-52569.53</v>
           </cell>
         </row>
         <row r="108">
@@ -9621,28 +9561,28 @@
             <v>66000</v>
           </cell>
           <cell r="N108">
-            <v>87447.03</v>
+            <v>97897.03</v>
           </cell>
           <cell r="O108">
-            <v>10450</v>
+            <v>5500</v>
           </cell>
           <cell r="P108">
-            <v>41600</v>
+            <v>25650</v>
           </cell>
           <cell r="Q108">
             <v>0</v>
           </cell>
           <cell r="R108">
-            <v>139497.03</v>
+            <v>129047.03</v>
           </cell>
           <cell r="T108">
             <v>-10477.5</v>
           </cell>
           <cell r="U108">
-            <v>129019.53</v>
+            <v>118569.53</v>
           </cell>
           <cell r="V108">
-            <v>-63019.53</v>
+            <v>-52569.53</v>
           </cell>
         </row>
         <row r="109">
@@ -9862,22 +9802,22 @@
             <v>2768891.01</v>
           </cell>
           <cell r="N113">
-            <v>1805636.84</v>
+            <v>1879230.2</v>
           </cell>
           <cell r="O113">
-            <v>55488.17</v>
+            <v>58480.07</v>
           </cell>
           <cell r="P113">
-            <v>126379.58</v>
+            <v>111879.58</v>
           </cell>
           <cell r="Q113">
             <v>0</v>
           </cell>
           <cell r="R113">
-            <v>1987504.59</v>
+            <v>2049589.85</v>
           </cell>
           <cell r="T113">
-            <v>578992.69999999972</v>
+            <v>516907.43999999977</v>
           </cell>
           <cell r="U113">
             <v>2566497.29</v>
@@ -9903,22 +9843,22 @@
             <v>1480467</v>
           </cell>
           <cell r="N114">
-            <v>815421.46</v>
+            <v>848385.48</v>
           </cell>
           <cell r="O114">
-            <v>30239.98</v>
+            <v>30333.29</v>
           </cell>
           <cell r="P114">
-            <v>126379.36</v>
+            <v>111879.36</v>
           </cell>
           <cell r="Q114">
             <v>0</v>
           </cell>
           <cell r="R114">
-            <v>972040.79999999993</v>
+            <v>990598.13</v>
           </cell>
           <cell r="T114">
-            <v>296920.76</v>
+            <v>278363.43000000005</v>
           </cell>
           <cell r="U114">
             <v>1268961.56</v>
@@ -9956,13 +9896,13 @@
             <v>380000</v>
           </cell>
           <cell r="N115">
-            <v>263520.68</v>
+            <v>274520.68</v>
           </cell>
           <cell r="O115">
-            <v>11000</v>
+            <v>12500</v>
           </cell>
           <cell r="P115">
-            <v>111229.32</v>
+            <v>98729.32</v>
           </cell>
           <cell r="Q115">
             <v>0</v>
@@ -10009,10 +9949,10 @@
             <v>478800</v>
           </cell>
           <cell r="N116">
-            <v>288490.42</v>
+            <v>299625.37000000005</v>
           </cell>
           <cell r="O116">
-            <v>9405.4599999999991</v>
+            <v>8441.98</v>
           </cell>
           <cell r="P116">
             <v>0</v>
@@ -10021,16 +9961,16 @@
             <v>0</v>
           </cell>
           <cell r="R116">
-            <v>297895.88</v>
+            <v>308067.35000000003</v>
           </cell>
           <cell r="T116">
-            <v>104973.15000000002</v>
+            <v>94801.680000000051</v>
           </cell>
           <cell r="U116">
-            <v>402869.03</v>
+            <v>402869.03000000009</v>
           </cell>
           <cell r="V116">
-            <v>75930.969999999972</v>
+            <v>75930.969999999914</v>
           </cell>
         </row>
         <row r="117">
@@ -10062,13 +10002,13 @@
             <v>108000</v>
           </cell>
           <cell r="N117">
-            <v>50972.29</v>
+            <v>52972.29</v>
           </cell>
           <cell r="O117">
             <v>2000</v>
           </cell>
           <cell r="P117">
-            <v>15150.039999999999</v>
+            <v>13150.039999999999</v>
           </cell>
           <cell r="Q117">
             <v>0</v>
@@ -10115,10 +10055,10 @@
             <v>96867</v>
           </cell>
           <cell r="N118">
-            <v>33585.639999999992</v>
+            <v>37538.969999999994</v>
           </cell>
           <cell r="O118">
-            <v>3953.33</v>
+            <v>3120</v>
           </cell>
           <cell r="P118">
             <v>0</v>
@@ -10127,10 +10067,10 @@
             <v>0</v>
           </cell>
           <cell r="R118">
-            <v>37538.969999999994</v>
+            <v>40658.969999999994</v>
           </cell>
           <cell r="T118">
-            <v>22290.9</v>
+            <v>19170.900000000001</v>
           </cell>
           <cell r="U118">
             <v>59829.869999999995</v>
@@ -10168,10 +10108,10 @@
             <v>190000</v>
           </cell>
           <cell r="N119">
-            <v>44245.330000000009</v>
+            <v>44265.330000000009</v>
           </cell>
           <cell r="O119">
-            <v>20</v>
+            <v>0</v>
           </cell>
           <cell r="P119">
             <v>0</v>
@@ -10221,10 +10161,10 @@
             <v>226800</v>
           </cell>
           <cell r="N120">
-            <v>134607.09999999998</v>
+            <v>139462.83999999997</v>
           </cell>
           <cell r="O120">
-            <v>3861.19</v>
+            <v>4271.3100000000004</v>
           </cell>
           <cell r="P120">
             <v>0</v>
@@ -10233,10 +10173,10 @@
             <v>0</v>
           </cell>
           <cell r="R120">
-            <v>138468.28999999998</v>
+            <v>143734.14999999997</v>
           </cell>
           <cell r="T120">
-            <v>36922.619999999995</v>
+            <v>31656.760000000009</v>
           </cell>
           <cell r="U120">
             <v>175390.90999999997</v>
@@ -10262,10 +10202,10 @@
             <v>1108398.01</v>
           </cell>
           <cell r="N121">
-            <v>790158.56000000017</v>
+            <v>830534.10000000021</v>
           </cell>
           <cell r="O121">
-            <v>25248.19</v>
+            <v>28106.799999999999</v>
           </cell>
           <cell r="P121">
             <v>0</v>
@@ -10274,16 +10214,16 @@
             <v>0</v>
           </cell>
           <cell r="R121">
-            <v>815406.75000000012</v>
+            <v>858640.90000000026</v>
           </cell>
           <cell r="T121">
-            <v>255631.25999999978</v>
+            <v>212397.10999999975</v>
           </cell>
           <cell r="U121">
-            <v>1071038.0099999998</v>
+            <v>1071038.01</v>
           </cell>
           <cell r="V121">
-            <v>37360.000000000233</v>
+            <v>37360</v>
           </cell>
         </row>
         <row r="122">
@@ -10368,10 +10308,10 @@
             <v>216466.69</v>
           </cell>
           <cell r="N123">
-            <v>202288.45</v>
+            <v>216693.69</v>
           </cell>
           <cell r="O123">
-            <v>9465</v>
+            <v>13513.730000000001</v>
           </cell>
           <cell r="P123">
             <v>0</v>
@@ -10380,10 +10320,10 @@
             <v>0</v>
           </cell>
           <cell r="R123">
-            <v>211753.45</v>
+            <v>230207.42</v>
           </cell>
           <cell r="T123">
-            <v>4713.2399999999907</v>
+            <v>-13740.73000000001</v>
           </cell>
           <cell r="U123">
             <v>216466.69</v>
@@ -10527,10 +10467,10 @@
             <v>453600</v>
           </cell>
           <cell r="N126">
-            <v>378513.98000000021</v>
+            <v>388836.93000000023</v>
           </cell>
           <cell r="O126">
-            <v>6265.42</v>
+            <v>9518.58</v>
           </cell>
           <cell r="P126">
             <v>0</v>
@@ -10539,10 +10479,10 @@
             <v>0</v>
           </cell>
           <cell r="R126">
-            <v>384779.4000000002</v>
+            <v>398355.51000000024</v>
           </cell>
           <cell r="T126">
-            <v>68820.599999999802</v>
+            <v>55244.489999999758</v>
           </cell>
           <cell r="U126">
             <v>453600</v>
@@ -10580,10 +10520,10 @@
             <v>172486.88</v>
           </cell>
           <cell r="N127">
-            <v>159667.24000000002</v>
+            <v>169457.83000000002</v>
           </cell>
           <cell r="O127">
-            <v>6308.2</v>
+            <v>3636.51</v>
           </cell>
           <cell r="P127">
             <v>0</v>
@@ -10592,10 +10532,10 @@
             <v>0</v>
           </cell>
           <cell r="R127">
-            <v>165975.44000000003</v>
+            <v>173094.34000000003</v>
           </cell>
           <cell r="T127">
-            <v>6511.4399999999732</v>
+            <v>-607.46000000002095</v>
           </cell>
           <cell r="U127">
             <v>172486.88</v>
@@ -10633,10 +10573,10 @@
             <v>151200</v>
           </cell>
           <cell r="N128">
-            <v>42550.119999999995</v>
+            <v>48406.879999999997</v>
           </cell>
           <cell r="O128">
-            <v>3209.5699999999997</v>
+            <v>1437.98</v>
           </cell>
           <cell r="P128">
             <v>0</v>
@@ -10645,10 +10585,10 @@
             <v>0</v>
           </cell>
           <cell r="R128">
-            <v>45759.689999999995</v>
+            <v>49844.86</v>
           </cell>
           <cell r="T128">
-            <v>105440.31</v>
+            <v>101355.14</v>
           </cell>
           <cell r="U128">
             <v>151200</v>
@@ -10674,10 +10614,10 @@
             <v>180026</v>
           </cell>
           <cell r="N129">
-            <v>200056.82</v>
+            <v>200310.61999999997</v>
           </cell>
           <cell r="O129">
-            <v>0</v>
+            <v>39.979999999999997</v>
           </cell>
           <cell r="P129">
             <v>0.21999999999999997</v>
@@ -10686,16 +10626,16 @@
             <v>0</v>
           </cell>
           <cell r="R129">
-            <v>200057.04</v>
+            <v>200350.81999999998</v>
           </cell>
           <cell r="T129">
-            <v>26440.679999999953</v>
+            <v>26146.899999999954</v>
           </cell>
           <cell r="U129">
-            <v>226497.71999999997</v>
+            <v>226497.71999999994</v>
           </cell>
           <cell r="V129">
-            <v>-46471.719999999972</v>
+            <v>-46471.719999999943</v>
           </cell>
         </row>
         <row r="130">
@@ -10727,10 +10667,10 @@
             <v>30690</v>
           </cell>
           <cell r="N130">
-            <v>31453.569999999996</v>
+            <v>31527.169999999995</v>
           </cell>
           <cell r="O130">
-            <v>0</v>
+            <v>39.979999999999997</v>
           </cell>
           <cell r="P130">
             <v>0.13999999999999999</v>
@@ -10739,10 +10679,10 @@
             <v>0</v>
           </cell>
           <cell r="R130">
-            <v>31453.709999999995</v>
+            <v>31567.289999999994</v>
           </cell>
           <cell r="T130">
-            <v>2285.4300000000039</v>
+            <v>2171.8500000000022</v>
           </cell>
           <cell r="U130">
             <v>33739.14</v>
@@ -10833,7 +10773,7 @@
             <v>31691</v>
           </cell>
           <cell r="N132">
-            <v>56766.739999999983</v>
+            <v>56946.939999999981</v>
           </cell>
           <cell r="O132">
             <v>0</v>
@@ -10845,10 +10785,10 @@
             <v>0</v>
           </cell>
           <cell r="R132">
-            <v>56766.739999999983</v>
+            <v>56946.939999999981</v>
           </cell>
           <cell r="T132">
-            <v>12610.949999999961</v>
+            <v>12430.749999999964</v>
           </cell>
           <cell r="U132">
             <v>69377.689999999944</v>
@@ -10874,28 +10814,28 @@
             <v>18691981.870000001</v>
           </cell>
           <cell r="N133">
-            <v>13004350.790000001</v>
+            <v>13462736.370000001</v>
           </cell>
           <cell r="O133">
-            <v>600860.22000000009</v>
+            <v>610881.37</v>
           </cell>
           <cell r="P133">
-            <v>1138612.8999999999</v>
+            <v>1178434.25</v>
           </cell>
           <cell r="Q133">
-            <v>127158.41</v>
+            <v>62461.27</v>
           </cell>
           <cell r="R133">
-            <v>14870982.320000002</v>
+            <v>15314513.26</v>
           </cell>
           <cell r="T133">
-            <v>2885731.8400000008</v>
+            <v>2458267.48</v>
           </cell>
           <cell r="U133">
-            <v>17756714.160000004</v>
+            <v>17772780.739999998</v>
           </cell>
           <cell r="V133">
-            <v>935267.70999999717</v>
+            <v>919201.13000000268</v>
           </cell>
         </row>
         <row r="134">
@@ -11397,10 +11337,10 @@
             <v>644368.6</v>
           </cell>
           <cell r="N144">
-            <v>730899.98999999987</v>
+            <v>731519.75999999989</v>
           </cell>
           <cell r="O144">
-            <v>1239.54</v>
+            <v>3411.15</v>
           </cell>
           <cell r="P144">
             <v>1711.28</v>
@@ -11409,16 +11349,16 @@
             <v>1424</v>
           </cell>
           <cell r="R144">
-            <v>735274.80999999994</v>
+            <v>738066.19</v>
           </cell>
           <cell r="T144">
             <v>0</v>
           </cell>
           <cell r="U144">
-            <v>735274.80999999994</v>
+            <v>738066.19</v>
           </cell>
           <cell r="V144">
-            <v>-90906.209999999963</v>
+            <v>-93697.589999999967</v>
           </cell>
         </row>
         <row r="145">
@@ -12062,10 +12002,10 @@
             <v>222047.29</v>
           </cell>
           <cell r="N157">
-            <v>233626.42999999993</v>
+            <v>234246.19999999995</v>
           </cell>
           <cell r="O157">
-            <v>1239.54</v>
+            <v>3411.15</v>
           </cell>
           <cell r="P157">
             <v>29</v>
@@ -12074,16 +12014,16 @@
             <v>1424</v>
           </cell>
           <cell r="R157">
-            <v>236318.96999999994</v>
+            <v>239110.34999999995</v>
           </cell>
           <cell r="T157">
             <v>0</v>
           </cell>
           <cell r="U157">
-            <v>236318.96999999994</v>
+            <v>239110.34999999995</v>
           </cell>
           <cell r="V157">
-            <v>-14271.679999999935</v>
+            <v>-17063.059999999939</v>
           </cell>
         </row>
         <row r="158">
@@ -12330,7 +12270,7 @@
             <v>83728.84</v>
           </cell>
           <cell r="O162">
-            <v>0</v>
+            <v>2592.38</v>
           </cell>
           <cell r="P162">
             <v>0</v>
@@ -12339,16 +12279,16 @@
             <v>1424</v>
           </cell>
           <cell r="R162">
-            <v>85152.84</v>
+            <v>87745.22</v>
           </cell>
           <cell r="T162">
             <v>0</v>
           </cell>
           <cell r="U162">
-            <v>85152.84</v>
+            <v>87745.22</v>
           </cell>
           <cell r="V162">
-            <v>58985.300000000017</v>
+            <v>56392.920000000013</v>
           </cell>
         </row>
         <row r="163">
@@ -12380,10 +12320,10 @@
             <v>40000</v>
           </cell>
           <cell r="N163">
-            <v>133440.16999999995</v>
+            <v>134059.93999999994</v>
           </cell>
           <cell r="O163">
-            <v>1239.54</v>
+            <v>818.77</v>
           </cell>
           <cell r="P163">
             <v>0</v>
@@ -12392,16 +12332,16 @@
             <v>0</v>
           </cell>
           <cell r="R163">
-            <v>134679.70999999996</v>
+            <v>134878.70999999993</v>
           </cell>
           <cell r="T163">
             <v>0</v>
           </cell>
           <cell r="U163">
-            <v>134679.70999999996</v>
+            <v>134878.70999999993</v>
           </cell>
           <cell r="V163">
-            <v>-94679.709999999963</v>
+            <v>-94878.709999999934</v>
           </cell>
         </row>
         <row r="164">
@@ -13804,28 +13744,28 @@
             <v>5180115.879999999</v>
           </cell>
           <cell r="N191">
-            <v>5182902.040000001</v>
+            <v>5188602.8400000008</v>
           </cell>
           <cell r="O191">
-            <v>6189.5</v>
+            <v>2139.3000000000002</v>
           </cell>
           <cell r="P191">
-            <v>28490.659999999996</v>
+            <v>28050.639999999996</v>
           </cell>
           <cell r="Q191">
-            <v>0</v>
+            <v>195.62</v>
           </cell>
           <cell r="R191">
-            <v>5217582.2000000011</v>
+            <v>5218988.4000000004</v>
           </cell>
           <cell r="T191">
             <v>-137000</v>
           </cell>
           <cell r="U191">
-            <v>5080582.2000000011</v>
+            <v>5081988.4000000004</v>
           </cell>
           <cell r="V191">
-            <v>99533.679999997839</v>
+            <v>98127.479999998584</v>
           </cell>
         </row>
         <row r="192">
@@ -13998,22 +13938,22 @@
             <v>134.52000000000001</v>
           </cell>
           <cell r="P195">
-            <v>440.02</v>
+            <v>0</v>
           </cell>
           <cell r="Q195">
             <v>0</v>
           </cell>
           <cell r="R195">
-            <v>469898.79000000004</v>
+            <v>469458.77</v>
           </cell>
           <cell r="T195">
             <v>0</v>
           </cell>
           <cell r="U195">
-            <v>469898.79000000004</v>
+            <v>469458.77</v>
           </cell>
           <cell r="V195">
-            <v>20813.509999999835</v>
+            <v>21253.529999999853</v>
           </cell>
         </row>
         <row r="196">
@@ -14846,22 +14786,22 @@
             <v>0</v>
           </cell>
           <cell r="P211">
-            <v>440.02</v>
+            <v>0</v>
           </cell>
           <cell r="Q211">
             <v>0</v>
           </cell>
           <cell r="R211">
-            <v>31939.760000000002</v>
+            <v>31499.74</v>
           </cell>
           <cell r="T211">
             <v>0</v>
           </cell>
           <cell r="U211">
-            <v>31939.760000000002</v>
+            <v>31499.74</v>
           </cell>
           <cell r="V211">
-            <v>8363.5</v>
+            <v>8803.52</v>
           </cell>
         </row>
         <row r="212">
@@ -14890,19 +14830,19 @@
             <v>0</v>
           </cell>
           <cell r="Q212">
-            <v>0</v>
+            <v>195.62</v>
           </cell>
           <cell r="R212">
-            <v>267461.73</v>
+            <v>267657.34999999998</v>
           </cell>
           <cell r="T212">
             <v>0</v>
           </cell>
           <cell r="U212">
-            <v>267461.73</v>
+            <v>267657.34999999998</v>
           </cell>
           <cell r="V212">
-            <v>247070.52000000008</v>
+            <v>246874.90000000008</v>
           </cell>
         </row>
         <row r="213">
@@ -15685,19 +15625,19 @@
             <v>0</v>
           </cell>
           <cell r="Q227">
-            <v>0</v>
+            <v>195.62</v>
           </cell>
           <cell r="R227">
-            <v>4948.0999999999995</v>
+            <v>5143.7199999999993</v>
           </cell>
           <cell r="T227">
             <v>0</v>
           </cell>
           <cell r="U227">
-            <v>4948.0999999999995</v>
+            <v>5143.7199999999993</v>
           </cell>
           <cell r="V227">
-            <v>-4948.0999999999995</v>
+            <v>-5143.7199999999993</v>
           </cell>
         </row>
         <row r="228">
@@ -15770,10 +15710,10 @@
             <v>1669340.5799999998</v>
           </cell>
           <cell r="N229">
-            <v>1328133.79</v>
+            <v>1331633.79</v>
           </cell>
           <cell r="O229">
-            <v>3500</v>
+            <v>0</v>
           </cell>
           <cell r="P229">
             <v>0</v>
@@ -15823,10 +15763,10 @@
             <v>799054.9</v>
           </cell>
           <cell r="N230">
-            <v>710264.24</v>
+            <v>713764.24</v>
           </cell>
           <cell r="O230">
-            <v>3500</v>
+            <v>0</v>
           </cell>
           <cell r="P230">
             <v>0</v>
@@ -16659,10 +16599,10 @@
             <v>833763.48999999964</v>
           </cell>
           <cell r="N246">
-            <v>982042.90000000014</v>
+            <v>984152.10000000009</v>
           </cell>
           <cell r="O246">
-            <v>2109.1999999999998</v>
+            <v>1650.6</v>
           </cell>
           <cell r="P246">
             <v>0</v>
@@ -16671,16 +16611,16 @@
             <v>0</v>
           </cell>
           <cell r="R246">
-            <v>984152.10000000009</v>
+            <v>985802.70000000007</v>
           </cell>
           <cell r="T246">
             <v>0</v>
           </cell>
           <cell r="U246">
-            <v>984152.10000000009</v>
+            <v>985802.70000000007</v>
           </cell>
           <cell r="V246">
-            <v>-150388.61000000045</v>
+            <v>-152039.21000000043</v>
           </cell>
         </row>
         <row r="247">
@@ -16712,10 +16652,10 @@
             <v>176092</v>
           </cell>
           <cell r="N247">
-            <v>192168.91999999998</v>
+            <v>194014.62</v>
           </cell>
           <cell r="O247">
-            <v>1845.7</v>
+            <v>1650.6</v>
           </cell>
           <cell r="P247">
             <v>0</v>
@@ -16724,16 +16664,16 @@
             <v>0</v>
           </cell>
           <cell r="R247">
-            <v>194014.62</v>
+            <v>195665.22</v>
           </cell>
           <cell r="T247">
             <v>0</v>
           </cell>
           <cell r="U247">
-            <v>194014.62</v>
+            <v>195665.22</v>
           </cell>
           <cell r="V247">
-            <v>-17922.619999999995</v>
+            <v>-19573.22</v>
           </cell>
         </row>
         <row r="248">
@@ -16765,10 +16705,10 @@
             <v>94344.1</v>
           </cell>
           <cell r="N248">
-            <v>185919.94</v>
+            <v>186183.44</v>
           </cell>
           <cell r="O248">
-            <v>263.5</v>
+            <v>0</v>
           </cell>
           <cell r="P248">
             <v>0</v>
@@ -19432,10 +19372,10 @@
             <v>1069012.3299999998</v>
           </cell>
           <cell r="N299">
-            <v>1376448.7</v>
+            <v>1376540.3</v>
           </cell>
           <cell r="O299">
-            <v>91.6</v>
+            <v>0</v>
           </cell>
           <cell r="P299">
             <v>0</v>
@@ -20227,10 +20167,10 @@
             <v>57412.33</v>
           </cell>
           <cell r="N314">
-            <v>47960.650000000016</v>
+            <v>48052.250000000015</v>
           </cell>
           <cell r="O314">
-            <v>91.6</v>
+            <v>0</v>
           </cell>
           <cell r="P314">
             <v>0</v>
@@ -22193,25 +22133,25 @@
             <v>1150847.8699999999</v>
           </cell>
           <cell r="N352">
-            <v>745972.17</v>
+            <v>796464.32000000007</v>
           </cell>
           <cell r="O352">
-            <v>38671.94</v>
+            <v>44749.82</v>
           </cell>
           <cell r="P352">
-            <v>69044.420000000013</v>
+            <v>68303.25</v>
           </cell>
           <cell r="Q352">
-            <v>71909.929999999993</v>
+            <v>656.45</v>
           </cell>
           <cell r="R352">
-            <v>925598.4600000002</v>
+            <v>910173.84</v>
           </cell>
           <cell r="T352">
-            <v>225249.41000000003</v>
+            <v>240674.02999999997</v>
           </cell>
           <cell r="U352">
-            <v>1150847.8700000001</v>
+            <v>1150847.8699999999</v>
           </cell>
           <cell r="V352">
             <v>0</v>
@@ -22234,25 +22174,25 @@
             <v>1150847.8699999999</v>
           </cell>
           <cell r="N353">
-            <v>745972.17</v>
+            <v>796464.32000000007</v>
           </cell>
           <cell r="O353">
-            <v>38671.94</v>
+            <v>44749.82</v>
           </cell>
           <cell r="P353">
-            <v>69044.420000000013</v>
+            <v>68303.25</v>
           </cell>
           <cell r="Q353">
-            <v>71909.929999999993</v>
+            <v>656.45</v>
           </cell>
           <cell r="R353">
-            <v>925598.4600000002</v>
+            <v>910173.84</v>
           </cell>
           <cell r="T353">
-            <v>225249.41000000003</v>
+            <v>240674.02999999997</v>
           </cell>
           <cell r="U353">
-            <v>1150847.8700000001</v>
+            <v>1150847.8699999999</v>
           </cell>
           <cell r="V353">
             <v>0</v>
@@ -22287,22 +22227,22 @@
             <v>377991.09</v>
           </cell>
           <cell r="N354">
-            <v>296942.82</v>
+            <v>320437.99</v>
           </cell>
           <cell r="O354">
-            <v>8974.6</v>
+            <v>2721.15</v>
           </cell>
           <cell r="P354">
-            <v>17335.88</v>
+            <v>0.02</v>
           </cell>
           <cell r="Q354">
-            <v>29799.94</v>
+            <v>557.98</v>
           </cell>
           <cell r="R354">
-            <v>353053.24</v>
+            <v>323717.14</v>
           </cell>
           <cell r="T354">
-            <v>24937.850000000035</v>
+            <v>54273.950000000012</v>
           </cell>
           <cell r="U354">
             <v>377991.09</v>
@@ -22340,22 +22280,22 @@
             <v>303742.84000000003</v>
           </cell>
           <cell r="N355">
-            <v>235935.2</v>
+            <v>237933.51</v>
           </cell>
           <cell r="O355">
-            <v>0</v>
+            <v>37330</v>
           </cell>
           <cell r="P355">
-            <v>21711.55</v>
+            <v>19304.899999999998</v>
           </cell>
           <cell r="Q355">
-            <v>42109.99</v>
+            <v>0</v>
           </cell>
           <cell r="R355">
-            <v>299756.74</v>
+            <v>294568.41000000003</v>
           </cell>
           <cell r="T355">
-            <v>3986.1000000000349</v>
+            <v>9174.429999999993</v>
           </cell>
           <cell r="U355">
             <v>303742.84000000003</v>
@@ -22446,22 +22386,22 @@
             <v>132296.88</v>
           </cell>
           <cell r="N357">
-            <v>63151.08</v>
+            <v>67849.75</v>
           </cell>
           <cell r="O357">
-            <v>9397.34</v>
+            <v>4698.67</v>
           </cell>
           <cell r="P357">
-            <v>29996.980000000003</v>
+            <v>29998.32</v>
           </cell>
           <cell r="Q357">
             <v>0</v>
           </cell>
           <cell r="R357">
-            <v>102545.4</v>
+            <v>102546.73999999999</v>
           </cell>
           <cell r="T357">
-            <v>29751.48000000001</v>
+            <v>29750.140000000014</v>
           </cell>
           <cell r="U357">
             <v>132296.88</v>
@@ -22508,13 +22448,13 @@
             <v>0</v>
           </cell>
           <cell r="Q358">
-            <v>0</v>
+            <v>98.47</v>
           </cell>
           <cell r="R358">
-            <v>32057.97</v>
+            <v>32156.440000000002</v>
           </cell>
           <cell r="T358">
-            <v>50290.09</v>
+            <v>50191.619999999995</v>
           </cell>
           <cell r="U358">
             <v>82348.06</v>
@@ -22605,22 +22545,22 @@
             <v>47248.89</v>
           </cell>
           <cell r="N360">
-            <v>58522.42</v>
+            <v>78822.42</v>
           </cell>
           <cell r="O360">
-            <v>20300</v>
+            <v>0</v>
           </cell>
           <cell r="P360">
-            <v>0</v>
+            <v>19000</v>
           </cell>
           <cell r="Q360">
             <v>0</v>
           </cell>
           <cell r="R360">
-            <v>78822.42</v>
+            <v>97822.42</v>
           </cell>
           <cell r="T360">
-            <v>-31573.53</v>
+            <v>-50573.53</v>
           </cell>
           <cell r="U360">
             <v>47248.89</v>
@@ -22699,28 +22639,28 @@
             <v>261893.82</v>
           </cell>
           <cell r="N362">
-            <v>88791.7</v>
+            <v>119523.54</v>
           </cell>
           <cell r="O362">
-            <v>20584.88</v>
+            <v>0</v>
           </cell>
           <cell r="P362">
-            <v>124448.31</v>
+            <v>114451.87</v>
           </cell>
           <cell r="Q362">
             <v>0</v>
           </cell>
           <cell r="R362">
-            <v>233824.89</v>
+            <v>233975.40999999997</v>
           </cell>
           <cell r="T362">
             <v>0</v>
           </cell>
           <cell r="U362">
-            <v>233824.89</v>
+            <v>233975.40999999997</v>
           </cell>
           <cell r="V362">
-            <v>28068.929999999993</v>
+            <v>27918.410000000033</v>
           </cell>
         </row>
         <row r="363">
@@ -22740,28 +22680,28 @@
             <v>261893.82</v>
           </cell>
           <cell r="N363">
-            <v>88791.7</v>
+            <v>119523.54</v>
           </cell>
           <cell r="O363">
-            <v>20584.88</v>
+            <v>0</v>
           </cell>
           <cell r="P363">
-            <v>124448.31</v>
+            <v>114451.87</v>
           </cell>
           <cell r="Q363">
             <v>0</v>
           </cell>
           <cell r="R363">
-            <v>233824.89</v>
+            <v>233975.40999999997</v>
           </cell>
           <cell r="T363">
             <v>0</v>
           </cell>
           <cell r="U363">
-            <v>233824.89</v>
+            <v>233975.40999999997</v>
           </cell>
           <cell r="V363">
-            <v>28068.929999999993</v>
+            <v>27918.410000000033</v>
           </cell>
         </row>
         <row r="364">
@@ -22793,10 +22733,10 @@
             <v>29699.3</v>
           </cell>
           <cell r="N364">
-            <v>30864.370000000003</v>
+            <v>31219.280000000002</v>
           </cell>
           <cell r="O364">
-            <v>207.95</v>
+            <v>0</v>
           </cell>
           <cell r="P364">
             <v>0</v>
@@ -22805,16 +22745,16 @@
             <v>0</v>
           </cell>
           <cell r="R364">
-            <v>31072.320000000003</v>
+            <v>31219.280000000002</v>
           </cell>
           <cell r="T364">
             <v>0</v>
           </cell>
           <cell r="U364">
-            <v>31072.320000000003</v>
+            <v>31219.280000000002</v>
           </cell>
           <cell r="V364">
-            <v>-1373.0200000000041</v>
+            <v>-1519.9800000000032</v>
           </cell>
         </row>
         <row r="365">
@@ -22846,28 +22786,28 @@
             <v>101247.61</v>
           </cell>
           <cell r="N365">
-            <v>45000</v>
+            <v>75376.929999999993</v>
           </cell>
           <cell r="O365">
-            <v>20376.93</v>
+            <v>0</v>
           </cell>
           <cell r="P365">
-            <v>29736.97</v>
+            <v>19740.53</v>
           </cell>
           <cell r="Q365">
             <v>0</v>
           </cell>
           <cell r="R365">
-            <v>95113.9</v>
+            <v>95117.459999999992</v>
           </cell>
           <cell r="T365">
             <v>0</v>
           </cell>
           <cell r="U365">
-            <v>95113.9</v>
+            <v>95117.459999999992</v>
           </cell>
           <cell r="V365">
-            <v>6133.7100000000064</v>
+            <v>6130.1500000000087</v>
           </cell>
         </row>
         <row r="366">
@@ -22993,28 +22933,28 @@
             <v>1142748.06</v>
           </cell>
           <cell r="N368">
-            <v>738769.64</v>
+            <v>761608.56000000017</v>
           </cell>
           <cell r="O368">
-            <v>26908.690000000002</v>
+            <v>12281.240000000002</v>
           </cell>
           <cell r="P368">
             <v>146526.44999999998</v>
           </cell>
           <cell r="Q368">
-            <v>5786.1</v>
+            <v>6869.08</v>
           </cell>
           <cell r="R368">
-            <v>917990.88</v>
+            <v>927285.33000000007</v>
           </cell>
           <cell r="T368">
-            <v>385891.80999999994</v>
+            <v>374979.93999999994</v>
           </cell>
           <cell r="U368">
-            <v>1303882.69</v>
+            <v>1302265.27</v>
           </cell>
           <cell r="V368">
-            <v>-161134.62999999989</v>
+            <v>-159517.20999999996</v>
           </cell>
         </row>
         <row r="369">
@@ -23034,28 +22974,28 @@
             <v>1142748.06</v>
           </cell>
           <cell r="N369">
-            <v>738769.64</v>
+            <v>761608.56000000017</v>
           </cell>
           <cell r="O369">
-            <v>26908.690000000002</v>
+            <v>12281.240000000002</v>
           </cell>
           <cell r="P369">
             <v>146526.44999999998</v>
           </cell>
           <cell r="Q369">
-            <v>5786.1</v>
+            <v>6869.08</v>
           </cell>
           <cell r="R369">
-            <v>917990.88</v>
+            <v>927285.33000000007</v>
           </cell>
           <cell r="T369">
-            <v>385891.80999999994</v>
+            <v>374979.93999999994</v>
           </cell>
           <cell r="U369">
-            <v>1303882.69</v>
+            <v>1302265.27</v>
           </cell>
           <cell r="V369">
-            <v>-161134.62999999989</v>
+            <v>-159517.20999999996</v>
           </cell>
         </row>
         <row r="370">
@@ -23087,10 +23027,10 @@
             <v>155246.34</v>
           </cell>
           <cell r="N370">
-            <v>45430.6</v>
+            <v>56169.86</v>
           </cell>
           <cell r="O370">
-            <v>11890.91</v>
+            <v>0</v>
           </cell>
           <cell r="P370">
             <v>14326.16</v>
@@ -23099,16 +23039,16 @@
             <v>0</v>
           </cell>
           <cell r="R370">
-            <v>71647.67</v>
+            <v>70496.02</v>
           </cell>
           <cell r="T370">
             <v>82111.349999999933</v>
           </cell>
           <cell r="U370">
-            <v>153759.01999999993</v>
+            <v>152607.36999999994</v>
           </cell>
           <cell r="V370">
-            <v>1487.3200000000652</v>
+            <v>2638.9700000000594</v>
           </cell>
         </row>
         <row r="371">
@@ -23140,28 +23080,28 @@
             <v>477888.73</v>
           </cell>
           <cell r="N371">
-            <v>319748.92000000004</v>
+            <v>323858.03000000009</v>
           </cell>
           <cell r="O371">
-            <v>5460</v>
+            <v>10539.78</v>
           </cell>
           <cell r="P371">
             <v>30810.100000000002</v>
           </cell>
           <cell r="Q371">
-            <v>5258.02</v>
+            <v>6341</v>
           </cell>
           <cell r="R371">
-            <v>361277.04000000004</v>
+            <v>371548.91000000009</v>
           </cell>
           <cell r="T371">
-            <v>112594.19000000006</v>
+            <v>102322.32000000007</v>
           </cell>
           <cell r="U371">
-            <v>473871.2300000001</v>
+            <v>473871.23000000016</v>
           </cell>
           <cell r="V371">
-            <v>4017.4999999998836</v>
+            <v>4017.4999999998254</v>
           </cell>
         </row>
         <row r="372">
@@ -23193,10 +23133,10 @@
             <v>321292.43</v>
           </cell>
           <cell r="N372">
-            <v>167753.80000000002</v>
+            <v>170870.53000000003</v>
           </cell>
           <cell r="O372">
-            <v>4218.1900000000005</v>
+            <v>1741.46</v>
           </cell>
           <cell r="P372">
             <v>0.01</v>
@@ -23205,10 +23145,10 @@
             <v>528.08000000000004</v>
           </cell>
           <cell r="R372">
-            <v>172500.08000000002</v>
+            <v>173140.08000000002</v>
           </cell>
           <cell r="T372">
-            <v>148792.35000000003</v>
+            <v>148152.35000000003</v>
           </cell>
           <cell r="U372">
             <v>321292.43000000005</v>
@@ -23246,10 +23186,10 @@
             <v>34424.19</v>
           </cell>
           <cell r="N373">
-            <v>55111.37</v>
+            <v>59708.79</v>
           </cell>
           <cell r="O373">
-            <v>5063.1900000000005</v>
+            <v>0</v>
           </cell>
           <cell r="P373">
             <v>10093.89</v>
@@ -23258,16 +23198,16 @@
             <v>0</v>
           </cell>
           <cell r="R373">
-            <v>70268.450000000012</v>
+            <v>69802.679999999993</v>
           </cell>
           <cell r="T373">
             <v>42393.919999999955</v>
           </cell>
           <cell r="U373">
-            <v>112662.36999999997</v>
+            <v>112196.59999999995</v>
           </cell>
           <cell r="V373">
-            <v>-78238.179999999964</v>
+            <v>-77772.409999999945</v>
           </cell>
         </row>
         <row r="374">
@@ -23352,10 +23292,10 @@
             <v>60748.57</v>
           </cell>
           <cell r="N375">
-            <v>66572.63</v>
+            <v>66849.03</v>
           </cell>
           <cell r="O375">
-            <v>276.39999999999998</v>
+            <v>0</v>
           </cell>
           <cell r="P375">
             <v>1985.4</v>
@@ -23393,25 +23333,25 @@
             <v>532432.98</v>
           </cell>
           <cell r="N376">
-            <v>88932.14</v>
+            <v>112697.45999999999</v>
           </cell>
           <cell r="O376">
             <v>0</v>
           </cell>
           <cell r="P376">
-            <v>44189.98</v>
+            <v>194181.90999999997</v>
           </cell>
           <cell r="Q376">
             <v>3760.5</v>
           </cell>
           <cell r="R376">
-            <v>136882.62</v>
+            <v>310639.87</v>
           </cell>
           <cell r="T376">
-            <v>395550.36</v>
+            <v>221793.11000000007</v>
           </cell>
           <cell r="U376">
-            <v>532432.98</v>
+            <v>532432.9800000001</v>
           </cell>
           <cell r="V376">
             <v>0</v>
@@ -23434,22 +23374,22 @@
             <v>373488.78</v>
           </cell>
           <cell r="N377">
-            <v>78247.14</v>
+            <v>82004.459999999992</v>
           </cell>
           <cell r="O377">
             <v>0</v>
           </cell>
           <cell r="P377">
-            <v>40880.020000000004</v>
+            <v>140031.41999999998</v>
           </cell>
           <cell r="Q377">
             <v>3760.5</v>
           </cell>
           <cell r="R377">
-            <v>122887.66</v>
+            <v>225796.37999999998</v>
           </cell>
           <cell r="T377">
-            <v>250601.12000000002</v>
+            <v>147692.40000000005</v>
           </cell>
           <cell r="U377">
             <v>373488.78</v>
@@ -23493,16 +23433,16 @@
             <v>0</v>
           </cell>
           <cell r="P378">
-            <v>0</v>
+            <v>99151.409999999974</v>
           </cell>
           <cell r="Q378">
             <v>0</v>
           </cell>
           <cell r="R378">
-            <v>62058.400000000001</v>
+            <v>161209.80999999997</v>
           </cell>
           <cell r="T378">
-            <v>255524.6</v>
+            <v>156373.19000000003</v>
           </cell>
           <cell r="U378">
             <v>317583</v>
@@ -23540,22 +23480,22 @@
             <v>52640</v>
           </cell>
           <cell r="N379">
-            <v>15764.619999999999</v>
+            <v>19521.939999999999</v>
           </cell>
           <cell r="O379">
             <v>0</v>
           </cell>
           <cell r="P379">
-            <v>40880.020000000004</v>
+            <v>40880.009999999995</v>
           </cell>
           <cell r="Q379">
             <v>3760.5</v>
           </cell>
           <cell r="R379">
-            <v>60405.14</v>
+            <v>64162.45</v>
           </cell>
           <cell r="T379">
-            <v>-7765.1399999999994</v>
+            <v>-11522.449999999997</v>
           </cell>
           <cell r="U379">
             <v>52640</v>
@@ -23634,22 +23574,22 @@
             <v>55583.040000000001</v>
           </cell>
           <cell r="N381">
-            <v>10685</v>
+            <v>30693</v>
           </cell>
           <cell r="O381">
             <v>0</v>
           </cell>
           <cell r="P381">
-            <v>3309.96</v>
+            <v>54150.489999999976</v>
           </cell>
           <cell r="Q381">
             <v>0</v>
           </cell>
           <cell r="R381">
-            <v>13994.96</v>
+            <v>84843.489999999976</v>
           </cell>
           <cell r="T381">
-            <v>41588.080000000002</v>
+            <v>-29260.449999999975</v>
           </cell>
           <cell r="U381">
             <v>55583.040000000001</v>
@@ -23687,22 +23627,22 @@
             <v>55583.040000000001</v>
           </cell>
           <cell r="N382">
-            <v>10685</v>
+            <v>30693</v>
           </cell>
           <cell r="O382">
             <v>0</v>
           </cell>
           <cell r="P382">
-            <v>3309.96</v>
+            <v>54150.489999999976</v>
           </cell>
           <cell r="Q382">
             <v>0</v>
           </cell>
           <cell r="R382">
-            <v>13994.96</v>
+            <v>84843.489999999976</v>
           </cell>
           <cell r="T382">
-            <v>41588.080000000002</v>
+            <v>-29260.449999999975</v>
           </cell>
           <cell r="U382">
             <v>55583.040000000001</v>
@@ -23822,28 +23762,28 @@
             <v>622914.20999999985</v>
           </cell>
           <cell r="N385">
-            <v>321130.44</v>
+            <v>343537.91</v>
           </cell>
           <cell r="O385">
-            <v>16993.109999999997</v>
+            <v>28100.98</v>
           </cell>
           <cell r="P385">
-            <v>14531.92</v>
+            <v>14396.32</v>
           </cell>
           <cell r="Q385">
             <v>0</v>
           </cell>
           <cell r="R385">
-            <v>352655.47</v>
+            <v>386035.20999999996</v>
           </cell>
           <cell r="T385">
-            <v>179586</v>
+            <v>147474.44</v>
           </cell>
           <cell r="U385">
-            <v>532241.47</v>
+            <v>533509.64999999991</v>
           </cell>
           <cell r="V385">
-            <v>90672.739999999874</v>
+            <v>89404.559999999939</v>
           </cell>
         </row>
         <row r="386">
@@ -23863,28 +23803,28 @@
             <v>88584.17</v>
           </cell>
           <cell r="N386">
-            <v>18031.400000000001</v>
+            <v>39396.39</v>
           </cell>
           <cell r="O386">
-            <v>16881.879999999997</v>
+            <v>28093.35</v>
           </cell>
           <cell r="P386">
-            <v>14531.92</v>
+            <v>14396.32</v>
           </cell>
           <cell r="Q386">
             <v>0</v>
           </cell>
           <cell r="R386">
-            <v>49445.2</v>
+            <v>81886.06</v>
           </cell>
           <cell r="T386">
-            <v>39138.97</v>
+            <v>23051.340000000004</v>
           </cell>
           <cell r="U386">
-            <v>88584.17</v>
+            <v>104937.4</v>
           </cell>
           <cell r="V386">
-            <v>0</v>
+            <v>-16353.229999999996</v>
           </cell>
         </row>
         <row r="387">
@@ -23916,10 +23856,10 @@
             <v>11175.95</v>
           </cell>
           <cell r="N387">
-            <v>8895</v>
+            <v>14174.49</v>
           </cell>
           <cell r="O387">
-            <v>4850.49</v>
+            <v>13354.689999999999</v>
           </cell>
           <cell r="P387">
             <v>0</v>
@@ -23928,16 +23868,16 @@
             <v>0</v>
           </cell>
           <cell r="R387">
-            <v>13745.49</v>
+            <v>27529.18</v>
           </cell>
           <cell r="T387">
-            <v>-2569.5399999999991</v>
+            <v>0</v>
           </cell>
           <cell r="U387">
-            <v>11175.95</v>
+            <v>27529.18</v>
           </cell>
           <cell r="V387">
-            <v>0</v>
+            <v>-16353.23</v>
           </cell>
         </row>
         <row r="388">
@@ -23969,22 +23909,22 @@
             <v>77408.22</v>
           </cell>
           <cell r="N388">
-            <v>9136.4</v>
+            <v>25221.9</v>
           </cell>
           <cell r="O388">
-            <v>12031.39</v>
+            <v>14738.66</v>
           </cell>
           <cell r="P388">
-            <v>14531.92</v>
+            <v>14396.32</v>
           </cell>
           <cell r="Q388">
             <v>0</v>
           </cell>
           <cell r="R388">
-            <v>35699.71</v>
+            <v>54356.88</v>
           </cell>
           <cell r="T388">
-            <v>41708.51</v>
+            <v>23051.340000000004</v>
           </cell>
           <cell r="U388">
             <v>77408.22</v>
@@ -25868,13 +25808,13 @@
             <v>0</v>
           </cell>
           <cell r="T424">
-            <v>66210.17</v>
+            <v>57856.97</v>
           </cell>
           <cell r="U424">
-            <v>66210.17</v>
+            <v>57856.97</v>
           </cell>
           <cell r="V424">
-            <v>0</v>
+            <v>8353.1999999999971</v>
           </cell>
         </row>
         <row r="425">
@@ -25921,13 +25861,13 @@
             <v>0</v>
           </cell>
           <cell r="T425">
+            <v>0</v>
+          </cell>
+          <cell r="U425">
+            <v>0</v>
+          </cell>
+          <cell r="V425">
             <v>8353.2000000000007</v>
-          </cell>
-          <cell r="U425">
-            <v>8353.2000000000007</v>
-          </cell>
-          <cell r="V425">
-            <v>0</v>
           </cell>
         </row>
         <row r="426">
@@ -28838,10 +28778,10 @@
             <v>8024.6399999999994</v>
           </cell>
           <cell r="N481">
-            <v>2358.5099999999998</v>
+            <v>3400.99</v>
           </cell>
           <cell r="O481">
-            <v>111.23</v>
+            <v>7.63</v>
           </cell>
           <cell r="P481">
             <v>0</v>
@@ -28850,16 +28790,16 @@
             <v>0</v>
           </cell>
           <cell r="R481">
-            <v>2469.7399999999998</v>
+            <v>3408.62</v>
           </cell>
           <cell r="T481">
-            <v>7670.73</v>
+            <v>0</v>
           </cell>
           <cell r="U481">
-            <v>10140.469999999999</v>
+            <v>3408.62</v>
           </cell>
           <cell r="V481">
-            <v>-2115.83</v>
+            <v>4616.0199999999995</v>
           </cell>
         </row>
         <row r="482">
@@ -28906,13 +28846,13 @@
             <v>0.47000000000000064</v>
           </cell>
           <cell r="T482">
+            <v>0</v>
+          </cell>
+          <cell r="U482">
+            <v>0.47000000000000064</v>
+          </cell>
+          <cell r="V482">
             <v>2530.44</v>
-          </cell>
-          <cell r="U482">
-            <v>2530.91</v>
-          </cell>
-          <cell r="V482">
-            <v>0</v>
           </cell>
         </row>
         <row r="483">
@@ -28944,10 +28884,10 @@
             <v>4366.33</v>
           </cell>
           <cell r="N483">
-            <v>242.21</v>
+            <v>1284.69</v>
           </cell>
           <cell r="O483">
-            <v>111.23</v>
+            <v>0</v>
           </cell>
           <cell r="P483">
             <v>0</v>
@@ -28956,16 +28896,16 @@
             <v>0</v>
           </cell>
           <cell r="R483">
-            <v>353.44</v>
+            <v>1284.69</v>
           </cell>
           <cell r="T483">
-            <v>4012.89</v>
+            <v>0</v>
           </cell>
           <cell r="U483">
-            <v>4366.33</v>
+            <v>1284.69</v>
           </cell>
           <cell r="V483">
-            <v>0</v>
+            <v>3081.64</v>
           </cell>
         </row>
         <row r="484">
@@ -29742,7 +29682,7 @@
             <v>48.6</v>
           </cell>
           <cell r="O498">
-            <v>0</v>
+            <v>7.63</v>
           </cell>
           <cell r="P498">
             <v>0</v>
@@ -29751,16 +29691,16 @@
             <v>0</v>
           </cell>
           <cell r="R498">
-            <v>48.6</v>
+            <v>56.230000000000004</v>
           </cell>
           <cell r="T498">
             <v>0</v>
           </cell>
           <cell r="U498">
-            <v>48.6</v>
+            <v>56.230000000000004</v>
           </cell>
           <cell r="V498">
-            <v>-48.6</v>
+            <v>-56.230000000000004</v>
           </cell>
         </row>
         <row r="499">
@@ -29807,13 +29747,13 @@
             <v>0</v>
           </cell>
           <cell r="T499">
+            <v>0</v>
+          </cell>
+          <cell r="U499">
+            <v>0</v>
+          </cell>
+          <cell r="V499">
             <v>1127.4000000000001</v>
-          </cell>
-          <cell r="U499">
-            <v>1127.4000000000001</v>
-          </cell>
-          <cell r="V499">
-            <v>0</v>
           </cell>
         </row>
         <row r="500">
@@ -32818,10 +32758,10 @@
             <v>734722.6399999999</v>
           </cell>
           <cell r="N557">
-            <v>27</v>
+            <v>5652.78</v>
           </cell>
           <cell r="O557">
-            <v>26641.9</v>
+            <v>48723.82</v>
           </cell>
           <cell r="P557">
             <v>0</v>
@@ -32830,16 +32770,16 @@
             <v>0</v>
           </cell>
           <cell r="R557">
-            <v>26668.9</v>
+            <v>54376.6</v>
           </cell>
           <cell r="T557">
-            <v>348729.93</v>
+            <v>305791.93</v>
           </cell>
           <cell r="U557">
-            <v>375398.83</v>
+            <v>360168.52999999997</v>
           </cell>
           <cell r="V557">
-            <v>359323.80999999988</v>
+            <v>374554.10999999993</v>
           </cell>
         </row>
         <row r="558">
@@ -32874,13 +32814,13 @@
             <v>27</v>
           </cell>
           <cell r="T558">
-            <v>319393.93</v>
+            <v>305455.93</v>
           </cell>
           <cell r="U558">
-            <v>319420.93</v>
+            <v>305482.93</v>
           </cell>
           <cell r="V558">
-            <v>350828.00999999995</v>
+            <v>364766.00999999995</v>
           </cell>
         </row>
         <row r="559">
@@ -33139,13 +33079,13 @@
             <v>0</v>
           </cell>
           <cell r="T563">
-            <v>37500</v>
+            <v>23562</v>
           </cell>
           <cell r="U563">
-            <v>37500</v>
+            <v>23562</v>
           </cell>
           <cell r="V563">
-            <v>-13938</v>
+            <v>0</v>
           </cell>
         </row>
         <row r="564">
@@ -33165,10 +33105,10 @@
             <v>64473.700000000004</v>
           </cell>
           <cell r="N564">
-            <v>0</v>
+            <v>5625.78</v>
           </cell>
           <cell r="O564">
-            <v>26641.9</v>
+            <v>48723.82</v>
           </cell>
           <cell r="P564">
             <v>0</v>
@@ -33177,16 +33117,16 @@
             <v>0</v>
           </cell>
           <cell r="R564">
-            <v>26641.9</v>
+            <v>54349.599999999999</v>
           </cell>
           <cell r="T564">
-            <v>29336</v>
+            <v>336</v>
           </cell>
           <cell r="U564">
-            <v>55977.9</v>
+            <v>54685.599999999999</v>
           </cell>
           <cell r="V564">
-            <v>8495.8000000000029</v>
+            <v>9788.1000000000058</v>
           </cell>
         </row>
         <row r="565">
@@ -33271,10 +33211,10 @@
             <v>40723.050000000003</v>
           </cell>
           <cell r="N566">
-            <v>0</v>
+            <v>5625.78</v>
           </cell>
           <cell r="O566">
-            <v>18649.330000000002</v>
+            <v>40731.25</v>
           </cell>
           <cell r="P566">
             <v>0</v>
@@ -33283,16 +33223,16 @@
             <v>0</v>
           </cell>
           <cell r="R566">
-            <v>18649.330000000002</v>
+            <v>46357.03</v>
           </cell>
           <cell r="T566">
-            <v>29000</v>
+            <v>0</v>
           </cell>
           <cell r="U566">
-            <v>47649.33</v>
+            <v>46357.03</v>
           </cell>
           <cell r="V566">
-            <v>-6926.2799999999988</v>
+            <v>-5633.9799999999959</v>
           </cell>
         </row>
         <row r="567">
@@ -33365,28 +33305,28 @@
             <v>1043744.0400000002</v>
           </cell>
           <cell r="N568">
-            <v>610617.55999999994</v>
+            <v>617578.93999999994</v>
           </cell>
           <cell r="O568">
-            <v>291461.38</v>
+            <v>285770.40000000002</v>
           </cell>
           <cell r="P568">
-            <v>80298.419999999984</v>
+            <v>80295.999999999985</v>
           </cell>
           <cell r="Q568">
-            <v>0</v>
+            <v>281.10000000000002</v>
           </cell>
           <cell r="R568">
-            <v>982377.35999999987</v>
+            <v>983926.44</v>
           </cell>
           <cell r="T568">
-            <v>41976.85</v>
+            <v>40927.770000000004</v>
           </cell>
           <cell r="U568">
-            <v>1024354.2099999998</v>
+            <v>1024854.21</v>
           </cell>
           <cell r="V568">
-            <v>19389.830000000307</v>
+            <v>18889.830000000191</v>
           </cell>
         </row>
         <row r="569">
@@ -33406,28 +33346,28 @@
             <v>1043744.0400000002</v>
           </cell>
           <cell r="N569">
-            <v>610617.55999999994</v>
+            <v>617578.93999999994</v>
           </cell>
           <cell r="O569">
-            <v>291461.38</v>
+            <v>285770.40000000002</v>
           </cell>
           <cell r="P569">
-            <v>80298.419999999984</v>
+            <v>80295.999999999985</v>
           </cell>
           <cell r="Q569">
-            <v>0</v>
+            <v>281.10000000000002</v>
           </cell>
           <cell r="R569">
-            <v>982377.35999999987</v>
+            <v>983926.44</v>
           </cell>
           <cell r="T569">
-            <v>41976.85</v>
+            <v>40927.770000000004</v>
           </cell>
           <cell r="U569">
-            <v>1024354.2099999998</v>
+            <v>1024854.21</v>
           </cell>
           <cell r="V569">
-            <v>19389.830000000307</v>
+            <v>18889.830000000191</v>
           </cell>
         </row>
         <row r="570">
@@ -33512,10 +33452,10 @@
             <v>694979.56</v>
           </cell>
           <cell r="N571">
-            <v>461694.22</v>
+            <v>465382.52999999997</v>
           </cell>
           <cell r="O571">
-            <v>288188.31</v>
+            <v>285000</v>
           </cell>
           <cell r="P571">
             <v>0</v>
@@ -33524,16 +33464,16 @@
             <v>0</v>
           </cell>
           <cell r="R571">
-            <v>749882.53</v>
+            <v>750382.53</v>
           </cell>
           <cell r="T571">
             <v>0</v>
           </cell>
           <cell r="U571">
-            <v>749882.53</v>
+            <v>750382.53</v>
           </cell>
           <cell r="V571">
-            <v>-54902.969999999972</v>
+            <v>-55402.969999999972</v>
           </cell>
         </row>
         <row r="572">
@@ -33574,13 +33514,13 @@
             <v>0</v>
           </cell>
           <cell r="Q572">
-            <v>0</v>
+            <v>281.10000000000002</v>
           </cell>
           <cell r="R572">
-            <v>43021.740000000005</v>
+            <v>43302.840000000004</v>
           </cell>
           <cell r="T572">
-            <v>24461.89</v>
+            <v>24180.79</v>
           </cell>
           <cell r="U572">
             <v>67483.63</v>
@@ -33621,7 +33561,7 @@
             <v>7618.01</v>
           </cell>
           <cell r="O573">
-            <v>0</v>
+            <v>770.4</v>
           </cell>
           <cell r="P573">
             <v>0</v>
@@ -33630,10 +33570,10 @@
             <v>0</v>
           </cell>
           <cell r="R573">
-            <v>7618.01</v>
+            <v>8388.41</v>
           </cell>
           <cell r="T573">
-            <v>14666.88</v>
+            <v>13896.48</v>
           </cell>
           <cell r="U573">
             <v>22284.89</v>
@@ -33724,22 +33664,22 @@
             <v>31391.93</v>
           </cell>
           <cell r="N575">
-            <v>0</v>
+            <v>3273.07</v>
           </cell>
           <cell r="O575">
-            <v>3273.07</v>
+            <v>0</v>
           </cell>
           <cell r="P575">
-            <v>28114.68</v>
+            <v>28112.26</v>
           </cell>
           <cell r="Q575">
             <v>0</v>
           </cell>
           <cell r="R575">
-            <v>31387.75</v>
+            <v>31385.329999999998</v>
           </cell>
           <cell r="T575">
-            <v>4.180000000000291</v>
+            <v>6.6000000000021828</v>
           </cell>
           <cell r="U575">
             <v>31391.93</v>
@@ -33977,10 +33917,10 @@
             <v>766689.91999999993</v>
           </cell>
           <cell r="N580">
-            <v>503590.75</v>
+            <v>541098.04</v>
           </cell>
           <cell r="O580">
-            <v>19922.97</v>
+            <v>8758.7999999999993</v>
           </cell>
           <cell r="P580">
             <v>0</v>
@@ -33989,16 +33929,16 @@
             <v>0</v>
           </cell>
           <cell r="R580">
-            <v>523513.72</v>
+            <v>549856.84000000008</v>
           </cell>
           <cell r="T580">
-            <v>62072.7</v>
+            <v>46113.64</v>
           </cell>
           <cell r="U580">
-            <v>585586.41999999993</v>
+            <v>595970.4800000001</v>
           </cell>
           <cell r="V580">
-            <v>181103.5</v>
+            <v>170719.43999999983</v>
           </cell>
         </row>
         <row r="581">
@@ -34033,13 +33973,13 @@
             <v>30438.5</v>
           </cell>
           <cell r="T581">
-            <v>3695.6</v>
+            <v>3736.54</v>
           </cell>
           <cell r="U581">
-            <v>34134.1</v>
+            <v>34175.040000000001</v>
           </cell>
           <cell r="V581">
-            <v>31405.1</v>
+            <v>31364.159999999996</v>
           </cell>
         </row>
         <row r="582">
@@ -34086,13 +34026,13 @@
             <v>2507.0300000000002</v>
           </cell>
           <cell r="T582">
+            <v>0</v>
+          </cell>
+          <cell r="U582">
+            <v>2507.0300000000002</v>
+          </cell>
+          <cell r="V582">
             <v>-40.940000000000055</v>
-          </cell>
-          <cell r="U582">
-            <v>2466.09</v>
-          </cell>
-          <cell r="V582">
-            <v>0</v>
           </cell>
         </row>
         <row r="583">
@@ -35013,10 +34953,10 @@
             <v>701150.71999999997</v>
           </cell>
           <cell r="N600">
-            <v>473152.25</v>
+            <v>510659.54000000004</v>
           </cell>
           <cell r="O600">
-            <v>19922.97</v>
+            <v>8758.7999999999993</v>
           </cell>
           <cell r="P600">
             <v>0</v>
@@ -35025,16 +34965,16 @@
             <v>0</v>
           </cell>
           <cell r="R600">
-            <v>493075.22</v>
+            <v>519418.34</v>
           </cell>
           <cell r="T600">
-            <v>58377.1</v>
+            <v>42377.1</v>
           </cell>
           <cell r="U600">
-            <v>551452.31999999995</v>
+            <v>561795.44000000006</v>
           </cell>
           <cell r="V600">
-            <v>149698.40000000002</v>
+            <v>139355.27999999991</v>
           </cell>
         </row>
         <row r="601">
@@ -35172,10 +35112,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N603">
-            <v>36417.660000000003</v>
+            <v>37207.060000000005</v>
           </cell>
           <cell r="O603">
-            <v>0</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P603">
             <v>0</v>
@@ -35184,16 +35124,16 @@
             <v>0</v>
           </cell>
           <cell r="R603">
-            <v>36417.660000000003</v>
+            <v>37820.180000000008</v>
           </cell>
           <cell r="T603">
             <v>0</v>
           </cell>
           <cell r="U603">
-            <v>36417.660000000003</v>
+            <v>37820.180000000008</v>
           </cell>
           <cell r="V603">
-            <v>4992.4099999999962</v>
+            <v>3589.8899999999921</v>
           </cell>
         </row>
         <row r="604">
@@ -35225,10 +35165,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N604">
-            <v>29344.97</v>
+            <v>30100.550000000003</v>
           </cell>
           <cell r="O604">
-            <v>0</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P604">
             <v>0</v>
@@ -35237,16 +35177,16 @@
             <v>0</v>
           </cell>
           <cell r="R604">
-            <v>29344.97</v>
+            <v>30713.670000000002</v>
           </cell>
           <cell r="T604">
             <v>0</v>
           </cell>
           <cell r="U604">
-            <v>29344.97</v>
+            <v>30713.670000000002</v>
           </cell>
           <cell r="V604">
-            <v>12065.099999999999</v>
+            <v>10696.399999999998</v>
           </cell>
         </row>
         <row r="605">
@@ -35278,10 +35218,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N605">
-            <v>45164.3</v>
+            <v>45919.880000000005</v>
           </cell>
           <cell r="O605">
-            <v>0</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P605">
             <v>0</v>
@@ -35290,16 +35230,16 @@
             <v>0</v>
           </cell>
           <cell r="R605">
-            <v>45164.3</v>
+            <v>46533.000000000007</v>
           </cell>
           <cell r="T605">
             <v>0</v>
           </cell>
           <cell r="U605">
-            <v>45164.3</v>
+            <v>46533.000000000007</v>
           </cell>
           <cell r="V605">
-            <v>-3754.2300000000032</v>
+            <v>-5122.9300000000076</v>
           </cell>
         </row>
         <row r="606">
@@ -35331,10 +35271,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N606">
-            <v>46118.94</v>
+            <v>46874.520000000004</v>
           </cell>
           <cell r="O606">
-            <v>0</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P606">
             <v>0</v>
@@ -35343,16 +35283,16 @@
             <v>0</v>
           </cell>
           <cell r="R606">
-            <v>46118.94</v>
+            <v>47487.640000000007</v>
           </cell>
           <cell r="T606">
             <v>0</v>
           </cell>
           <cell r="U606">
-            <v>46118.94</v>
+            <v>47487.640000000007</v>
           </cell>
           <cell r="V606">
-            <v>-4708.8700000000026</v>
+            <v>-6077.570000000007</v>
           </cell>
         </row>
         <row r="607">
@@ -35384,10 +35324,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N607">
-            <v>40404.319999999992</v>
+            <v>41173.429999999993</v>
           </cell>
           <cell r="O607">
-            <v>0</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P607">
             <v>0</v>
@@ -35396,16 +35336,16 @@
             <v>0</v>
           </cell>
           <cell r="R607">
-            <v>40404.319999999992</v>
+            <v>41786.549999999996</v>
           </cell>
           <cell r="T607">
             <v>0</v>
           </cell>
           <cell r="U607">
-            <v>40404.319999999992</v>
+            <v>41786.549999999996</v>
           </cell>
           <cell r="V607">
-            <v>1005.7500000000073</v>
+            <v>-376.47999999999593</v>
           </cell>
         </row>
         <row r="608">
@@ -35437,10 +35377,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N608">
-            <v>40269.520000000004</v>
+            <v>40993.480000000003</v>
           </cell>
           <cell r="O608">
-            <v>0</v>
+            <v>525.52</v>
           </cell>
           <cell r="P608">
             <v>0</v>
@@ -35449,16 +35389,16 @@
             <v>0</v>
           </cell>
           <cell r="R608">
-            <v>40269.520000000004</v>
+            <v>41519</v>
           </cell>
           <cell r="T608">
             <v>0</v>
           </cell>
           <cell r="U608">
-            <v>40269.520000000004</v>
+            <v>41519</v>
           </cell>
           <cell r="V608">
-            <v>1140.5499999999956</v>
+            <v>-108.93000000000029</v>
           </cell>
         </row>
         <row r="609">
@@ -35490,10 +35430,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N609">
-            <v>29455.690000000002</v>
+            <v>30179.65</v>
           </cell>
           <cell r="O609">
-            <v>0</v>
+            <v>525.52</v>
           </cell>
           <cell r="P609">
             <v>0</v>
@@ -35502,16 +35442,16 @@
             <v>0</v>
           </cell>
           <cell r="R609">
-            <v>29455.690000000002</v>
+            <v>30705.170000000002</v>
           </cell>
           <cell r="T609">
             <v>0</v>
           </cell>
           <cell r="U609">
-            <v>29455.690000000002</v>
+            <v>30705.170000000002</v>
           </cell>
           <cell r="V609">
-            <v>11954.379999999997</v>
+            <v>10704.899999999998</v>
           </cell>
         </row>
         <row r="610">
@@ -35543,10 +35483,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N610">
-            <v>26570.84</v>
+            <v>27294.799999999999</v>
           </cell>
           <cell r="O610">
-            <v>0</v>
+            <v>525.52</v>
           </cell>
           <cell r="P610">
             <v>0</v>
@@ -35555,16 +35495,16 @@
             <v>0</v>
           </cell>
           <cell r="R610">
-            <v>26570.84</v>
+            <v>27820.32</v>
           </cell>
           <cell r="T610">
             <v>0</v>
           </cell>
           <cell r="U610">
-            <v>26570.84</v>
+            <v>27820.32</v>
           </cell>
           <cell r="V610">
-            <v>14839.23</v>
+            <v>13589.75</v>
           </cell>
         </row>
         <row r="611">
@@ -35596,10 +35536,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N611">
-            <v>38427.049999999996</v>
+            <v>39196.159999999996</v>
           </cell>
           <cell r="O611">
-            <v>0</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P611">
             <v>0</v>
@@ -35608,16 +35548,16 @@
             <v>0</v>
           </cell>
           <cell r="R611">
-            <v>38427.049999999996</v>
+            <v>39809.279999999999</v>
           </cell>
           <cell r="T611">
             <v>0</v>
           </cell>
           <cell r="U611">
-            <v>38427.049999999996</v>
+            <v>39809.279999999999</v>
           </cell>
           <cell r="V611">
-            <v>2983.0200000000041</v>
+            <v>1600.7900000000009</v>
           </cell>
         </row>
         <row r="612">
@@ -35649,10 +35589,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N612">
-            <v>35027.170000000006</v>
+            <v>38447.69</v>
           </cell>
           <cell r="O612">
-            <v>2696.56</v>
+            <v>525.52</v>
           </cell>
           <cell r="P612">
             <v>0</v>
@@ -35661,16 +35601,16 @@
             <v>0</v>
           </cell>
           <cell r="R612">
-            <v>37723.730000000003</v>
+            <v>38973.21</v>
           </cell>
           <cell r="T612">
             <v>0</v>
           </cell>
           <cell r="U612">
-            <v>37723.730000000003</v>
+            <v>38973.21</v>
           </cell>
           <cell r="V612">
-            <v>3686.3399999999965</v>
+            <v>2436.8600000000006</v>
           </cell>
         </row>
         <row r="613">
@@ -35702,10 +35642,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N613">
-            <v>32571.050000000007</v>
+            <v>36036.720000000008</v>
           </cell>
           <cell r="O613">
-            <v>2696.56</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P613">
             <v>0</v>
@@ -35714,16 +35654,16 @@
             <v>0</v>
           </cell>
           <cell r="R613">
-            <v>35267.610000000008</v>
+            <v>36649.840000000011</v>
           </cell>
           <cell r="T613">
             <v>0</v>
           </cell>
           <cell r="U613">
-            <v>35267.610000000008</v>
+            <v>36649.840000000011</v>
           </cell>
           <cell r="V613">
-            <v>6142.4599999999919</v>
+            <v>4760.2299999999886</v>
           </cell>
         </row>
         <row r="614">
@@ -35755,10 +35695,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N614">
-            <v>33266.03</v>
+            <v>34021.61</v>
           </cell>
           <cell r="O614">
-            <v>0</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P614">
             <v>0</v>
@@ -35767,16 +35707,16 @@
             <v>0</v>
           </cell>
           <cell r="R614">
-            <v>33266.03</v>
+            <v>34634.730000000003</v>
           </cell>
           <cell r="T614">
             <v>0</v>
           </cell>
           <cell r="U614">
-            <v>33266.03</v>
+            <v>34634.730000000003</v>
           </cell>
           <cell r="V614">
-            <v>8144.0400000000009</v>
+            <v>6775.3399999999965</v>
           </cell>
         </row>
         <row r="615">
@@ -35808,10 +35748,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N615">
-            <v>15892.659999999998</v>
+            <v>27487.4</v>
           </cell>
           <cell r="O615">
-            <v>7620.27</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P615">
             <v>0</v>
@@ -35820,16 +35760,16 @@
             <v>0</v>
           </cell>
           <cell r="R615">
-            <v>23512.93</v>
+            <v>28100.52</v>
           </cell>
           <cell r="T615">
             <v>0</v>
           </cell>
           <cell r="U615">
-            <v>23512.93</v>
+            <v>28100.52</v>
           </cell>
           <cell r="V615">
-            <v>17897.14</v>
+            <v>13309.55</v>
           </cell>
         </row>
         <row r="616">
@@ -35861,10 +35801,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N616">
-            <v>15022.710000000001</v>
+            <v>24633.74</v>
           </cell>
           <cell r="O616">
-            <v>6159.58</v>
+            <v>613.11999999999989</v>
           </cell>
           <cell r="P616">
             <v>0</v>
@@ -35873,16 +35813,16 @@
             <v>0</v>
           </cell>
           <cell r="R616">
-            <v>21182.29</v>
+            <v>25246.86</v>
           </cell>
           <cell r="T616">
             <v>0</v>
           </cell>
           <cell r="U616">
-            <v>21182.29</v>
+            <v>25246.86</v>
           </cell>
           <cell r="V616">
-            <v>20227.78</v>
+            <v>16163.21</v>
           </cell>
         </row>
         <row r="617">
@@ -35914,10 +35854,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N617">
-            <v>12694.37</v>
+            <v>14587.88</v>
           </cell>
           <cell r="O617">
-            <v>750</v>
+            <v>525.52</v>
           </cell>
           <cell r="P617">
             <v>0</v>
@@ -35926,16 +35866,16 @@
             <v>0</v>
           </cell>
           <cell r="R617">
-            <v>13444.37</v>
+            <v>15113.4</v>
           </cell>
           <cell r="T617">
-            <v>16000</v>
+            <v>0</v>
           </cell>
           <cell r="U617">
-            <v>29444.370000000003</v>
+            <v>15113.4</v>
           </cell>
           <cell r="V617">
-            <v>11965.699999999997</v>
+            <v>26296.67</v>
           </cell>
         </row>
         <row r="618">
@@ -35981,7 +35921,9 @@
           <cell r="R618">
             <v>-1560.97</v>
           </cell>
-          <cell r="T618"/>
+          <cell r="T618">
+            <v>0</v>
+          </cell>
           <cell r="U618">
             <v>-1560.97</v>
           </cell>
@@ -36006,28 +35948,28 @@
             <v>718642.58999999973</v>
           </cell>
           <cell r="N619">
-            <v>175764.47000000003</v>
+            <v>181892.92</v>
           </cell>
           <cell r="O619">
-            <v>1608.73</v>
+            <v>4432.91</v>
           </cell>
           <cell r="P619">
-            <v>47354.29</v>
+            <v>38401.549999999996</v>
           </cell>
           <cell r="Q619">
             <v>0</v>
           </cell>
           <cell r="R619">
-            <v>224727.49000000005</v>
+            <v>224727.38</v>
           </cell>
           <cell r="T619">
-            <v>228781.3</v>
+            <v>165998.12</v>
           </cell>
           <cell r="U619">
-            <v>453508.79000000004</v>
+            <v>390725.5</v>
           </cell>
           <cell r="V619">
-            <v>265133.7999999997</v>
+            <v>327917.08999999973</v>
           </cell>
         </row>
         <row r="620">
@@ -36047,28 +35989,28 @@
             <v>714676.40999999968</v>
           </cell>
           <cell r="N620">
-            <v>175764.47000000003</v>
+            <v>181892.92</v>
           </cell>
           <cell r="O620">
-            <v>1608.73</v>
+            <v>4432.91</v>
           </cell>
           <cell r="P620">
-            <v>47354.29</v>
+            <v>38401.549999999996</v>
           </cell>
           <cell r="Q620">
             <v>0</v>
           </cell>
           <cell r="R620">
-            <v>224727.49000000005</v>
+            <v>224727.38</v>
           </cell>
           <cell r="T620">
-            <v>224815.12</v>
+            <v>162031.94</v>
           </cell>
           <cell r="U620">
-            <v>449542.61000000004</v>
+            <v>386759.32</v>
           </cell>
           <cell r="V620">
-            <v>265133.79999999964</v>
+            <v>327917.08999999968</v>
           </cell>
         </row>
         <row r="621">
@@ -36212,22 +36154,22 @@
             <v>0</v>
           </cell>
           <cell r="P623">
-            <v>0.8</v>
+            <v>0.81</v>
           </cell>
           <cell r="Q623">
             <v>0</v>
           </cell>
           <cell r="R623">
-            <v>16836.47</v>
+            <v>16836.480000000003</v>
           </cell>
           <cell r="T623">
             <v>0</v>
           </cell>
           <cell r="U623">
-            <v>16836.47</v>
+            <v>16836.480000000003</v>
           </cell>
           <cell r="V623">
-            <v>26889.25</v>
+            <v>26889.239999999998</v>
           </cell>
         </row>
         <row r="624">
@@ -36318,22 +36260,22 @@
             <v>0</v>
           </cell>
           <cell r="P625">
-            <v>535.63</v>
+            <v>535.64</v>
           </cell>
           <cell r="Q625">
             <v>0</v>
           </cell>
           <cell r="R625">
-            <v>13229.09</v>
+            <v>13229.1</v>
           </cell>
           <cell r="T625">
             <v>0</v>
           </cell>
           <cell r="U625">
-            <v>13229.09</v>
+            <v>13229.1</v>
           </cell>
           <cell r="V625">
-            <v>30496.63</v>
+            <v>30496.620000000003</v>
           </cell>
         </row>
         <row r="626">
@@ -36371,22 +36313,22 @@
             <v>0</v>
           </cell>
           <cell r="P626">
-            <v>1902.17</v>
+            <v>1902.19</v>
           </cell>
           <cell r="Q626">
             <v>0</v>
           </cell>
           <cell r="R626">
-            <v>13229.1</v>
+            <v>13229.12</v>
           </cell>
           <cell r="T626">
             <v>0</v>
           </cell>
           <cell r="U626">
-            <v>13229.1</v>
+            <v>13229.12</v>
           </cell>
           <cell r="V626">
-            <v>30496.620000000003</v>
+            <v>30496.6</v>
           </cell>
         </row>
         <row r="627">
@@ -36424,22 +36366,22 @@
             <v>0</v>
           </cell>
           <cell r="P627">
-            <v>596.88000000000011</v>
+            <v>596.9</v>
           </cell>
           <cell r="Q627">
             <v>0</v>
           </cell>
           <cell r="R627">
-            <v>13210.369999999999</v>
+            <v>13210.389999999998</v>
           </cell>
           <cell r="T627">
             <v>0</v>
           </cell>
           <cell r="U627">
-            <v>13210.369999999999</v>
+            <v>13210.389999999998</v>
           </cell>
           <cell r="V627">
-            <v>30515.350000000002</v>
+            <v>30515.33</v>
           </cell>
         </row>
         <row r="628">
@@ -36477,22 +36419,22 @@
             <v>0</v>
           </cell>
           <cell r="P628">
-            <v>596.88000000000011</v>
+            <v>596.9</v>
           </cell>
           <cell r="Q628">
             <v>0</v>
           </cell>
           <cell r="R628">
-            <v>14074.170000000002</v>
+            <v>14074.19</v>
           </cell>
           <cell r="T628">
             <v>0</v>
           </cell>
           <cell r="U628">
-            <v>14074.170000000002</v>
+            <v>14074.19</v>
           </cell>
           <cell r="V628">
-            <v>29651.55</v>
+            <v>29651.53</v>
           </cell>
         </row>
         <row r="629">
@@ -36530,22 +36472,22 @@
             <v>0</v>
           </cell>
           <cell r="P629">
-            <v>596.88000000000011</v>
+            <v>596.9</v>
           </cell>
           <cell r="Q629">
             <v>0</v>
           </cell>
           <cell r="R629">
-            <v>12462.98</v>
+            <v>12463</v>
           </cell>
           <cell r="T629">
             <v>0</v>
           </cell>
           <cell r="U629">
-            <v>12462.98</v>
+            <v>12463</v>
           </cell>
           <cell r="V629">
-            <v>31262.74</v>
+            <v>31262.720000000001</v>
           </cell>
         </row>
         <row r="630">
@@ -36583,22 +36525,22 @@
             <v>0</v>
           </cell>
           <cell r="P630">
-            <v>1338.8899999999999</v>
+            <v>1338.9</v>
           </cell>
           <cell r="Q630">
             <v>0</v>
           </cell>
           <cell r="R630">
-            <v>12462.99</v>
+            <v>12463</v>
           </cell>
           <cell r="T630">
             <v>0</v>
           </cell>
           <cell r="U630">
-            <v>12462.99</v>
+            <v>12463</v>
           </cell>
           <cell r="V630">
-            <v>31262.730000000003</v>
+            <v>31262.720000000001</v>
           </cell>
         </row>
         <row r="631">
@@ -36636,22 +36578,22 @@
             <v>0</v>
           </cell>
           <cell r="P631">
-            <v>1106.8899999999999</v>
+            <v>1106.8799999999999</v>
           </cell>
           <cell r="Q631">
             <v>0</v>
           </cell>
           <cell r="R631">
-            <v>12462.99</v>
+            <v>12462.98</v>
           </cell>
           <cell r="T631">
             <v>0</v>
           </cell>
           <cell r="U631">
-            <v>12462.99</v>
+            <v>12462.98</v>
           </cell>
           <cell r="V631">
-            <v>31262.730000000003</v>
+            <v>31262.74</v>
           </cell>
         </row>
         <row r="632">
@@ -36683,28 +36625,28 @@
             <v>43725.72</v>
           </cell>
           <cell r="N632">
-            <v>6024.2300000000005</v>
+            <v>10812.070000000002</v>
           </cell>
           <cell r="O632">
-            <v>268.12</v>
+            <v>0</v>
           </cell>
           <cell r="P632">
-            <v>5644.8</v>
+            <v>1124.8800000000001</v>
           </cell>
           <cell r="Q632">
             <v>0</v>
           </cell>
           <cell r="R632">
-            <v>11937.150000000001</v>
+            <v>11936.95</v>
           </cell>
           <cell r="T632">
-            <v>31788.57</v>
+            <v>0</v>
           </cell>
           <cell r="U632">
-            <v>43725.72</v>
+            <v>11936.95</v>
           </cell>
           <cell r="V632">
-            <v>0</v>
+            <v>31788.77</v>
           </cell>
         </row>
         <row r="633">
@@ -36736,28 +36678,28 @@
             <v>43725.72</v>
           </cell>
           <cell r="N633">
-            <v>6818.1900000000005</v>
+            <v>7086.31</v>
           </cell>
           <cell r="O633">
-            <v>268.12</v>
+            <v>4432.91</v>
           </cell>
           <cell r="P633">
-            <v>5644.8</v>
+            <v>1211.8800000000001</v>
           </cell>
           <cell r="Q633">
             <v>0</v>
           </cell>
           <cell r="R633">
-            <v>12731.11</v>
+            <v>12731.100000000002</v>
           </cell>
           <cell r="T633">
-            <v>30994.61</v>
+            <v>0</v>
           </cell>
           <cell r="U633">
-            <v>43725.72</v>
+            <v>12731.100000000002</v>
           </cell>
           <cell r="V633">
-            <v>0</v>
+            <v>30994.62</v>
           </cell>
         </row>
         <row r="634">
@@ -36789,10 +36731,10 @@
             <v>43725.72</v>
           </cell>
           <cell r="N634">
-            <v>6818.1900000000005</v>
+            <v>7086.31</v>
           </cell>
           <cell r="O634">
-            <v>268.12</v>
+            <v>0</v>
           </cell>
           <cell r="P634">
             <v>5644.8</v>
@@ -36842,10 +36784,10 @@
             <v>43725.72</v>
           </cell>
           <cell r="N635">
-            <v>8533.19</v>
+            <v>8801.3100000000013</v>
           </cell>
           <cell r="O635">
-            <v>268.12</v>
+            <v>0</v>
           </cell>
           <cell r="P635">
             <v>5644.8</v>
@@ -36895,10 +36837,10 @@
             <v>43725.72</v>
           </cell>
           <cell r="N636">
-            <v>8533.19</v>
+            <v>8801.3100000000013</v>
           </cell>
           <cell r="O636">
-            <v>268.12</v>
+            <v>0</v>
           </cell>
           <cell r="P636">
             <v>5644.8</v>
@@ -36948,10 +36890,10 @@
             <v>43725.72</v>
           </cell>
           <cell r="N637">
-            <v>8533.19</v>
+            <v>8801.32</v>
           </cell>
           <cell r="O637">
-            <v>268.13</v>
+            <v>0</v>
           </cell>
           <cell r="P637">
             <v>5644.8</v>
@@ -37136,28 +37078,28 @@
             <v>457093.31999999995</v>
           </cell>
           <cell r="N641">
-            <v>272447.16000000003</v>
+            <v>292479.10000000003</v>
           </cell>
           <cell r="O641">
-            <v>6061.52</v>
+            <v>11341.23</v>
           </cell>
           <cell r="P641">
-            <v>62689.079999999994</v>
+            <v>50559.19</v>
           </cell>
           <cell r="Q641">
-            <v>2626.96</v>
+            <v>2054.9899999999998</v>
           </cell>
           <cell r="R641">
-            <v>343824.72000000009</v>
+            <v>356434.51</v>
           </cell>
           <cell r="T641">
-            <v>48846.32</v>
+            <v>49305.16</v>
           </cell>
           <cell r="U641">
-            <v>392671.0400000001</v>
+            <v>405739.67000000004</v>
           </cell>
           <cell r="V641">
-            <v>64422.279999999853</v>
+            <v>51353.649999999907</v>
           </cell>
         </row>
         <row r="642">
@@ -37177,28 +37119,28 @@
             <v>87122.2</v>
           </cell>
           <cell r="N642">
-            <v>55219.9</v>
+            <v>69539.899999999994</v>
           </cell>
           <cell r="O642">
-            <v>5960</v>
+            <v>0</v>
           </cell>
           <cell r="P642">
-            <v>12275</v>
+            <v>7074.99</v>
           </cell>
           <cell r="Q642">
             <v>0</v>
           </cell>
           <cell r="R642">
-            <v>73454.899999999994</v>
+            <v>76614.89</v>
           </cell>
           <cell r="T642">
             <v>11717.2</v>
           </cell>
           <cell r="U642">
-            <v>85172.099999999991</v>
+            <v>88332.09</v>
           </cell>
           <cell r="V642">
-            <v>1950.1000000000058</v>
+            <v>-1209.8899999999994</v>
           </cell>
         </row>
         <row r="643">
@@ -37713,22 +37655,22 @@
             <v>0</v>
           </cell>
           <cell r="P652">
-            <v>274.8</v>
+            <v>274.81</v>
           </cell>
           <cell r="Q652">
             <v>0</v>
           </cell>
           <cell r="R652">
-            <v>3144.8</v>
+            <v>3144.81</v>
           </cell>
           <cell r="T652">
             <v>0</v>
           </cell>
           <cell r="U652">
-            <v>3144.8</v>
+            <v>3144.81</v>
           </cell>
           <cell r="V652">
-            <v>1882.1999999999998</v>
+            <v>1882.19</v>
           </cell>
         </row>
         <row r="653">
@@ -37866,28 +37808,28 @@
             <v>5027</v>
           </cell>
           <cell r="N655">
-            <v>3887</v>
+            <v>7202</v>
           </cell>
           <cell r="O655">
-            <v>915</v>
+            <v>0</v>
           </cell>
           <cell r="P655">
-            <v>2400.04</v>
+            <v>0</v>
           </cell>
           <cell r="Q655">
             <v>0</v>
           </cell>
           <cell r="R655">
-            <v>7202.04</v>
+            <v>7202</v>
           </cell>
           <cell r="T655">
             <v>0</v>
           </cell>
           <cell r="U655">
-            <v>7202.04</v>
+            <v>7202</v>
           </cell>
           <cell r="V655">
-            <v>-2175.04</v>
+            <v>-2175</v>
           </cell>
         </row>
         <row r="656">
@@ -37919,28 +37861,28 @@
             <v>5027</v>
           </cell>
           <cell r="N656">
-            <v>3887</v>
+            <v>7202</v>
           </cell>
           <cell r="O656">
-            <v>915</v>
+            <v>0</v>
           </cell>
           <cell r="P656">
-            <v>2400.04</v>
+            <v>0</v>
           </cell>
           <cell r="Q656">
             <v>0</v>
           </cell>
           <cell r="R656">
-            <v>7202.04</v>
+            <v>7202</v>
           </cell>
           <cell r="T656">
             <v>0</v>
           </cell>
           <cell r="U656">
-            <v>7202.04</v>
+            <v>7202</v>
           </cell>
           <cell r="V656">
-            <v>-2175.04</v>
+            <v>-2175</v>
           </cell>
         </row>
         <row r="657">
@@ -37972,28 +37914,28 @@
             <v>5027</v>
           </cell>
           <cell r="N657">
-            <v>3887</v>
+            <v>5202</v>
           </cell>
           <cell r="O657">
-            <v>915</v>
+            <v>0</v>
           </cell>
           <cell r="P657">
-            <v>2400.04</v>
+            <v>2000</v>
           </cell>
           <cell r="Q657">
             <v>0</v>
           </cell>
           <cell r="R657">
-            <v>7202.04</v>
+            <v>7202</v>
           </cell>
           <cell r="T657">
             <v>0</v>
           </cell>
           <cell r="U657">
-            <v>7202.04</v>
+            <v>7202</v>
           </cell>
           <cell r="V657">
-            <v>-2175.04</v>
+            <v>-2175</v>
           </cell>
         </row>
         <row r="658">
@@ -38025,28 +37967,28 @@
             <v>5027</v>
           </cell>
           <cell r="N658">
-            <v>3887</v>
+            <v>6032</v>
           </cell>
           <cell r="O658">
-            <v>2065</v>
+            <v>0</v>
           </cell>
           <cell r="P658">
-            <v>2400.04</v>
+            <v>2400.09</v>
           </cell>
           <cell r="Q658">
             <v>0</v>
           </cell>
           <cell r="R658">
-            <v>8352.0400000000009</v>
+            <v>8432.09</v>
           </cell>
           <cell r="T658">
             <v>0</v>
           </cell>
           <cell r="U658">
-            <v>8352.0400000000009</v>
+            <v>8432.09</v>
           </cell>
           <cell r="V658">
-            <v>-3325.0400000000009</v>
+            <v>-3405.09</v>
           </cell>
         </row>
         <row r="659">
@@ -38078,28 +38020,28 @@
             <v>5027</v>
           </cell>
           <cell r="N659">
-            <v>3887</v>
+            <v>8117</v>
           </cell>
           <cell r="O659">
-            <v>1150</v>
+            <v>0</v>
           </cell>
           <cell r="P659">
-            <v>2400.04</v>
+            <v>2400.09</v>
           </cell>
           <cell r="Q659">
             <v>0</v>
           </cell>
           <cell r="R659">
-            <v>7437.04</v>
+            <v>10517.09</v>
           </cell>
           <cell r="T659">
             <v>0</v>
           </cell>
           <cell r="U659">
-            <v>7437.04</v>
+            <v>10517.09</v>
           </cell>
           <cell r="V659">
-            <v>-2410.04</v>
+            <v>-5490.09</v>
           </cell>
         </row>
         <row r="660">
@@ -40162,10 +40104,10 @@
             <v>97708.799999999988</v>
           </cell>
           <cell r="N699">
-            <v>183498.60000000003</v>
+            <v>189210.54000000004</v>
           </cell>
           <cell r="O699">
-            <v>101.52000000000001</v>
+            <v>0</v>
           </cell>
           <cell r="P699">
             <v>0</v>
@@ -40174,16 +40116,16 @@
             <v>0</v>
           </cell>
           <cell r="R699">
-            <v>183600.12000000002</v>
+            <v>189210.54000000004</v>
           </cell>
           <cell r="T699">
-            <v>-458.84999999999997</v>
+            <v>0</v>
           </cell>
           <cell r="U699">
-            <v>183141.27000000002</v>
+            <v>189210.54000000004</v>
           </cell>
           <cell r="V699">
-            <v>-85432.47000000003</v>
+            <v>-91501.740000000049</v>
           </cell>
         </row>
         <row r="700">
@@ -40230,13 +40172,13 @@
             <v>458.84999999999997</v>
           </cell>
           <cell r="T700">
+            <v>0</v>
+          </cell>
+          <cell r="U700">
+            <v>458.84999999999997</v>
+          </cell>
+          <cell r="V700">
             <v>-458.84999999999997</v>
-          </cell>
-          <cell r="U700">
-            <v>0</v>
-          </cell>
-          <cell r="V700">
-            <v>0</v>
           </cell>
         </row>
         <row r="701">
@@ -41010,7 +40952,7 @@
             <v>6513.92</v>
           </cell>
           <cell r="N715">
-            <v>4262.4999999999991</v>
+            <v>5603.6699999999992</v>
           </cell>
           <cell r="O715">
             <v>0</v>
@@ -41022,16 +40964,16 @@
             <v>0</v>
           </cell>
           <cell r="R715">
-            <v>4262.4999999999991</v>
+            <v>5603.6699999999992</v>
           </cell>
           <cell r="T715">
             <v>0</v>
           </cell>
           <cell r="U715">
-            <v>4262.4999999999991</v>
+            <v>5603.6699999999992</v>
           </cell>
           <cell r="V715">
-            <v>2251.420000000001</v>
+            <v>910.25000000000091</v>
           </cell>
         </row>
         <row r="716">
@@ -41063,10 +41005,10 @@
             <v>6513.92</v>
           </cell>
           <cell r="N716">
-            <v>8235.66</v>
+            <v>12606.43</v>
           </cell>
           <cell r="O716">
-            <v>101.52000000000001</v>
+            <v>0</v>
           </cell>
           <cell r="P716">
             <v>0</v>
@@ -41075,16 +41017,16 @@
             <v>0</v>
           </cell>
           <cell r="R716">
-            <v>8337.18</v>
+            <v>12606.43</v>
           </cell>
           <cell r="T716">
             <v>0</v>
           </cell>
           <cell r="U716">
-            <v>8337.18</v>
+            <v>12606.43</v>
           </cell>
           <cell r="V716">
-            <v>-1823.2600000000002</v>
+            <v>-6092.51</v>
           </cell>
         </row>
         <row r="717">
@@ -42155,25 +42097,25 @@
             <v>39892.479999999981</v>
           </cell>
           <cell r="O737">
-            <v>0</v>
+            <v>9019.9599999999991</v>
           </cell>
           <cell r="P737">
-            <v>36962.199999999997</v>
+            <v>32353.45</v>
           </cell>
           <cell r="Q737">
-            <v>2626.96</v>
+            <v>2054.9899999999998</v>
           </cell>
           <cell r="R737">
-            <v>79481.639999999985</v>
+            <v>83320.87999999999</v>
           </cell>
           <cell r="T737">
             <v>0</v>
           </cell>
           <cell r="U737">
-            <v>79481.639999999985</v>
+            <v>83320.87999999999</v>
           </cell>
           <cell r="V737">
-            <v>22070.570000000007</v>
+            <v>18231.330000000002</v>
           </cell>
         </row>
         <row r="738">
@@ -42261,25 +42203,25 @@
             <v>0</v>
           </cell>
           <cell r="O739">
-            <v>0</v>
+            <v>1784</v>
           </cell>
           <cell r="P739">
-            <v>4608.9799999999996</v>
+            <v>4609.0200000000004</v>
           </cell>
           <cell r="Q739">
-            <v>0</v>
+            <v>293.57</v>
           </cell>
           <cell r="R739">
-            <v>4608.9799999999996</v>
+            <v>6686.59</v>
           </cell>
           <cell r="T739">
             <v>0</v>
           </cell>
           <cell r="U739">
-            <v>4608.9799999999996</v>
+            <v>6686.59</v>
           </cell>
           <cell r="V739">
-            <v>335.28000000000065</v>
+            <v>-1742.33</v>
           </cell>
         </row>
         <row r="740">
@@ -42317,22 +42259,22 @@
             <v>0</v>
           </cell>
           <cell r="P740">
-            <v>2232.14</v>
+            <v>2232.13</v>
           </cell>
           <cell r="Q740">
-            <v>0</v>
+            <v>293.57</v>
           </cell>
           <cell r="R740">
-            <v>6216.36</v>
+            <v>6509.92</v>
           </cell>
           <cell r="T740">
             <v>0</v>
           </cell>
           <cell r="U740">
-            <v>6216.36</v>
+            <v>6509.92</v>
           </cell>
           <cell r="V740">
-            <v>224.17000000000007</v>
+            <v>-69.390000000000327</v>
           </cell>
         </row>
         <row r="741">
@@ -42373,19 +42315,19 @@
             <v>2467.1999999999998</v>
           </cell>
           <cell r="Q741">
-            <v>0</v>
+            <v>293.57</v>
           </cell>
           <cell r="R741">
-            <v>4667.91</v>
+            <v>4961.4799999999996</v>
           </cell>
           <cell r="T741">
             <v>0</v>
           </cell>
           <cell r="U741">
-            <v>4667.91</v>
+            <v>4961.4799999999996</v>
           </cell>
           <cell r="V741">
-            <v>1772.62</v>
+            <v>1479.0500000000002</v>
           </cell>
         </row>
         <row r="742">
@@ -42426,19 +42368,19 @@
             <v>0</v>
           </cell>
           <cell r="Q742">
-            <v>0</v>
+            <v>293.57</v>
           </cell>
           <cell r="R742">
-            <v>4676.3500000000004</v>
+            <v>4969.92</v>
           </cell>
           <cell r="T742">
             <v>0</v>
           </cell>
           <cell r="U742">
-            <v>4676.3500000000004</v>
+            <v>4969.92</v>
           </cell>
           <cell r="V742">
-            <v>1764.1799999999994</v>
+            <v>1470.6099999999997</v>
           </cell>
         </row>
         <row r="743">
@@ -42479,19 +42421,19 @@
             <v>0</v>
           </cell>
           <cell r="Q743">
-            <v>0</v>
+            <v>293.57</v>
           </cell>
           <cell r="R743">
-            <v>4676.3500000000004</v>
+            <v>4969.92</v>
           </cell>
           <cell r="T743">
             <v>0</v>
           </cell>
           <cell r="U743">
-            <v>4676.3500000000004</v>
+            <v>4969.92</v>
           </cell>
           <cell r="V743">
-            <v>1764.1799999999994</v>
+            <v>1470.6099999999997</v>
           </cell>
         </row>
         <row r="744">
@@ -42532,19 +42474,19 @@
             <v>0</v>
           </cell>
           <cell r="Q744">
-            <v>0</v>
+            <v>293.57</v>
           </cell>
           <cell r="R744">
-            <v>4667.8500000000004</v>
+            <v>4961.42</v>
           </cell>
           <cell r="T744">
             <v>0</v>
           </cell>
           <cell r="U744">
-            <v>4667.8500000000004</v>
+            <v>4961.42</v>
           </cell>
           <cell r="V744">
-            <v>1772.6799999999994</v>
+            <v>1479.1099999999997</v>
           </cell>
         </row>
         <row r="745">
@@ -42585,19 +42527,19 @@
             <v>0</v>
           </cell>
           <cell r="Q745">
-            <v>0</v>
+            <v>293.57</v>
           </cell>
           <cell r="R745">
-            <v>4644.1000000000004</v>
+            <v>4937.67</v>
           </cell>
           <cell r="T745">
             <v>0</v>
           </cell>
           <cell r="U745">
-            <v>4644.1000000000004</v>
+            <v>4937.67</v>
           </cell>
           <cell r="V745">
-            <v>1796.4299999999994</v>
+            <v>1502.8599999999997</v>
           </cell>
         </row>
         <row r="746">
@@ -42738,13 +42680,13 @@
             <v>4644.1000000000004</v>
           </cell>
           <cell r="O748">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P748">
             <v>0</v>
           </cell>
           <cell r="Q748">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R748">
             <v>5019.38</v>
@@ -42791,25 +42733,25 @@
             <v>35.1</v>
           </cell>
           <cell r="O749">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P749">
-            <v>4608.9799999999996</v>
+            <v>4609.0200000000004</v>
           </cell>
           <cell r="Q749">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R749">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="T749">
             <v>0</v>
           </cell>
           <cell r="U749">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="V749">
-            <v>1421.17</v>
+            <v>1421.1299999999992</v>
           </cell>
         </row>
         <row r="750">
@@ -42844,25 +42786,25 @@
             <v>35.1</v>
           </cell>
           <cell r="O750">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P750">
-            <v>4608.9799999999996</v>
+            <v>4609.0200000000004</v>
           </cell>
           <cell r="Q750">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R750">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="T750">
             <v>0</v>
           </cell>
           <cell r="U750">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="V750">
-            <v>1421.17</v>
+            <v>1421.1299999999992</v>
           </cell>
         </row>
         <row r="751">
@@ -42897,25 +42839,25 @@
             <v>35.1</v>
           </cell>
           <cell r="O751">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P751">
-            <v>4608.9799999999996</v>
+            <v>4609.0200000000004</v>
           </cell>
           <cell r="Q751">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R751">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="T751">
             <v>0</v>
           </cell>
           <cell r="U751">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="V751">
-            <v>1421.17</v>
+            <v>1421.1299999999992</v>
           </cell>
         </row>
         <row r="752">
@@ -42950,25 +42892,25 @@
             <v>35.1</v>
           </cell>
           <cell r="O752">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P752">
-            <v>4608.9799999999996</v>
+            <v>4609.0200000000004</v>
           </cell>
           <cell r="Q752">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R752">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="T752">
             <v>0</v>
           </cell>
           <cell r="U752">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="V752">
-            <v>1421.17</v>
+            <v>1421.1299999999992</v>
           </cell>
         </row>
         <row r="753">
@@ -43003,25 +42945,25 @@
             <v>35.1</v>
           </cell>
           <cell r="O753">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P753">
-            <v>4608.9799999999996</v>
+            <v>4609.0200000000004</v>
           </cell>
           <cell r="Q753">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R753">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="T753">
             <v>0</v>
           </cell>
           <cell r="U753">
-            <v>5019.3599999999997</v>
+            <v>5019.4000000000005</v>
           </cell>
           <cell r="V753">
-            <v>1421.17</v>
+            <v>1421.1299999999992</v>
           </cell>
         </row>
         <row r="754">
@@ -43056,25 +42998,25 @@
             <v>35.1</v>
           </cell>
           <cell r="O754">
-            <v>0</v>
+            <v>4984.28</v>
           </cell>
           <cell r="P754">
-            <v>4608.9799999999996</v>
+            <v>0</v>
           </cell>
           <cell r="Q754">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R754">
-            <v>5019.3599999999997</v>
+            <v>5019.38</v>
           </cell>
           <cell r="T754">
             <v>0</v>
           </cell>
           <cell r="U754">
-            <v>5019.3599999999997</v>
+            <v>5019.38</v>
           </cell>
           <cell r="V754">
-            <v>1421.17</v>
+            <v>1421.1499999999996</v>
           </cell>
         </row>
         <row r="755">
@@ -43150,25 +43092,25 @@
             <v>6743</v>
           </cell>
           <cell r="O756">
-            <v>0</v>
+            <v>2321.27</v>
           </cell>
           <cell r="P756">
-            <v>13451.88</v>
+            <v>11130.75</v>
           </cell>
           <cell r="Q756">
             <v>0</v>
           </cell>
           <cell r="R756">
-            <v>20194.879999999997</v>
+            <v>20195.02</v>
           </cell>
           <cell r="T756">
-            <v>28720.559999999998</v>
+            <v>28720.55</v>
           </cell>
           <cell r="U756">
-            <v>48915.439999999995</v>
+            <v>48915.57</v>
           </cell>
           <cell r="V756">
-            <v>-28563.99000000002</v>
+            <v>-28564.120000000024</v>
           </cell>
         </row>
         <row r="757">
@@ -43206,16 +43148,16 @@
             <v>0</v>
           </cell>
           <cell r="P757">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q757">
             <v>0</v>
           </cell>
           <cell r="R757">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T757">
-            <v>14720.56</v>
+            <v>14720.55</v>
           </cell>
           <cell r="U757">
             <v>15841.55</v>
@@ -43259,22 +43201,22 @@
             <v>0</v>
           </cell>
           <cell r="P758">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q758">
             <v>0</v>
           </cell>
           <cell r="R758">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T758">
             <v>6000</v>
           </cell>
           <cell r="U758">
-            <v>7120.99</v>
+            <v>7121</v>
           </cell>
           <cell r="V758">
-            <v>-6586.93</v>
+            <v>-6586.9400000000005</v>
           </cell>
         </row>
         <row r="759">
@@ -43312,22 +43254,22 @@
             <v>0</v>
           </cell>
           <cell r="P759">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q759">
             <v>0</v>
           </cell>
           <cell r="R759">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T759">
             <v>500</v>
           </cell>
           <cell r="U759">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V759">
-            <v>-1381.73</v>
+            <v>-1381.74</v>
           </cell>
         </row>
         <row r="760">
@@ -43365,22 +43307,22 @@
             <v>0</v>
           </cell>
           <cell r="P760">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q760">
             <v>0</v>
           </cell>
           <cell r="R760">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T760">
             <v>500</v>
           </cell>
           <cell r="U760">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V760">
-            <v>-1381.73</v>
+            <v>-1381.74</v>
           </cell>
         </row>
         <row r="761">
@@ -43733,25 +43675,25 @@
             <v>0</v>
           </cell>
           <cell r="O767">
-            <v>0</v>
+            <v>1121</v>
           </cell>
           <cell r="P767">
-            <v>1120.99</v>
+            <v>0</v>
           </cell>
           <cell r="Q767">
             <v>0</v>
           </cell>
           <cell r="R767">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T767">
             <v>500</v>
           </cell>
           <cell r="U767">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V767">
-            <v>-1381.73</v>
+            <v>-1381.74</v>
           </cell>
         </row>
         <row r="768">
@@ -43786,25 +43728,25 @@
             <v>0</v>
           </cell>
           <cell r="O768">
-            <v>0</v>
+            <v>1121</v>
           </cell>
           <cell r="P768">
-            <v>1120.99</v>
+            <v>0</v>
           </cell>
           <cell r="Q768">
             <v>0</v>
           </cell>
           <cell r="R768">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T768">
             <v>500</v>
           </cell>
           <cell r="U768">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V768">
-            <v>-1381.73</v>
+            <v>-1381.74</v>
           </cell>
         </row>
         <row r="769">
@@ -43839,25 +43781,25 @@
             <v>0</v>
           </cell>
           <cell r="O769">
-            <v>0</v>
+            <v>79.27</v>
           </cell>
           <cell r="P769">
-            <v>1120.99</v>
+            <v>1041.75</v>
           </cell>
           <cell r="Q769">
             <v>0</v>
           </cell>
           <cell r="R769">
-            <v>1120.99</v>
+            <v>1121.02</v>
           </cell>
           <cell r="T769">
             <v>500</v>
           </cell>
           <cell r="U769">
-            <v>1620.99</v>
+            <v>1621.02</v>
           </cell>
           <cell r="V769">
-            <v>-1381.73</v>
+            <v>-1381.76</v>
           </cell>
         </row>
         <row r="770">
@@ -43895,22 +43837,22 @@
             <v>0</v>
           </cell>
           <cell r="P770">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q770">
             <v>0</v>
           </cell>
           <cell r="R770">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T770">
             <v>500</v>
           </cell>
           <cell r="U770">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V770">
-            <v>-1381.73</v>
+            <v>-1381.74</v>
           </cell>
         </row>
         <row r="771">
@@ -43948,22 +43890,22 @@
             <v>0</v>
           </cell>
           <cell r="P771">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q771">
             <v>0</v>
           </cell>
           <cell r="R771">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T771">
             <v>500</v>
           </cell>
           <cell r="U771">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V771">
-            <v>-1381.73</v>
+            <v>-1381.74</v>
           </cell>
         </row>
         <row r="772">
@@ -44001,22 +43943,22 @@
             <v>0</v>
           </cell>
           <cell r="P772">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q772">
             <v>0</v>
           </cell>
           <cell r="R772">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T772">
             <v>500</v>
           </cell>
           <cell r="U772">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V772">
-            <v>-1381.73</v>
+            <v>-1381.74</v>
           </cell>
         </row>
         <row r="773">
@@ -44054,22 +43996,22 @@
             <v>0</v>
           </cell>
           <cell r="P773">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q773">
             <v>0</v>
           </cell>
           <cell r="R773">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T773">
             <v>500</v>
           </cell>
           <cell r="U773">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V773">
-            <v>-1381.73</v>
+            <v>-1381.74</v>
           </cell>
         </row>
         <row r="774">
@@ -44107,22 +44049,22 @@
             <v>0</v>
           </cell>
           <cell r="P774">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="Q774">
             <v>0</v>
           </cell>
           <cell r="R774">
-            <v>1120.99</v>
+            <v>1121</v>
           </cell>
           <cell r="T774">
             <v>500</v>
           </cell>
           <cell r="U774">
-            <v>1620.99</v>
+            <v>1621</v>
           </cell>
           <cell r="V774">
-            <v>-1234.05</v>
+            <v>-1234.06</v>
           </cell>
         </row>
         <row r="775">
@@ -44142,28 +44084,28 @@
             <v>1301538.4799999997</v>
           </cell>
           <cell r="N775">
-            <v>796582.93</v>
+            <v>834611.95</v>
           </cell>
           <cell r="O775">
-            <v>18191.990000000002</v>
+            <v>15706.619999999999</v>
           </cell>
           <cell r="P775">
-            <v>91999.85</v>
+            <v>66210.189999999988</v>
           </cell>
           <cell r="Q775">
-            <v>1651.9</v>
+            <v>1786.65</v>
           </cell>
           <cell r="R775">
-            <v>908426.67</v>
+            <v>918315.40999999992</v>
           </cell>
           <cell r="T775">
-            <v>193514.21</v>
+            <v>172186.28999999998</v>
           </cell>
           <cell r="U775">
-            <v>1101940.8800000001</v>
+            <v>1090501.7</v>
           </cell>
           <cell r="V775">
-            <v>199597.59999999963</v>
+            <v>211036.7799999998</v>
           </cell>
         </row>
         <row r="776">
@@ -44183,7 +44125,7 @@
             <v>300525.42</v>
           </cell>
           <cell r="N776">
-            <v>136660.52000000002</v>
+            <v>139095.39000000001</v>
           </cell>
           <cell r="O776">
             <v>0</v>
@@ -44195,16 +44137,16 @@
             <v>0</v>
           </cell>
           <cell r="R776">
-            <v>136660.52000000002</v>
+            <v>139095.39000000001</v>
           </cell>
           <cell r="T776">
-            <v>94943.200000000026</v>
+            <v>90524.91</v>
           </cell>
           <cell r="U776">
-            <v>231603.72000000003</v>
+            <v>229620.30000000002</v>
           </cell>
           <cell r="V776">
-            <v>68921.699999999953</v>
+            <v>70905.119999999966</v>
           </cell>
         </row>
         <row r="777">
@@ -44289,7 +44231,7 @@
             <v>264279.38</v>
           </cell>
           <cell r="N778">
-            <v>121277.64</v>
+            <v>123712.51</v>
           </cell>
           <cell r="O778">
             <v>0</v>
@@ -44301,16 +44243,16 @@
             <v>0</v>
           </cell>
           <cell r="R778">
-            <v>121277.64</v>
+            <v>123712.51</v>
           </cell>
           <cell r="T778">
-            <v>73303.570000000022</v>
+            <v>68885.279999999999</v>
           </cell>
           <cell r="U778">
-            <v>194581.21000000002</v>
+            <v>192597.78999999998</v>
           </cell>
           <cell r="V778">
-            <v>69698.169999999984</v>
+            <v>71681.590000000026</v>
           </cell>
         </row>
         <row r="779">
@@ -44451,13 +44393,13 @@
             <v>23431.620000000003</v>
           </cell>
           <cell r="T781">
-            <v>1091.9100000000001</v>
+            <v>895.28</v>
           </cell>
           <cell r="U781">
-            <v>24523.530000000002</v>
+            <v>24326.9</v>
           </cell>
           <cell r="V781">
-            <v>-11170.620000000006</v>
+            <v>-10973.990000000005</v>
           </cell>
         </row>
         <row r="782">
@@ -44504,13 +44446,13 @@
             <v>0</v>
           </cell>
           <cell r="T782">
+            <v>0</v>
+          </cell>
+          <cell r="U782">
+            <v>0</v>
+          </cell>
+          <cell r="V782">
             <v>196.63</v>
-          </cell>
-          <cell r="U782">
-            <v>196.63</v>
-          </cell>
-          <cell r="V782">
-            <v>0</v>
           </cell>
         </row>
         <row r="783">
@@ -45431,10 +45373,10 @@
             <v>284879.06999999989</v>
           </cell>
           <cell r="N800">
-            <v>158536.24</v>
+            <v>174692.47999999998</v>
           </cell>
           <cell r="O800">
-            <v>13032.36</v>
+            <v>2820.81</v>
           </cell>
           <cell r="P800">
             <v>0</v>
@@ -45443,16 +45385,16 @@
             <v>1432</v>
           </cell>
           <cell r="R800">
-            <v>173000.59999999998</v>
+            <v>178945.28999999998</v>
           </cell>
           <cell r="T800">
-            <v>22982.14</v>
+            <v>17846.95</v>
           </cell>
           <cell r="U800">
-            <v>195982.74</v>
+            <v>196792.24</v>
           </cell>
           <cell r="V800">
-            <v>88896.3299999999</v>
+            <v>88086.8299999999</v>
           </cell>
         </row>
         <row r="801">
@@ -45499,13 +45441,13 @@
             <v>0</v>
           </cell>
           <cell r="T801">
+            <v>0</v>
+          </cell>
+          <cell r="U801">
+            <v>0</v>
+          </cell>
+          <cell r="V801">
             <v>4194.92</v>
-          </cell>
-          <cell r="U801">
-            <v>4194.92</v>
-          </cell>
-          <cell r="V801">
-            <v>0</v>
           </cell>
         </row>
         <row r="802">
@@ -45540,7 +45482,7 @@
             <v>0</v>
           </cell>
           <cell r="O802">
-            <v>0</v>
+            <v>940.27</v>
           </cell>
           <cell r="P802">
             <v>0</v>
@@ -45549,10 +45491,10 @@
             <v>0</v>
           </cell>
           <cell r="R802">
-            <v>0</v>
+            <v>940.27</v>
           </cell>
           <cell r="T802">
-            <v>18787.22</v>
+            <v>17846.95</v>
           </cell>
           <cell r="U802">
             <v>18787.22</v>
@@ -46279,10 +46221,10 @@
             <v>17438.919999999998</v>
           </cell>
           <cell r="N816">
-            <v>8010.8799999999992</v>
+            <v>13697.4</v>
           </cell>
           <cell r="O816">
-            <v>4374.58</v>
+            <v>940.27</v>
           </cell>
           <cell r="P816">
             <v>0</v>
@@ -46291,16 +46233,16 @@
             <v>0</v>
           </cell>
           <cell r="R816">
-            <v>12385.46</v>
+            <v>14637.67</v>
           </cell>
           <cell r="T816">
             <v>0</v>
           </cell>
           <cell r="U816">
-            <v>12385.46</v>
+            <v>14637.67</v>
           </cell>
           <cell r="V816">
-            <v>5053.4599999999991</v>
+            <v>2801.2499999999982</v>
           </cell>
         </row>
         <row r="817">
@@ -46332,10 +46274,10 @@
             <v>17438.919999999998</v>
           </cell>
           <cell r="N817">
-            <v>22893.399999999998</v>
+            <v>33363.119999999995</v>
           </cell>
           <cell r="O817">
-            <v>8657.7800000000007</v>
+            <v>940.27</v>
           </cell>
           <cell r="P817">
             <v>0</v>
@@ -46344,16 +46286,16 @@
             <v>0</v>
           </cell>
           <cell r="R817">
-            <v>31551.18</v>
+            <v>34303.389999999992</v>
           </cell>
           <cell r="T817">
             <v>0</v>
           </cell>
           <cell r="U817">
-            <v>31551.18</v>
+            <v>34303.389999999992</v>
           </cell>
           <cell r="V817">
-            <v>-14112.260000000002</v>
+            <v>-16864.469999999994</v>
           </cell>
         </row>
         <row r="818">
@@ -46426,28 +46368,28 @@
             <v>647406.15</v>
           </cell>
           <cell r="N819">
-            <v>470471.65</v>
+            <v>489909.55999999994</v>
           </cell>
           <cell r="O819">
-            <v>5159.63</v>
+            <v>12885.81</v>
           </cell>
           <cell r="P819">
-            <v>91999.85</v>
+            <v>66210.189999999988</v>
           </cell>
           <cell r="Q819">
-            <v>219.89999999999998</v>
+            <v>354.65000000000015</v>
           </cell>
           <cell r="R819">
-            <v>567851.03</v>
+            <v>569360.21</v>
           </cell>
           <cell r="T819">
-            <v>53280.189999999981</v>
+            <v>41702.379999999983</v>
           </cell>
           <cell r="U819">
-            <v>621131.22</v>
+            <v>611062.59</v>
           </cell>
           <cell r="V819">
-            <v>26274.930000000051</v>
+            <v>36343.560000000056</v>
           </cell>
         </row>
         <row r="820">
@@ -46541,13 +46483,13 @@
             <v>0</v>
           </cell>
           <cell r="Q821">
-            <v>0</v>
+            <v>134.75</v>
           </cell>
           <cell r="R821">
-            <v>2759.0599999999995</v>
+            <v>2893.8099999999995</v>
           </cell>
           <cell r="T821">
-            <v>25711.39</v>
+            <v>25576.639999999999</v>
           </cell>
           <cell r="U821">
             <v>28470.449999999997</v>
@@ -46591,22 +46533,22 @@
             <v>0</v>
           </cell>
           <cell r="P822">
-            <v>6401.16</v>
+            <v>6401.17</v>
           </cell>
           <cell r="Q822">
             <v>14.66</v>
           </cell>
           <cell r="R822">
-            <v>45397.259999999995</v>
+            <v>45397.27</v>
           </cell>
           <cell r="T822">
             <v>0</v>
           </cell>
           <cell r="U822">
-            <v>45397.259999999995</v>
+            <v>45397.27</v>
           </cell>
           <cell r="V822">
-            <v>-4134.8799999999974</v>
+            <v>-4134.8899999999994</v>
           </cell>
         </row>
         <row r="823">
@@ -46691,28 +46633,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N824">
-            <v>36539.17</v>
+            <v>36431.269999999997</v>
           </cell>
           <cell r="O824">
             <v>0</v>
           </cell>
           <cell r="P824">
-            <v>917.8</v>
+            <v>917.79</v>
           </cell>
           <cell r="Q824">
             <v>14.66</v>
           </cell>
           <cell r="R824">
-            <v>37471.630000000005</v>
+            <v>37363.72</v>
           </cell>
           <cell r="T824">
             <v>0</v>
           </cell>
           <cell r="U824">
-            <v>37471.630000000005</v>
+            <v>37363.72</v>
           </cell>
           <cell r="V824">
-            <v>3790.7499999999927</v>
+            <v>3898.6599999999962</v>
           </cell>
         </row>
         <row r="825">
@@ -46744,7 +46686,7 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N825">
-            <v>37400.89</v>
+            <v>37334.75</v>
           </cell>
           <cell r="O825">
             <v>0</v>
@@ -46756,16 +46698,16 @@
             <v>14.66</v>
           </cell>
           <cell r="R825">
-            <v>37415.550000000003</v>
+            <v>37349.410000000003</v>
           </cell>
           <cell r="T825">
             <v>0</v>
           </cell>
           <cell r="U825">
-            <v>37415.550000000003</v>
+            <v>37349.410000000003</v>
           </cell>
           <cell r="V825">
-            <v>3846.8299999999945</v>
+            <v>3912.9699999999939</v>
           </cell>
         </row>
         <row r="826">
@@ -46856,22 +46798,22 @@
             <v>0</v>
           </cell>
           <cell r="P827">
-            <v>549.29</v>
+            <v>549.29999999999995</v>
           </cell>
           <cell r="Q827">
             <v>14.66</v>
           </cell>
           <cell r="R827">
-            <v>38560.549999999996</v>
+            <v>38560.559999999998</v>
           </cell>
           <cell r="T827">
             <v>0</v>
           </cell>
           <cell r="U827">
-            <v>38560.549999999996</v>
+            <v>38560.559999999998</v>
           </cell>
           <cell r="V827">
-            <v>2701.8300000000017</v>
+            <v>2701.8199999999997</v>
           </cell>
         </row>
         <row r="828">
@@ -46903,28 +46845,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N828">
-            <v>35237.17</v>
+            <v>35324.189999999995</v>
           </cell>
           <cell r="O828">
             <v>0</v>
           </cell>
           <cell r="P828">
-            <v>549.29</v>
+            <v>549.29999999999995</v>
           </cell>
           <cell r="Q828">
             <v>14.66</v>
           </cell>
           <cell r="R828">
-            <v>35801.120000000003</v>
+            <v>35888.15</v>
           </cell>
           <cell r="T828">
             <v>0</v>
           </cell>
           <cell r="U828">
-            <v>35801.120000000003</v>
+            <v>35888.15</v>
           </cell>
           <cell r="V828">
-            <v>5461.2599999999948</v>
+            <v>5374.2299999999959</v>
           </cell>
         </row>
         <row r="829">
@@ -46956,28 +46898,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N829">
-            <v>35285.399999999994</v>
+            <v>35372.419999999991</v>
           </cell>
           <cell r="O829">
             <v>0</v>
           </cell>
           <cell r="P829">
-            <v>549.29</v>
+            <v>549.29999999999995</v>
           </cell>
           <cell r="Q829">
             <v>14.66</v>
           </cell>
           <cell r="R829">
-            <v>35849.35</v>
+            <v>35936.379999999997</v>
           </cell>
           <cell r="T829">
             <v>0</v>
           </cell>
           <cell r="U829">
-            <v>35849.35</v>
+            <v>35936.379999999997</v>
           </cell>
           <cell r="V829">
-            <v>5413.0299999999988</v>
+            <v>5326</v>
           </cell>
         </row>
         <row r="830">
@@ -47015,22 +46957,22 @@
             <v>0</v>
           </cell>
           <cell r="P830">
-            <v>549.29</v>
+            <v>549.29999999999995</v>
           </cell>
           <cell r="Q830">
             <v>14.66</v>
           </cell>
           <cell r="R830">
-            <v>36161.85</v>
+            <v>36161.86</v>
           </cell>
           <cell r="T830">
             <v>0</v>
           </cell>
           <cell r="U830">
-            <v>36161.85</v>
+            <v>36161.86</v>
           </cell>
           <cell r="V830">
-            <v>5100.5299999999988</v>
+            <v>5100.5199999999968</v>
           </cell>
         </row>
         <row r="831">
@@ -47062,28 +47004,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N831">
-            <v>22712.089999999997</v>
+            <v>35883.49</v>
           </cell>
           <cell r="O831">
-            <v>268.12</v>
+            <v>0</v>
           </cell>
           <cell r="P831">
-            <v>13435.11</v>
+            <v>531.29999999999995</v>
           </cell>
           <cell r="Q831">
             <v>14.66</v>
           </cell>
           <cell r="R831">
-            <v>36429.979999999996</v>
+            <v>36429.450000000004</v>
           </cell>
           <cell r="T831">
-            <v>4832.4000000000015</v>
+            <v>0</v>
           </cell>
           <cell r="U831">
-            <v>41262.379999999997</v>
+            <v>36429.450000000004</v>
           </cell>
           <cell r="V831">
-            <v>0</v>
+            <v>4832.929999999993</v>
           </cell>
         </row>
         <row r="832">
@@ -47115,28 +47057,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N832">
-            <v>21622.75</v>
+            <v>22576.87</v>
           </cell>
           <cell r="O832">
-            <v>954.12</v>
+            <v>12885.81</v>
           </cell>
           <cell r="P832">
-            <v>13435.11</v>
+            <v>549.29999999999995</v>
           </cell>
           <cell r="Q832">
             <v>14.66</v>
           </cell>
           <cell r="R832">
-            <v>36026.639999999999</v>
+            <v>36026.640000000007</v>
           </cell>
           <cell r="T832">
-            <v>5235.739999999998</v>
+            <v>0</v>
           </cell>
           <cell r="U832">
-            <v>41262.379999999997</v>
+            <v>36026.640000000007</v>
           </cell>
           <cell r="V832">
-            <v>0</v>
+            <v>5235.7399999999907</v>
           </cell>
         </row>
         <row r="833">
@@ -47168,22 +47110,22 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N833">
-            <v>22757.190000000002</v>
+            <v>25086.31</v>
           </cell>
           <cell r="O833">
-            <v>954.12</v>
+            <v>0</v>
           </cell>
           <cell r="P833">
-            <v>13435.11</v>
+            <v>13435.09</v>
           </cell>
           <cell r="Q833">
             <v>14.66</v>
           </cell>
           <cell r="R833">
-            <v>37161.08</v>
+            <v>38536.060000000005</v>
           </cell>
           <cell r="T833">
-            <v>4101.2999999999956</v>
+            <v>2726.3199999999924</v>
           </cell>
           <cell r="U833">
             <v>41262.379999999997</v>
@@ -47221,22 +47163,22 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N834">
-            <v>22356.92</v>
+            <v>23311.039999999997</v>
           </cell>
           <cell r="O834">
-            <v>954.12</v>
+            <v>0</v>
           </cell>
           <cell r="P834">
-            <v>13435.11</v>
+            <v>13435.09</v>
           </cell>
           <cell r="Q834">
             <v>14.66</v>
           </cell>
           <cell r="R834">
-            <v>36760.81</v>
+            <v>36760.79</v>
           </cell>
           <cell r="T834">
-            <v>4501.57</v>
+            <v>4501.5899999999965</v>
           </cell>
           <cell r="U834">
             <v>41262.379999999997</v>
@@ -47274,22 +47216,22 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N835">
-            <v>22348.519999999997</v>
+            <v>23302.639999999996</v>
           </cell>
           <cell r="O835">
-            <v>954.12</v>
+            <v>0</v>
           </cell>
           <cell r="P835">
-            <v>13435.11</v>
+            <v>13435.09</v>
           </cell>
           <cell r="Q835">
             <v>14.66</v>
           </cell>
           <cell r="R835">
-            <v>36752.410000000003</v>
+            <v>36752.39</v>
           </cell>
           <cell r="T835">
-            <v>4509.9699999999939</v>
+            <v>4509.989999999998</v>
           </cell>
           <cell r="U835">
             <v>41262.379999999997</v>
@@ -47327,22 +47269,22 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N836">
-            <v>22804.799999999999</v>
+            <v>23879.829999999998</v>
           </cell>
           <cell r="O836">
-            <v>1075.03</v>
+            <v>0</v>
           </cell>
           <cell r="P836">
-            <v>13435.11</v>
+            <v>13435.09</v>
           </cell>
           <cell r="Q836">
             <v>14.66</v>
           </cell>
           <cell r="R836">
-            <v>37329.600000000006</v>
+            <v>37329.58</v>
           </cell>
           <cell r="T836">
-            <v>3932.7799999999916</v>
+            <v>3932.7999999999956</v>
           </cell>
           <cell r="U836">
             <v>41262.379999999997</v>
@@ -47768,28 +47710,28 @@
             <v>523651.85000000015</v>
           </cell>
           <cell r="N845">
-            <v>40035.339999999997</v>
+            <v>64633.14</v>
           </cell>
           <cell r="O845">
-            <v>20791.120000000003</v>
+            <v>13070.71</v>
           </cell>
           <cell r="P845">
-            <v>199095.40000000002</v>
+            <v>188651.67</v>
           </cell>
           <cell r="Q845">
-            <v>2801.9599999999991</v>
+            <v>175</v>
           </cell>
           <cell r="R845">
-            <v>262723.82</v>
+            <v>266530.52</v>
           </cell>
           <cell r="T845">
-            <v>46492.05</v>
+            <v>45311.9</v>
           </cell>
           <cell r="U845">
-            <v>309215.87</v>
+            <v>311842.42000000004</v>
           </cell>
           <cell r="V845">
-            <v>214435.98000000016</v>
+            <v>211809.43000000011</v>
           </cell>
         </row>
         <row r="846">
@@ -47809,28 +47751,28 @@
             <v>523651.85000000015</v>
           </cell>
           <cell r="N846">
-            <v>40035.339999999997</v>
+            <v>64633.14</v>
           </cell>
           <cell r="O846">
-            <v>20791.120000000003</v>
+            <v>13070.71</v>
           </cell>
           <cell r="P846">
-            <v>199095.40000000002</v>
+            <v>188651.67</v>
           </cell>
           <cell r="Q846">
-            <v>2801.9599999999991</v>
+            <v>175</v>
           </cell>
           <cell r="R846">
-            <v>262723.82</v>
+            <v>266530.52</v>
           </cell>
           <cell r="T846">
-            <v>46492.05</v>
+            <v>45311.9</v>
           </cell>
           <cell r="U846">
-            <v>309215.87</v>
+            <v>311842.42000000004</v>
           </cell>
           <cell r="V846">
-            <v>214435.98000000016</v>
+            <v>211809.43000000011</v>
           </cell>
         </row>
         <row r="847">
@@ -47862,22 +47804,22 @@
             <v>19931.82</v>
           </cell>
           <cell r="N847">
-            <v>733.1</v>
+            <v>751.14</v>
           </cell>
           <cell r="O847">
-            <v>0</v>
+            <v>2231.13</v>
           </cell>
           <cell r="P847">
-            <v>13880.05</v>
+            <v>11648.86</v>
           </cell>
           <cell r="Q847">
             <v>0</v>
           </cell>
           <cell r="R847">
-            <v>14613.15</v>
+            <v>14631.130000000001</v>
           </cell>
           <cell r="T847">
-            <v>5318.67</v>
+            <v>5300.6899999999987</v>
           </cell>
           <cell r="U847">
             <v>19931.82</v>
@@ -47915,22 +47857,22 @@
             <v>24141.08</v>
           </cell>
           <cell r="N848">
-            <v>462.69</v>
+            <v>3980.73</v>
           </cell>
           <cell r="O848">
             <v>0</v>
           </cell>
           <cell r="P848">
-            <v>14330.009999999998</v>
+            <v>14330.019999999999</v>
           </cell>
           <cell r="Q848">
             <v>175</v>
           </cell>
           <cell r="R848">
-            <v>14967.699999999999</v>
+            <v>18485.75</v>
           </cell>
           <cell r="T848">
-            <v>9173.3800000000028</v>
+            <v>5655.3300000000017</v>
           </cell>
           <cell r="U848">
             <v>24141.08</v>
@@ -47968,28 +47910,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N849">
-            <v>2949.54</v>
+            <v>2967.58</v>
           </cell>
           <cell r="O849">
             <v>0</v>
           </cell>
           <cell r="P849">
-            <v>11952.66</v>
+            <v>11952.64</v>
           </cell>
           <cell r="Q849">
             <v>0</v>
           </cell>
           <cell r="R849">
-            <v>14902.2</v>
+            <v>14920.22</v>
           </cell>
           <cell r="T849">
-            <v>2000</v>
+            <v>1982.0000000000018</v>
           </cell>
           <cell r="U849">
-            <v>16902.2</v>
+            <v>16902.22</v>
           </cell>
           <cell r="V849">
-            <v>14450.689999999999</v>
+            <v>14450.669999999998</v>
           </cell>
         </row>
         <row r="850">
@@ -48021,28 +47963,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N850">
-            <v>4342.5700000000006</v>
+            <v>4360.6100000000006</v>
           </cell>
           <cell r="O850">
             <v>0</v>
           </cell>
           <cell r="P850">
-            <v>10046.77</v>
+            <v>10046.76</v>
           </cell>
           <cell r="Q850">
             <v>0</v>
           </cell>
           <cell r="R850">
-            <v>14389.34</v>
+            <v>14407.37</v>
           </cell>
           <cell r="T850">
-            <v>2000</v>
+            <v>1981.9600000000009</v>
           </cell>
           <cell r="U850">
-            <v>16389.34</v>
+            <v>16389.330000000002</v>
           </cell>
           <cell r="V850">
-            <v>14963.55</v>
+            <v>14963.559999999998</v>
           </cell>
         </row>
         <row r="851">
@@ -48074,7 +48016,7 @@
             <v>31352.89</v>
           </cell>
           <cell r="N851">
-            <v>1937.29</v>
+            <v>1955.33</v>
           </cell>
           <cell r="O851">
             <v>0</v>
@@ -48086,16 +48028,16 @@
             <v>0</v>
           </cell>
           <cell r="R851">
-            <v>14397.23</v>
+            <v>14415.27</v>
           </cell>
           <cell r="T851">
-            <v>2000</v>
+            <v>1982</v>
           </cell>
           <cell r="U851">
-            <v>16397.23</v>
+            <v>16397.27</v>
           </cell>
           <cell r="V851">
-            <v>14955.66</v>
+            <v>14955.619999999999</v>
           </cell>
         </row>
         <row r="852">
@@ -48127,7 +48069,7 @@
             <v>31352.89</v>
           </cell>
           <cell r="N852">
-            <v>1937.29</v>
+            <v>1955.33</v>
           </cell>
           <cell r="O852">
             <v>0</v>
@@ -48139,16 +48081,16 @@
             <v>0</v>
           </cell>
           <cell r="R852">
-            <v>14397.23</v>
+            <v>14415.27</v>
           </cell>
           <cell r="T852">
-            <v>2000</v>
+            <v>1982</v>
           </cell>
           <cell r="U852">
-            <v>16397.23</v>
+            <v>16397.27</v>
           </cell>
           <cell r="V852">
-            <v>14955.66</v>
+            <v>14955.619999999999</v>
           </cell>
         </row>
         <row r="853">
@@ -48180,28 +48122,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N853">
-            <v>1178.0899999999999</v>
+            <v>1196.1299999999999</v>
           </cell>
           <cell r="O853">
             <v>0</v>
           </cell>
           <cell r="P853">
-            <v>13210.82</v>
+            <v>13210.84</v>
           </cell>
           <cell r="Q853">
             <v>0</v>
           </cell>
           <cell r="R853">
-            <v>14388.91</v>
+            <v>14406.97</v>
           </cell>
           <cell r="T853">
-            <v>2000</v>
+            <v>1982.0000000000018</v>
           </cell>
           <cell r="U853">
-            <v>16388.91</v>
+            <v>16388.97</v>
           </cell>
           <cell r="V853">
-            <v>14963.98</v>
+            <v>14963.919999999998</v>
           </cell>
         </row>
         <row r="854">
@@ -48233,28 +48175,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N854">
-            <v>1154.3399999999999</v>
+            <v>1172.3799999999999</v>
           </cell>
           <cell r="O854">
             <v>0</v>
           </cell>
           <cell r="P854">
-            <v>13210.82</v>
+            <v>13210.84</v>
           </cell>
           <cell r="Q854">
             <v>0</v>
           </cell>
           <cell r="R854">
-            <v>14365.16</v>
+            <v>14383.22</v>
           </cell>
           <cell r="T854">
-            <v>2000</v>
+            <v>1982.0000000000018</v>
           </cell>
           <cell r="U854">
-            <v>16365.16</v>
+            <v>16365.220000000001</v>
           </cell>
           <cell r="V854">
-            <v>14987.73</v>
+            <v>14987.669999999998</v>
           </cell>
         </row>
         <row r="855">
@@ -48286,28 +48228,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N855">
-            <v>1214.08</v>
+            <v>1232.1199999999999</v>
           </cell>
           <cell r="O855">
             <v>0</v>
           </cell>
           <cell r="P855">
-            <v>13210.82</v>
+            <v>13210.84</v>
           </cell>
           <cell r="Q855">
             <v>0</v>
           </cell>
           <cell r="R855">
-            <v>14424.9</v>
+            <v>14442.96</v>
           </cell>
           <cell r="T855">
-            <v>2000</v>
+            <v>1982</v>
           </cell>
           <cell r="U855">
-            <v>16424.900000000001</v>
+            <v>16424.96</v>
           </cell>
           <cell r="V855">
-            <v>14927.989999999998</v>
+            <v>14927.93</v>
           </cell>
         </row>
         <row r="856">
@@ -48339,28 +48281,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N856">
-            <v>6341.2400000000007</v>
+            <v>6359.2800000000007</v>
           </cell>
           <cell r="O856">
             <v>0</v>
           </cell>
           <cell r="P856">
-            <v>8023.3899999999994</v>
+            <v>8023.38</v>
           </cell>
           <cell r="Q856">
             <v>0</v>
           </cell>
           <cell r="R856">
-            <v>14364.630000000001</v>
+            <v>14382.66</v>
           </cell>
           <cell r="T856">
-            <v>2000</v>
+            <v>1981.9600000000009</v>
           </cell>
           <cell r="U856">
-            <v>16364.630000000001</v>
+            <v>16364.62</v>
           </cell>
           <cell r="V856">
-            <v>14988.259999999998</v>
+            <v>14988.269999999999</v>
           </cell>
         </row>
         <row r="857">
@@ -48392,28 +48334,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N857">
-            <v>35.1</v>
+            <v>53.14</v>
           </cell>
           <cell r="O857">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P857">
-            <v>14330.009999999998</v>
+            <v>14330.019999999999</v>
           </cell>
           <cell r="Q857">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R857">
-            <v>14740.39</v>
+            <v>14758.439999999999</v>
           </cell>
           <cell r="T857">
-            <v>2000</v>
+            <v>2357.2999999999993</v>
           </cell>
           <cell r="U857">
-            <v>16740.39</v>
+            <v>17115.739999999998</v>
           </cell>
           <cell r="V857">
-            <v>14612.5</v>
+            <v>14237.150000000001</v>
           </cell>
         </row>
         <row r="858">
@@ -48445,28 +48387,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N858">
-            <v>7101.1600000000008</v>
+            <v>7119.2000000000007</v>
           </cell>
           <cell r="O858">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P858">
-            <v>7263.87</v>
+            <v>7263.869999999999</v>
           </cell>
           <cell r="Q858">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R858">
-            <v>14740.310000000001</v>
+            <v>14758.349999999999</v>
           </cell>
           <cell r="T858">
-            <v>2000</v>
+            <v>2357.3100000000013</v>
           </cell>
           <cell r="U858">
-            <v>16740.310000000001</v>
+            <v>17115.66</v>
           </cell>
           <cell r="V858">
-            <v>14612.579999999998</v>
+            <v>14237.23</v>
           </cell>
         </row>
         <row r="859">
@@ -48498,28 +48440,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N859">
-            <v>10508.45</v>
+            <v>10526.490000000002</v>
           </cell>
           <cell r="O859">
-            <v>0</v>
+            <v>375.28</v>
           </cell>
           <cell r="P859">
-            <v>3856.1899999999996</v>
+            <v>3856.2</v>
           </cell>
           <cell r="Q859">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R859">
-            <v>14739.92</v>
+            <v>14757.970000000001</v>
           </cell>
           <cell r="T859">
-            <v>2000</v>
+            <v>2357.2999999999993</v>
           </cell>
           <cell r="U859">
-            <v>16739.919999999998</v>
+            <v>17115.27</v>
           </cell>
           <cell r="V859">
-            <v>14612.970000000001</v>
+            <v>14237.619999999999</v>
           </cell>
         </row>
         <row r="860">
@@ -48551,28 +48493,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N860">
-            <v>35.1</v>
+            <v>6983.4900000000007</v>
           </cell>
           <cell r="O860">
-            <v>6930.35</v>
+            <v>375.28</v>
           </cell>
           <cell r="P860">
-            <v>7400.0300000000007</v>
+            <v>7400.01</v>
           </cell>
           <cell r="Q860">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R860">
-            <v>14740.760000000002</v>
+            <v>14758.78</v>
           </cell>
           <cell r="T860">
-            <v>2000</v>
+            <v>2356.9599999999973</v>
           </cell>
           <cell r="U860">
-            <v>16740.760000000002</v>
+            <v>17115.739999999998</v>
           </cell>
           <cell r="V860">
-            <v>14612.129999999997</v>
+            <v>14237.150000000001</v>
           </cell>
         </row>
         <row r="861">
@@ -48604,28 +48546,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N861">
-            <v>35.1</v>
+            <v>6983.56</v>
           </cell>
           <cell r="O861">
-            <v>6930.42</v>
+            <v>375.28</v>
           </cell>
           <cell r="P861">
-            <v>7400.0300000000007</v>
+            <v>7400.01</v>
           </cell>
           <cell r="Q861">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R861">
-            <v>14740.830000000002</v>
+            <v>14758.85</v>
           </cell>
           <cell r="T861">
-            <v>2000</v>
+            <v>2356.8899999999976</v>
           </cell>
           <cell r="U861">
-            <v>16740.830000000002</v>
+            <v>17115.739999999998</v>
           </cell>
           <cell r="V861">
-            <v>14612.059999999998</v>
+            <v>14237.150000000001</v>
           </cell>
         </row>
         <row r="862">
@@ -48657,28 +48599,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N862">
-            <v>35.1</v>
+            <v>6983.4900000000007</v>
           </cell>
           <cell r="O862">
-            <v>6930.35</v>
+            <v>375.28</v>
           </cell>
           <cell r="P862">
-            <v>7400.0300000000007</v>
+            <v>7400.01</v>
           </cell>
           <cell r="Q862">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R862">
-            <v>14740.760000000002</v>
+            <v>14758.78</v>
           </cell>
           <cell r="T862">
-            <v>2000</v>
+            <v>2356.9599999999973</v>
           </cell>
           <cell r="U862">
-            <v>16740.760000000002</v>
+            <v>17115.739999999998</v>
           </cell>
           <cell r="V862">
-            <v>14612.129999999997</v>
+            <v>14237.150000000001</v>
           </cell>
         </row>
         <row r="863">
@@ -48710,28 +48652,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N863">
-            <v>35.1</v>
+            <v>53.14</v>
           </cell>
           <cell r="O863">
-            <v>0</v>
+            <v>8587.9000000000015</v>
           </cell>
           <cell r="P863">
-            <v>14330.009999999998</v>
+            <v>6117.4699999999993</v>
           </cell>
           <cell r="Q863">
-            <v>375.28</v>
+            <v>0</v>
           </cell>
           <cell r="R863">
-            <v>14740.39</v>
+            <v>14758.51</v>
           </cell>
           <cell r="T863">
-            <v>2000</v>
+            <v>2357.2299999999959</v>
           </cell>
           <cell r="U863">
-            <v>16740.39</v>
+            <v>17115.739999999998</v>
           </cell>
           <cell r="V863">
-            <v>14612.5</v>
+            <v>14237.150000000001</v>
           </cell>
         </row>
         <row r="864">
@@ -48769,22 +48711,22 @@
             <v>0</v>
           </cell>
           <cell r="P864">
-            <v>14330.009999999998</v>
+            <v>14330.019999999999</v>
           </cell>
           <cell r="Q864">
             <v>0</v>
           </cell>
           <cell r="R864">
-            <v>14330.009999999998</v>
+            <v>14330.019999999999</v>
           </cell>
           <cell r="T864">
-            <v>2000</v>
+            <v>2000.0100000000002</v>
           </cell>
           <cell r="U864">
-            <v>16330.009999999998</v>
+            <v>16330.029999999999</v>
           </cell>
           <cell r="V864">
-            <v>-7044.409999999998</v>
+            <v>-7044.4299999999985</v>
           </cell>
         </row>
         <row r="865">
@@ -48804,28 +48746,28 @@
             <v>332545.65000000002</v>
           </cell>
           <cell r="N865">
-            <v>376762.35</v>
+            <v>493526.97999999986</v>
           </cell>
           <cell r="O865">
-            <v>57336.54</v>
+            <v>76704.799999999988</v>
           </cell>
           <cell r="P865">
-            <v>145093.57</v>
+            <v>145093.53000000003</v>
           </cell>
           <cell r="Q865">
-            <v>37197.06</v>
+            <v>45257.88</v>
           </cell>
           <cell r="R865">
-            <v>616389.52</v>
+            <v>760583.18999999983</v>
           </cell>
           <cell r="T865">
-            <v>108977.84</v>
+            <v>39429.739999999991</v>
           </cell>
           <cell r="U865">
-            <v>725367.36</v>
+            <v>800012.92999999982</v>
           </cell>
           <cell r="V865">
-            <v>-392821.70999999996</v>
+            <v>-467467.2799999998</v>
           </cell>
         </row>
         <row r="866">
@@ -48845,28 +48787,28 @@
             <v>186326.13</v>
           </cell>
           <cell r="N866">
-            <v>339404.25999999995</v>
+            <v>437559.98999999987</v>
           </cell>
           <cell r="O866">
-            <v>38727.64</v>
+            <v>38246.359999999993</v>
           </cell>
           <cell r="P866">
             <v>0</v>
           </cell>
           <cell r="Q866">
-            <v>13784.92</v>
+            <v>0</v>
           </cell>
           <cell r="R866">
-            <v>391916.81999999995</v>
+            <v>475806.34999999986</v>
           </cell>
           <cell r="T866">
-            <v>86580.1</v>
+            <v>20000</v>
           </cell>
           <cell r="U866">
-            <v>478496.91999999993</v>
+            <v>495806.34999999986</v>
           </cell>
           <cell r="V866">
-            <v>-292170.78999999992</v>
+            <v>-309480.21999999986</v>
           </cell>
         </row>
         <row r="867">
@@ -48913,13 +48855,13 @@
             <v>3785.18</v>
           </cell>
           <cell r="T867">
+            <v>0</v>
+          </cell>
+          <cell r="U867">
+            <v>3785.18</v>
+          </cell>
+          <cell r="V867">
             <v>6580.1</v>
-          </cell>
-          <cell r="U867">
-            <v>10365.280000000001</v>
-          </cell>
-          <cell r="V867">
-            <v>0</v>
           </cell>
         </row>
         <row r="868">
@@ -49004,28 +48946,28 @@
             <v>146212.53</v>
           </cell>
           <cell r="N869">
-            <v>322254.43999999994</v>
+            <v>420410.16999999987</v>
           </cell>
           <cell r="O869">
-            <v>38727.64</v>
+            <v>38246.359999999993</v>
           </cell>
           <cell r="P869">
             <v>0</v>
           </cell>
           <cell r="Q869">
-            <v>13784.92</v>
+            <v>0</v>
           </cell>
           <cell r="R869">
-            <v>374766.99999999994</v>
+            <v>458656.52999999985</v>
           </cell>
           <cell r="T869">
-            <v>80000</v>
+            <v>20000</v>
           </cell>
           <cell r="U869">
-            <v>454766.99999999994</v>
+            <v>478656.52999999985</v>
           </cell>
           <cell r="V869">
-            <v>-308554.46999999997</v>
+            <v>-332443.99999999988</v>
           </cell>
         </row>
         <row r="870">
@@ -49045,28 +48987,28 @@
             <v>146219.52000000002</v>
           </cell>
           <cell r="N870">
-            <v>37358.090000000004</v>
+            <v>55966.990000000005</v>
           </cell>
           <cell r="O870">
-            <v>18608.900000000001</v>
+            <v>38458.44</v>
           </cell>
           <cell r="P870">
-            <v>145093.57</v>
+            <v>145093.53000000003</v>
           </cell>
           <cell r="Q870">
-            <v>23412.14</v>
+            <v>45257.88</v>
           </cell>
           <cell r="R870">
-            <v>224472.7</v>
+            <v>284776.84000000003</v>
           </cell>
           <cell r="T870">
-            <v>22397.739999999991</v>
+            <v>19429.739999999991</v>
           </cell>
           <cell r="U870">
-            <v>246870.44</v>
+            <v>304206.58</v>
           </cell>
           <cell r="V870">
-            <v>-100650.91999999998</v>
+            <v>-157987.06</v>
           </cell>
         </row>
         <row r="871">
@@ -49098,28 +49040,28 @@
             <v>106219.52</v>
           </cell>
           <cell r="N871">
-            <v>0</v>
+            <v>16368.9</v>
           </cell>
           <cell r="O871">
-            <v>16368.9</v>
+            <v>36828.44</v>
           </cell>
           <cell r="P871">
-            <v>145093.57</v>
+            <v>145093.53000000003</v>
           </cell>
           <cell r="Q871">
-            <v>23412.14</v>
+            <v>45257.88</v>
           </cell>
           <cell r="R871">
-            <v>184874.61</v>
+            <v>243548.75000000003</v>
           </cell>
           <cell r="T871">
             <v>19429.739999999991</v>
           </cell>
           <cell r="U871">
-            <v>204304.34999999998</v>
+            <v>262978.49</v>
           </cell>
           <cell r="V871">
-            <v>-98084.829999999973</v>
+            <v>-156758.96999999997</v>
           </cell>
         </row>
         <row r="872">
@@ -49151,10 +49093,10 @@
             <v>40000</v>
           </cell>
           <cell r="N872">
-            <v>37358.090000000004</v>
+            <v>39598.090000000004</v>
           </cell>
           <cell r="O872">
-            <v>2240</v>
+            <v>1630</v>
           </cell>
           <cell r="P872">
             <v>0</v>
@@ -49163,16 +49105,16 @@
             <v>0</v>
           </cell>
           <cell r="R872">
-            <v>39598.090000000004</v>
+            <v>41228.090000000004</v>
           </cell>
           <cell r="T872">
-            <v>2968</v>
+            <v>0</v>
           </cell>
           <cell r="U872">
-            <v>42566.090000000004</v>
+            <v>41228.090000000004</v>
           </cell>
           <cell r="V872">
-            <v>-2566.0900000000038</v>
+            <v>-1228.0900000000038</v>
           </cell>
         </row>
         <row r="873">
@@ -49192,10 +49134,10 @@
             <v>355821.09</v>
           </cell>
           <cell r="N873">
-            <v>63010.81</v>
+            <v>67359.26999999999</v>
           </cell>
           <cell r="O873">
-            <v>6717.5300000000007</v>
+            <v>14150.710000000001</v>
           </cell>
           <cell r="P873">
             <v>0</v>
@@ -49204,10 +49146,10 @@
             <v>0</v>
           </cell>
           <cell r="R873">
-            <v>69728.34</v>
+            <v>81509.98</v>
           </cell>
           <cell r="T873">
-            <v>242233.53000000003</v>
+            <v>230451.89</v>
           </cell>
           <cell r="U873">
             <v>311961.87</v>
@@ -49380,10 +49322,10 @@
             <v>191813.07</v>
           </cell>
           <cell r="N877">
-            <v>62386.31</v>
+            <v>66734.76999999999</v>
           </cell>
           <cell r="O877">
-            <v>6717.5300000000007</v>
+            <v>14150.710000000001</v>
           </cell>
           <cell r="P877">
             <v>0</v>
@@ -49392,10 +49334,10 @@
             <v>0</v>
           </cell>
           <cell r="R877">
-            <v>69103.839999999997</v>
+            <v>80885.48</v>
           </cell>
           <cell r="T877">
-            <v>78850.010000000009</v>
+            <v>67068.37000000001</v>
           </cell>
           <cell r="U877">
             <v>147953.85</v>
@@ -49433,10 +49375,10 @@
             <v>126999.44</v>
           </cell>
           <cell r="N878">
-            <v>22540.309999999998</v>
+            <v>26888.769999999997</v>
           </cell>
           <cell r="O878">
-            <v>6717.5300000000007</v>
+            <v>14150.710000000001</v>
           </cell>
           <cell r="P878">
             <v>0</v>
@@ -49445,10 +49387,10 @@
             <v>0</v>
           </cell>
           <cell r="R878">
-            <v>29257.839999999997</v>
+            <v>41039.479999999996</v>
           </cell>
           <cell r="T878">
-            <v>23282.47</v>
+            <v>11500.830000000002</v>
           </cell>
           <cell r="U878">
             <v>52540.31</v>
@@ -49633,7 +49575,7 @@
             <v>544000</v>
           </cell>
           <cell r="N882">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="O882">
             <v>0</v>
@@ -49645,16 +49587,16 @@
             <v>0</v>
           </cell>
           <cell r="R882">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="T882">
             <v>0</v>
           </cell>
           <cell r="U882">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="V882">
-            <v>-24456.520000000135</v>
+            <v>-24752.20000000007</v>
           </cell>
         </row>
         <row r="883">
@@ -49674,7 +49616,7 @@
             <v>544000</v>
           </cell>
           <cell r="N883">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="O883">
             <v>0</v>
@@ -49686,16 +49628,16 @@
             <v>0</v>
           </cell>
           <cell r="R883">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="T883">
             <v>0</v>
           </cell>
           <cell r="U883">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="V883">
-            <v>-24456.520000000135</v>
+            <v>-24752.20000000007</v>
           </cell>
         </row>
         <row r="884">
@@ -49727,7 +49669,7 @@
             <v>544000</v>
           </cell>
           <cell r="N884">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="O884">
             <v>0</v>
@@ -49739,16 +49681,16 @@
             <v>0</v>
           </cell>
           <cell r="R884">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="T884">
             <v>0</v>
           </cell>
           <cell r="U884">
-            <v>568456.52000000014</v>
+            <v>568752.20000000007</v>
           </cell>
           <cell r="V884">
-            <v>-24456.520000000135</v>
+            <v>-24752.20000000007</v>
           </cell>
         </row>
         <row r="885">
@@ -49768,25 +49710,25 @@
             <v>461189.67000000004</v>
           </cell>
           <cell r="N885">
-            <v>90573.439999999988</v>
+            <v>132112.32000000001</v>
           </cell>
           <cell r="O885">
+            <v>41538.880000000005</v>
+          </cell>
+          <cell r="P885">
             <v>41538.879999999997</v>
           </cell>
-          <cell r="P885">
-            <v>83077.75</v>
-          </cell>
           <cell r="Q885">
             <v>0</v>
           </cell>
           <cell r="R885">
-            <v>215190.06999999998</v>
+            <v>215190.08000000002</v>
           </cell>
           <cell r="T885">
-            <v>245999.6</v>
+            <v>245999.59</v>
           </cell>
           <cell r="U885">
-            <v>461189.67</v>
+            <v>461189.67000000004</v>
           </cell>
           <cell r="V885">
             <v>0</v>
@@ -49809,13 +49751,13 @@
             <v>356703.78</v>
           </cell>
           <cell r="N886">
-            <v>83077.76999999999</v>
+            <v>124616.65</v>
           </cell>
           <cell r="O886">
-            <v>41538.879999999997</v>
+            <v>38287.22</v>
           </cell>
           <cell r="P886">
-            <v>38712.340000000004</v>
+            <v>425.12</v>
           </cell>
           <cell r="Q886">
             <v>0</v>
@@ -49862,13 +49804,13 @@
             <v>166326.19</v>
           </cell>
           <cell r="N887">
-            <v>83077.76999999999</v>
+            <v>90176.65</v>
           </cell>
           <cell r="O887">
-            <v>7098.88</v>
+            <v>14142.66</v>
           </cell>
           <cell r="P887">
-            <v>14142.66</v>
+            <v>0</v>
           </cell>
           <cell r="Q887">
             <v>0</v>
@@ -49918,10 +49860,10 @@
             <v>0</v>
           </cell>
           <cell r="O888">
-            <v>0</v>
+            <v>869.34</v>
           </cell>
           <cell r="P888">
-            <v>869.34</v>
+            <v>0</v>
           </cell>
           <cell r="Q888">
             <v>0</v>
@@ -49971,10 +49913,10 @@
             <v>0</v>
           </cell>
           <cell r="O889">
-            <v>0</v>
+            <v>2904.02</v>
           </cell>
           <cell r="P889">
-            <v>2904.02</v>
+            <v>0</v>
           </cell>
           <cell r="Q889">
             <v>0</v>
@@ -50024,10 +49966,10 @@
             <v>0</v>
           </cell>
           <cell r="O890">
-            <v>0</v>
+            <v>20371.2</v>
           </cell>
           <cell r="P890">
-            <v>20371.2</v>
+            <v>0</v>
           </cell>
           <cell r="Q890">
             <v>0</v>
@@ -50180,10 +50122,10 @@
             <v>53416.56</v>
           </cell>
           <cell r="N893">
-            <v>0</v>
+            <v>34440</v>
           </cell>
           <cell r="O893">
-            <v>34440</v>
+            <v>0</v>
           </cell>
           <cell r="P893">
             <v>0</v>
@@ -50224,22 +50166,22 @@
             <v>7495.67</v>
           </cell>
           <cell r="O894">
-            <v>0</v>
+            <v>3251.66</v>
           </cell>
           <cell r="P894">
-            <v>44365.409999999996</v>
+            <v>41113.759999999995</v>
           </cell>
           <cell r="Q894">
             <v>0</v>
           </cell>
           <cell r="R894">
-            <v>51861.079999999994</v>
+            <v>51861.09</v>
           </cell>
           <cell r="T894">
-            <v>52624.810000000005</v>
+            <v>52624.799999999996</v>
           </cell>
           <cell r="U894">
-            <v>104485.89</v>
+            <v>104485.88999999998</v>
           </cell>
           <cell r="V894">
             <v>0</v>
@@ -50439,16 +50381,16 @@
             <v>0</v>
           </cell>
           <cell r="P898">
-            <v>1017.62</v>
+            <v>1017.63</v>
           </cell>
           <cell r="Q898">
             <v>0</v>
           </cell>
           <cell r="R898">
-            <v>1017.62</v>
+            <v>1017.63</v>
           </cell>
           <cell r="T898">
-            <v>2706.5</v>
+            <v>2706.49</v>
           </cell>
           <cell r="U898">
             <v>3724.12</v>
@@ -50542,10 +50484,10 @@
             <v>0</v>
           </cell>
           <cell r="O900">
-            <v>0</v>
+            <v>3251.66</v>
           </cell>
           <cell r="P900">
-            <v>10198.93</v>
+            <v>6947.27</v>
           </cell>
           <cell r="Q900">
             <v>0</v>
@@ -52526,19 +52468,19 @@
             <v>46204</v>
           </cell>
           <cell r="F63">
-            <v>0</v>
+            <v>1509180.4900000002</v>
           </cell>
           <cell r="G63">
-            <v>366221.7199999998</v>
+            <v>0</v>
           </cell>
           <cell r="H63">
-            <v>49765.179999999993</v>
+            <v>0</v>
           </cell>
           <cell r="I63">
-            <v>79352.860000000015</v>
+            <v>0</v>
           </cell>
           <cell r="J63">
-            <v>495339.76</v>
+            <v>1509180.4900000002</v>
           </cell>
         </row>
         <row r="64">
@@ -52549,16 +52491,16 @@
             <v>0</v>
           </cell>
           <cell r="G64">
-            <v>43549.840000000004</v>
+            <v>374270.22999999981</v>
           </cell>
           <cell r="H64">
-            <v>274854.85000000003</v>
+            <v>116711.15000000007</v>
           </cell>
           <cell r="I64">
-            <v>22699.129999999997</v>
+            <v>24294.039999999997</v>
           </cell>
           <cell r="J64">
-            <v>341103.81999999966</v>
+            <v>515275.42000000051</v>
           </cell>
         </row>
         <row r="65">
@@ -52569,16 +52511,16 @@
             <v>0</v>
           </cell>
           <cell r="G65">
-            <v>6691.35</v>
+            <v>28556.610000000022</v>
           </cell>
           <cell r="H65">
-            <v>210829.22999999995</v>
+            <v>250980.36000000007</v>
           </cell>
           <cell r="I65">
-            <v>18930.759999999998</v>
+            <v>15178.140000000001</v>
           </cell>
           <cell r="J65">
-            <v>236451.33999999979</v>
+            <v>294715.10999999993</v>
           </cell>
         </row>
         <row r="66">
@@ -52589,16 +52531,16 @@
             <v>0</v>
           </cell>
           <cell r="G66">
-            <v>2485.6799999999998</v>
+            <v>24354.770000000011</v>
           </cell>
           <cell r="H66">
-            <v>175957.66999999993</v>
+            <v>214225.75000000009</v>
           </cell>
           <cell r="I66">
-            <v>8187.7699999999995</v>
+            <v>24970.289999999997</v>
           </cell>
           <cell r="J66">
-            <v>186631.11999999988</v>
+            <v>263550.80999999988</v>
           </cell>
         </row>
         <row r="67">
@@ -52609,16 +52551,16 @@
             <v>0</v>
           </cell>
           <cell r="G67">
-            <v>2974.3799999999997</v>
+            <v>9720.86</v>
           </cell>
           <cell r="H67">
-            <v>280304.86999999988</v>
+            <v>281010.50999999995</v>
           </cell>
           <cell r="I67">
-            <v>0</v>
+            <v>214.95000000000007</v>
           </cell>
           <cell r="J67">
-            <v>283279.24999999988</v>
+            <v>290946.31999999995</v>
           </cell>
         </row>
         <row r="68">
@@ -52629,16 +52571,16 @@
             <v>0</v>
           </cell>
           <cell r="G68">
-            <v>54535.840000000004</v>
+            <v>55761.840000000004</v>
           </cell>
           <cell r="H68">
-            <v>76249.420000000042</v>
+            <v>62354.84</v>
           </cell>
           <cell r="I68">
             <v>0</v>
           </cell>
           <cell r="J68">
-            <v>130785.25999999994</v>
+            <v>118116.68000000001</v>
           </cell>
         </row>
         <row r="69">
@@ -52649,16 +52591,16 @@
             <v>0</v>
           </cell>
           <cell r="G69">
-            <v>286350</v>
+            <v>287576</v>
           </cell>
           <cell r="H69">
-            <v>113466.21999999991</v>
+            <v>159653.63000000003</v>
           </cell>
           <cell r="I69">
             <v>0</v>
           </cell>
           <cell r="J69">
-            <v>399816.22</v>
+            <v>447229.63000000006</v>
           </cell>
         </row>
         <row r="70">
@@ -52669,16 +52611,16 @@
             <v>0</v>
           </cell>
           <cell r="G70">
-            <v>0</v>
+            <v>1226</v>
           </cell>
           <cell r="H70">
-            <v>73626.260000000024</v>
+            <v>85084.569999999978</v>
           </cell>
           <cell r="I70">
             <v>0</v>
           </cell>
           <cell r="J70">
-            <v>73626.260000000024</v>
+            <v>86310.569999999963</v>
           </cell>
         </row>
         <row r="71">
@@ -52689,36 +52631,36 @@
             <v>0</v>
           </cell>
           <cell r="G71">
-            <v>0</v>
+            <v>1226</v>
           </cell>
           <cell r="H71">
-            <v>170460.22999999995</v>
+            <v>191066.37000000011</v>
           </cell>
           <cell r="I71">
             <v>0</v>
           </cell>
           <cell r="J71">
-            <v>170460.22999999995</v>
+            <v>192292.37000000011</v>
           </cell>
         </row>
         <row r="72">
-          <cell r="E72" t="str">
-            <v>Total Geral</v>
+          <cell r="E72">
+            <v>46478</v>
           </cell>
           <cell r="F72">
-            <v>23097062.570000008</v>
+            <v>0</v>
           </cell>
           <cell r="G72">
-            <v>762808.80999999982</v>
+            <v>1226</v>
           </cell>
           <cell r="H72">
-            <v>1425513.9299999997</v>
+            <v>17596.669999999998</v>
           </cell>
           <cell r="I72">
-            <v>129170.52000000002</v>
+            <v>0</v>
           </cell>
           <cell r="J72">
-            <v>25414555.830000013</v>
+            <v>18822.669999999998</v>
           </cell>
         </row>
       </sheetData>
@@ -53156,7 +53098,7 @@
       </c>
       <c r="D2" s="2">
         <f>VLOOKUP($C2,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>528081.84000000008</v>
+        <v>529117.84000000008</v>
       </c>
       <c r="E2" s="2">
         <f>VLOOKUP($C2,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
@@ -53164,7 +53106,7 @@
       </c>
       <c r="F2" s="2">
         <f>VLOOKUP($C2,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>13325.9</v>
+        <v>12289.9</v>
       </c>
       <c r="G2" s="2">
         <f>VLOOKUP($C2,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -53276,31 +53218,31 @@
       </c>
       <c r="D3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>745972.17</v>
+        <v>796464.32000000007</v>
       </c>
       <c r="E3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>38671.94</v>
+        <v>44749.82</v>
       </c>
       <c r="F3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>69044.420000000013</v>
+        <v>68303.25</v>
       </c>
       <c r="G3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>71909.929999999993</v>
+        <v>656.45</v>
       </c>
       <c r="H3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>925598.4600000002</v>
+        <v>910173.84</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>225249.41000000003</v>
+        <v>240674.02999999997</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>1150847.8700000001</v>
+        <v>1150847.8699999999</v>
       </c>
       <c r="K3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
@@ -53396,35 +53338,35 @@
       </c>
       <c r="D4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>439612.45000000007</v>
+        <v>447658.82000000007</v>
       </c>
       <c r="E4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>11708.23</v>
+        <v>11472.399999999998</v>
       </c>
       <c r="F4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>64824.01</v>
+        <v>62490.37</v>
       </c>
       <c r="G4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>482.47</v>
+        <v>52.300000000000004</v>
       </c>
       <c r="H4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>516627.16000000003</v>
+        <v>521673.89000000007</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>88540.14</v>
+        <v>86517.679999999978</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>605167.30000000005</v>
+        <v>608191.57000000007</v>
       </c>
       <c r="K4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-63367.300000000047</v>
+        <v>-66391.570000000065</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="5">
@@ -53516,15 +53458,15 @@
       </c>
       <c r="D5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>88791.7</v>
+        <v>119523.54</v>
       </c>
       <c r="E5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>20584.88</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>124448.31</v>
+        <v>114451.87</v>
       </c>
       <c r="G5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -53532,7 +53474,7 @@
       </c>
       <c r="H5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>233824.89</v>
+        <v>233975.40999999997</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -53540,11 +53482,11 @@
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>233824.89</v>
+        <v>233975.40999999997</v>
       </c>
       <c r="K5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>28068.929999999993</v>
+        <v>27918.410000000033</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="5">
@@ -53636,35 +53578,35 @@
       </c>
       <c r="D6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>610345.14</v>
+        <v>627501.06000000006</v>
       </c>
       <c r="E6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>11391.74</v>
+        <v>16747.489999999998</v>
       </c>
       <c r="F6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>147870</v>
+        <v>139270</v>
       </c>
       <c r="G6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>1745.02</v>
+        <v>2359.23</v>
       </c>
       <c r="H6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>771351.9</v>
+        <v>785877.78</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>87542.99</v>
+        <v>79675.130000000019</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>858894.89</v>
+        <v>865552.91</v>
       </c>
       <c r="K6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>62912.510000000009</v>
+        <v>56254.489999999991</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="5">
@@ -53756,11 +53698,11 @@
       </c>
       <c r="D7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>738769.64</v>
+        <v>761608.56000000017</v>
       </c>
       <c r="E7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>26908.690000000002</v>
+        <v>12281.240000000002</v>
       </c>
       <c r="F7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -53768,23 +53710,23 @@
       </c>
       <c r="G7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>5786.1</v>
+        <v>6869.08</v>
       </c>
       <c r="H7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>917990.88</v>
+        <v>927285.33000000007</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>385891.80999999994</v>
+        <v>374979.93999999994</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>1303882.69</v>
+        <v>1302265.27</v>
       </c>
       <c r="K7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-161134.62999999989</v>
+        <v>-159517.20999999996</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" s="5">
@@ -53877,15 +53819,15 @@
       </c>
       <c r="D8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>89087.17</v>
+        <v>99537.17</v>
       </c>
       <c r="E8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>10450</v>
+        <v>5500</v>
       </c>
       <c r="F8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>41600</v>
+        <v>25650</v>
       </c>
       <c r="G8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -53893,7 +53835,7 @@
       </c>
       <c r="H8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>141137.16999999998</v>
+        <v>130687.17</v>
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -53901,11 +53843,11 @@
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>149519.52999999997</v>
+        <v>139069.53</v>
       </c>
       <c r="K8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-63019.52999999997</v>
+        <v>-52569.53</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="5">
@@ -53996,7 +53938,7 @@
       </c>
       <c r="D9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>88932.14</v>
+        <v>112697.45999999999</v>
       </c>
       <c r="E9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
@@ -54004,7 +53946,7 @@
       </c>
       <c r="F9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>44189.98</v>
+        <v>194181.90999999997</v>
       </c>
       <c r="G9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -54012,15 +53954,15 @@
       </c>
       <c r="H9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>136882.62</v>
+        <v>310639.87</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>395550.36</v>
+        <v>221793.11000000007</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>532432.98</v>
+        <v>532432.9800000001</v>
       </c>
       <c r="K9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
@@ -54115,15 +54057,15 @@
       </c>
       <c r="D10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>1805636.84</v>
+        <v>1879230.2</v>
       </c>
       <c r="E10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>55488.17</v>
+        <v>58480.07</v>
       </c>
       <c r="F10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>126379.58</v>
+        <v>111879.58</v>
       </c>
       <c r="G10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -54131,11 +54073,11 @@
       </c>
       <c r="H10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>1987504.59</v>
+        <v>2049589.85</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>578992.69999999972</v>
+        <v>516907.43999999977</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
@@ -54353,15 +54295,15 @@
       </c>
       <c r="D12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>321130.44</v>
+        <v>343537.91</v>
       </c>
       <c r="E12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>16993.109999999997</v>
+        <v>28100.98</v>
       </c>
       <c r="F12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>14531.92</v>
+        <v>14396.32</v>
       </c>
       <c r="G12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -54369,19 +54311,19 @@
       </c>
       <c r="H12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>352655.47</v>
+        <v>386035.20999999996</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>179586</v>
+        <v>147474.44</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>532241.47</v>
+        <v>533509.64999999991</v>
       </c>
       <c r="K12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>90672.739999999874</v>
+        <v>89404.559999999939</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="5">
@@ -54470,11 +54412,11 @@
       </c>
       <c r="D13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>27</v>
+        <v>5652.78</v>
       </c>
       <c r="E13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>26641.9</v>
+        <v>48723.82</v>
       </c>
       <c r="F13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -54486,19 +54428,19 @@
       </c>
       <c r="H13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>26668.9</v>
+        <v>54376.6</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>348729.93</v>
+        <v>305791.93</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>375398.83</v>
+        <v>360168.52999999997</v>
       </c>
       <c r="K13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>359323.80999999988</v>
+        <v>374554.10999999993</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="5">
@@ -54706,35 +54648,35 @@
       </c>
       <c r="D15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>610617.55999999994</v>
+        <v>617578.93999999994</v>
       </c>
       <c r="E15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>291461.38</v>
+        <v>285770.40000000002</v>
       </c>
       <c r="F15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>80298.419999999984</v>
+        <v>80295.999999999985</v>
       </c>
       <c r="G15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>0</v>
+        <v>281.10000000000002</v>
       </c>
       <c r="H15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>982377.35999999987</v>
+        <v>983926.44</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>41976.85</v>
+        <v>40927.770000000004</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>1024354.2099999998</v>
+        <v>1024854.21</v>
       </c>
       <c r="K15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>19389.830000000307</v>
+        <v>18889.830000000191</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="5">
@@ -54761,6 +54703,12 @@
         <f>[1]RESUMO!J24</f>
         <v>42274.979999999996</v>
       </c>
+      <c r="U15" s="4">
+        <v>46204</v>
+      </c>
+      <c r="V15" s="2">
+        <v>712365.75</v>
+      </c>
       <c r="X15" s="4">
         <v>45901</v>
       </c>
@@ -54771,7 +54719,18 @@
         <f t="shared" si="0"/>
         <v>9277229.9499999974</v>
       </c>
-      <c r="AC15" s="2"/>
+      <c r="AB15" s="4">
+        <v>46204</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>458385.58000000007</v>
+      </c>
+      <c r="AD15" s="2">
+        <v>110281.65000000002</v>
+      </c>
+      <c r="AE15" s="2">
+        <v>323691.20999999996</v>
+      </c>
       <c r="AG15" s="4">
         <v>45901</v>
       </c>
@@ -54910,11 +54869,11 @@
       </c>
       <c r="D17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>503590.75</v>
+        <v>541098.04</v>
       </c>
       <c r="E17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>19922.97</v>
+        <v>8758.7999999999993</v>
       </c>
       <c r="F17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -54926,19 +54885,19 @@
       </c>
       <c r="H17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>523513.72</v>
+        <v>549856.84000000008</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>62072.7</v>
+        <v>46113.64</v>
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>585586.41999999993</v>
+        <v>595970.4800000001</v>
       </c>
       <c r="K17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>181103.5</v>
+        <v>170719.43999999983</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="5">
@@ -55012,11 +54971,11 @@
       </c>
       <c r="D18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>730899.98999999987</v>
+        <v>731519.75999999989</v>
       </c>
       <c r="E18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>1239.54</v>
+        <v>3411.15</v>
       </c>
       <c r="F18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -55028,7 +54987,7 @@
       </c>
       <c r="H18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>735274.80999999994</v>
+        <v>738066.19</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -55036,11 +54995,11 @@
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>735274.80999999994</v>
+        <v>738066.19</v>
       </c>
       <c r="K18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-90906.209999999963</v>
+        <v>-93697.589999999967</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="5">
@@ -55113,15 +55072,15 @@
       </c>
       <c r="D19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>175764.47000000003</v>
+        <v>181892.92</v>
       </c>
       <c r="E19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>1608.73</v>
+        <v>4432.91</v>
       </c>
       <c r="F19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>47354.29</v>
+        <v>38401.549999999996</v>
       </c>
       <c r="G19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -55129,19 +55088,19 @@
       </c>
       <c r="H19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>224727.49000000005</v>
+        <v>224727.38</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>228781.3</v>
+        <v>165998.12</v>
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>453508.79000000004</v>
+        <v>390725.5</v>
       </c>
       <c r="K19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>265133.7999999997</v>
+        <v>327917.08999999973</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="5">
@@ -55316,35 +55275,35 @@
       </c>
       <c r="D21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>272447.16000000003</v>
+        <v>292479.10000000003</v>
       </c>
       <c r="E21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>6061.52</v>
+        <v>11341.23</v>
       </c>
       <c r="F21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>62689.079999999994</v>
+        <v>50559.19</v>
       </c>
       <c r="G21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>2626.96</v>
+        <v>2054.9899999999998</v>
       </c>
       <c r="H21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>343824.72000000009</v>
+        <v>356434.51</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>48846.32</v>
+        <v>49305.16</v>
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>392671.0400000001</v>
+        <v>405739.67000000004</v>
       </c>
       <c r="K21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>64422.279999999853</v>
+        <v>51353.649999999907</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="5">
@@ -55416,23 +55375,23 @@
       </c>
       <c r="D22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>5182902.040000001</v>
+        <v>5188602.8400000008</v>
       </c>
       <c r="E22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>6189.5</v>
+        <v>2139.3000000000002</v>
       </c>
       <c r="F22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>28490.659999999996</v>
+        <v>28050.639999999996</v>
       </c>
       <c r="G22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>0</v>
+        <v>195.62</v>
       </c>
       <c r="H22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>5217582.2000000011</v>
+        <v>5218988.4000000004</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -55440,11 +55399,11 @@
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>5080582.2000000011</v>
+        <v>5081988.4000000004</v>
       </c>
       <c r="K22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>99533.679999997839</v>
+        <v>98127.479999998584</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="5">
@@ -55516,35 +55475,35 @@
       </c>
       <c r="D23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>796582.93</v>
+        <v>834611.95</v>
       </c>
       <c r="E23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>18191.990000000002</v>
+        <v>15706.619999999999</v>
       </c>
       <c r="F23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>91999.85</v>
+        <v>66210.189999999988</v>
       </c>
       <c r="G23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>1651.9</v>
+        <v>1786.65</v>
       </c>
       <c r="H23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>908426.67</v>
+        <v>918315.40999999992</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>193514.21</v>
+        <v>172186.28999999998</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>1101940.8800000001</v>
+        <v>1090501.7</v>
       </c>
       <c r="K23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>199597.59999999963</v>
+        <v>211036.7799999998</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="5">
@@ -55616,35 +55575,35 @@
       </c>
       <c r="D24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>40035.339999999997</v>
+        <v>64633.14</v>
       </c>
       <c r="E24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>20791.120000000003</v>
+        <v>13070.71</v>
       </c>
       <c r="F24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>199095.40000000002</v>
+        <v>188651.67</v>
       </c>
       <c r="G24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>2801.9599999999991</v>
+        <v>175</v>
       </c>
       <c r="H24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>262723.82</v>
+        <v>266530.52</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>46492.05</v>
+        <v>45311.9</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>309215.87</v>
+        <v>311842.42000000004</v>
       </c>
       <c r="K24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>214435.98000000016</v>
+        <v>211809.43000000011</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="5">
@@ -55717,35 +55676,35 @@
       </c>
       <c r="D25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>376762.35</v>
+        <v>493526.97999999986</v>
       </c>
       <c r="E25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>57336.54</v>
+        <v>76704.799999999988</v>
       </c>
       <c r="F25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>145093.57</v>
+        <v>145093.53000000003</v>
       </c>
       <c r="G25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>37197.06</v>
+        <v>45257.88</v>
       </c>
       <c r="H25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>616389.52</v>
+        <v>760583.18999999983</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>108977.84</v>
+        <v>39429.739999999991</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>725367.36</v>
+        <v>800012.92999999982</v>
       </c>
       <c r="K25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-392821.70999999996</v>
+        <v>-467467.2799999998</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="5">
@@ -55772,6 +55731,15 @@
         <f>[1]RESUMO!J34</f>
         <v>135790.87</v>
       </c>
+      <c r="X25" s="4">
+        <v>46204</v>
+      </c>
+      <c r="Y25" s="2">
+        <v>1015226.1112999998</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>18388977.443753842</v>
+      </c>
       <c r="AC25" s="2"/>
       <c r="AG25" s="4">
         <v>45931</v>
@@ -55809,11 +55777,11 @@
       </c>
       <c r="D26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>63010.81</v>
+        <v>67359.26999999999</v>
       </c>
       <c r="E26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>6717.5300000000007</v>
+        <v>14150.710000000001</v>
       </c>
       <c r="F26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -55825,11 +55793,11 @@
       </c>
       <c r="H26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>69728.34</v>
+        <v>81509.98</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>242233.53000000003</v>
+        <v>230451.89</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
@@ -55897,7 +55865,7 @@
       </c>
       <c r="D27" s="2">
         <f>VLOOKUP($C27,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>568456.52000000014</v>
+        <v>568752.20000000007</v>
       </c>
       <c r="E27" s="2">
         <f>VLOOKUP($C27,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
@@ -55913,7 +55881,7 @@
       </c>
       <c r="H27" s="2">
         <f>VLOOKUP($C27,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>568456.52000000014</v>
+        <v>568752.20000000007</v>
       </c>
       <c r="I27" s="2">
         <f>VLOOKUP($C27,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -55921,11 +55889,11 @@
       </c>
       <c r="J27" s="2">
         <f>VLOOKUP($C27,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>568456.52000000014</v>
+        <v>568752.20000000007</v>
       </c>
       <c r="K27" s="2">
         <f>VLOOKUP($C27,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-24456.520000000135</v>
+        <v>-24752.20000000007</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" s="5">
@@ -55987,15 +55955,15 @@
       </c>
       <c r="D28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>90573.439999999988</v>
+        <v>132112.32000000001</v>
       </c>
       <c r="E28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>41538.879999999997</v>
+        <v>41538.880000000005</v>
       </c>
       <c r="F28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>83077.75</v>
+        <v>41538.879999999997</v>
       </c>
       <c r="G28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -56003,15 +55971,15 @@
       </c>
       <c r="H28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>215190.06999999998</v>
+        <v>215190.08000000002</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>245999.6</v>
+        <v>245999.59</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>461189.67</v>
+        <v>461189.67000000004</v>
       </c>
       <c r="K28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
@@ -56132,6 +56100,7 @@
         <f>[1]RESUMO!J38</f>
         <v>374885.31</v>
       </c>
+      <c r="Z29" s="13"/>
       <c r="AG29" s="4">
         <v>45931</v>
       </c>
@@ -56257,7 +56226,7 @@
       </c>
       <c r="D31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,11,0)</f>
-        <v>1657021.3599999999</v>
+        <v>1752027.23</v>
       </c>
       <c r="E31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,12,0)</f>
@@ -56273,19 +56242,19 @@
       </c>
       <c r="H31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,15,0)</f>
-        <v>1657021.3599999999</v>
+        <v>1752027.23</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,17,0)</f>
-        <v>610820.23800000036</v>
+        <v>517344.25500000035</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,18,0)</f>
-        <v>2267841.5980000002</v>
+        <v>2269371.4850000003</v>
       </c>
       <c r="K31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,19,0)</f>
-        <v>123224.40199999977</v>
+        <v>121694.51499999966</v>
       </c>
       <c r="M31" s="5">
         <f>[1]RESUMO!E40</f>
@@ -56345,15 +56314,15 @@
       </c>
       <c r="D32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,11,0)</f>
-        <v>3968993.2399999993</v>
+        <v>4197678.5799999991</v>
       </c>
       <c r="E32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,12,0)</f>
-        <v>71560.45</v>
+        <v>83164.98000000001</v>
       </c>
       <c r="F32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,13,0)</f>
-        <v>92651.159999999989</v>
+        <v>82233.159999999989</v>
       </c>
       <c r="G32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,14,0)</f>
@@ -56361,19 +56330,19 @@
       </c>
       <c r="H32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,15,0)</f>
-        <v>4133204.8499999996</v>
+        <v>4363076.72</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,17,0)</f>
-        <v>3576065.7200000007</v>
+        <v>3371401.4500000007</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,18,0)</f>
-        <v>7709270.5700000003</v>
+        <v>7734478.1699999999</v>
       </c>
       <c r="K32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,19,0)</f>
-        <v>-1339270.5700000003</v>
+        <v>-1364478.17</v>
       </c>
       <c r="M32" s="5">
         <f>[1]RESUMO!E41</f>
@@ -56502,6 +56471,12 @@
       <c r="AK33" s="2">
         <v>4004.75</v>
       </c>
+      <c r="AM33" s="4">
+        <v>46204</v>
+      </c>
+      <c r="AN33" s="2">
+        <v>130276.66000000003</v>
+      </c>
     </row>
     <row r="34" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -56515,7 +56490,7 @@
       </c>
       <c r="D34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,11,0)</f>
-        <v>970298.36</v>
+        <v>1587120.41</v>
       </c>
       <c r="E34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,12,0)</f>
@@ -56531,19 +56506,19 @@
       </c>
       <c r="H34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,15,0)</f>
-        <v>970298.36</v>
+        <v>1587120.41</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,17,0)</f>
-        <v>-879346.6399999999</v>
+        <v>-1496168.69</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,18,0)</f>
-        <v>90951.720000000088</v>
+        <v>90951.719999999972</v>
       </c>
       <c r="K34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,19,0)</f>
-        <v>-90951.720000000088</v>
+        <v>-90951.719999999972</v>
       </c>
       <c r="M34" s="5">
         <f>[1]RESUMO!E43</f>
@@ -57391,23 +57366,23 @@
       </c>
       <c r="N54" s="9">
         <f>[1]RESUMO!F63</f>
-        <v>0</v>
+        <v>1509180.4900000002</v>
       </c>
       <c r="O54" s="9">
         <f>[1]RESUMO!G63</f>
-        <v>366221.7199999998</v>
+        <v>0</v>
       </c>
       <c r="P54" s="9">
         <f>[1]RESUMO!H63</f>
-        <v>49765.179999999993</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="9">
         <f>[1]RESUMO!I63</f>
-        <v>79352.860000000015</v>
+        <v>0</v>
       </c>
       <c r="R54" s="2">
         <f>[1]RESUMO!J63</f>
-        <v>495339.76</v>
+        <v>1509180.4900000002</v>
       </c>
       <c r="AG54" s="4">
         <v>46023</v>
@@ -57437,19 +57412,19 @@
       </c>
       <c r="O55" s="9">
         <f>[1]RESUMO!G64</f>
-        <v>43549.840000000004</v>
+        <v>374270.22999999981</v>
       </c>
       <c r="P55" s="9">
         <f>[1]RESUMO!H64</f>
-        <v>274854.85000000003</v>
+        <v>116711.15000000007</v>
       </c>
       <c r="Q55" s="9">
         <f>[1]RESUMO!I64</f>
-        <v>22699.129999999997</v>
+        <v>24294.039999999997</v>
       </c>
       <c r="R55" s="2">
         <f>[1]RESUMO!J64</f>
-        <v>341103.81999999966</v>
+        <v>515275.42000000051</v>
       </c>
       <c r="AG55" s="4">
         <v>46023</v>
@@ -57478,19 +57453,19 @@
       </c>
       <c r="O56" s="9">
         <f>[1]RESUMO!G65</f>
-        <v>6691.35</v>
+        <v>28556.610000000022</v>
       </c>
       <c r="P56" s="9">
         <f>[1]RESUMO!H65</f>
-        <v>210829.22999999995</v>
+        <v>250980.36000000007</v>
       </c>
       <c r="Q56" s="9">
         <f>[1]RESUMO!I65</f>
-        <v>18930.759999999998</v>
+        <v>15178.140000000001</v>
       </c>
       <c r="R56" s="2">
         <f>[1]RESUMO!J65</f>
-        <v>236451.33999999979</v>
+        <v>294715.10999999993</v>
       </c>
       <c r="AG56" s="4">
         <v>46023</v>
@@ -57519,19 +57494,19 @@
       </c>
       <c r="O57" s="9">
         <f>[1]RESUMO!G66</f>
-        <v>2485.6799999999998</v>
+        <v>24354.770000000011</v>
       </c>
       <c r="P57" s="9">
         <f>[1]RESUMO!H66</f>
-        <v>175957.66999999993</v>
+        <v>214225.75000000009</v>
       </c>
       <c r="Q57" s="9">
         <f>[1]RESUMO!I66</f>
-        <v>8187.7699999999995</v>
+        <v>24970.289999999997</v>
       </c>
       <c r="R57" s="2">
         <f>[1]RESUMO!J66</f>
-        <v>186631.11999999988</v>
+        <v>263550.80999999988</v>
       </c>
       <c r="AG57" s="4"/>
       <c r="AH57" s="8"/>
@@ -57547,19 +57522,19 @@
       </c>
       <c r="O58" s="9">
         <f>[1]RESUMO!G67</f>
-        <v>2974.3799999999997</v>
+        <v>9720.86</v>
       </c>
       <c r="P58" s="9">
         <f>[1]RESUMO!H67</f>
-        <v>280304.86999999988</v>
+        <v>281010.50999999995</v>
       </c>
       <c r="Q58" s="9">
         <f>[1]RESUMO!I67</f>
-        <v>0</v>
+        <v>214.95000000000007</v>
       </c>
       <c r="R58" s="2">
         <f>[1]RESUMO!J67</f>
-        <v>283279.24999999988</v>
+        <v>290946.31999999995</v>
       </c>
       <c r="AG58" s="4"/>
     </row>
@@ -57574,11 +57549,11 @@
       </c>
       <c r="O59" s="9">
         <f>[1]RESUMO!G68</f>
-        <v>54535.840000000004</v>
+        <v>55761.840000000004</v>
       </c>
       <c r="P59" s="9">
         <f>[1]RESUMO!H68</f>
-        <v>76249.420000000042</v>
+        <v>62354.84</v>
       </c>
       <c r="Q59" s="9">
         <f>[1]RESUMO!I68</f>
@@ -57586,7 +57561,7 @@
       </c>
       <c r="R59" s="2">
         <f>[1]RESUMO!J68</f>
-        <v>130785.25999999994</v>
+        <v>118116.68000000001</v>
       </c>
       <c r="AG59" s="4"/>
     </row>
@@ -57601,11 +57576,11 @@
       </c>
       <c r="O60" s="9">
         <f>[1]RESUMO!G69</f>
-        <v>286350</v>
+        <v>287576</v>
       </c>
       <c r="P60" s="9">
         <f>[1]RESUMO!H69</f>
-        <v>113466.21999999991</v>
+        <v>159653.63000000003</v>
       </c>
       <c r="Q60" s="9">
         <f>[1]RESUMO!I69</f>
@@ -57613,7 +57588,7 @@
       </c>
       <c r="R60" s="2">
         <f>[1]RESUMO!J69</f>
-        <v>399816.22</v>
+        <v>447229.63000000006</v>
       </c>
       <c r="AG60" s="4"/>
     </row>
@@ -57628,11 +57603,11 @@
       </c>
       <c r="O61" s="9">
         <f>[1]RESUMO!G70</f>
-        <v>0</v>
+        <v>1226</v>
       </c>
       <c r="P61" s="9">
         <f>[1]RESUMO!H70</f>
-        <v>73626.260000000024</v>
+        <v>85084.569999999978</v>
       </c>
       <c r="Q61" s="9">
         <f>[1]RESUMO!I70</f>
@@ -57640,7 +57615,7 @@
       </c>
       <c r="R61" s="2">
         <f>[1]RESUMO!J70</f>
-        <v>73626.260000000024</v>
+        <v>86310.569999999963</v>
       </c>
       <c r="AG61" s="4"/>
     </row>
@@ -57655,11 +57630,11 @@
       </c>
       <c r="O62" s="9">
         <f>[1]RESUMO!G71</f>
-        <v>0</v>
+        <v>1226</v>
       </c>
       <c r="P62" s="9">
         <f>[1]RESUMO!H71</f>
-        <v>170460.22999999995</v>
+        <v>191066.37000000011</v>
       </c>
       <c r="Q62" s="9">
         <f>[1]RESUMO!I71</f>
@@ -57667,33 +57642,33 @@
       </c>
       <c r="R62" s="2">
         <f>[1]RESUMO!J71</f>
-        <v>170460.22999999995</v>
+        <v>192292.37000000011</v>
       </c>
     </row>
     <row r="63" spans="13:38" x14ac:dyDescent="0.3">
-      <c r="M63" s="5" t="str">
+      <c r="M63" s="5">
         <f>[1]RESUMO!E72</f>
-        <v>Total Geral</v>
+        <v>46478</v>
       </c>
       <c r="N63" s="9">
         <f>[1]RESUMO!F72</f>
-        <v>23097062.570000008</v>
+        <v>0</v>
       </c>
       <c r="O63" s="9">
         <f>[1]RESUMO!G72</f>
-        <v>762808.80999999982</v>
+        <v>1226</v>
       </c>
       <c r="P63" s="9">
         <f>[1]RESUMO!H72</f>
-        <v>1425513.9299999997</v>
+        <v>17596.669999999998</v>
       </c>
       <c r="Q63" s="9">
         <f>[1]RESUMO!I72</f>
-        <v>129170.52000000002</v>
+        <v>0</v>
       </c>
       <c r="R63" s="2">
         <f>[1]RESUMO!J72</f>
-        <v>25414555.830000013</v>
+        <v>18822.669999999998</v>
       </c>
     </row>
     <row r="64" spans="13:38" x14ac:dyDescent="0.3">

--- a/data/financeiro.xlsx
+++ b/data/financeiro.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="EstaPastaDeTrabalho" hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65708F8A-302A-4C8D-BA9E-617DD09D7885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{65708F8A-302A-4C8D-BA9E-617DD09D7885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F1DAEE-3D1B-4A16-BF95-7C0AE909316E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2258,28 +2258,28 @@
             <v>6370000</v>
           </cell>
           <cell r="N7">
-            <v>4197678.5799999991</v>
+            <v>4458256.629999998</v>
           </cell>
           <cell r="O7">
-            <v>83164.98000000001</v>
+            <v>96431.510000000009</v>
           </cell>
           <cell r="P7">
-            <v>82233.159999999989</v>
+            <v>71973.159999999974</v>
           </cell>
           <cell r="Q7">
             <v>0</v>
           </cell>
           <cell r="R7">
-            <v>4363076.72</v>
+            <v>4626661.299999998</v>
           </cell>
           <cell r="T7">
-            <v>3371401.4500000007</v>
+            <v>3113420.4900000007</v>
           </cell>
           <cell r="U7">
-            <v>7734478.1699999999</v>
+            <v>7740081.7899999991</v>
           </cell>
           <cell r="V7">
-            <v>-1364478.17</v>
+            <v>-1370081.7899999991</v>
           </cell>
         </row>
         <row r="8">
@@ -2299,28 +2299,28 @@
             <v>6370000</v>
           </cell>
           <cell r="N8">
-            <v>4197678.5799999991</v>
+            <v>4458256.629999998</v>
           </cell>
           <cell r="O8">
-            <v>83164.98000000001</v>
+            <v>96431.510000000009</v>
           </cell>
           <cell r="P8">
-            <v>82233.159999999989</v>
+            <v>71973.159999999974</v>
           </cell>
           <cell r="Q8">
             <v>0</v>
           </cell>
           <cell r="R8">
-            <v>4363076.72</v>
+            <v>4626661.299999998</v>
           </cell>
           <cell r="T8">
-            <v>3371401.4500000007</v>
+            <v>3113420.4900000007</v>
           </cell>
           <cell r="U8">
-            <v>7734478.1699999999</v>
+            <v>7740081.7899999991</v>
           </cell>
           <cell r="V8">
-            <v>-1364478.17</v>
+            <v>-1370081.7899999991</v>
           </cell>
         </row>
         <row r="9">
@@ -2540,13 +2540,13 @@
             <v>134000</v>
           </cell>
           <cell r="N13">
-            <v>117630.31999999999</v>
+            <v>121490.31999999999</v>
           </cell>
           <cell r="O13">
             <v>0</v>
           </cell>
           <cell r="P13">
-            <v>12351.16</v>
+            <v>8491.16</v>
           </cell>
           <cell r="Q13">
             <v>0</v>
@@ -2593,13 +2593,13 @@
             <v>100000</v>
           </cell>
           <cell r="N14">
-            <v>103949.84</v>
+            <v>107809.84</v>
           </cell>
           <cell r="O14">
             <v>0</v>
           </cell>
           <cell r="P14">
-            <v>12351.16</v>
+            <v>8491.16</v>
           </cell>
           <cell r="Q14">
             <v>0</v>
@@ -2740,7 +2740,7 @@
             <v>150000</v>
           </cell>
           <cell r="N17">
-            <v>239938.21</v>
+            <v>245541.83000000002</v>
           </cell>
           <cell r="O17">
             <v>0</v>
@@ -2752,16 +2752,16 @@
             <v>0</v>
           </cell>
           <cell r="R17">
-            <v>239938.21</v>
+            <v>245541.83000000002</v>
           </cell>
           <cell r="T17">
             <v>0</v>
           </cell>
           <cell r="U17">
-            <v>239938.21</v>
+            <v>245541.83000000002</v>
           </cell>
           <cell r="V17">
-            <v>-89938.209999999992</v>
+            <v>-95541.830000000016</v>
           </cell>
         </row>
         <row r="18">
@@ -2846,7 +2846,7 @@
             <v>150000</v>
           </cell>
           <cell r="N19">
-            <v>216650.71</v>
+            <v>222254.33000000002</v>
           </cell>
           <cell r="O19">
             <v>0</v>
@@ -2858,16 +2858,16 @@
             <v>0</v>
           </cell>
           <cell r="R19">
-            <v>216650.71</v>
+            <v>222254.33000000002</v>
           </cell>
           <cell r="T19">
             <v>0</v>
           </cell>
           <cell r="U19">
-            <v>216650.71</v>
+            <v>222254.33000000002</v>
           </cell>
           <cell r="V19">
-            <v>-66650.709999999992</v>
+            <v>-72254.330000000016</v>
           </cell>
         </row>
         <row r="20">
@@ -2887,22 +2887,22 @@
             <v>3500000</v>
           </cell>
           <cell r="N20">
-            <v>1635432.51</v>
+            <v>1736627.0399999998</v>
           </cell>
           <cell r="O20">
-            <v>54460</v>
+            <v>72000</v>
           </cell>
           <cell r="P20">
-            <v>2432.1999999999998</v>
+            <v>1332.2</v>
           </cell>
           <cell r="Q20">
             <v>0</v>
           </cell>
           <cell r="R20">
-            <v>1692324.71</v>
+            <v>1809959.2399999998</v>
           </cell>
           <cell r="T20">
-            <v>2177944.19</v>
+            <v>2060309.6600000001</v>
           </cell>
           <cell r="U20">
             <v>3870268.9</v>
@@ -2940,10 +2940,10 @@
             <v>300000</v>
           </cell>
           <cell r="N21">
-            <v>497578.89</v>
+            <v>507558.33</v>
           </cell>
           <cell r="O21">
-            <v>960</v>
+            <v>0</v>
           </cell>
           <cell r="P21">
             <v>0</v>
@@ -2952,10 +2952,10 @@
             <v>0</v>
           </cell>
           <cell r="R21">
-            <v>498538.89</v>
+            <v>507558.33</v>
           </cell>
           <cell r="T21">
-            <v>102040</v>
+            <v>93020.56</v>
           </cell>
           <cell r="U21">
             <v>600578.89</v>
@@ -2993,13 +2993,13 @@
             <v>300000</v>
           </cell>
           <cell r="N22">
-            <v>547931.29</v>
+            <v>549031.29</v>
           </cell>
           <cell r="O22">
             <v>53500</v>
           </cell>
           <cell r="P22">
-            <v>2432.1999999999998</v>
+            <v>1332.2</v>
           </cell>
           <cell r="Q22">
             <v>0</v>
@@ -3046,10 +3046,10 @@
             <v>1600000</v>
           </cell>
           <cell r="N23">
-            <v>233069.19</v>
+            <v>287019.19</v>
           </cell>
           <cell r="O23">
-            <v>0</v>
+            <v>18500</v>
           </cell>
           <cell r="P23">
             <v>0</v>
@@ -3058,10 +3058,10 @@
             <v>0</v>
           </cell>
           <cell r="R23">
-            <v>233069.19</v>
+            <v>305519.19</v>
           </cell>
           <cell r="T23">
-            <v>608102.06000000006</v>
+            <v>535652.06000000006</v>
           </cell>
           <cell r="U23">
             <v>841171.25</v>
@@ -3099,7 +3099,7 @@
             <v>1300000</v>
           </cell>
           <cell r="N24">
-            <v>245233.02</v>
+            <v>281398.11</v>
           </cell>
           <cell r="O24">
             <v>0</v>
@@ -3111,10 +3111,10 @@
             <v>0</v>
           </cell>
           <cell r="R24">
-            <v>245233.02</v>
+            <v>281398.11</v>
           </cell>
           <cell r="T24">
-            <v>1054766.98</v>
+            <v>1018601.89</v>
           </cell>
           <cell r="U24">
             <v>1300000</v>
@@ -3193,13 +3193,13 @@
             <v>627000</v>
           </cell>
           <cell r="N26">
-            <v>242225.67000000004</v>
+            <v>251799.14000000004</v>
           </cell>
           <cell r="O26">
-            <v>28704.980000000003</v>
+            <v>24431.510000000002</v>
           </cell>
           <cell r="P26">
-            <v>67449.799999999988</v>
+            <v>62149.799999999981</v>
           </cell>
           <cell r="Q26">
             <v>0</v>
@@ -3246,13 +3246,13 @@
             <v>627000</v>
           </cell>
           <cell r="N27">
-            <v>172150</v>
+            <v>177450</v>
           </cell>
           <cell r="O27">
             <v>5300</v>
           </cell>
           <cell r="P27">
-            <v>67449.799999999988</v>
+            <v>62149.799999999981</v>
           </cell>
           <cell r="Q27">
             <v>0</v>
@@ -3299,10 +3299,10 @@
             <v>0</v>
           </cell>
           <cell r="N28">
-            <v>70075.670000000027</v>
+            <v>74349.140000000043</v>
           </cell>
           <cell r="O28">
-            <v>23404.980000000003</v>
+            <v>19131.510000000002</v>
           </cell>
           <cell r="P28">
             <v>0</v>
@@ -3311,16 +3311,16 @@
             <v>0</v>
           </cell>
           <cell r="R28">
-            <v>93480.650000000023</v>
+            <v>93480.650000000052</v>
           </cell>
           <cell r="T28">
             <v>0</v>
           </cell>
           <cell r="U28">
-            <v>93480.650000000023</v>
+            <v>93480.650000000052</v>
           </cell>
           <cell r="V28">
-            <v>-93480.650000000023</v>
+            <v>-93480.650000000052</v>
           </cell>
         </row>
         <row r="29">
@@ -3340,7 +3340,7 @@
             <v>990000</v>
           </cell>
           <cell r="N29">
-            <v>1463488.65</v>
+            <v>1602764.5799999998</v>
           </cell>
           <cell r="O29">
             <v>0</v>
@@ -3352,10 +3352,10 @@
             <v>0</v>
           </cell>
           <cell r="R29">
-            <v>1463488.65</v>
+            <v>1602764.5799999998</v>
           </cell>
           <cell r="T29">
-            <v>443279.24</v>
+            <v>304003.31000000006</v>
           </cell>
           <cell r="U29">
             <v>1906767.89</v>
@@ -3393,7 +3393,7 @@
             <v>900000</v>
           </cell>
           <cell r="N30">
-            <v>1431808.65</v>
+            <v>1569644.5799999998</v>
           </cell>
           <cell r="O30">
             <v>0</v>
@@ -3405,10 +3405,10 @@
             <v>0</v>
           </cell>
           <cell r="R30">
-            <v>1431808.65</v>
+            <v>1569644.5799999998</v>
           </cell>
           <cell r="T30">
-            <v>410159.24</v>
+            <v>272323.31000000006</v>
           </cell>
           <cell r="U30">
             <v>1841967.89</v>
@@ -3446,22 +3446,22 @@
             <v>90000</v>
           </cell>
           <cell r="N31">
+            <v>33120</v>
+          </cell>
+          <cell r="O31">
+            <v>0</v>
+          </cell>
+          <cell r="P31">
+            <v>0</v>
+          </cell>
+          <cell r="Q31">
+            <v>0</v>
+          </cell>
+          <cell r="R31">
+            <v>33120</v>
+          </cell>
+          <cell r="T31">
             <v>31680</v>
-          </cell>
-          <cell r="O31">
-            <v>0</v>
-          </cell>
-          <cell r="P31">
-            <v>0</v>
-          </cell>
-          <cell r="Q31">
-            <v>0</v>
-          </cell>
-          <cell r="R31">
-            <v>31680</v>
-          </cell>
-          <cell r="T31">
-            <v>33120</v>
           </cell>
           <cell r="U31">
             <v>64800</v>
@@ -3487,7 +3487,7 @@
             <v>27000</v>
           </cell>
           <cell r="N32">
-            <v>73911.559999999139</v>
+            <v>74982.059999999095</v>
           </cell>
           <cell r="O32">
             <v>0</v>
@@ -3499,16 +3499,16 @@
             <v>0</v>
           </cell>
           <cell r="R32">
-            <v>73911.559999999139</v>
+            <v>74982.059999999095</v>
           </cell>
           <cell r="T32">
-            <v>18679.850000000166</v>
+            <v>17609.350000000239</v>
           </cell>
           <cell r="U32">
-            <v>92591.409999999305</v>
+            <v>92591.409999999334</v>
           </cell>
           <cell r="V32">
-            <v>-65591.409999999305</v>
+            <v>-65591.409999999334</v>
           </cell>
         </row>
         <row r="33">
@@ -3593,7 +3593,7 @@
             <v>15000</v>
           </cell>
           <cell r="N34">
-            <v>71821.559999999139</v>
+            <v>72892.059999999095</v>
           </cell>
           <cell r="O34">
             <v>0</v>
@@ -3605,16 +3605,16 @@
             <v>0</v>
           </cell>
           <cell r="R34">
-            <v>71821.559999999139</v>
+            <v>72892.059999999095</v>
           </cell>
           <cell r="T34">
-            <v>8769.8500000001659</v>
+            <v>7699.3500000002387</v>
           </cell>
           <cell r="U34">
-            <v>80591.409999999305</v>
+            <v>80591.409999999334</v>
           </cell>
           <cell r="V34">
-            <v>-65591.409999999305</v>
+            <v>-65591.409999999334</v>
           </cell>
         </row>
         <row r="35">
@@ -3834,7 +3834,7 @@
             <v>2391066</v>
           </cell>
           <cell r="N39">
-            <v>1752027.23</v>
+            <v>1818331.6099999999</v>
           </cell>
           <cell r="O39">
             <v>0</v>
@@ -3846,16 +3846,16 @@
             <v>0</v>
           </cell>
           <cell r="R39">
-            <v>1752027.23</v>
+            <v>1818331.6099999999</v>
           </cell>
           <cell r="T39">
-            <v>517344.25500000035</v>
+            <v>463433.42400000058</v>
           </cell>
           <cell r="U39">
-            <v>2269371.4850000003</v>
+            <v>2281765.0340000005</v>
           </cell>
           <cell r="V39">
-            <v>121694.51499999966</v>
+            <v>109300.96599999955</v>
           </cell>
         </row>
         <row r="40">
@@ -3875,7 +3875,7 @@
             <v>2391066</v>
           </cell>
           <cell r="N40">
-            <v>1752027.23</v>
+            <v>1818331.6099999999</v>
           </cell>
           <cell r="O40">
             <v>0</v>
@@ -3887,16 +3887,16 @@
             <v>0</v>
           </cell>
           <cell r="R40">
-            <v>1752027.23</v>
+            <v>1818331.6099999999</v>
           </cell>
           <cell r="T40">
-            <v>517344.25500000035</v>
+            <v>463433.42400000058</v>
           </cell>
           <cell r="U40">
-            <v>2269371.4850000003</v>
+            <v>2281765.0340000005</v>
           </cell>
           <cell r="V40">
-            <v>121694.51499999966</v>
+            <v>109300.96599999955</v>
           </cell>
         </row>
         <row r="41">
@@ -3916,7 +3916,7 @@
             <v>2391066</v>
           </cell>
           <cell r="N41">
-            <v>1752027.23</v>
+            <v>1818331.6099999999</v>
           </cell>
           <cell r="O41">
             <v>0</v>
@@ -3928,16 +3928,16 @@
             <v>0</v>
           </cell>
           <cell r="R41">
-            <v>1752027.23</v>
+            <v>1818331.6099999999</v>
           </cell>
           <cell r="T41">
-            <v>517344.25500000035</v>
+            <v>463433.42400000058</v>
           </cell>
           <cell r="U41">
-            <v>2269371.4850000003</v>
+            <v>2281765.0340000005</v>
           </cell>
           <cell r="V41">
-            <v>121694.51499999966</v>
+            <v>109300.96599999955</v>
           </cell>
         </row>
         <row r="42">
@@ -3969,7 +3969,7 @@
             <v>2391066</v>
           </cell>
           <cell r="N42">
-            <v>1752027.23</v>
+            <v>1818331.6099999999</v>
           </cell>
           <cell r="O42">
             <v>0</v>
@@ -3981,16 +3981,16 @@
             <v>0</v>
           </cell>
           <cell r="R42">
-            <v>1752027.23</v>
+            <v>1818331.6099999999</v>
           </cell>
           <cell r="T42">
-            <v>517344.25500000035</v>
+            <v>463433.42400000058</v>
           </cell>
           <cell r="U42">
-            <v>2269371.4850000003</v>
+            <v>2281765.0340000005</v>
           </cell>
           <cell r="V42">
-            <v>121694.51499999966</v>
+            <v>109300.96599999955</v>
           </cell>
         </row>
         <row r="43">
@@ -4280,7 +4280,7 @@
             <v>0</v>
           </cell>
           <cell r="N49">
-            <v>1587120.41</v>
+            <v>2043120.41</v>
           </cell>
           <cell r="O49">
             <v>0</v>
@@ -4292,16 +4292,16 @@
             <v>0</v>
           </cell>
           <cell r="R49">
-            <v>1587120.41</v>
+            <v>2043120.41</v>
           </cell>
           <cell r="T49">
-            <v>-1496168.69</v>
+            <v>-2042368.69</v>
           </cell>
           <cell r="U49">
-            <v>90951.719999999972</v>
+            <v>751.71999999997206</v>
           </cell>
           <cell r="V49">
-            <v>-90951.719999999972</v>
+            <v>-751.71999999997206</v>
           </cell>
         </row>
       </sheetData>
@@ -4314,28 +4314,28 @@
             <v>23902729.770000003</v>
           </cell>
           <cell r="N6">
-            <v>17045781.460000001</v>
+            <v>17709261.730000004</v>
           </cell>
           <cell r="O6">
-            <v>704431.33</v>
+            <v>703370.67</v>
           </cell>
           <cell r="P6">
-            <v>1530014.1</v>
+            <v>1410543.08</v>
           </cell>
           <cell r="Q6">
-            <v>64872.799999999996</v>
+            <v>79051.8</v>
           </cell>
           <cell r="R6">
-            <v>19345099.690000001</v>
+            <v>19902227.280000005</v>
           </cell>
           <cell r="T6">
-            <v>3348615.1599999997</v>
+            <v>2915423.0599999987</v>
           </cell>
           <cell r="U6">
-            <v>22693714.850000001</v>
+            <v>22817650.340000004</v>
           </cell>
           <cell r="V6">
-            <v>1209014.9200000018</v>
+            <v>1085079.4299999997</v>
           </cell>
         </row>
         <row r="7">
@@ -4355,28 +4355,28 @@
             <v>5210747.9000000004</v>
           </cell>
           <cell r="N7">
-            <v>3583045.09</v>
+            <v>3709410.16</v>
           </cell>
           <cell r="O7">
-            <v>93549.959999999992</v>
+            <v>82396.13</v>
           </cell>
           <cell r="P7">
-            <v>351579.85000000003</v>
+            <v>320041.18000000005</v>
           </cell>
           <cell r="Q7">
-            <v>2411.5300000000002</v>
+            <v>2661.26</v>
           </cell>
           <cell r="R7">
-            <v>4030586.4299999997</v>
+            <v>4114508.73</v>
           </cell>
           <cell r="T7">
-            <v>890347.6799999997</v>
+            <v>867687.15999999968</v>
           </cell>
           <cell r="U7">
-            <v>4920934.1099999994</v>
+            <v>4982195.8899999997</v>
           </cell>
           <cell r="V7">
-            <v>289813.79000000097</v>
+            <v>228552.01000000071</v>
           </cell>
         </row>
         <row r="8">
@@ -4396,13 +4396,13 @@
             <v>891749.49</v>
           </cell>
           <cell r="N8">
-            <v>529117.84000000008</v>
+            <v>531321.84000000008</v>
           </cell>
           <cell r="O8">
             <v>1350</v>
           </cell>
           <cell r="P8">
-            <v>12289.9</v>
+            <v>10085.9</v>
           </cell>
           <cell r="Q8">
             <v>0</v>
@@ -4955,13 +4955,13 @@
             <v>524668.59</v>
           </cell>
           <cell r="N19">
-            <v>395639.27</v>
+            <v>397843.27</v>
           </cell>
           <cell r="O19">
             <v>1350</v>
           </cell>
           <cell r="P19">
-            <v>12289.9</v>
+            <v>10085.9</v>
           </cell>
           <cell r="Q19">
             <v>0</v>
@@ -5061,13 +5061,13 @@
             <v>0</v>
           </cell>
           <cell r="N21">
-            <v>24160</v>
+            <v>25200</v>
           </cell>
           <cell r="O21">
             <v>0</v>
           </cell>
           <cell r="P21">
-            <v>1040</v>
+            <v>0</v>
           </cell>
           <cell r="Q21">
             <v>0</v>
@@ -5220,13 +5220,13 @@
             <v>140000</v>
           </cell>
           <cell r="N24">
-            <v>60916.68</v>
+            <v>61916.68</v>
           </cell>
           <cell r="O24">
             <v>0</v>
           </cell>
           <cell r="P24">
-            <v>7550</v>
+            <v>6550</v>
           </cell>
           <cell r="Q24">
             <v>0</v>
@@ -5694,13 +5694,13 @@
             <v>11100</v>
           </cell>
           <cell r="N33">
-            <v>8494</v>
+            <v>8658</v>
           </cell>
           <cell r="O33">
             <v>0</v>
           </cell>
           <cell r="P33">
-            <v>3699.9</v>
+            <v>3535.9</v>
           </cell>
           <cell r="Q33">
             <v>0</v>
@@ -5735,28 +5735,28 @@
             <v>541800</v>
           </cell>
           <cell r="N34">
-            <v>447658.82000000007</v>
+            <v>458680.4800000001</v>
           </cell>
           <cell r="O34">
-            <v>11472.399999999998</v>
+            <v>9336.2000000000007</v>
           </cell>
           <cell r="P34">
-            <v>62490.37</v>
+            <v>57455.7</v>
           </cell>
           <cell r="Q34">
-            <v>52.300000000000004</v>
+            <v>270.5</v>
           </cell>
           <cell r="R34">
-            <v>521673.89000000007</v>
+            <v>525742.88000000012</v>
           </cell>
           <cell r="T34">
-            <v>86517.679999999978</v>
+            <v>82970.019999999975</v>
           </cell>
           <cell r="U34">
-            <v>608191.57000000007</v>
+            <v>608712.90000000014</v>
           </cell>
           <cell r="V34">
-            <v>-66391.570000000065</v>
+            <v>-66912.90000000014</v>
           </cell>
         </row>
         <row r="35">
@@ -5776,28 +5776,28 @@
             <v>212000</v>
           </cell>
           <cell r="N35">
-            <v>203830.85000000003</v>
+            <v>206523.85000000003</v>
           </cell>
           <cell r="O35">
-            <v>0</v>
+            <v>668</v>
           </cell>
           <cell r="P35">
-            <v>18046</v>
+            <v>15035</v>
           </cell>
           <cell r="Q35">
-            <v>0</v>
+            <v>270.5</v>
           </cell>
           <cell r="R35">
-            <v>221876.85000000003</v>
+            <v>222497.35000000003</v>
           </cell>
           <cell r="T35">
             <v>13202.86</v>
           </cell>
           <cell r="U35">
-            <v>235079.71000000002</v>
+            <v>235700.21000000002</v>
           </cell>
           <cell r="V35">
-            <v>-23079.710000000021</v>
+            <v>-23700.210000000021</v>
           </cell>
         </row>
         <row r="36">
@@ -5832,25 +5832,25 @@
             <v>128792.79000000001</v>
           </cell>
           <cell r="O36">
-            <v>0</v>
+            <v>350</v>
           </cell>
           <cell r="P36">
             <v>10350</v>
           </cell>
           <cell r="Q36">
-            <v>0</v>
+            <v>270.5</v>
           </cell>
           <cell r="R36">
-            <v>139142.79</v>
+            <v>139763.29</v>
           </cell>
           <cell r="T36">
             <v>0</v>
           </cell>
           <cell r="U36">
-            <v>139142.79</v>
+            <v>139763.29</v>
           </cell>
           <cell r="V36">
-            <v>-44142.790000000008</v>
+            <v>-44763.290000000008</v>
           </cell>
         </row>
         <row r="37">
@@ -5935,13 +5935,13 @@
             <v>18000</v>
           </cell>
           <cell r="N38">
-            <v>15746</v>
+            <v>18439</v>
           </cell>
           <cell r="O38">
-            <v>0</v>
+            <v>318</v>
           </cell>
           <cell r="P38">
-            <v>7696</v>
+            <v>4685</v>
           </cell>
           <cell r="Q38">
             <v>0</v>
@@ -6241,28 +6241,28 @@
             <v>329800</v>
           </cell>
           <cell r="N44">
-            <v>243827.97000000003</v>
+            <v>252156.63000000003</v>
           </cell>
           <cell r="O44">
-            <v>11472.399999999998</v>
+            <v>8668.2000000000007</v>
           </cell>
           <cell r="P44">
-            <v>44444.37</v>
+            <v>42420.7</v>
           </cell>
           <cell r="Q44">
-            <v>52.300000000000004</v>
+            <v>0</v>
           </cell>
           <cell r="R44">
-            <v>299797.04000000004</v>
+            <v>303245.53000000003</v>
           </cell>
           <cell r="T44">
-            <v>73314.819999999978</v>
+            <v>69767.159999999974</v>
           </cell>
           <cell r="U44">
-            <v>373111.86</v>
+            <v>373012.69</v>
           </cell>
           <cell r="V44">
-            <v>-43311.859999999986</v>
+            <v>-43212.69</v>
           </cell>
         </row>
         <row r="45">
@@ -6294,10 +6294,10 @@
             <v>18000</v>
           </cell>
           <cell r="N45">
-            <v>13314.78</v>
+            <v>14622.52</v>
           </cell>
           <cell r="O45">
-            <v>1500</v>
+            <v>1807.74</v>
           </cell>
           <cell r="P45">
             <v>0</v>
@@ -6306,10 +6306,10 @@
             <v>0</v>
           </cell>
           <cell r="R45">
-            <v>14814.78</v>
+            <v>16430.260000000002</v>
           </cell>
           <cell r="T45">
-            <v>3185.2199999999993</v>
+            <v>1569.739999999998</v>
           </cell>
           <cell r="U45">
             <v>18000</v>
@@ -6347,10 +6347,10 @@
             <v>72000</v>
           </cell>
           <cell r="N46">
-            <v>34202.479999999996</v>
+            <v>36258.329999999994</v>
           </cell>
           <cell r="O46">
-            <v>5000</v>
+            <v>4000</v>
           </cell>
           <cell r="P46">
             <v>0</v>
@@ -6359,10 +6359,10 @@
             <v>0</v>
           </cell>
           <cell r="R46">
-            <v>39202.479999999996</v>
+            <v>40258.329999999994</v>
           </cell>
           <cell r="T46">
-            <v>12745.190000000002</v>
+            <v>11689.340000000004</v>
           </cell>
           <cell r="U46">
             <v>51947.67</v>
@@ -6400,10 +6400,10 @@
             <v>10800</v>
           </cell>
           <cell r="N47">
-            <v>4089.4199999999978</v>
+            <v>4209.409999999998</v>
           </cell>
           <cell r="O47">
-            <v>750.1099999999999</v>
+            <v>630.12</v>
           </cell>
           <cell r="P47">
             <v>0</v>
@@ -6453,22 +6453,22 @@
             <v>7200</v>
           </cell>
           <cell r="N48">
-            <v>10144.950000000003</v>
+            <v>10503.29</v>
           </cell>
           <cell r="O48">
-            <v>292.24</v>
+            <v>181.07999999999998</v>
           </cell>
           <cell r="P48">
             <v>0</v>
           </cell>
           <cell r="Q48">
-            <v>52.300000000000004</v>
+            <v>0</v>
           </cell>
           <cell r="R48">
-            <v>10489.490000000002</v>
+            <v>10684.37</v>
           </cell>
           <cell r="T48">
-            <v>4350.41</v>
+            <v>4155.5300000000007</v>
           </cell>
           <cell r="U48">
             <v>14839.900000000001</v>
@@ -6506,10 +6506,10 @@
             <v>7200</v>
           </cell>
           <cell r="N49">
-            <v>9563.5899999999983</v>
+            <v>9700.5399999999991</v>
           </cell>
           <cell r="O49">
-            <v>128</v>
+            <v>222.5</v>
           </cell>
           <cell r="P49">
             <v>0</v>
@@ -6518,10 +6518,10 @@
             <v>0</v>
           </cell>
           <cell r="R49">
-            <v>9691.5899999999983</v>
+            <v>9923.0399999999991</v>
           </cell>
           <cell r="T49">
-            <v>4958.1299999999992</v>
+            <v>4726.6799999999985</v>
           </cell>
           <cell r="U49">
             <v>14649.719999999998</v>
@@ -6559,28 +6559,28 @@
             <v>21600</v>
           </cell>
           <cell r="N50">
-            <v>31960.16</v>
+            <v>34452.160000000003</v>
           </cell>
           <cell r="O50">
-            <v>2492</v>
+            <v>66.680000000000007</v>
           </cell>
           <cell r="P50">
-            <v>19964</v>
+            <v>19884</v>
           </cell>
           <cell r="Q50">
             <v>0</v>
           </cell>
           <cell r="R50">
-            <v>54416.160000000003</v>
+            <v>54402.840000000004</v>
           </cell>
           <cell r="T50">
             <v>0</v>
           </cell>
           <cell r="U50">
-            <v>54416.160000000003</v>
+            <v>54402.840000000004</v>
           </cell>
           <cell r="V50">
-            <v>-32816.160000000003</v>
+            <v>-32802.840000000004</v>
           </cell>
         </row>
         <row r="51">
@@ -6774,7 +6774,7 @@
             <v>5279.56</v>
           </cell>
           <cell r="O54">
-            <v>0</v>
+            <v>450</v>
           </cell>
           <cell r="P54">
             <v>0</v>
@@ -6783,10 +6783,10 @@
             <v>0</v>
           </cell>
           <cell r="R54">
-            <v>5279.56</v>
+            <v>5729.56</v>
           </cell>
           <cell r="T54">
-            <v>9720.4399999999987</v>
+            <v>9270.4399999999987</v>
           </cell>
           <cell r="U54">
             <v>15000</v>
@@ -6983,28 +6983,28 @@
             <v>58800</v>
           </cell>
           <cell r="N58">
-            <v>53962.91000000004</v>
+            <v>55272.960000000043</v>
           </cell>
           <cell r="O58">
-            <v>1310.05</v>
+            <v>1310.08</v>
           </cell>
           <cell r="P58">
-            <v>16982.400000000001</v>
+            <v>15586.47</v>
           </cell>
           <cell r="Q58">
             <v>0</v>
           </cell>
           <cell r="R58">
-            <v>72255.360000000044</v>
+            <v>72169.510000000038</v>
           </cell>
           <cell r="T58">
             <v>3010.9599999999773</v>
           </cell>
           <cell r="U58">
-            <v>75266.320000000022</v>
+            <v>75180.470000000016</v>
           </cell>
           <cell r="V58">
-            <v>-16466.320000000022</v>
+            <v>-16380.470000000016</v>
           </cell>
         </row>
         <row r="59">
@@ -7089,13 +7089,13 @@
             <v>24000</v>
           </cell>
           <cell r="N60">
-            <v>42424.77999999997</v>
+            <v>42972.519999999968</v>
           </cell>
           <cell r="O60">
             <v>0</v>
           </cell>
           <cell r="P60">
-            <v>7497.97</v>
+            <v>6950.23</v>
           </cell>
           <cell r="Q60">
             <v>0</v>
@@ -7130,28 +7130,28 @@
             <v>921807.4</v>
           </cell>
           <cell r="N61">
-            <v>627501.06000000006</v>
+            <v>652166.56999999995</v>
           </cell>
           <cell r="O61">
-            <v>16747.489999999998</v>
+            <v>13173.1</v>
           </cell>
           <cell r="P61">
-            <v>139270</v>
+            <v>128970.00000000001</v>
           </cell>
           <cell r="Q61">
-            <v>2359.23</v>
+            <v>2390.7600000000002</v>
           </cell>
           <cell r="R61">
-            <v>785877.78</v>
+            <v>796700.42999999993</v>
           </cell>
           <cell r="T61">
-            <v>79675.130000000019</v>
+            <v>75366</v>
           </cell>
           <cell r="U61">
-            <v>865552.91</v>
+            <v>872066.42999999993</v>
           </cell>
           <cell r="V61">
-            <v>56254.489999999991</v>
+            <v>49740.970000000088</v>
           </cell>
         </row>
         <row r="62">
@@ -7171,28 +7171,28 @@
             <v>683792.8</v>
           </cell>
           <cell r="N62">
-            <v>390649.28</v>
+            <v>412984.54999999993</v>
           </cell>
           <cell r="O62">
-            <v>16211.68</v>
+            <v>10054</v>
           </cell>
           <cell r="P62">
-            <v>139270</v>
+            <v>128970.00000000001</v>
           </cell>
           <cell r="Q62">
             <v>0</v>
           </cell>
           <cell r="R62">
-            <v>546130.96</v>
+            <v>552008.54999999993</v>
           </cell>
           <cell r="T62">
-            <v>149325.36000000002</v>
+            <v>149215.79</v>
           </cell>
           <cell r="U62">
-            <v>695456.32</v>
+            <v>701224.34</v>
           </cell>
           <cell r="V62">
-            <v>-11663.519999999902</v>
+            <v>-17431.539999999921</v>
           </cell>
         </row>
         <row r="63">
@@ -7224,7 +7224,7 @@
             <v>16100</v>
           </cell>
           <cell r="N63">
-            <v>22000</v>
+            <v>26400</v>
           </cell>
           <cell r="O63">
             <v>2200</v>
@@ -7236,16 +7236,16 @@
             <v>0</v>
           </cell>
           <cell r="R63">
-            <v>24200</v>
+            <v>28600</v>
           </cell>
           <cell r="T63">
             <v>0</v>
           </cell>
           <cell r="U63">
-            <v>24200</v>
+            <v>28600</v>
           </cell>
           <cell r="V63">
-            <v>-8100</v>
+            <v>-12500</v>
           </cell>
         </row>
         <row r="64">
@@ -7330,28 +7330,28 @@
             <v>114000</v>
           </cell>
           <cell r="N65">
-            <v>18106.280000000002</v>
+            <v>21310.280000000002</v>
           </cell>
           <cell r="O65">
-            <v>3336</v>
+            <v>5080</v>
           </cell>
           <cell r="P65">
-            <v>91978.559999999998</v>
+            <v>86678.74</v>
           </cell>
           <cell r="Q65">
             <v>0</v>
           </cell>
           <cell r="R65">
-            <v>113420.84</v>
+            <v>113069.02</v>
           </cell>
           <cell r="T65">
             <v>0</v>
           </cell>
           <cell r="U65">
-            <v>113420.84</v>
+            <v>113069.02</v>
           </cell>
           <cell r="V65">
-            <v>579.16000000000349</v>
+            <v>930.97999999999593</v>
           </cell>
         </row>
         <row r="66">
@@ -7383,28 +7383,28 @@
             <v>13000</v>
           </cell>
           <cell r="N66">
-            <v>12405.93</v>
+            <v>15705.93</v>
           </cell>
           <cell r="O66">
-            <v>3300</v>
+            <v>1424</v>
           </cell>
           <cell r="P66">
-            <v>1601.46</v>
+            <v>1.3</v>
           </cell>
           <cell r="Q66">
             <v>0</v>
           </cell>
           <cell r="R66">
-            <v>17307.39</v>
+            <v>17131.23</v>
           </cell>
           <cell r="T66">
             <v>0</v>
           </cell>
           <cell r="U66">
-            <v>17307.39</v>
+            <v>17131.23</v>
           </cell>
           <cell r="V66">
-            <v>-4307.3899999999994</v>
+            <v>-4131.2299999999996</v>
           </cell>
         </row>
         <row r="67">
@@ -7442,16 +7442,16 @@
             <v>0</v>
           </cell>
           <cell r="P67">
-            <v>209.98</v>
+            <v>209.96</v>
           </cell>
           <cell r="Q67">
             <v>0</v>
           </cell>
           <cell r="R67">
-            <v>10058.08</v>
+            <v>10058.06</v>
           </cell>
           <cell r="T67">
-            <v>441.92000000000007</v>
+            <v>441.94000000000051</v>
           </cell>
           <cell r="U67">
             <v>10500</v>
@@ -7542,10 +7542,10 @@
             <v>1800</v>
           </cell>
           <cell r="N69">
-            <v>267</v>
+            <v>377</v>
           </cell>
           <cell r="O69">
-            <v>110</v>
+            <v>0</v>
           </cell>
           <cell r="P69">
             <v>0</v>
@@ -7701,22 +7701,22 @@
             <v>352000</v>
           </cell>
           <cell r="N72">
-            <v>165624.99</v>
+            <v>173600.25999999998</v>
           </cell>
           <cell r="O72">
-            <v>4465.68</v>
+            <v>0</v>
           </cell>
           <cell r="P72">
-            <v>40800</v>
+            <v>37400</v>
           </cell>
           <cell r="Q72">
             <v>0</v>
           </cell>
           <cell r="R72">
-            <v>210890.66999999998</v>
+            <v>211000.25999999998</v>
           </cell>
           <cell r="T72">
-            <v>141109.33000000002</v>
+            <v>140999.74000000002</v>
           </cell>
           <cell r="U72">
             <v>352000</v>
@@ -8072,10 +8072,10 @@
             <v>20000</v>
           </cell>
           <cell r="N79">
-            <v>36347.68</v>
+            <v>36697.68</v>
           </cell>
           <cell r="O79">
-            <v>350</v>
+            <v>0</v>
           </cell>
           <cell r="P79">
             <v>0</v>
@@ -8125,10 +8125,10 @@
             <v>30000</v>
           </cell>
           <cell r="N80">
-            <v>68334.709999999992</v>
+            <v>71330.709999999992</v>
           </cell>
           <cell r="O80">
-            <v>2450</v>
+            <v>1350</v>
           </cell>
           <cell r="P80">
             <v>0</v>
@@ -8137,16 +8137,16 @@
             <v>0</v>
           </cell>
           <cell r="R80">
-            <v>70784.709999999992</v>
+            <v>72680.709999999992</v>
           </cell>
           <cell r="T80">
             <v>0</v>
           </cell>
           <cell r="U80">
-            <v>70784.709999999992</v>
+            <v>72680.709999999992</v>
           </cell>
           <cell r="V80">
-            <v>-40784.709999999992</v>
+            <v>-42680.709999999992</v>
           </cell>
         </row>
         <row r="81">
@@ -8696,28 +8696,28 @@
             <v>30000</v>
           </cell>
           <cell r="N91">
-            <v>70155.169999999984</v>
+            <v>70724.809999999983</v>
           </cell>
           <cell r="O91">
-            <v>131.80000000000001</v>
+            <v>852.16000000000008</v>
           </cell>
           <cell r="P91">
             <v>0</v>
           </cell>
           <cell r="Q91">
-            <v>82.5</v>
+            <v>1277.5</v>
           </cell>
           <cell r="R91">
-            <v>70369.469999999987</v>
+            <v>72854.469999999987</v>
           </cell>
           <cell r="T91">
-            <v>-49258.628999999986</v>
+            <v>-50998.128999999986</v>
           </cell>
           <cell r="U91">
-            <v>21110.841</v>
+            <v>21856.341</v>
           </cell>
           <cell r="V91">
-            <v>8889.1589999999997</v>
+            <v>8143.6589999999997</v>
           </cell>
         </row>
         <row r="92">
@@ -8749,28 +8749,28 @@
             <v>30000</v>
           </cell>
           <cell r="N92">
-            <v>70155.169999999984</v>
+            <v>70724.809999999983</v>
           </cell>
           <cell r="O92">
-            <v>131.80000000000001</v>
+            <v>852.16000000000008</v>
           </cell>
           <cell r="P92">
             <v>0</v>
           </cell>
           <cell r="Q92">
-            <v>82.5</v>
+            <v>1277.5</v>
           </cell>
           <cell r="R92">
-            <v>70369.469999999987</v>
+            <v>72854.469999999987</v>
           </cell>
           <cell r="T92">
-            <v>-49258.628999999986</v>
+            <v>-50998.128999999986</v>
           </cell>
           <cell r="U92">
-            <v>21110.841</v>
+            <v>21856.341</v>
           </cell>
           <cell r="V92">
-            <v>8889.1589999999997</v>
+            <v>8143.6589999999997</v>
           </cell>
         </row>
         <row r="93">
@@ -8790,22 +8790,22 @@
             <v>208014.59999999998</v>
           </cell>
           <cell r="N93">
-            <v>166696.61000000002</v>
+            <v>168457.21000000005</v>
           </cell>
           <cell r="O93">
-            <v>404.01</v>
+            <v>2266.94</v>
           </cell>
           <cell r="P93">
             <v>0</v>
           </cell>
           <cell r="Q93">
-            <v>2276.73</v>
+            <v>1113.26</v>
           </cell>
           <cell r="R93">
-            <v>169377.35000000003</v>
+            <v>171837.41000000006</v>
           </cell>
           <cell r="T93">
-            <v>-20391.601000000006</v>
+            <v>-22851.661000000018</v>
           </cell>
           <cell r="U93">
             <v>148985.74900000004</v>
@@ -9161,22 +9161,22 @@
             <v>73158.62</v>
           </cell>
           <cell r="N100">
-            <v>64833.59</v>
+            <v>66454.190000000017</v>
           </cell>
           <cell r="O100">
-            <v>404.01</v>
+            <v>2266.94</v>
           </cell>
           <cell r="P100">
             <v>0</v>
           </cell>
           <cell r="Q100">
-            <v>2276.73</v>
+            <v>1113.26</v>
           </cell>
           <cell r="R100">
-            <v>67514.33</v>
+            <v>69834.390000000014</v>
           </cell>
           <cell r="T100">
-            <v>5644.2899999999936</v>
+            <v>3324.2299999999814</v>
           </cell>
           <cell r="U100">
             <v>73158.62</v>
@@ -9214,7 +9214,7 @@
             <v>19365.52</v>
           </cell>
           <cell r="N101">
-            <v>35569.47</v>
+            <v>35709.47</v>
           </cell>
           <cell r="O101">
             <v>0</v>
@@ -9226,10 +9226,10 @@
             <v>0</v>
           </cell>
           <cell r="R101">
-            <v>35569.47</v>
+            <v>35709.47</v>
           </cell>
           <cell r="T101">
-            <v>-16203.95</v>
+            <v>-16343.95</v>
           </cell>
           <cell r="U101">
             <v>19365.52</v>
@@ -9467,10 +9467,10 @@
             <v>86500</v>
           </cell>
           <cell r="N106">
-            <v>99537.17</v>
+            <v>105037.17</v>
           </cell>
           <cell r="O106">
-            <v>5500</v>
+            <v>0</v>
           </cell>
           <cell r="P106">
             <v>25650</v>
@@ -9482,13 +9482,13 @@
             <v>130687.17</v>
           </cell>
           <cell r="T106">
-            <v>8382.36</v>
+            <v>18859.86</v>
           </cell>
           <cell r="U106">
-            <v>139069.53</v>
+            <v>149547.03</v>
           </cell>
           <cell r="V106">
-            <v>-52569.53</v>
+            <v>-63047.03</v>
           </cell>
         </row>
         <row r="107">
@@ -9508,10 +9508,10 @@
             <v>76500</v>
           </cell>
           <cell r="N107">
-            <v>99337.17</v>
+            <v>104837.17</v>
           </cell>
           <cell r="O107">
-            <v>5500</v>
+            <v>0</v>
           </cell>
           <cell r="P107">
             <v>25650</v>
@@ -9523,13 +9523,13 @@
             <v>130487.17</v>
           </cell>
           <cell r="T107">
-            <v>-1417.6399999999994</v>
+            <v>9059.86</v>
           </cell>
           <cell r="U107">
-            <v>129069.53</v>
+            <v>139547.03</v>
           </cell>
           <cell r="V107">
-            <v>-52569.53</v>
+            <v>-63047.03</v>
           </cell>
         </row>
         <row r="108">
@@ -9561,10 +9561,10 @@
             <v>66000</v>
           </cell>
           <cell r="N108">
-            <v>97897.03</v>
+            <v>103397.03</v>
           </cell>
           <cell r="O108">
-            <v>5500</v>
+            <v>0</v>
           </cell>
           <cell r="P108">
             <v>25650</v>
@@ -9576,13 +9576,13 @@
             <v>129047.03</v>
           </cell>
           <cell r="T108">
-            <v>-10477.5</v>
+            <v>0</v>
           </cell>
           <cell r="U108">
-            <v>118569.53</v>
+            <v>129047.03</v>
           </cell>
           <cell r="V108">
-            <v>-52569.53</v>
+            <v>-63047.03</v>
           </cell>
         </row>
         <row r="109">
@@ -9802,28 +9802,28 @@
             <v>2768891.01</v>
           </cell>
           <cell r="N113">
-            <v>1879230.2</v>
+            <v>1962204.1000000003</v>
           </cell>
           <cell r="O113">
-            <v>58480.07</v>
+            <v>58536.83</v>
           </cell>
           <cell r="P113">
-            <v>111879.58</v>
+            <v>97879.580000000016</v>
           </cell>
           <cell r="Q113">
             <v>0</v>
           </cell>
           <cell r="R113">
-            <v>2049589.85</v>
+            <v>2118620.5100000002</v>
           </cell>
           <cell r="T113">
-            <v>516907.43999999977</v>
+            <v>491626.20999999967</v>
           </cell>
           <cell r="U113">
-            <v>2566497.29</v>
+            <v>2610246.7199999997</v>
           </cell>
           <cell r="V113">
-            <v>202393.71999999974</v>
+            <v>158644.29000000004</v>
           </cell>
         </row>
         <row r="114">
@@ -9843,28 +9843,28 @@
             <v>1480467</v>
           </cell>
           <cell r="N114">
-            <v>848385.48</v>
+            <v>884805.31</v>
           </cell>
           <cell r="O114">
-            <v>30333.29</v>
+            <v>28961.95</v>
           </cell>
           <cell r="P114">
-            <v>111879.36</v>
+            <v>97879.360000000015</v>
           </cell>
           <cell r="Q114">
             <v>0</v>
           </cell>
           <cell r="R114">
-            <v>990598.13</v>
+            <v>1011646.62</v>
           </cell>
           <cell r="T114">
-            <v>278363.43000000005</v>
+            <v>257314.93999999989</v>
           </cell>
           <cell r="U114">
-            <v>1268961.56</v>
+            <v>1268961.5599999998</v>
           </cell>
           <cell r="V114">
-            <v>211505.43999999994</v>
+            <v>211505.44000000018</v>
           </cell>
         </row>
         <row r="115">
@@ -9896,13 +9896,13 @@
             <v>380000</v>
           </cell>
           <cell r="N115">
-            <v>274520.68</v>
+            <v>287020.68</v>
           </cell>
           <cell r="O115">
-            <v>12500</v>
+            <v>12000</v>
           </cell>
           <cell r="P115">
-            <v>98729.32</v>
+            <v>86729.32</v>
           </cell>
           <cell r="Q115">
             <v>0</v>
@@ -9949,10 +9949,10 @@
             <v>478800</v>
           </cell>
           <cell r="N116">
-            <v>299625.37000000005</v>
+            <v>311686.24000000011</v>
           </cell>
           <cell r="O116">
-            <v>8441.98</v>
+            <v>8407.15</v>
           </cell>
           <cell r="P116">
             <v>0</v>
@@ -9961,16 +9961,16 @@
             <v>0</v>
           </cell>
           <cell r="R116">
-            <v>308067.35000000003</v>
+            <v>320093.39000000013</v>
           </cell>
           <cell r="T116">
-            <v>94801.680000000051</v>
+            <v>82775.639999999898</v>
           </cell>
           <cell r="U116">
-            <v>402869.03000000009</v>
+            <v>402869.03</v>
           </cell>
           <cell r="V116">
-            <v>75930.969999999914</v>
+            <v>75930.969999999972</v>
           </cell>
         </row>
         <row r="117">
@@ -10002,13 +10002,13 @@
             <v>108000</v>
           </cell>
           <cell r="N117">
-            <v>52972.29</v>
+            <v>54972.29</v>
           </cell>
           <cell r="O117">
             <v>2000</v>
           </cell>
           <cell r="P117">
-            <v>13150.039999999999</v>
+            <v>11150.04</v>
           </cell>
           <cell r="Q117">
             <v>0</v>
@@ -10055,7 +10055,7 @@
             <v>96867</v>
           </cell>
           <cell r="N118">
-            <v>37538.969999999994</v>
+            <v>40658.969999999994</v>
           </cell>
           <cell r="O118">
             <v>3120</v>
@@ -10067,10 +10067,10 @@
             <v>0</v>
           </cell>
           <cell r="R118">
-            <v>40658.969999999994</v>
+            <v>43778.969999999994</v>
           </cell>
           <cell r="T118">
-            <v>19170.900000000001</v>
+            <v>16050.900000000001</v>
           </cell>
           <cell r="U118">
             <v>59829.869999999995</v>
@@ -10161,10 +10161,10 @@
             <v>226800</v>
           </cell>
           <cell r="N120">
-            <v>139462.83999999997</v>
+            <v>146201.79999999999</v>
           </cell>
           <cell r="O120">
-            <v>4271.3100000000004</v>
+            <v>3434.8</v>
           </cell>
           <cell r="P120">
             <v>0</v>
@@ -10173,10 +10173,10 @@
             <v>0</v>
           </cell>
           <cell r="R120">
-            <v>143734.14999999997</v>
+            <v>149636.59999999998</v>
           </cell>
           <cell r="T120">
-            <v>31656.760000000009</v>
+            <v>25754.309999999998</v>
           </cell>
           <cell r="U120">
             <v>175390.90999999997</v>
@@ -10202,10 +10202,10 @@
             <v>1108398.01</v>
           </cell>
           <cell r="N121">
-            <v>830534.10000000021</v>
+            <v>875444.01000000013</v>
           </cell>
           <cell r="O121">
-            <v>28106.799999999999</v>
+            <v>28213.43</v>
           </cell>
           <cell r="P121">
             <v>0</v>
@@ -10214,16 +10214,16 @@
             <v>0</v>
           </cell>
           <cell r="R121">
-            <v>858640.90000000026</v>
+            <v>903657.44000000018</v>
           </cell>
           <cell r="T121">
-            <v>212397.10999999975</v>
+            <v>211129.99999999983</v>
           </cell>
           <cell r="U121">
-            <v>1071038.01</v>
+            <v>1114787.44</v>
           </cell>
           <cell r="V121">
-            <v>37360</v>
+            <v>-6389.4299999999348</v>
           </cell>
         </row>
         <row r="122">
@@ -10308,10 +10308,10 @@
             <v>216466.69</v>
           </cell>
           <cell r="N123">
-            <v>216693.69</v>
+            <v>236257.99000000002</v>
           </cell>
           <cell r="O123">
-            <v>13513.730000000001</v>
+            <v>8670.7999999999993</v>
           </cell>
           <cell r="P123">
             <v>0</v>
@@ -10320,16 +10320,16 @@
             <v>0</v>
           </cell>
           <cell r="R123">
-            <v>230207.42</v>
+            <v>244928.79</v>
           </cell>
           <cell r="T123">
-            <v>-13740.73000000001</v>
+            <v>0</v>
           </cell>
           <cell r="U123">
-            <v>216466.69</v>
+            <v>244928.79</v>
           </cell>
           <cell r="V123">
-            <v>0</v>
+            <v>-28462.100000000006</v>
           </cell>
         </row>
         <row r="124">
@@ -10467,10 +10467,10 @@
             <v>453600</v>
           </cell>
           <cell r="N126">
-            <v>388836.93000000023</v>
+            <v>401717.07000000018</v>
           </cell>
           <cell r="O126">
-            <v>9518.58</v>
+            <v>5441.45</v>
           </cell>
           <cell r="P126">
             <v>0</v>
@@ -10479,10 +10479,10 @@
             <v>0</v>
           </cell>
           <cell r="R126">
-            <v>398355.51000000024</v>
+            <v>407158.52000000019</v>
           </cell>
           <cell r="T126">
-            <v>55244.489999999758</v>
+            <v>46441.479999999807</v>
           </cell>
           <cell r="U126">
             <v>453600</v>
@@ -10520,10 +10520,10 @@
             <v>172486.88</v>
           </cell>
           <cell r="N127">
-            <v>169457.83000000002</v>
+            <v>176860.09000000003</v>
           </cell>
           <cell r="O127">
-            <v>3636.51</v>
+            <v>10914.119999999999</v>
           </cell>
           <cell r="P127">
             <v>0</v>
@@ -10532,16 +10532,16 @@
             <v>0</v>
           </cell>
           <cell r="R127">
-            <v>173094.34000000003</v>
+            <v>187774.21000000002</v>
           </cell>
           <cell r="T127">
-            <v>-607.46000000002095</v>
+            <v>0</v>
           </cell>
           <cell r="U127">
-            <v>172486.88</v>
+            <v>187774.21000000002</v>
           </cell>
           <cell r="V127">
-            <v>0</v>
+            <v>-15287.330000000016</v>
           </cell>
         </row>
         <row r="128">
@@ -10573,10 +10573,10 @@
             <v>151200</v>
           </cell>
           <cell r="N128">
-            <v>48406.879999999997</v>
+            <v>53470.09</v>
           </cell>
           <cell r="O128">
-            <v>1437.98</v>
+            <v>3187.06</v>
           </cell>
           <cell r="P128">
             <v>0</v>
@@ -10585,10 +10585,10 @@
             <v>0</v>
           </cell>
           <cell r="R128">
-            <v>49844.86</v>
+            <v>56657.149999999994</v>
           </cell>
           <cell r="T128">
-            <v>101355.14</v>
+            <v>94542.85</v>
           </cell>
           <cell r="U128">
             <v>151200</v>
@@ -10614,10 +10614,10 @@
             <v>180026</v>
           </cell>
           <cell r="N129">
-            <v>200310.61999999997</v>
+            <v>201954.78</v>
           </cell>
           <cell r="O129">
-            <v>39.979999999999997</v>
+            <v>1361.45</v>
           </cell>
           <cell r="P129">
             <v>0.21999999999999997</v>
@@ -10626,16 +10626,16 @@
             <v>0</v>
           </cell>
           <cell r="R129">
-            <v>200350.81999999998</v>
+            <v>203316.45</v>
           </cell>
           <cell r="T129">
-            <v>26146.899999999954</v>
+            <v>23181.269999999964</v>
           </cell>
           <cell r="U129">
-            <v>226497.71999999994</v>
+            <v>226497.71999999997</v>
           </cell>
           <cell r="V129">
-            <v>-46471.719999999943</v>
+            <v>-46471.719999999972</v>
           </cell>
         </row>
         <row r="130">
@@ -10667,10 +10667,10 @@
             <v>30690</v>
           </cell>
           <cell r="N130">
-            <v>31527.169999999995</v>
+            <v>31877.129999999994</v>
           </cell>
           <cell r="O130">
-            <v>39.979999999999997</v>
+            <v>0</v>
           </cell>
           <cell r="P130">
             <v>0.13999999999999999</v>
@@ -10679,10 +10679,10 @@
             <v>0</v>
           </cell>
           <cell r="R130">
-            <v>31567.289999999994</v>
+            <v>31877.269999999993</v>
           </cell>
           <cell r="T130">
-            <v>2171.8500000000022</v>
+            <v>1861.8700000000063</v>
           </cell>
           <cell r="U130">
             <v>33739.14</v>
@@ -10720,10 +10720,10 @@
             <v>117645</v>
           </cell>
           <cell r="N131">
-            <v>111836.51000000001</v>
+            <v>112941.51000000001</v>
           </cell>
           <cell r="O131">
-            <v>0</v>
+            <v>1361.45</v>
           </cell>
           <cell r="P131">
             <v>0.08</v>
@@ -10732,10 +10732,10 @@
             <v>0</v>
           </cell>
           <cell r="R131">
-            <v>111836.59000000001</v>
+            <v>114303.04000000001</v>
           </cell>
           <cell r="T131">
-            <v>11544.299999999988</v>
+            <v>9077.8499999999913</v>
           </cell>
           <cell r="U131">
             <v>123380.89</v>
@@ -10773,7 +10773,7 @@
             <v>31691</v>
           </cell>
           <cell r="N132">
-            <v>56946.939999999981</v>
+            <v>57136.139999999978</v>
           </cell>
           <cell r="O132">
             <v>0</v>
@@ -10785,10 +10785,10 @@
             <v>0</v>
           </cell>
           <cell r="R132">
-            <v>56946.939999999981</v>
+            <v>57136.139999999978</v>
           </cell>
           <cell r="T132">
-            <v>12430.749999999964</v>
+            <v>12241.549999999967</v>
           </cell>
           <cell r="U132">
             <v>69377.689999999944</v>
@@ -10814,28 +10814,28 @@
             <v>18691981.870000001</v>
           </cell>
           <cell r="N133">
-            <v>13462736.370000001</v>
+            <v>13999851.570000002</v>
           </cell>
           <cell r="O133">
-            <v>610881.37</v>
+            <v>620974.54</v>
           </cell>
           <cell r="P133">
-            <v>1178434.25</v>
+            <v>1090501.8999999999</v>
           </cell>
           <cell r="Q133">
-            <v>62461.27</v>
+            <v>76390.540000000008</v>
           </cell>
           <cell r="R133">
-            <v>15314513.26</v>
+            <v>15787718.550000003</v>
           </cell>
           <cell r="T133">
-            <v>2458267.48</v>
+            <v>2047735.8999999992</v>
           </cell>
           <cell r="U133">
-            <v>17772780.739999998</v>
+            <v>17835454.450000003</v>
           </cell>
           <cell r="V133">
-            <v>919201.13000000268</v>
+            <v>856527.41999999806</v>
           </cell>
         </row>
         <row r="134">
@@ -11337,10 +11337,10 @@
             <v>644368.6</v>
           </cell>
           <cell r="N144">
-            <v>731519.75999999989</v>
+            <v>740758.89999999991</v>
           </cell>
           <cell r="O144">
-            <v>3411.15</v>
+            <v>0</v>
           </cell>
           <cell r="P144">
             <v>1711.28</v>
@@ -11349,16 +11349,16 @@
             <v>1424</v>
           </cell>
           <cell r="R144">
-            <v>738066.19</v>
+            <v>743894.17999999993</v>
           </cell>
           <cell r="T144">
             <v>0</v>
           </cell>
           <cell r="U144">
-            <v>738066.19</v>
+            <v>743894.17999999993</v>
           </cell>
           <cell r="V144">
-            <v>-93697.589999999967</v>
+            <v>-99525.579999999958</v>
           </cell>
         </row>
         <row r="145">
@@ -12002,10 +12002,10 @@
             <v>222047.29</v>
           </cell>
           <cell r="N157">
-            <v>234246.19999999995</v>
+            <v>243485.33999999991</v>
           </cell>
           <cell r="O157">
-            <v>3411.15</v>
+            <v>0</v>
           </cell>
           <cell r="P157">
             <v>29</v>
@@ -12014,16 +12014,16 @@
             <v>1424</v>
           </cell>
           <cell r="R157">
-            <v>239110.34999999995</v>
+            <v>244938.33999999991</v>
           </cell>
           <cell r="T157">
             <v>0</v>
           </cell>
           <cell r="U157">
-            <v>239110.34999999995</v>
+            <v>244938.33999999991</v>
           </cell>
           <cell r="V157">
-            <v>-17063.059999999939</v>
+            <v>-22891.049999999901</v>
           </cell>
         </row>
         <row r="158">
@@ -12108,7 +12108,7 @@
             <v>20908.55</v>
           </cell>
           <cell r="N159">
-            <v>1896.9499999999998</v>
+            <v>1950.9499999999998</v>
           </cell>
           <cell r="O159">
             <v>0</v>
@@ -12120,16 +12120,16 @@
             <v>0</v>
           </cell>
           <cell r="R159">
-            <v>1896.9499999999998</v>
+            <v>1950.9499999999998</v>
           </cell>
           <cell r="T159">
             <v>0</v>
           </cell>
           <cell r="U159">
-            <v>1896.9499999999998</v>
+            <v>1950.9499999999998</v>
           </cell>
           <cell r="V159">
-            <v>19011.599999999999</v>
+            <v>18957.599999999999</v>
           </cell>
         </row>
         <row r="160">
@@ -12267,10 +12267,10 @@
             <v>144138.14000000001</v>
           </cell>
           <cell r="N162">
-            <v>83728.84</v>
+            <v>92095.209999999992</v>
           </cell>
           <cell r="O162">
-            <v>2592.38</v>
+            <v>0</v>
           </cell>
           <cell r="P162">
             <v>0</v>
@@ -12279,16 +12279,16 @@
             <v>1424</v>
           </cell>
           <cell r="R162">
-            <v>87745.22</v>
+            <v>93519.209999999992</v>
           </cell>
           <cell r="T162">
             <v>0</v>
           </cell>
           <cell r="U162">
-            <v>87745.22</v>
+            <v>93519.209999999992</v>
           </cell>
           <cell r="V162">
-            <v>56392.920000000013</v>
+            <v>50618.930000000022</v>
           </cell>
         </row>
         <row r="163">
@@ -12320,10 +12320,10 @@
             <v>40000</v>
           </cell>
           <cell r="N163">
-            <v>134059.93999999994</v>
+            <v>134878.70999999993</v>
           </cell>
           <cell r="O163">
-            <v>818.77</v>
+            <v>0</v>
           </cell>
           <cell r="P163">
             <v>0</v>
@@ -13744,28 +13744,28 @@
             <v>5180115.879999999</v>
           </cell>
           <cell r="N191">
-            <v>5188602.8400000008</v>
+            <v>5190646.38</v>
           </cell>
           <cell r="O191">
-            <v>2139.3000000000002</v>
+            <v>6904.3</v>
           </cell>
           <cell r="P191">
             <v>28050.639999999996</v>
           </cell>
           <cell r="Q191">
-            <v>195.62</v>
+            <v>0</v>
           </cell>
           <cell r="R191">
-            <v>5218988.4000000004</v>
+            <v>5225601.3199999994</v>
           </cell>
           <cell r="T191">
             <v>-137000</v>
           </cell>
           <cell r="U191">
-            <v>5081988.4000000004</v>
+            <v>5088601.3199999994</v>
           </cell>
           <cell r="V191">
-            <v>98127.479999998584</v>
+            <v>91514.55999999959</v>
           </cell>
         </row>
         <row r="192">
@@ -13932,7 +13932,7 @@
             <v>490712.29999999987</v>
           </cell>
           <cell r="N195">
-            <v>469324.25</v>
+            <v>469455.64999999997</v>
           </cell>
           <cell r="O195">
             <v>134.52000000000001</v>
@@ -13944,16 +13944,16 @@
             <v>0</v>
           </cell>
           <cell r="R195">
-            <v>469458.77</v>
+            <v>469590.17</v>
           </cell>
           <cell r="T195">
             <v>0</v>
           </cell>
           <cell r="U195">
-            <v>469458.77</v>
+            <v>469590.17</v>
           </cell>
           <cell r="V195">
-            <v>21253.529999999853</v>
+            <v>21122.129999999888</v>
           </cell>
         </row>
         <row r="196">
@@ -14727,7 +14727,7 @@
             <v>20506.54</v>
           </cell>
           <cell r="N210">
-            <v>19078.22</v>
+            <v>19209.620000000003</v>
           </cell>
           <cell r="O210">
             <v>0</v>
@@ -14739,16 +14739,16 @@
             <v>0</v>
           </cell>
           <cell r="R210">
-            <v>19078.22</v>
+            <v>19209.620000000003</v>
           </cell>
           <cell r="T210">
             <v>0</v>
           </cell>
           <cell r="U210">
-            <v>19078.22</v>
+            <v>19209.620000000003</v>
           </cell>
           <cell r="V210">
-            <v>1428.3199999999997</v>
+            <v>1296.9199999999983</v>
           </cell>
         </row>
         <row r="211">
@@ -14821,7 +14821,7 @@
             <v>514532.25000000006</v>
           </cell>
           <cell r="N212">
-            <v>267107.55</v>
+            <v>267303.17</v>
           </cell>
           <cell r="O212">
             <v>354.18</v>
@@ -14830,7 +14830,7 @@
             <v>0</v>
           </cell>
           <cell r="Q212">
-            <v>195.62</v>
+            <v>0</v>
           </cell>
           <cell r="R212">
             <v>267657.34999999998</v>
@@ -15616,7 +15616,7 @@
             <v>0</v>
           </cell>
           <cell r="N227">
-            <v>4948.0999999999995</v>
+            <v>5143.7199999999993</v>
           </cell>
           <cell r="O227">
             <v>0</v>
@@ -15625,7 +15625,7 @@
             <v>0</v>
           </cell>
           <cell r="Q227">
-            <v>195.62</v>
+            <v>0</v>
           </cell>
           <cell r="R227">
             <v>5143.7199999999993</v>
@@ -16599,10 +16599,10 @@
             <v>833763.48999999964</v>
           </cell>
           <cell r="N246">
-            <v>984152.10000000009</v>
+            <v>985802.70000000019</v>
           </cell>
           <cell r="O246">
-            <v>1650.6</v>
+            <v>3366.9</v>
           </cell>
           <cell r="P246">
             <v>0</v>
@@ -16611,16 +16611,16 @@
             <v>0</v>
           </cell>
           <cell r="R246">
-            <v>985802.70000000007</v>
+            <v>989169.60000000021</v>
           </cell>
           <cell r="T246">
             <v>0</v>
           </cell>
           <cell r="U246">
-            <v>985802.70000000007</v>
+            <v>989169.60000000021</v>
           </cell>
           <cell r="V246">
-            <v>-152039.21000000043</v>
+            <v>-155406.11000000057</v>
           </cell>
         </row>
         <row r="247">
@@ -16652,10 +16652,10 @@
             <v>176092</v>
           </cell>
           <cell r="N247">
-            <v>194014.62</v>
+            <v>195665.22</v>
           </cell>
           <cell r="O247">
-            <v>1650.6</v>
+            <v>3366.9</v>
           </cell>
           <cell r="P247">
             <v>0</v>
@@ -16664,16 +16664,16 @@
             <v>0</v>
           </cell>
           <cell r="R247">
-            <v>195665.22</v>
+            <v>199032.12</v>
           </cell>
           <cell r="T247">
             <v>0</v>
           </cell>
           <cell r="U247">
-            <v>195665.22</v>
+            <v>199032.12</v>
           </cell>
           <cell r="V247">
-            <v>-19573.22</v>
+            <v>-22940.119999999995</v>
           </cell>
         </row>
         <row r="248">
@@ -17597,7 +17597,7 @@
             <v>190731.34</v>
           </cell>
           <cell r="O265">
-            <v>0</v>
+            <v>3048.7</v>
           </cell>
           <cell r="P265">
             <v>0</v>
@@ -17606,16 +17606,16 @@
             <v>0</v>
           </cell>
           <cell r="R265">
-            <v>190731.34</v>
+            <v>193780.04</v>
           </cell>
           <cell r="T265">
             <v>0</v>
           </cell>
           <cell r="U265">
-            <v>190731.34</v>
+            <v>193780.04</v>
           </cell>
           <cell r="V265">
-            <v>-122439.84</v>
+            <v>-125488.54000000001</v>
           </cell>
         </row>
         <row r="266">
@@ -17650,7 +17650,7 @@
             <v>30855.879999999997</v>
           </cell>
           <cell r="O266">
-            <v>0</v>
+            <v>3048.7</v>
           </cell>
           <cell r="P266">
             <v>0</v>
@@ -17659,16 +17659,16 @@
             <v>0</v>
           </cell>
           <cell r="R266">
-            <v>30855.879999999997</v>
+            <v>33904.579999999994</v>
           </cell>
           <cell r="T266">
             <v>0</v>
           </cell>
           <cell r="U266">
-            <v>30855.879999999997</v>
+            <v>33904.579999999994</v>
           </cell>
           <cell r="V266">
-            <v>-9929.3799999999974</v>
+            <v>-12978.079999999994</v>
           </cell>
         </row>
         <row r="267">
@@ -19372,7 +19372,7 @@
             <v>1069012.3299999998</v>
           </cell>
           <cell r="N299">
-            <v>1376540.3</v>
+            <v>1376606.2200000002</v>
           </cell>
           <cell r="O299">
             <v>0</v>
@@ -19384,16 +19384,16 @@
             <v>0</v>
           </cell>
           <cell r="R299">
-            <v>1376540.3</v>
+            <v>1376606.2200000002</v>
           </cell>
           <cell r="T299">
             <v>0</v>
           </cell>
           <cell r="U299">
-            <v>1376540.3</v>
+            <v>1376606.2200000002</v>
           </cell>
           <cell r="V299">
-            <v>-307527.9700000002</v>
+            <v>-307593.89000000036</v>
           </cell>
         </row>
         <row r="300">
@@ -19425,7 +19425,7 @@
             <v>84611.65</v>
           </cell>
           <cell r="N300">
-            <v>123460.87999999999</v>
+            <v>123469.12</v>
           </cell>
           <cell r="O300">
             <v>0</v>
@@ -19437,16 +19437,16 @@
             <v>0</v>
           </cell>
           <cell r="R300">
-            <v>123460.87999999999</v>
+            <v>123469.12</v>
           </cell>
           <cell r="T300">
             <v>0</v>
           </cell>
           <cell r="U300">
-            <v>123460.87999999999</v>
+            <v>123469.12</v>
           </cell>
           <cell r="V300">
-            <v>-38849.229999999996</v>
+            <v>-38857.47</v>
           </cell>
         </row>
         <row r="301">
@@ -19478,7 +19478,7 @@
             <v>84614.65</v>
           </cell>
           <cell r="N301">
-            <v>108483.40999999996</v>
+            <v>108491.64999999997</v>
           </cell>
           <cell r="O301">
             <v>0</v>
@@ -19490,16 +19490,16 @@
             <v>0</v>
           </cell>
           <cell r="R301">
-            <v>108483.40999999996</v>
+            <v>108491.64999999997</v>
           </cell>
           <cell r="T301">
             <v>0</v>
           </cell>
           <cell r="U301">
-            <v>108483.40999999996</v>
+            <v>108491.64999999997</v>
           </cell>
           <cell r="V301">
-            <v>-23868.759999999966</v>
+            <v>-23876.999999999971</v>
           </cell>
         </row>
         <row r="302">
@@ -19531,7 +19531,7 @@
             <v>84614.65</v>
           </cell>
           <cell r="N302">
-            <v>94789.820000000051</v>
+            <v>94798.060000000056</v>
           </cell>
           <cell r="O302">
             <v>0</v>
@@ -19543,16 +19543,16 @@
             <v>0</v>
           </cell>
           <cell r="R302">
-            <v>94789.820000000051</v>
+            <v>94798.060000000056</v>
           </cell>
           <cell r="T302">
             <v>0</v>
           </cell>
           <cell r="U302">
-            <v>94789.820000000051</v>
+            <v>94798.060000000056</v>
           </cell>
           <cell r="V302">
-            <v>-10175.170000000056</v>
+            <v>-10183.410000000062</v>
           </cell>
         </row>
         <row r="303">
@@ -19584,7 +19584,7 @@
             <v>84614.65</v>
           </cell>
           <cell r="N303">
-            <v>108080.56000000001</v>
+            <v>108088.80000000002</v>
           </cell>
           <cell r="O303">
             <v>0</v>
@@ -19596,16 +19596,16 @@
             <v>0</v>
           </cell>
           <cell r="R303">
-            <v>108080.56000000001</v>
+            <v>108088.80000000002</v>
           </cell>
           <cell r="T303">
             <v>0</v>
           </cell>
           <cell r="U303">
-            <v>108080.56000000001</v>
+            <v>108088.80000000002</v>
           </cell>
           <cell r="V303">
-            <v>-23465.910000000018</v>
+            <v>-23474.150000000023</v>
           </cell>
         </row>
         <row r="304">
@@ -19637,7 +19637,7 @@
             <v>71683.02</v>
           </cell>
           <cell r="N304">
-            <v>104490.58000000006</v>
+            <v>104498.82000000007</v>
           </cell>
           <cell r="O304">
             <v>0</v>
@@ -19649,16 +19649,16 @@
             <v>0</v>
           </cell>
           <cell r="R304">
-            <v>104490.58000000006</v>
+            <v>104498.82000000007</v>
           </cell>
           <cell r="T304">
             <v>0</v>
           </cell>
           <cell r="U304">
-            <v>104490.58000000006</v>
+            <v>104498.82000000007</v>
           </cell>
           <cell r="V304">
-            <v>-32807.560000000056</v>
+            <v>-32815.800000000061</v>
           </cell>
         </row>
         <row r="305">
@@ -19690,7 +19690,7 @@
             <v>71683.02</v>
           </cell>
           <cell r="N305">
-            <v>103740.25999999998</v>
+            <v>103748.49999999999</v>
           </cell>
           <cell r="O305">
             <v>0</v>
@@ -19702,16 +19702,16 @@
             <v>0</v>
           </cell>
           <cell r="R305">
-            <v>103740.25999999998</v>
+            <v>103748.49999999999</v>
           </cell>
           <cell r="T305">
             <v>0</v>
           </cell>
           <cell r="U305">
-            <v>103740.25999999998</v>
+            <v>103748.49999999999</v>
           </cell>
           <cell r="V305">
-            <v>-32057.239999999976</v>
+            <v>-32065.479999999981</v>
           </cell>
         </row>
         <row r="306">
@@ -19743,7 +19743,7 @@
             <v>71683.02</v>
           </cell>
           <cell r="N306">
-            <v>101553.39999999998</v>
+            <v>101561.63999999998</v>
           </cell>
           <cell r="O306">
             <v>0</v>
@@ -19755,16 +19755,16 @@
             <v>0</v>
           </cell>
           <cell r="R306">
-            <v>101553.39999999998</v>
+            <v>101561.63999999998</v>
           </cell>
           <cell r="T306">
             <v>0</v>
           </cell>
           <cell r="U306">
-            <v>101553.39999999998</v>
+            <v>101561.63999999998</v>
           </cell>
           <cell r="V306">
-            <v>-29870.379999999976</v>
+            <v>-29878.619999999981</v>
           </cell>
         </row>
         <row r="307">
@@ -19796,7 +19796,7 @@
             <v>71683.02</v>
           </cell>
           <cell r="N307">
-            <v>89909.929999999978</v>
+            <v>89918.169999999984</v>
           </cell>
           <cell r="O307">
             <v>0</v>
@@ -19808,16 +19808,16 @@
             <v>0</v>
           </cell>
           <cell r="R307">
-            <v>89909.929999999978</v>
+            <v>89918.169999999984</v>
           </cell>
           <cell r="T307">
             <v>0</v>
           </cell>
           <cell r="U307">
-            <v>89909.929999999978</v>
+            <v>89918.169999999984</v>
           </cell>
           <cell r="V307">
-            <v>-18226.909999999974</v>
+            <v>-18235.14999999998</v>
           </cell>
         </row>
         <row r="308">
@@ -22133,28 +22133,28 @@
             <v>1150847.8699999999</v>
           </cell>
           <cell r="N352">
-            <v>796464.32000000007</v>
+            <v>901606.7300000001</v>
           </cell>
           <cell r="O352">
-            <v>44749.82</v>
+            <v>96522.340000000011</v>
           </cell>
           <cell r="P352">
-            <v>68303.25</v>
+            <v>136235.72</v>
           </cell>
           <cell r="Q352">
-            <v>656.45</v>
+            <v>36692.490000000005</v>
           </cell>
           <cell r="R352">
-            <v>910173.84</v>
+            <v>1171057.28</v>
           </cell>
           <cell r="T352">
-            <v>240674.02999999997</v>
+            <v>187540.56</v>
           </cell>
           <cell r="U352">
-            <v>1150847.8699999999</v>
+            <v>1358597.84</v>
           </cell>
           <cell r="V352">
-            <v>0</v>
+            <v>-207749.9700000002</v>
           </cell>
         </row>
         <row r="353">
@@ -22174,28 +22174,28 @@
             <v>1150847.8699999999</v>
           </cell>
           <cell r="N353">
-            <v>796464.32000000007</v>
+            <v>901606.7300000001</v>
           </cell>
           <cell r="O353">
-            <v>44749.82</v>
+            <v>96522.340000000011</v>
           </cell>
           <cell r="P353">
-            <v>68303.25</v>
+            <v>136235.72</v>
           </cell>
           <cell r="Q353">
-            <v>656.45</v>
+            <v>36692.490000000005</v>
           </cell>
           <cell r="R353">
-            <v>910173.84</v>
+            <v>1171057.28</v>
           </cell>
           <cell r="T353">
-            <v>240674.02999999997</v>
+            <v>187540.56</v>
           </cell>
           <cell r="U353">
-            <v>1150847.8699999999</v>
+            <v>1358597.84</v>
           </cell>
           <cell r="V353">
-            <v>0</v>
+            <v>-207749.9700000002</v>
           </cell>
         </row>
         <row r="354">
@@ -22227,28 +22227,28 @@
             <v>377991.09</v>
           </cell>
           <cell r="N354">
-            <v>320437.99</v>
+            <v>332587.75000000006</v>
           </cell>
           <cell r="O354">
-            <v>2721.15</v>
+            <v>5848.46</v>
           </cell>
           <cell r="P354">
-            <v>0.02</v>
+            <v>22500.02</v>
           </cell>
           <cell r="Q354">
-            <v>557.98</v>
+            <v>28086.99</v>
           </cell>
           <cell r="R354">
-            <v>323717.14</v>
+            <v>389023.22000000009</v>
           </cell>
           <cell r="T354">
-            <v>54273.950000000012</v>
+            <v>0</v>
           </cell>
           <cell r="U354">
-            <v>377991.09</v>
+            <v>389023.22000000009</v>
           </cell>
           <cell r="V354">
-            <v>0</v>
+            <v>-11032.130000000063</v>
           </cell>
         </row>
         <row r="355">
@@ -22280,28 +22280,28 @@
             <v>303742.84000000003</v>
           </cell>
           <cell r="N355">
-            <v>237933.51</v>
+            <v>275263.51</v>
           </cell>
           <cell r="O355">
-            <v>37330</v>
+            <v>0</v>
           </cell>
           <cell r="P355">
-            <v>19304.899999999998</v>
+            <v>41803.22</v>
           </cell>
           <cell r="Q355">
-            <v>0</v>
+            <v>4779.99</v>
           </cell>
           <cell r="R355">
-            <v>294568.41000000003</v>
+            <v>321846.71999999997</v>
           </cell>
           <cell r="T355">
-            <v>9174.429999999993</v>
+            <v>0</v>
           </cell>
           <cell r="U355">
-            <v>303742.84000000003</v>
+            <v>321846.71999999997</v>
           </cell>
           <cell r="V355">
-            <v>0</v>
+            <v>-18103.879999999946</v>
           </cell>
         </row>
         <row r="356">
@@ -22333,28 +22333,28 @@
             <v>80998.09</v>
           </cell>
           <cell r="N356">
-            <v>50266.5</v>
+            <v>101230.48000000001</v>
           </cell>
           <cell r="O356">
-            <v>0</v>
+            <v>83408.03</v>
           </cell>
           <cell r="P356">
-            <v>0.01</v>
+            <v>24399.059999999998</v>
           </cell>
           <cell r="Q356">
             <v>0</v>
           </cell>
           <cell r="R356">
-            <v>50266.51</v>
+            <v>209037.57</v>
           </cell>
           <cell r="T356">
-            <v>30731.579999999994</v>
+            <v>0</v>
           </cell>
           <cell r="U356">
-            <v>80998.09</v>
+            <v>209037.57</v>
           </cell>
           <cell r="V356">
-            <v>0</v>
+            <v>-128039.48000000001</v>
           </cell>
         </row>
         <row r="357">
@@ -22386,22 +22386,22 @@
             <v>132296.88</v>
           </cell>
           <cell r="N357">
-            <v>67849.75</v>
+            <v>72548.42</v>
           </cell>
           <cell r="O357">
-            <v>4698.67</v>
+            <v>0</v>
           </cell>
           <cell r="P357">
             <v>29998.32</v>
           </cell>
           <cell r="Q357">
-            <v>0</v>
+            <v>3727.04</v>
           </cell>
           <cell r="R357">
-            <v>102546.73999999999</v>
+            <v>106273.77999999998</v>
           </cell>
           <cell r="T357">
-            <v>29750.140000000014</v>
+            <v>26023.10000000002</v>
           </cell>
           <cell r="U357">
             <v>132296.88</v>
@@ -22445,16 +22445,16 @@
             <v>0</v>
           </cell>
           <cell r="P358">
-            <v>0</v>
+            <v>5000</v>
           </cell>
           <cell r="Q358">
             <v>98.47</v>
           </cell>
           <cell r="R358">
-            <v>32156.440000000002</v>
+            <v>37156.44</v>
           </cell>
           <cell r="T358">
-            <v>50191.619999999995</v>
+            <v>45191.619999999995</v>
           </cell>
           <cell r="U358">
             <v>82348.06</v>
@@ -22548,25 +22548,25 @@
             <v>78822.42</v>
           </cell>
           <cell r="O360">
-            <v>0</v>
+            <v>6465.85</v>
           </cell>
           <cell r="P360">
-            <v>19000</v>
+            <v>12535.1</v>
           </cell>
           <cell r="Q360">
             <v>0</v>
           </cell>
           <cell r="R360">
-            <v>97822.42</v>
+            <v>97823.37000000001</v>
           </cell>
           <cell r="T360">
-            <v>-50573.53</v>
+            <v>0</v>
           </cell>
           <cell r="U360">
-            <v>47248.89</v>
+            <v>97823.37000000001</v>
           </cell>
           <cell r="V360">
-            <v>0</v>
+            <v>-50574.48000000001</v>
           </cell>
         </row>
         <row r="361">
@@ -22601,7 +22601,7 @@
             <v>9096.18</v>
           </cell>
           <cell r="O361">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="P361">
             <v>0</v>
@@ -22610,10 +22610,10 @@
             <v>0</v>
           </cell>
           <cell r="R361">
-            <v>9096.18</v>
+            <v>9896.18</v>
           </cell>
           <cell r="T361">
-            <v>9128.39</v>
+            <v>8328.39</v>
           </cell>
           <cell r="U361">
             <v>18224.57</v>
@@ -22639,28 +22639,28 @@
             <v>261893.82</v>
           </cell>
           <cell r="N362">
-            <v>119523.54</v>
+            <v>166807.29999999999</v>
           </cell>
           <cell r="O362">
             <v>0</v>
           </cell>
           <cell r="P362">
-            <v>114451.87</v>
+            <v>60024.62000000001</v>
           </cell>
           <cell r="Q362">
             <v>0</v>
           </cell>
           <cell r="R362">
-            <v>233975.40999999997</v>
+            <v>226831.91999999998</v>
           </cell>
           <cell r="T362">
             <v>0</v>
           </cell>
           <cell r="U362">
-            <v>233975.40999999997</v>
+            <v>226831.91999999998</v>
           </cell>
           <cell r="V362">
-            <v>27918.410000000033</v>
+            <v>35061.900000000023</v>
           </cell>
         </row>
         <row r="363">
@@ -22680,28 +22680,28 @@
             <v>261893.82</v>
           </cell>
           <cell r="N363">
-            <v>119523.54</v>
+            <v>166807.29999999999</v>
           </cell>
           <cell r="O363">
             <v>0</v>
           </cell>
           <cell r="P363">
-            <v>114451.87</v>
+            <v>60024.62000000001</v>
           </cell>
           <cell r="Q363">
             <v>0</v>
           </cell>
           <cell r="R363">
-            <v>233975.40999999997</v>
+            <v>226831.91999999998</v>
           </cell>
           <cell r="T363">
             <v>0</v>
           </cell>
           <cell r="U363">
-            <v>233975.40999999997</v>
+            <v>226831.91999999998</v>
           </cell>
           <cell r="V363">
-            <v>27918.410000000033</v>
+            <v>35061.900000000023</v>
           </cell>
         </row>
         <row r="364">
@@ -22786,28 +22786,28 @@
             <v>101247.61</v>
           </cell>
           <cell r="N365">
-            <v>75376.929999999993</v>
+            <v>95108.87</v>
           </cell>
           <cell r="O365">
             <v>0</v>
           </cell>
           <cell r="P365">
-            <v>19740.53</v>
+            <v>9.51</v>
           </cell>
           <cell r="Q365">
             <v>0</v>
           </cell>
           <cell r="R365">
-            <v>95117.459999999992</v>
+            <v>95118.37999999999</v>
           </cell>
           <cell r="T365">
             <v>0</v>
           </cell>
           <cell r="U365">
-            <v>95117.459999999992</v>
+            <v>95118.37999999999</v>
           </cell>
           <cell r="V365">
-            <v>6130.1500000000087</v>
+            <v>6129.2300000000105</v>
           </cell>
         </row>
         <row r="366">
@@ -22839,28 +22839,28 @@
             <v>87747.93</v>
           </cell>
           <cell r="N366">
-            <v>12927.330000000002</v>
+            <v>40479.15</v>
           </cell>
           <cell r="O366">
             <v>0</v>
           </cell>
           <cell r="P366">
-            <v>52692.929999999993</v>
+            <v>17996.7</v>
           </cell>
           <cell r="Q366">
             <v>0</v>
           </cell>
           <cell r="R366">
-            <v>65620.259999999995</v>
+            <v>58475.850000000006</v>
           </cell>
           <cell r="T366">
             <v>0</v>
           </cell>
           <cell r="U366">
-            <v>65620.259999999995</v>
+            <v>58475.850000000006</v>
           </cell>
           <cell r="V366">
-            <v>22127.67</v>
+            <v>29272.079999999987</v>
           </cell>
         </row>
         <row r="367">
@@ -22933,22 +22933,22 @@
             <v>1142748.06</v>
           </cell>
           <cell r="N368">
-            <v>761608.56000000017</v>
+            <v>768178.99000000022</v>
           </cell>
           <cell r="O368">
-            <v>12281.240000000002</v>
+            <v>11913.74</v>
           </cell>
           <cell r="P368">
-            <v>146526.44999999998</v>
+            <v>152834.26999999999</v>
           </cell>
           <cell r="Q368">
-            <v>6869.08</v>
+            <v>11490.25</v>
           </cell>
           <cell r="R368">
-            <v>927285.33000000007</v>
+            <v>944417.25000000023</v>
           </cell>
           <cell r="T368">
-            <v>374979.93999999994</v>
+            <v>357848.0199999999</v>
           </cell>
           <cell r="U368">
             <v>1302265.27</v>
@@ -22974,22 +22974,22 @@
             <v>1142748.06</v>
           </cell>
           <cell r="N369">
-            <v>761608.56000000017</v>
+            <v>768178.99000000022</v>
           </cell>
           <cell r="O369">
-            <v>12281.240000000002</v>
+            <v>11913.74</v>
           </cell>
           <cell r="P369">
-            <v>146526.44999999998</v>
+            <v>152834.26999999999</v>
           </cell>
           <cell r="Q369">
-            <v>6869.08</v>
+            <v>11490.25</v>
           </cell>
           <cell r="R369">
-            <v>927285.33000000007</v>
+            <v>944417.25000000023</v>
           </cell>
           <cell r="T369">
-            <v>374979.93999999994</v>
+            <v>357848.0199999999</v>
           </cell>
           <cell r="U369">
             <v>1302265.27</v>
@@ -23033,16 +23033,16 @@
             <v>0</v>
           </cell>
           <cell r="P370">
-            <v>14326.16</v>
+            <v>17012.439999999999</v>
           </cell>
           <cell r="Q370">
             <v>0</v>
           </cell>
           <cell r="R370">
-            <v>70496.02</v>
+            <v>73182.3</v>
           </cell>
           <cell r="T370">
-            <v>82111.349999999933</v>
+            <v>79425.069999999934</v>
           </cell>
           <cell r="U370">
             <v>152607.36999999994</v>
@@ -23080,28 +23080,28 @@
             <v>477888.73</v>
           </cell>
           <cell r="N371">
-            <v>323858.03000000009</v>
+            <v>329557.73000000016</v>
           </cell>
           <cell r="O371">
-            <v>10539.78</v>
+            <v>10540.67</v>
           </cell>
           <cell r="P371">
-            <v>30810.100000000002</v>
+            <v>32538.939999999991</v>
           </cell>
           <cell r="Q371">
-            <v>6341</v>
+            <v>7306.13</v>
           </cell>
           <cell r="R371">
-            <v>371548.91000000009</v>
+            <v>379943.47000000015</v>
           </cell>
           <cell r="T371">
-            <v>102322.32000000007</v>
+            <v>93927.759999999951</v>
           </cell>
           <cell r="U371">
-            <v>473871.23000000016</v>
+            <v>473871.2300000001</v>
           </cell>
           <cell r="V371">
-            <v>4017.4999999998254</v>
+            <v>4017.4999999998836</v>
           </cell>
         </row>
         <row r="372">
@@ -23133,22 +23133,22 @@
             <v>321292.43</v>
           </cell>
           <cell r="N372">
-            <v>170870.53000000003</v>
+            <v>171741.26000000004</v>
           </cell>
           <cell r="O372">
-            <v>1741.46</v>
+            <v>1373.07</v>
           </cell>
           <cell r="P372">
             <v>0.01</v>
           </cell>
           <cell r="Q372">
-            <v>528.08000000000004</v>
+            <v>4184.12</v>
           </cell>
           <cell r="R372">
-            <v>173140.08000000002</v>
+            <v>177298.46000000005</v>
           </cell>
           <cell r="T372">
-            <v>148152.35000000003</v>
+            <v>143993.97</v>
           </cell>
           <cell r="U372">
             <v>321292.43000000005</v>
@@ -23192,16 +23192,16 @@
             <v>0</v>
           </cell>
           <cell r="P373">
-            <v>10093.89</v>
+            <v>11986.59</v>
           </cell>
           <cell r="Q373">
             <v>0</v>
           </cell>
           <cell r="R373">
-            <v>69802.679999999993</v>
+            <v>71695.38</v>
           </cell>
           <cell r="T373">
-            <v>42393.919999999955</v>
+            <v>40501.219999999943</v>
           </cell>
           <cell r="U373">
             <v>112196.59999999995</v>
@@ -23333,28 +23333,28 @@
             <v>532432.98</v>
           </cell>
           <cell r="N376">
-            <v>112697.45999999999</v>
+            <v>137717.29999999999</v>
           </cell>
           <cell r="O376">
-            <v>0</v>
+            <v>34510</v>
           </cell>
           <cell r="P376">
-            <v>194181.90999999997</v>
+            <v>160631.90000000002</v>
           </cell>
           <cell r="Q376">
-            <v>3760.5</v>
+            <v>3972.86</v>
           </cell>
           <cell r="R376">
-            <v>310639.87</v>
+            <v>336832.06</v>
           </cell>
           <cell r="T376">
-            <v>221793.11000000007</v>
+            <v>238753.96000000002</v>
           </cell>
           <cell r="U376">
-            <v>532432.9800000001</v>
+            <v>575586.02</v>
           </cell>
           <cell r="V376">
-            <v>0</v>
+            <v>-43153.040000000037</v>
           </cell>
         </row>
         <row r="377">
@@ -23374,28 +23374,28 @@
             <v>373488.78</v>
           </cell>
           <cell r="N377">
-            <v>82004.459999999992</v>
+            <v>107024.29999999999</v>
           </cell>
           <cell r="O377">
-            <v>0</v>
+            <v>34510</v>
           </cell>
           <cell r="P377">
-            <v>140031.41999999998</v>
+            <v>106481.46</v>
           </cell>
           <cell r="Q377">
-            <v>3760.5</v>
+            <v>3972.86</v>
           </cell>
           <cell r="R377">
-            <v>225796.37999999998</v>
+            <v>251988.62</v>
           </cell>
           <cell r="T377">
-            <v>147692.40000000005</v>
+            <v>135392.80000000002</v>
           </cell>
           <cell r="U377">
-            <v>373488.78</v>
+            <v>387381.42000000004</v>
           </cell>
           <cell r="V377">
-            <v>0</v>
+            <v>-13892.640000000014</v>
           </cell>
         </row>
         <row r="378">
@@ -23427,22 +23427,22 @@
             <v>317583</v>
           </cell>
           <cell r="N378">
-            <v>62058.400000000001</v>
+            <v>85880.4</v>
           </cell>
           <cell r="O378">
-            <v>0</v>
+            <v>33550</v>
           </cell>
           <cell r="P378">
-            <v>99151.409999999974</v>
+            <v>65601.460000000006</v>
           </cell>
           <cell r="Q378">
             <v>0</v>
           </cell>
           <cell r="R378">
-            <v>161209.80999999997</v>
+            <v>185031.86</v>
           </cell>
           <cell r="T378">
-            <v>156373.19000000003</v>
+            <v>132551.14000000001</v>
           </cell>
           <cell r="U378">
             <v>317583</v>
@@ -23480,28 +23480,28 @@
             <v>52640</v>
           </cell>
           <cell r="N379">
-            <v>19521.939999999999</v>
+            <v>20719.78</v>
           </cell>
           <cell r="O379">
-            <v>0</v>
+            <v>960</v>
           </cell>
           <cell r="P379">
-            <v>40880.009999999995</v>
+            <v>40880</v>
           </cell>
           <cell r="Q379">
-            <v>3760.5</v>
+            <v>3972.86</v>
           </cell>
           <cell r="R379">
-            <v>64162.45</v>
+            <v>66532.639999999999</v>
           </cell>
           <cell r="T379">
-            <v>-11522.449999999997</v>
+            <v>0</v>
           </cell>
           <cell r="U379">
-            <v>52640</v>
+            <v>66532.639999999999</v>
           </cell>
           <cell r="V379">
-            <v>0</v>
+            <v>-13892.64</v>
           </cell>
         </row>
         <row r="380">
@@ -23580,22 +23580,22 @@
             <v>0</v>
           </cell>
           <cell r="P381">
-            <v>54150.489999999976</v>
+            <v>54150.44</v>
           </cell>
           <cell r="Q381">
             <v>0</v>
           </cell>
           <cell r="R381">
-            <v>84843.489999999976</v>
+            <v>84843.44</v>
           </cell>
           <cell r="T381">
-            <v>-29260.449999999975</v>
+            <v>0</v>
           </cell>
           <cell r="U381">
-            <v>55583.040000000001</v>
+            <v>84843.44</v>
           </cell>
           <cell r="V381">
-            <v>0</v>
+            <v>-29260.400000000001</v>
           </cell>
         </row>
         <row r="382">
@@ -23633,22 +23633,22 @@
             <v>0</v>
           </cell>
           <cell r="P382">
-            <v>54150.489999999976</v>
+            <v>54150.44</v>
           </cell>
           <cell r="Q382">
             <v>0</v>
           </cell>
           <cell r="R382">
-            <v>84843.489999999976</v>
+            <v>84843.44</v>
           </cell>
           <cell r="T382">
-            <v>-29260.449999999975</v>
+            <v>0</v>
           </cell>
           <cell r="U382">
-            <v>55583.040000000001</v>
+            <v>84843.44</v>
           </cell>
           <cell r="V382">
-            <v>0</v>
+            <v>-29260.400000000001</v>
           </cell>
         </row>
         <row r="383">
@@ -23762,10 +23762,10 @@
             <v>622914.20999999985</v>
           </cell>
           <cell r="N385">
-            <v>343537.91</v>
+            <v>372223.73</v>
           </cell>
           <cell r="O385">
-            <v>28100.98</v>
+            <v>9862.24</v>
           </cell>
           <cell r="P385">
             <v>14396.32</v>
@@ -23774,16 +23774,16 @@
             <v>0</v>
           </cell>
           <cell r="R385">
-            <v>386035.20999999996</v>
+            <v>396482.29</v>
           </cell>
           <cell r="T385">
-            <v>147474.44</v>
+            <v>137067.35999999999</v>
           </cell>
           <cell r="U385">
-            <v>533509.64999999991</v>
+            <v>533549.64999999991</v>
           </cell>
           <cell r="V385">
-            <v>89404.559999999939</v>
+            <v>89364.559999999939</v>
           </cell>
         </row>
         <row r="386">
@@ -23803,10 +23803,10 @@
             <v>88584.17</v>
           </cell>
           <cell r="N386">
-            <v>39396.39</v>
+            <v>68074.579999999987</v>
           </cell>
           <cell r="O386">
-            <v>28093.35</v>
+            <v>7429.95</v>
           </cell>
           <cell r="P386">
             <v>14396.32</v>
@@ -23815,10 +23815,10 @@
             <v>0</v>
           </cell>
           <cell r="R386">
-            <v>81886.06</v>
+            <v>89900.849999999977</v>
           </cell>
           <cell r="T386">
-            <v>23051.340000000004</v>
+            <v>15036.55000000001</v>
           </cell>
           <cell r="U386">
             <v>104937.4</v>
@@ -23856,10 +23856,10 @@
             <v>11175.95</v>
           </cell>
           <cell r="N387">
-            <v>14174.49</v>
+            <v>27529.18</v>
           </cell>
           <cell r="O387">
-            <v>13354.689999999999</v>
+            <v>0</v>
           </cell>
           <cell r="P387">
             <v>0</v>
@@ -23909,10 +23909,10 @@
             <v>77408.22</v>
           </cell>
           <cell r="N388">
-            <v>25221.9</v>
+            <v>40545.399999999994</v>
           </cell>
           <cell r="O388">
-            <v>14738.66</v>
+            <v>7429.95</v>
           </cell>
           <cell r="P388">
             <v>14396.32</v>
@@ -23921,10 +23921,10 @@
             <v>0</v>
           </cell>
           <cell r="R388">
-            <v>54356.88</v>
+            <v>62371.669999999991</v>
           </cell>
           <cell r="T388">
-            <v>23051.340000000004</v>
+            <v>15036.55000000001</v>
           </cell>
           <cell r="U388">
             <v>77408.22</v>
@@ -25796,7 +25796,7 @@
             <v>0</v>
           </cell>
           <cell r="O424">
-            <v>0</v>
+            <v>2392.29</v>
           </cell>
           <cell r="P424">
             <v>0</v>
@@ -25805,10 +25805,10 @@
             <v>0</v>
           </cell>
           <cell r="R424">
-            <v>0</v>
+            <v>2392.29</v>
           </cell>
           <cell r="T424">
-            <v>57856.97</v>
+            <v>55464.68</v>
           </cell>
           <cell r="U424">
             <v>57856.97</v>
@@ -25902,7 +25902,7 @@
             <v>0</v>
           </cell>
           <cell r="O426">
-            <v>0</v>
+            <v>2392.29</v>
           </cell>
           <cell r="P426">
             <v>0</v>
@@ -25911,10 +25911,10 @@
             <v>0</v>
           </cell>
           <cell r="R426">
-            <v>0</v>
+            <v>2392.29</v>
           </cell>
           <cell r="T426">
-            <v>57856.97</v>
+            <v>55464.68</v>
           </cell>
           <cell r="U426">
             <v>57856.97</v>
@@ -28778,10 +28778,10 @@
             <v>8024.6399999999994</v>
           </cell>
           <cell r="N481">
-            <v>3400.99</v>
+            <v>3408.62</v>
           </cell>
           <cell r="O481">
-            <v>7.63</v>
+            <v>40</v>
           </cell>
           <cell r="P481">
             <v>0</v>
@@ -28790,16 +28790,16 @@
             <v>0</v>
           </cell>
           <cell r="R481">
-            <v>3408.62</v>
+            <v>3448.62</v>
           </cell>
           <cell r="T481">
             <v>0</v>
           </cell>
           <cell r="U481">
-            <v>3408.62</v>
+            <v>3448.62</v>
           </cell>
           <cell r="V481">
-            <v>4616.0199999999995</v>
+            <v>4576.0199999999995</v>
           </cell>
         </row>
         <row r="482">
@@ -29629,7 +29629,7 @@
             <v>247.86</v>
           </cell>
           <cell r="O497">
-            <v>0</v>
+            <v>20</v>
           </cell>
           <cell r="P497">
             <v>0</v>
@@ -29638,16 +29638,16 @@
             <v>0</v>
           </cell>
           <cell r="R497">
-            <v>247.86</v>
+            <v>267.86</v>
           </cell>
           <cell r="T497">
             <v>0</v>
           </cell>
           <cell r="U497">
-            <v>247.86</v>
+            <v>267.86</v>
           </cell>
           <cell r="V497">
-            <v>-247.86</v>
+            <v>-267.86</v>
           </cell>
         </row>
         <row r="498">
@@ -29679,10 +29679,10 @@
             <v>0</v>
           </cell>
           <cell r="N498">
-            <v>48.6</v>
+            <v>56.230000000000004</v>
           </cell>
           <cell r="O498">
-            <v>7.63</v>
+            <v>20</v>
           </cell>
           <cell r="P498">
             <v>0</v>
@@ -29691,16 +29691,16 @@
             <v>0</v>
           </cell>
           <cell r="R498">
-            <v>56.230000000000004</v>
+            <v>76.23</v>
           </cell>
           <cell r="T498">
             <v>0</v>
           </cell>
           <cell r="U498">
-            <v>56.230000000000004</v>
+            <v>76.23</v>
           </cell>
           <cell r="V498">
-            <v>-56.230000000000004</v>
+            <v>-76.23</v>
           </cell>
         </row>
         <row r="499">
@@ -32758,10 +32758,10 @@
             <v>734722.6399999999</v>
           </cell>
           <cell r="N557">
-            <v>5652.78</v>
+            <v>46720.409999999996</v>
           </cell>
           <cell r="O557">
-            <v>48723.82</v>
+            <v>11040.96</v>
           </cell>
           <cell r="P557">
             <v>0</v>
@@ -32770,10 +32770,10 @@
             <v>0</v>
           </cell>
           <cell r="R557">
-            <v>54376.6</v>
+            <v>57761.369999999995</v>
           </cell>
           <cell r="T557">
-            <v>305791.93</v>
+            <v>302407.15999999997</v>
           </cell>
           <cell r="U557">
             <v>360168.52999999997</v>
@@ -32799,7 +32799,7 @@
             <v>670248.93999999994</v>
           </cell>
           <cell r="N558">
-            <v>27</v>
+            <v>3411.77</v>
           </cell>
           <cell r="O558">
             <v>0</v>
@@ -32811,10 +32811,10 @@
             <v>0</v>
           </cell>
           <cell r="R558">
-            <v>27</v>
+            <v>3411.77</v>
           </cell>
           <cell r="T558">
-            <v>305455.93</v>
+            <v>302071.15999999997</v>
           </cell>
           <cell r="U558">
             <v>305482.93</v>
@@ -32958,7 +32958,7 @@
             <v>134162.79999999999</v>
           </cell>
           <cell r="N561">
-            <v>0</v>
+            <v>3384.77</v>
           </cell>
           <cell r="O561">
             <v>0</v>
@@ -32970,10 +32970,10 @@
             <v>0</v>
           </cell>
           <cell r="R561">
-            <v>0</v>
+            <v>3384.77</v>
           </cell>
           <cell r="T561">
-            <v>79024.679999999993</v>
+            <v>75639.909999999989</v>
           </cell>
           <cell r="U561">
             <v>79024.679999999993</v>
@@ -33105,10 +33105,10 @@
             <v>64473.700000000004</v>
           </cell>
           <cell r="N564">
-            <v>5625.78</v>
+            <v>43308.639999999999</v>
           </cell>
           <cell r="O564">
-            <v>48723.82</v>
+            <v>11040.96</v>
           </cell>
           <cell r="P564">
             <v>0</v>
@@ -33158,10 +33158,10 @@
             <v>23414.65</v>
           </cell>
           <cell r="N565">
-            <v>0</v>
+            <v>7992.57</v>
           </cell>
           <cell r="O565">
-            <v>7992.57</v>
+            <v>0</v>
           </cell>
           <cell r="P565">
             <v>0</v>
@@ -33211,10 +33211,10 @@
             <v>40723.050000000003</v>
           </cell>
           <cell r="N566">
-            <v>5625.78</v>
+            <v>35316.07</v>
           </cell>
           <cell r="O566">
-            <v>40731.25</v>
+            <v>11040.96</v>
           </cell>
           <cell r="P566">
             <v>0</v>
@@ -33305,28 +33305,28 @@
             <v>1043744.0400000002</v>
           </cell>
           <cell r="N568">
-            <v>617578.93999999994</v>
+            <v>659128.20000000007</v>
           </cell>
           <cell r="O568">
-            <v>285770.40000000002</v>
+            <v>286886.40000000002</v>
           </cell>
           <cell r="P568">
-            <v>80295.999999999985</v>
+            <v>67378.709999999992</v>
           </cell>
           <cell r="Q568">
-            <v>281.10000000000002</v>
+            <v>0</v>
           </cell>
           <cell r="R568">
-            <v>983926.44</v>
+            <v>1013393.31</v>
           </cell>
           <cell r="T568">
-            <v>40927.770000000004</v>
+            <v>30671.969999999998</v>
           </cell>
           <cell r="U568">
-            <v>1024854.21</v>
+            <v>1044065.28</v>
           </cell>
           <cell r="V568">
-            <v>18889.830000000191</v>
+            <v>-321.23999999987427</v>
           </cell>
         </row>
         <row r="569">
@@ -33346,28 +33346,28 @@
             <v>1043744.0400000002</v>
           </cell>
           <cell r="N569">
-            <v>617578.93999999994</v>
+            <v>659128.20000000007</v>
           </cell>
           <cell r="O569">
-            <v>285770.40000000002</v>
+            <v>286886.40000000002</v>
           </cell>
           <cell r="P569">
-            <v>80295.999999999985</v>
+            <v>67378.709999999992</v>
           </cell>
           <cell r="Q569">
-            <v>281.10000000000002</v>
+            <v>0</v>
           </cell>
           <cell r="R569">
-            <v>983926.44</v>
+            <v>1013393.31</v>
           </cell>
           <cell r="T569">
-            <v>40927.770000000004</v>
+            <v>30671.969999999998</v>
           </cell>
           <cell r="U569">
-            <v>1024854.21</v>
+            <v>1044065.28</v>
           </cell>
           <cell r="V569">
-            <v>18889.830000000191</v>
+            <v>-321.23999999987427</v>
           </cell>
         </row>
         <row r="570">
@@ -33508,19 +33508,19 @@
             <v>43021.740000000005</v>
           </cell>
           <cell r="O572">
-            <v>0</v>
+            <v>586.4</v>
           </cell>
           <cell r="P572">
             <v>0</v>
           </cell>
           <cell r="Q572">
-            <v>281.10000000000002</v>
+            <v>0</v>
           </cell>
           <cell r="R572">
-            <v>43302.840000000004</v>
+            <v>43608.140000000007</v>
           </cell>
           <cell r="T572">
-            <v>24180.79</v>
+            <v>23875.489999999998</v>
           </cell>
           <cell r="U572">
             <v>67483.63</v>
@@ -33558,10 +33558,10 @@
             <v>22284.89</v>
           </cell>
           <cell r="N573">
-            <v>7618.01</v>
+            <v>15488.41</v>
           </cell>
           <cell r="O573">
-            <v>770.4</v>
+            <v>0</v>
           </cell>
           <cell r="P573">
             <v>0</v>
@@ -33570,10 +33570,10 @@
             <v>0</v>
           </cell>
           <cell r="R573">
-            <v>8388.41</v>
+            <v>15488.41</v>
           </cell>
           <cell r="T573">
-            <v>13896.48</v>
+            <v>6796.48</v>
           </cell>
           <cell r="U573">
             <v>22284.89</v>
@@ -33611,7 +33611,7 @@
             <v>2843.9</v>
           </cell>
           <cell r="N574">
-            <v>0</v>
+            <v>4482</v>
           </cell>
           <cell r="O574">
             <v>0</v>
@@ -33623,16 +33623,16 @@
             <v>0</v>
           </cell>
           <cell r="R574">
-            <v>0</v>
+            <v>4482</v>
           </cell>
           <cell r="T574">
-            <v>2843.9</v>
+            <v>0</v>
           </cell>
           <cell r="U574">
-            <v>2843.9</v>
+            <v>4482</v>
           </cell>
           <cell r="V574">
-            <v>0</v>
+            <v>-1638.1</v>
           </cell>
         </row>
         <row r="575">
@@ -33664,28 +33664,28 @@
             <v>31391.93</v>
           </cell>
           <cell r="N575">
-            <v>3273.07</v>
+            <v>32469.93</v>
           </cell>
           <cell r="O575">
-            <v>0</v>
+            <v>1300</v>
           </cell>
           <cell r="P575">
-            <v>28112.26</v>
+            <v>15194.97</v>
           </cell>
           <cell r="Q575">
             <v>0</v>
           </cell>
           <cell r="R575">
-            <v>31385.329999999998</v>
+            <v>48964.9</v>
           </cell>
           <cell r="T575">
-            <v>6.6000000000021828</v>
+            <v>0</v>
           </cell>
           <cell r="U575">
-            <v>31391.93</v>
+            <v>48964.9</v>
           </cell>
           <cell r="V575">
-            <v>0</v>
+            <v>-17572.97</v>
           </cell>
         </row>
         <row r="576">
@@ -33917,10 +33917,10 @@
             <v>766689.91999999993</v>
           </cell>
           <cell r="N580">
-            <v>541098.04</v>
+            <v>550896.84000000008</v>
           </cell>
           <cell r="O580">
-            <v>8758.7999999999993</v>
+            <v>0</v>
           </cell>
           <cell r="P580">
             <v>0</v>
@@ -33929,16 +33929,16 @@
             <v>0</v>
           </cell>
           <cell r="R580">
-            <v>549856.84000000008</v>
+            <v>550896.84000000008</v>
           </cell>
           <cell r="T580">
             <v>46113.64</v>
           </cell>
           <cell r="U580">
-            <v>595970.4800000001</v>
+            <v>597010.4800000001</v>
           </cell>
           <cell r="V580">
-            <v>170719.43999999983</v>
+            <v>169679.43999999983</v>
           </cell>
         </row>
         <row r="581">
@@ -34953,10 +34953,10 @@
             <v>701150.71999999997</v>
           </cell>
           <cell r="N600">
-            <v>510659.54000000004</v>
+            <v>520458.34000000008</v>
           </cell>
           <cell r="O600">
-            <v>8758.7999999999993</v>
+            <v>0</v>
           </cell>
           <cell r="P600">
             <v>0</v>
@@ -34965,16 +34965,16 @@
             <v>0</v>
           </cell>
           <cell r="R600">
-            <v>519418.34</v>
+            <v>520458.34000000008</v>
           </cell>
           <cell r="T600">
             <v>42377.1</v>
           </cell>
           <cell r="U600">
-            <v>561795.44000000006</v>
+            <v>562835.44000000006</v>
           </cell>
           <cell r="V600">
-            <v>139355.27999999991</v>
+            <v>138315.27999999991</v>
           </cell>
         </row>
         <row r="601">
@@ -35112,10 +35112,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N603">
-            <v>37207.060000000005</v>
+            <v>37820.180000000008</v>
           </cell>
           <cell r="O603">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P603">
             <v>0</v>
@@ -35165,10 +35165,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N604">
-            <v>30100.550000000003</v>
+            <v>30713.67</v>
           </cell>
           <cell r="O604">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P604">
             <v>0</v>
@@ -35177,16 +35177,16 @@
             <v>0</v>
           </cell>
           <cell r="R604">
-            <v>30713.670000000002</v>
+            <v>30713.67</v>
           </cell>
           <cell r="T604">
             <v>0</v>
           </cell>
           <cell r="U604">
-            <v>30713.670000000002</v>
+            <v>30713.67</v>
           </cell>
           <cell r="V604">
-            <v>10696.399999999998</v>
+            <v>10696.400000000001</v>
           </cell>
         </row>
         <row r="605">
@@ -35218,10 +35218,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N605">
-            <v>45919.880000000005</v>
+            <v>46533.000000000007</v>
           </cell>
           <cell r="O605">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P605">
             <v>0</v>
@@ -35271,10 +35271,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N606">
-            <v>46874.520000000004</v>
+            <v>47487.640000000007</v>
           </cell>
           <cell r="O606">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P606">
             <v>0</v>
@@ -35324,10 +35324,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N607">
-            <v>41173.429999999993</v>
+            <v>41786.549999999996</v>
           </cell>
           <cell r="O607">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P607">
             <v>0</v>
@@ -35377,10 +35377,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N608">
-            <v>40993.480000000003</v>
+            <v>41519</v>
           </cell>
           <cell r="O608">
-            <v>525.52</v>
+            <v>0</v>
           </cell>
           <cell r="P608">
             <v>0</v>
@@ -35430,10 +35430,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N609">
-            <v>30179.65</v>
+            <v>30705.170000000002</v>
           </cell>
           <cell r="O609">
-            <v>525.52</v>
+            <v>0</v>
           </cell>
           <cell r="P609">
             <v>0</v>
@@ -35483,10 +35483,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N610">
-            <v>27294.799999999999</v>
+            <v>27820.32</v>
           </cell>
           <cell r="O610">
-            <v>525.52</v>
+            <v>0</v>
           </cell>
           <cell r="P610">
             <v>0</v>
@@ -35536,10 +35536,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N611">
-            <v>39196.159999999996</v>
+            <v>39809.279999999999</v>
           </cell>
           <cell r="O611">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P611">
             <v>0</v>
@@ -35589,10 +35589,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N612">
-            <v>38447.69</v>
+            <v>38973.21</v>
           </cell>
           <cell r="O612">
-            <v>525.52</v>
+            <v>0</v>
           </cell>
           <cell r="P612">
             <v>0</v>
@@ -35642,10 +35642,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N613">
-            <v>36036.720000000008</v>
+            <v>36649.840000000011</v>
           </cell>
           <cell r="O613">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P613">
             <v>0</v>
@@ -35695,10 +35695,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N614">
-            <v>34021.61</v>
+            <v>34634.730000000003</v>
           </cell>
           <cell r="O614">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P614">
             <v>0</v>
@@ -35748,10 +35748,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N615">
-            <v>27487.4</v>
+            <v>28100.519999999997</v>
           </cell>
           <cell r="O615">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P615">
             <v>0</v>
@@ -35760,16 +35760,16 @@
             <v>0</v>
           </cell>
           <cell r="R615">
-            <v>28100.52</v>
+            <v>28100.519999999997</v>
           </cell>
           <cell r="T615">
             <v>0</v>
           </cell>
           <cell r="U615">
-            <v>28100.52</v>
+            <v>28100.519999999997</v>
           </cell>
           <cell r="V615">
-            <v>13309.55</v>
+            <v>13309.550000000003</v>
           </cell>
         </row>
         <row r="616">
@@ -35801,10 +35801,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N616">
-            <v>24633.74</v>
+            <v>25246.859999999997</v>
           </cell>
           <cell r="O616">
-            <v>613.11999999999989</v>
+            <v>0</v>
           </cell>
           <cell r="P616">
             <v>0</v>
@@ -35813,16 +35813,16 @@
             <v>0</v>
           </cell>
           <cell r="R616">
-            <v>25246.86</v>
+            <v>25246.859999999997</v>
           </cell>
           <cell r="T616">
             <v>0</v>
           </cell>
           <cell r="U616">
-            <v>25246.86</v>
+            <v>25246.859999999997</v>
           </cell>
           <cell r="V616">
-            <v>16163.21</v>
+            <v>16163.210000000003</v>
           </cell>
         </row>
         <row r="617">
@@ -35854,10 +35854,10 @@
             <v>41410.07</v>
           </cell>
           <cell r="N617">
-            <v>14587.88</v>
+            <v>16153.4</v>
           </cell>
           <cell r="O617">
-            <v>525.52</v>
+            <v>0</v>
           </cell>
           <cell r="P617">
             <v>0</v>
@@ -35866,16 +35866,16 @@
             <v>0</v>
           </cell>
           <cell r="R617">
-            <v>15113.4</v>
+            <v>16153.4</v>
           </cell>
           <cell r="T617">
             <v>0</v>
           </cell>
           <cell r="U617">
-            <v>15113.4</v>
+            <v>16153.4</v>
           </cell>
           <cell r="V617">
-            <v>26296.67</v>
+            <v>25256.67</v>
           </cell>
         </row>
         <row r="618">
@@ -35948,28 +35948,28 @@
             <v>718642.58999999973</v>
           </cell>
           <cell r="N619">
-            <v>181892.92</v>
+            <v>190653.74000000002</v>
           </cell>
           <cell r="O619">
-            <v>4432.91</v>
+            <v>0</v>
           </cell>
           <cell r="P619">
-            <v>38401.549999999996</v>
+            <v>34073.61</v>
           </cell>
           <cell r="Q619">
             <v>0</v>
           </cell>
           <cell r="R619">
-            <v>224727.38</v>
+            <v>224727.35000000003</v>
           </cell>
           <cell r="T619">
             <v>165998.12</v>
           </cell>
           <cell r="U619">
-            <v>390725.5</v>
+            <v>390725.47000000003</v>
           </cell>
           <cell r="V619">
-            <v>327917.08999999973</v>
+            <v>327917.1199999997</v>
           </cell>
         </row>
         <row r="620">
@@ -35989,28 +35989,28 @@
             <v>714676.40999999968</v>
           </cell>
           <cell r="N620">
-            <v>181892.92</v>
+            <v>190653.74000000002</v>
           </cell>
           <cell r="O620">
-            <v>4432.91</v>
+            <v>0</v>
           </cell>
           <cell r="P620">
-            <v>38401.549999999996</v>
+            <v>34073.61</v>
           </cell>
           <cell r="Q620">
             <v>0</v>
           </cell>
           <cell r="R620">
-            <v>224727.38</v>
+            <v>224727.35000000003</v>
           </cell>
           <cell r="T620">
             <v>162031.94</v>
           </cell>
           <cell r="U620">
-            <v>386759.32</v>
+            <v>386759.29000000004</v>
           </cell>
           <cell r="V620">
-            <v>327917.08999999968</v>
+            <v>327917.11999999965</v>
           </cell>
         </row>
         <row r="621">
@@ -36154,22 +36154,22 @@
             <v>0</v>
           </cell>
           <cell r="P623">
-            <v>0.81</v>
+            <v>0.8</v>
           </cell>
           <cell r="Q623">
             <v>0</v>
           </cell>
           <cell r="R623">
-            <v>16836.480000000003</v>
+            <v>16836.47</v>
           </cell>
           <cell r="T623">
             <v>0</v>
           </cell>
           <cell r="U623">
-            <v>16836.480000000003</v>
+            <v>16836.47</v>
           </cell>
           <cell r="V623">
-            <v>26889.239999999998</v>
+            <v>26889.25</v>
           </cell>
         </row>
         <row r="624">
@@ -36207,22 +36207,22 @@
             <v>0</v>
           </cell>
           <cell r="P624">
-            <v>1165.67</v>
+            <v>1165.6599999999999</v>
           </cell>
           <cell r="Q624">
             <v>0</v>
           </cell>
           <cell r="R624">
-            <v>20429.519999999997</v>
+            <v>20429.509999999998</v>
           </cell>
           <cell r="T624">
             <v>0</v>
           </cell>
           <cell r="U624">
-            <v>20429.519999999997</v>
+            <v>20429.509999999998</v>
           </cell>
           <cell r="V624">
-            <v>23296.200000000004</v>
+            <v>23296.210000000003</v>
           </cell>
         </row>
         <row r="625">
@@ -36260,22 +36260,22 @@
             <v>0</v>
           </cell>
           <cell r="P625">
-            <v>535.64</v>
+            <v>535.65</v>
           </cell>
           <cell r="Q625">
             <v>0</v>
           </cell>
           <cell r="R625">
-            <v>13229.1</v>
+            <v>13229.11</v>
           </cell>
           <cell r="T625">
             <v>0</v>
           </cell>
           <cell r="U625">
-            <v>13229.1</v>
+            <v>13229.11</v>
           </cell>
           <cell r="V625">
-            <v>30496.620000000003</v>
+            <v>30496.61</v>
           </cell>
         </row>
         <row r="626">
@@ -36313,22 +36313,22 @@
             <v>0</v>
           </cell>
           <cell r="P626">
-            <v>1902.19</v>
+            <v>1902.18</v>
           </cell>
           <cell r="Q626">
             <v>0</v>
           </cell>
           <cell r="R626">
-            <v>13229.12</v>
+            <v>13229.11</v>
           </cell>
           <cell r="T626">
             <v>0</v>
           </cell>
           <cell r="U626">
-            <v>13229.12</v>
+            <v>13229.11</v>
           </cell>
           <cell r="V626">
-            <v>30496.6</v>
+            <v>30496.61</v>
           </cell>
         </row>
         <row r="627">
@@ -36366,22 +36366,22 @@
             <v>0</v>
           </cell>
           <cell r="P627">
-            <v>596.9</v>
+            <v>596.89</v>
           </cell>
           <cell r="Q627">
             <v>0</v>
           </cell>
           <cell r="R627">
-            <v>13210.389999999998</v>
+            <v>13210.379999999997</v>
           </cell>
           <cell r="T627">
             <v>0</v>
           </cell>
           <cell r="U627">
-            <v>13210.389999999998</v>
+            <v>13210.379999999997</v>
           </cell>
           <cell r="V627">
-            <v>30515.33</v>
+            <v>30515.340000000004</v>
           </cell>
         </row>
         <row r="628">
@@ -36419,22 +36419,22 @@
             <v>0</v>
           </cell>
           <cell r="P628">
-            <v>596.9</v>
+            <v>596.89</v>
           </cell>
           <cell r="Q628">
             <v>0</v>
           </cell>
           <cell r="R628">
-            <v>14074.19</v>
+            <v>14074.18</v>
           </cell>
           <cell r="T628">
             <v>0</v>
           </cell>
           <cell r="U628">
-            <v>14074.19</v>
+            <v>14074.18</v>
           </cell>
           <cell r="V628">
-            <v>29651.53</v>
+            <v>29651.54</v>
           </cell>
         </row>
         <row r="629">
@@ -36472,22 +36472,22 @@
             <v>0</v>
           </cell>
           <cell r="P629">
-            <v>596.9</v>
+            <v>596.89</v>
           </cell>
           <cell r="Q629">
             <v>0</v>
           </cell>
           <cell r="R629">
-            <v>12463</v>
+            <v>12462.99</v>
           </cell>
           <cell r="T629">
             <v>0</v>
           </cell>
           <cell r="U629">
-            <v>12463</v>
+            <v>12462.99</v>
           </cell>
           <cell r="V629">
-            <v>31262.720000000001</v>
+            <v>31262.730000000003</v>
           </cell>
         </row>
         <row r="630">
@@ -36525,22 +36525,22 @@
             <v>0</v>
           </cell>
           <cell r="P630">
-            <v>1338.9</v>
+            <v>1338.89</v>
           </cell>
           <cell r="Q630">
             <v>0</v>
           </cell>
           <cell r="R630">
-            <v>12463</v>
+            <v>12462.99</v>
           </cell>
           <cell r="T630">
             <v>0</v>
           </cell>
           <cell r="U630">
-            <v>12463</v>
+            <v>12462.99</v>
           </cell>
           <cell r="V630">
-            <v>31262.720000000001</v>
+            <v>31262.730000000003</v>
           </cell>
         </row>
         <row r="631">
@@ -36578,22 +36578,22 @@
             <v>0</v>
           </cell>
           <cell r="P631">
-            <v>1106.8799999999999</v>
+            <v>1106.8899999999999</v>
           </cell>
           <cell r="Q631">
             <v>0</v>
           </cell>
           <cell r="R631">
-            <v>12462.98</v>
+            <v>12462.99</v>
           </cell>
           <cell r="T631">
             <v>0</v>
           </cell>
           <cell r="U631">
-            <v>12462.98</v>
+            <v>12462.99</v>
           </cell>
           <cell r="V631">
-            <v>31262.74</v>
+            <v>31262.730000000003</v>
           </cell>
         </row>
         <row r="632">
@@ -36631,22 +36631,22 @@
             <v>0</v>
           </cell>
           <cell r="P632">
-            <v>1124.8800000000001</v>
+            <v>1124.8900000000001</v>
           </cell>
           <cell r="Q632">
             <v>0</v>
           </cell>
           <cell r="R632">
-            <v>11936.95</v>
+            <v>11936.960000000001</v>
           </cell>
           <cell r="T632">
             <v>0</v>
           </cell>
           <cell r="U632">
-            <v>11936.95</v>
+            <v>11936.960000000001</v>
           </cell>
           <cell r="V632">
-            <v>31788.77</v>
+            <v>31788.760000000002</v>
           </cell>
         </row>
         <row r="633">
@@ -36678,28 +36678,28 @@
             <v>43725.72</v>
           </cell>
           <cell r="N633">
-            <v>7086.31</v>
+            <v>11519.220000000001</v>
           </cell>
           <cell r="O633">
-            <v>4432.91</v>
+            <v>0</v>
           </cell>
           <cell r="P633">
-            <v>1211.8800000000001</v>
+            <v>1211.8899999999999</v>
           </cell>
           <cell r="Q633">
             <v>0</v>
           </cell>
           <cell r="R633">
-            <v>12731.100000000002</v>
+            <v>12731.11</v>
           </cell>
           <cell r="T633">
             <v>0</v>
           </cell>
           <cell r="U633">
-            <v>12731.100000000002</v>
+            <v>12731.11</v>
           </cell>
           <cell r="V633">
-            <v>30994.62</v>
+            <v>30994.61</v>
           </cell>
         </row>
         <row r="634">
@@ -36731,13 +36731,13 @@
             <v>43725.72</v>
           </cell>
           <cell r="N634">
-            <v>7086.31</v>
+            <v>11414.220000000001</v>
           </cell>
           <cell r="O634">
             <v>0</v>
           </cell>
           <cell r="P634">
-            <v>5644.8</v>
+            <v>1316.89</v>
           </cell>
           <cell r="Q634">
             <v>0</v>
@@ -37078,28 +37078,28 @@
             <v>457093.31999999995</v>
           </cell>
           <cell r="N641">
-            <v>292479.10000000003</v>
+            <v>322514.71000000008</v>
           </cell>
           <cell r="O641">
-            <v>11341.23</v>
+            <v>3121.4399999999991</v>
           </cell>
           <cell r="P641">
-            <v>50559.19</v>
+            <v>33174.26</v>
           </cell>
           <cell r="Q641">
-            <v>2054.9899999999998</v>
+            <v>3317.4</v>
           </cell>
           <cell r="R641">
-            <v>356434.51</v>
+            <v>362127.81000000011</v>
           </cell>
           <cell r="T641">
             <v>49305.16</v>
           </cell>
           <cell r="U641">
-            <v>405739.67000000004</v>
+            <v>411432.97000000009</v>
           </cell>
           <cell r="V641">
-            <v>51353.649999999907</v>
+            <v>45660.34999999986</v>
           </cell>
         </row>
         <row r="642">
@@ -37119,28 +37119,28 @@
             <v>87122.2</v>
           </cell>
           <cell r="N642">
-            <v>69539.899999999994</v>
+            <v>74739.899999999994</v>
           </cell>
           <cell r="O642">
             <v>0</v>
           </cell>
           <cell r="P642">
-            <v>7074.99</v>
+            <v>1875</v>
           </cell>
           <cell r="Q642">
             <v>0</v>
           </cell>
           <cell r="R642">
-            <v>76614.89</v>
+            <v>76614.899999999994</v>
           </cell>
           <cell r="T642">
             <v>11717.2</v>
           </cell>
           <cell r="U642">
-            <v>88332.09</v>
+            <v>88332.099999999991</v>
           </cell>
           <cell r="V642">
-            <v>-1209.8899999999994</v>
+            <v>-1209.8999999999942</v>
           </cell>
         </row>
         <row r="643">
@@ -37655,22 +37655,22 @@
             <v>0</v>
           </cell>
           <cell r="P652">
-            <v>274.81</v>
+            <v>274.82</v>
           </cell>
           <cell r="Q652">
             <v>0</v>
           </cell>
           <cell r="R652">
-            <v>3144.81</v>
+            <v>3144.82</v>
           </cell>
           <cell r="T652">
             <v>0</v>
           </cell>
           <cell r="U652">
-            <v>3144.81</v>
+            <v>3144.82</v>
           </cell>
           <cell r="V652">
-            <v>1882.19</v>
+            <v>1882.1799999999998</v>
           </cell>
         </row>
         <row r="653">
@@ -37914,13 +37914,13 @@
             <v>5027</v>
           </cell>
           <cell r="N657">
-            <v>5202</v>
+            <v>7202</v>
           </cell>
           <cell r="O657">
             <v>0</v>
           </cell>
           <cell r="P657">
-            <v>2000</v>
+            <v>0</v>
           </cell>
           <cell r="Q657">
             <v>0</v>
@@ -37967,28 +37967,28 @@
             <v>5027</v>
           </cell>
           <cell r="N658">
-            <v>6032</v>
+            <v>8432</v>
           </cell>
           <cell r="O658">
             <v>0</v>
           </cell>
           <cell r="P658">
-            <v>2400.09</v>
+            <v>0</v>
           </cell>
           <cell r="Q658">
             <v>0</v>
           </cell>
           <cell r="R658">
-            <v>8432.09</v>
+            <v>8432</v>
           </cell>
           <cell r="T658">
             <v>0</v>
           </cell>
           <cell r="U658">
-            <v>8432.09</v>
+            <v>8432</v>
           </cell>
           <cell r="V658">
-            <v>-3405.09</v>
+            <v>-3405</v>
           </cell>
         </row>
         <row r="659">
@@ -38020,28 +38020,28 @@
             <v>5027</v>
           </cell>
           <cell r="N659">
-            <v>8117</v>
+            <v>8917</v>
           </cell>
           <cell r="O659">
             <v>0</v>
           </cell>
           <cell r="P659">
-            <v>2400.09</v>
+            <v>1600.18</v>
           </cell>
           <cell r="Q659">
             <v>0</v>
           </cell>
           <cell r="R659">
-            <v>10517.09</v>
+            <v>10517.18</v>
           </cell>
           <cell r="T659">
             <v>0</v>
           </cell>
           <cell r="U659">
-            <v>10517.09</v>
+            <v>10517.18</v>
           </cell>
           <cell r="V659">
-            <v>-5490.09</v>
+            <v>-5490.18</v>
           </cell>
         </row>
         <row r="660">
@@ -40104,7 +40104,7 @@
             <v>97708.799999999988</v>
           </cell>
           <cell r="N699">
-            <v>189210.54000000004</v>
+            <v>192270.54000000004</v>
           </cell>
           <cell r="O699">
             <v>0</v>
@@ -40116,16 +40116,16 @@
             <v>0</v>
           </cell>
           <cell r="R699">
-            <v>189210.54000000004</v>
+            <v>192270.54000000004</v>
           </cell>
           <cell r="T699">
             <v>0</v>
           </cell>
           <cell r="U699">
-            <v>189210.54000000004</v>
+            <v>192270.54000000004</v>
           </cell>
           <cell r="V699">
-            <v>-91501.740000000049</v>
+            <v>-94561.740000000049</v>
           </cell>
         </row>
         <row r="700">
@@ -41005,7 +41005,7 @@
             <v>6513.92</v>
           </cell>
           <cell r="N716">
-            <v>12606.43</v>
+            <v>15666.43</v>
           </cell>
           <cell r="O716">
             <v>0</v>
@@ -41017,16 +41017,16 @@
             <v>0</v>
           </cell>
           <cell r="R716">
-            <v>12606.43</v>
+            <v>15666.43</v>
           </cell>
           <cell r="T716">
             <v>0</v>
           </cell>
           <cell r="U716">
-            <v>12606.43</v>
+            <v>15666.43</v>
           </cell>
           <cell r="V716">
-            <v>-6092.51</v>
+            <v>-9152.51</v>
           </cell>
         </row>
         <row r="717">
@@ -42094,28 +42094,28 @@
             <v>101552.20999999999</v>
           </cell>
           <cell r="N737">
-            <v>39892.479999999981</v>
+            <v>59346.819999999992</v>
           </cell>
           <cell r="O737">
-            <v>9019.9599999999991</v>
+            <v>3121.4399999999991</v>
           </cell>
           <cell r="P737">
-            <v>32353.45</v>
+            <v>20168.5</v>
           </cell>
           <cell r="Q737">
-            <v>2054.9899999999998</v>
+            <v>3317.4</v>
           </cell>
           <cell r="R737">
-            <v>83320.87999999999</v>
+            <v>85954.159999999989</v>
           </cell>
           <cell r="T737">
             <v>0</v>
           </cell>
           <cell r="U737">
-            <v>83320.87999999999</v>
+            <v>85954.159999999989</v>
           </cell>
           <cell r="V737">
-            <v>18231.330000000002</v>
+            <v>15598.050000000003</v>
           </cell>
         </row>
         <row r="738">
@@ -42200,28 +42200,28 @@
             <v>4944.26</v>
           </cell>
           <cell r="N739">
-            <v>0</v>
+            <v>1881.86</v>
           </cell>
           <cell r="O739">
-            <v>1784</v>
+            <v>195.72</v>
           </cell>
           <cell r="P739">
-            <v>4609.0200000000004</v>
+            <v>4608.99</v>
           </cell>
           <cell r="Q739">
-            <v>293.57</v>
+            <v>0</v>
           </cell>
           <cell r="R739">
-            <v>6686.59</v>
+            <v>6686.57</v>
           </cell>
           <cell r="T739">
             <v>0</v>
           </cell>
           <cell r="U739">
-            <v>6686.59</v>
+            <v>6686.57</v>
           </cell>
           <cell r="V739">
-            <v>-1742.33</v>
+            <v>-1742.3099999999995</v>
           </cell>
         </row>
         <row r="740">
@@ -42253,28 +42253,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N740">
-            <v>3984.22</v>
+            <v>4082.08</v>
           </cell>
           <cell r="O740">
-            <v>0</v>
+            <v>195.72</v>
           </cell>
           <cell r="P740">
-            <v>2232.13</v>
+            <v>2232.14</v>
           </cell>
           <cell r="Q740">
-            <v>293.57</v>
+            <v>0</v>
           </cell>
           <cell r="R740">
-            <v>6509.92</v>
+            <v>6509.9400000000005</v>
           </cell>
           <cell r="T740">
             <v>0</v>
           </cell>
           <cell r="U740">
-            <v>6509.92</v>
+            <v>6509.9400000000005</v>
           </cell>
           <cell r="V740">
-            <v>-69.390000000000327</v>
+            <v>-69.410000000000764</v>
           </cell>
         </row>
         <row r="741">
@@ -42306,28 +42306,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N741">
-            <v>2200.71</v>
+            <v>2298.5700000000002</v>
           </cell>
           <cell r="O741">
-            <v>0</v>
+            <v>195.72</v>
           </cell>
           <cell r="P741">
             <v>2467.1999999999998</v>
           </cell>
           <cell r="Q741">
-            <v>293.57</v>
+            <v>0</v>
           </cell>
           <cell r="R741">
-            <v>4961.4799999999996</v>
+            <v>4961.49</v>
           </cell>
           <cell r="T741">
             <v>0</v>
           </cell>
           <cell r="U741">
-            <v>4961.4799999999996</v>
+            <v>4961.49</v>
           </cell>
           <cell r="V741">
-            <v>1479.0500000000002</v>
+            <v>1479.04</v>
           </cell>
         </row>
         <row r="742">
@@ -42359,28 +42359,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N742">
-            <v>4676.3500000000004</v>
+            <v>4774.21</v>
           </cell>
           <cell r="O742">
-            <v>0</v>
+            <v>195.72</v>
           </cell>
           <cell r="P742">
             <v>0</v>
           </cell>
           <cell r="Q742">
-            <v>293.57</v>
+            <v>0</v>
           </cell>
           <cell r="R742">
-            <v>4969.92</v>
+            <v>4969.93</v>
           </cell>
           <cell r="T742">
             <v>0</v>
           </cell>
           <cell r="U742">
-            <v>4969.92</v>
+            <v>4969.93</v>
           </cell>
           <cell r="V742">
-            <v>1470.6099999999997</v>
+            <v>1470.5999999999995</v>
           </cell>
         </row>
         <row r="743">
@@ -42412,28 +42412,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N743">
-            <v>4676.3500000000004</v>
+            <v>4774.21</v>
           </cell>
           <cell r="O743">
-            <v>0</v>
+            <v>195.72</v>
           </cell>
           <cell r="P743">
             <v>0</v>
           </cell>
           <cell r="Q743">
-            <v>293.57</v>
+            <v>0</v>
           </cell>
           <cell r="R743">
-            <v>4969.92</v>
+            <v>4969.93</v>
           </cell>
           <cell r="T743">
             <v>0</v>
           </cell>
           <cell r="U743">
-            <v>4969.92</v>
+            <v>4969.93</v>
           </cell>
           <cell r="V743">
-            <v>1470.6099999999997</v>
+            <v>1470.5999999999995</v>
           </cell>
         </row>
         <row r="744">
@@ -42465,28 +42465,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N744">
-            <v>4667.8500000000004</v>
+            <v>4765.71</v>
           </cell>
           <cell r="O744">
-            <v>0</v>
+            <v>195.72</v>
           </cell>
           <cell r="P744">
             <v>0</v>
           </cell>
           <cell r="Q744">
-            <v>293.57</v>
+            <v>552.9</v>
           </cell>
           <cell r="R744">
-            <v>4961.42</v>
+            <v>5514.33</v>
           </cell>
           <cell r="T744">
             <v>0</v>
           </cell>
           <cell r="U744">
-            <v>4961.42</v>
+            <v>5514.33</v>
           </cell>
           <cell r="V744">
-            <v>1479.1099999999997</v>
+            <v>926.19999999999982</v>
           </cell>
         </row>
         <row r="745">
@@ -42518,28 +42518,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N745">
-            <v>4644.1000000000004</v>
+            <v>4741.96</v>
           </cell>
           <cell r="O745">
-            <v>0</v>
+            <v>195.72</v>
           </cell>
           <cell r="P745">
             <v>0</v>
           </cell>
           <cell r="Q745">
-            <v>293.57</v>
+            <v>552.9</v>
           </cell>
           <cell r="R745">
-            <v>4937.67</v>
+            <v>5490.58</v>
           </cell>
           <cell r="T745">
             <v>0</v>
           </cell>
           <cell r="U745">
-            <v>4937.67</v>
+            <v>5490.58</v>
           </cell>
           <cell r="V745">
-            <v>1502.8599999999997</v>
+            <v>949.94999999999982</v>
           </cell>
         </row>
         <row r="746">
@@ -42580,19 +42580,19 @@
             <v>0</v>
           </cell>
           <cell r="Q746">
-            <v>0</v>
+            <v>552.9</v>
           </cell>
           <cell r="R746">
-            <v>4644.1000000000004</v>
+            <v>5197</v>
           </cell>
           <cell r="T746">
             <v>0</v>
           </cell>
           <cell r="U746">
-            <v>4644.1000000000004</v>
+            <v>5197</v>
           </cell>
           <cell r="V746">
-            <v>1796.4299999999994</v>
+            <v>1243.5299999999997</v>
           </cell>
         </row>
         <row r="747">
@@ -42633,19 +42633,19 @@
             <v>0</v>
           </cell>
           <cell r="Q747">
-            <v>0</v>
+            <v>552.9</v>
           </cell>
           <cell r="R747">
-            <v>4644.1000000000004</v>
+            <v>5197</v>
           </cell>
           <cell r="T747">
             <v>0</v>
           </cell>
           <cell r="U747">
-            <v>4644.1000000000004</v>
+            <v>5197</v>
           </cell>
           <cell r="V747">
-            <v>1796.4299999999994</v>
+            <v>1243.5299999999997</v>
           </cell>
         </row>
         <row r="748">
@@ -42677,28 +42677,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N748">
-            <v>4644.1000000000004</v>
+            <v>4671.4500000000007</v>
           </cell>
           <cell r="O748">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P748">
             <v>0</v>
           </cell>
           <cell r="Q748">
-            <v>0</v>
+            <v>552.9</v>
           </cell>
           <cell r="R748">
-            <v>5019.38</v>
+            <v>5474.55</v>
           </cell>
           <cell r="T748">
             <v>0</v>
           </cell>
           <cell r="U748">
-            <v>5019.38</v>
+            <v>5474.55</v>
           </cell>
           <cell r="V748">
-            <v>1421.1499999999996</v>
+            <v>965.97999999999956</v>
           </cell>
         </row>
         <row r="749">
@@ -42730,28 +42730,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N749">
-            <v>35.1</v>
+            <v>4671.45</v>
           </cell>
           <cell r="O749">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P749">
-            <v>4609.0200000000004</v>
+            <v>0</v>
           </cell>
           <cell r="Q749">
-            <v>0</v>
+            <v>552.9</v>
           </cell>
           <cell r="R749">
-            <v>5019.4000000000005</v>
+            <v>5474.5499999999993</v>
           </cell>
           <cell r="T749">
             <v>0</v>
           </cell>
           <cell r="U749">
-            <v>5019.4000000000005</v>
+            <v>5474.5499999999993</v>
           </cell>
           <cell r="V749">
-            <v>1421.1299999999992</v>
+            <v>965.98000000000047</v>
           </cell>
         </row>
         <row r="750">
@@ -42783,28 +42783,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N750">
-            <v>35.1</v>
+            <v>4671.45</v>
           </cell>
           <cell r="O750">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P750">
-            <v>4609.0200000000004</v>
+            <v>0</v>
           </cell>
           <cell r="Q750">
             <v>0</v>
           </cell>
           <cell r="R750">
-            <v>5019.4000000000005</v>
+            <v>4921.6499999999996</v>
           </cell>
           <cell r="T750">
             <v>0</v>
           </cell>
           <cell r="U750">
-            <v>5019.4000000000005</v>
+            <v>4921.6499999999996</v>
           </cell>
           <cell r="V750">
-            <v>1421.1299999999992</v>
+            <v>1518.88</v>
           </cell>
         </row>
         <row r="751">
@@ -42836,28 +42836,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N751">
-            <v>35.1</v>
+            <v>3029.3199999999997</v>
           </cell>
           <cell r="O751">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P751">
-            <v>4609.0200000000004</v>
+            <v>1642.19</v>
           </cell>
           <cell r="Q751">
             <v>0</v>
           </cell>
           <cell r="R751">
-            <v>5019.4000000000005</v>
+            <v>4921.7099999999991</v>
           </cell>
           <cell r="T751">
             <v>0</v>
           </cell>
           <cell r="U751">
-            <v>5019.4000000000005</v>
+            <v>4921.7099999999991</v>
           </cell>
           <cell r="V751">
-            <v>1421.1299999999992</v>
+            <v>1518.8200000000006</v>
           </cell>
         </row>
         <row r="752">
@@ -42889,28 +42889,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N752">
-            <v>35.1</v>
+            <v>62.45</v>
           </cell>
           <cell r="O752">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P752">
-            <v>4609.0200000000004</v>
+            <v>4608.99</v>
           </cell>
           <cell r="Q752">
             <v>0</v>
           </cell>
           <cell r="R752">
-            <v>5019.4000000000005</v>
+            <v>4921.6399999999994</v>
           </cell>
           <cell r="T752">
             <v>0</v>
           </cell>
           <cell r="U752">
-            <v>5019.4000000000005</v>
+            <v>4921.6399999999994</v>
           </cell>
           <cell r="V752">
-            <v>1421.1299999999992</v>
+            <v>1518.8900000000003</v>
           </cell>
         </row>
         <row r="753">
@@ -42942,28 +42942,28 @@
             <v>6440.53</v>
           </cell>
           <cell r="N753">
-            <v>35.1</v>
+            <v>62.45</v>
           </cell>
           <cell r="O753">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P753">
-            <v>4609.0200000000004</v>
+            <v>4608.99</v>
           </cell>
           <cell r="Q753">
             <v>0</v>
           </cell>
           <cell r="R753">
-            <v>5019.4000000000005</v>
+            <v>4921.6399999999994</v>
           </cell>
           <cell r="T753">
             <v>0</v>
           </cell>
           <cell r="U753">
-            <v>5019.4000000000005</v>
+            <v>4921.6399999999994</v>
           </cell>
           <cell r="V753">
-            <v>1421.1299999999992</v>
+            <v>1518.8900000000003</v>
           </cell>
         </row>
         <row r="754">
@@ -42995,10 +42995,10 @@
             <v>6440.53</v>
           </cell>
           <cell r="N754">
-            <v>35.1</v>
+            <v>4671.4500000000007</v>
           </cell>
           <cell r="O754">
-            <v>4984.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P754">
             <v>0</v>
@@ -43007,16 +43007,16 @@
             <v>0</v>
           </cell>
           <cell r="R754">
-            <v>5019.38</v>
+            <v>4921.6500000000005</v>
           </cell>
           <cell r="T754">
             <v>0</v>
           </cell>
           <cell r="U754">
-            <v>5019.38</v>
+            <v>4921.6500000000005</v>
           </cell>
           <cell r="V754">
-            <v>1421.1499999999996</v>
+            <v>1518.8799999999992</v>
           </cell>
         </row>
         <row r="755">
@@ -43089,28 +43089,28 @@
             <v>20351.449999999975</v>
           </cell>
           <cell r="N756">
-            <v>6743</v>
+            <v>9064.27</v>
           </cell>
           <cell r="O756">
-            <v>2321.27</v>
+            <v>0</v>
           </cell>
           <cell r="P756">
-            <v>11130.75</v>
+            <v>11130.76</v>
           </cell>
           <cell r="Q756">
             <v>0</v>
           </cell>
           <cell r="R756">
-            <v>20195.02</v>
+            <v>20195.03</v>
           </cell>
           <cell r="T756">
             <v>28720.55</v>
           </cell>
           <cell r="U756">
-            <v>48915.57</v>
+            <v>48915.58</v>
           </cell>
           <cell r="V756">
-            <v>-28564.120000000024</v>
+            <v>-28564.130000000026</v>
           </cell>
         </row>
         <row r="757">
@@ -43672,10 +43672,10 @@
             <v>239.26</v>
           </cell>
           <cell r="N767">
-            <v>0</v>
+            <v>1121</v>
           </cell>
           <cell r="O767">
-            <v>1121</v>
+            <v>0</v>
           </cell>
           <cell r="P767">
             <v>0</v>
@@ -43725,10 +43725,10 @@
             <v>239.26</v>
           </cell>
           <cell r="N768">
-            <v>0</v>
+            <v>1121</v>
           </cell>
           <cell r="O768">
-            <v>1121</v>
+            <v>0</v>
           </cell>
           <cell r="P768">
             <v>0</v>
@@ -43778,28 +43778,28 @@
             <v>239.26</v>
           </cell>
           <cell r="N769">
-            <v>0</v>
+            <v>79.27</v>
           </cell>
           <cell r="O769">
-            <v>79.27</v>
+            <v>0</v>
           </cell>
           <cell r="P769">
-            <v>1041.75</v>
+            <v>1041.76</v>
           </cell>
           <cell r="Q769">
             <v>0</v>
           </cell>
           <cell r="R769">
-            <v>1121.02</v>
+            <v>1121.03</v>
           </cell>
           <cell r="T769">
             <v>500</v>
           </cell>
           <cell r="U769">
-            <v>1621.02</v>
+            <v>1621.03</v>
           </cell>
           <cell r="V769">
-            <v>-1381.76</v>
+            <v>-1381.77</v>
           </cell>
         </row>
         <row r="770">
@@ -44084,28 +44084,28 @@
             <v>1301538.4799999997</v>
           </cell>
           <cell r="N775">
-            <v>834611.95</v>
+            <v>866509.13</v>
           </cell>
           <cell r="O775">
-            <v>15706.619999999999</v>
+            <v>1971.21</v>
           </cell>
           <cell r="P775">
-            <v>66210.189999999988</v>
+            <v>53324.380000000005</v>
           </cell>
           <cell r="Q775">
-            <v>1786.65</v>
+            <v>12995.43</v>
           </cell>
           <cell r="R775">
-            <v>918315.40999999992</v>
+            <v>934800.15</v>
           </cell>
           <cell r="T775">
-            <v>172186.28999999998</v>
+            <v>156010.19</v>
           </cell>
           <cell r="U775">
-            <v>1090501.7</v>
+            <v>1090810.3400000001</v>
           </cell>
           <cell r="V775">
-            <v>211036.7799999998</v>
+            <v>210728.13999999966</v>
           </cell>
         </row>
         <row r="776">
@@ -45373,28 +45373,28 @@
             <v>284879.06999999989</v>
           </cell>
           <cell r="N800">
-            <v>174692.47999999998</v>
+            <v>177513.29</v>
           </cell>
           <cell r="O800">
-            <v>2820.81</v>
+            <v>1411.21</v>
           </cell>
           <cell r="P800">
             <v>0</v>
           </cell>
           <cell r="Q800">
-            <v>1432</v>
+            <v>2741.52</v>
           </cell>
           <cell r="R800">
-            <v>178945.28999999998</v>
+            <v>181666.02</v>
           </cell>
           <cell r="T800">
-            <v>17846.95</v>
+            <v>17376.550000000003</v>
           </cell>
           <cell r="U800">
-            <v>196792.24</v>
+            <v>199042.57</v>
           </cell>
           <cell r="V800">
-            <v>88086.8299999999</v>
+            <v>85836.499999999884</v>
           </cell>
         </row>
         <row r="801">
@@ -45479,10 +45479,10 @@
             <v>18787.22</v>
           </cell>
           <cell r="N802">
-            <v>0</v>
+            <v>940.27</v>
           </cell>
           <cell r="O802">
-            <v>940.27</v>
+            <v>470.4</v>
           </cell>
           <cell r="P802">
             <v>0</v>
@@ -45491,10 +45491,10 @@
             <v>0</v>
           </cell>
           <cell r="R802">
-            <v>940.27</v>
+            <v>1410.67</v>
           </cell>
           <cell r="T802">
-            <v>17846.95</v>
+            <v>17376.550000000003</v>
           </cell>
           <cell r="U802">
             <v>18787.22</v>
@@ -45912,19 +45912,19 @@
             <v>0</v>
           </cell>
           <cell r="Q810">
-            <v>358</v>
+            <v>685.38</v>
           </cell>
           <cell r="R810">
-            <v>7662.55</v>
+            <v>7989.93</v>
           </cell>
           <cell r="T810">
             <v>0</v>
           </cell>
           <cell r="U810">
-            <v>7662.55</v>
+            <v>7989.93</v>
           </cell>
           <cell r="V810">
-            <v>9776.369999999999</v>
+            <v>9448.989999999998</v>
           </cell>
         </row>
         <row r="811">
@@ -45965,19 +45965,19 @@
             <v>0</v>
           </cell>
           <cell r="Q811">
-            <v>358</v>
+            <v>685.38</v>
           </cell>
           <cell r="R811">
-            <v>367.68000000000018</v>
+            <v>695.06000000000017</v>
           </cell>
           <cell r="T811">
             <v>0</v>
           </cell>
           <cell r="U811">
-            <v>367.68000000000018</v>
+            <v>695.06000000000017</v>
           </cell>
           <cell r="V811">
-            <v>17071.239999999998</v>
+            <v>16743.859999999997</v>
           </cell>
         </row>
         <row r="812">
@@ -46018,19 +46018,19 @@
             <v>0</v>
           </cell>
           <cell r="Q812">
-            <v>358</v>
+            <v>685.38</v>
           </cell>
           <cell r="R812">
-            <v>8770.3500000000022</v>
+            <v>9097.7300000000014</v>
           </cell>
           <cell r="T812">
             <v>0</v>
           </cell>
           <cell r="U812">
-            <v>8770.3500000000022</v>
+            <v>9097.7300000000014</v>
           </cell>
           <cell r="V812">
-            <v>8668.5699999999961</v>
+            <v>8341.1899999999969</v>
           </cell>
         </row>
         <row r="813">
@@ -46071,19 +46071,19 @@
             <v>0</v>
           </cell>
           <cell r="Q813">
-            <v>358</v>
+            <v>685.38</v>
           </cell>
           <cell r="R813">
-            <v>7846.79</v>
+            <v>8174.17</v>
           </cell>
           <cell r="T813">
             <v>0</v>
           </cell>
           <cell r="U813">
-            <v>7846.79</v>
+            <v>8174.17</v>
           </cell>
           <cell r="V813">
-            <v>9592.1299999999974</v>
+            <v>9264.7499999999982</v>
           </cell>
         </row>
         <row r="814">
@@ -46221,10 +46221,10 @@
             <v>17438.919999999998</v>
           </cell>
           <cell r="N816">
-            <v>13697.4</v>
+            <v>14637.669999999998</v>
           </cell>
           <cell r="O816">
-            <v>940.27</v>
+            <v>470.41</v>
           </cell>
           <cell r="P816">
             <v>0</v>
@@ -46233,16 +46233,16 @@
             <v>0</v>
           </cell>
           <cell r="R816">
-            <v>14637.67</v>
+            <v>15108.079999999998</v>
           </cell>
           <cell r="T816">
             <v>0</v>
           </cell>
           <cell r="U816">
-            <v>14637.67</v>
+            <v>15108.079999999998</v>
           </cell>
           <cell r="V816">
-            <v>2801.2499999999982</v>
+            <v>2330.84</v>
           </cell>
         </row>
         <row r="817">
@@ -46274,10 +46274,10 @@
             <v>17438.919999999998</v>
           </cell>
           <cell r="N817">
-            <v>33363.119999999995</v>
+            <v>34303.39</v>
           </cell>
           <cell r="O817">
-            <v>940.27</v>
+            <v>470.4</v>
           </cell>
           <cell r="P817">
             <v>0</v>
@@ -46286,16 +46286,16 @@
             <v>0</v>
           </cell>
           <cell r="R817">
-            <v>34303.389999999992</v>
+            <v>34773.79</v>
           </cell>
           <cell r="T817">
             <v>0</v>
           </cell>
           <cell r="U817">
-            <v>34303.389999999992</v>
+            <v>34773.79</v>
           </cell>
           <cell r="V817">
-            <v>-16864.469999999994</v>
+            <v>-17334.870000000003</v>
           </cell>
         </row>
         <row r="818">
@@ -46368,28 +46368,28 @@
             <v>647406.15</v>
           </cell>
           <cell r="N819">
-            <v>489909.55999999994</v>
+            <v>518985.92999999993</v>
           </cell>
           <cell r="O819">
-            <v>12885.81</v>
+            <v>560</v>
           </cell>
           <cell r="P819">
-            <v>66210.189999999988</v>
+            <v>53324.380000000005</v>
           </cell>
           <cell r="Q819">
-            <v>354.65000000000015</v>
+            <v>10253.91</v>
           </cell>
           <cell r="R819">
-            <v>569360.21</v>
+            <v>583124.22</v>
           </cell>
           <cell r="T819">
-            <v>41702.379999999983</v>
+            <v>25996.68</v>
           </cell>
           <cell r="U819">
-            <v>611062.59</v>
+            <v>609120.9</v>
           </cell>
           <cell r="V819">
-            <v>36343.560000000056</v>
+            <v>38285.25</v>
           </cell>
         </row>
         <row r="820">
@@ -46474,7 +46474,7 @@
             <v>28470.45</v>
           </cell>
           <cell r="N821">
-            <v>2759.0599999999995</v>
+            <v>2893.8099999999995</v>
           </cell>
           <cell r="O821">
             <v>0</v>
@@ -46483,7 +46483,7 @@
             <v>0</v>
           </cell>
           <cell r="Q821">
-            <v>134.75</v>
+            <v>0</v>
           </cell>
           <cell r="R821">
             <v>2893.8099999999995</v>
@@ -46530,7 +46530,7 @@
             <v>38981.439999999995</v>
           </cell>
           <cell r="O822">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P822">
             <v>6401.17</v>
@@ -46539,16 +46539,16 @@
             <v>14.66</v>
           </cell>
           <cell r="R822">
-            <v>45397.27</v>
+            <v>45432.27</v>
           </cell>
           <cell r="T822">
             <v>0</v>
           </cell>
           <cell r="U822">
-            <v>45397.27</v>
+            <v>45432.27</v>
           </cell>
           <cell r="V822">
-            <v>-4134.8899999999994</v>
+            <v>-4169.8899999999994</v>
           </cell>
         </row>
         <row r="823">
@@ -46583,25 +46583,25 @@
             <v>36766.49</v>
           </cell>
           <cell r="O823">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P823">
-            <v>567.78</v>
+            <v>567.79</v>
           </cell>
           <cell r="Q823">
             <v>14.66</v>
           </cell>
           <cell r="R823">
-            <v>37348.93</v>
+            <v>37383.94</v>
           </cell>
           <cell r="T823">
             <v>0</v>
           </cell>
           <cell r="U823">
-            <v>37348.93</v>
+            <v>37383.94</v>
           </cell>
           <cell r="V823">
-            <v>3913.4499999999971</v>
+            <v>3878.4399999999951</v>
           </cell>
         </row>
         <row r="824">
@@ -46636,25 +46636,25 @@
             <v>36431.269999999997</v>
           </cell>
           <cell r="O824">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P824">
-            <v>917.79</v>
+            <v>917.80000000000007</v>
           </cell>
           <cell r="Q824">
             <v>14.66</v>
           </cell>
           <cell r="R824">
-            <v>37363.72</v>
+            <v>37398.730000000003</v>
           </cell>
           <cell r="T824">
             <v>0</v>
           </cell>
           <cell r="U824">
-            <v>37363.72</v>
+            <v>37398.730000000003</v>
           </cell>
           <cell r="V824">
-            <v>3898.6599999999962</v>
+            <v>3863.6499999999942</v>
           </cell>
         </row>
         <row r="825">
@@ -46689,7 +46689,7 @@
             <v>37334.75</v>
           </cell>
           <cell r="O825">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P825">
             <v>0</v>
@@ -46698,16 +46698,16 @@
             <v>14.66</v>
           </cell>
           <cell r="R825">
-            <v>37349.410000000003</v>
+            <v>37384.410000000003</v>
           </cell>
           <cell r="T825">
             <v>0</v>
           </cell>
           <cell r="U825">
-            <v>37349.410000000003</v>
+            <v>37384.410000000003</v>
           </cell>
           <cell r="V825">
-            <v>3912.9699999999939</v>
+            <v>3877.9699999999939</v>
           </cell>
         </row>
         <row r="826">
@@ -46742,7 +46742,7 @@
             <v>37115.780000000006</v>
           </cell>
           <cell r="O826">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P826">
             <v>1305.29</v>
@@ -46751,16 +46751,16 @@
             <v>14.66</v>
           </cell>
           <cell r="R826">
-            <v>38435.73000000001</v>
+            <v>38470.73000000001</v>
           </cell>
           <cell r="T826">
             <v>0</v>
           </cell>
           <cell r="U826">
-            <v>38435.73000000001</v>
+            <v>38470.73000000001</v>
           </cell>
           <cell r="V826">
-            <v>2826.6499999999869</v>
+            <v>2791.6499999999869</v>
           </cell>
         </row>
         <row r="827">
@@ -46795,25 +46795,25 @@
             <v>37996.599999999991</v>
           </cell>
           <cell r="O827">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P827">
-            <v>549.29999999999995</v>
+            <v>549.29</v>
           </cell>
           <cell r="Q827">
             <v>14.66</v>
           </cell>
           <cell r="R827">
-            <v>38560.559999999998</v>
+            <v>38595.549999999996</v>
           </cell>
           <cell r="T827">
             <v>0</v>
           </cell>
           <cell r="U827">
-            <v>38560.559999999998</v>
+            <v>38595.549999999996</v>
           </cell>
           <cell r="V827">
-            <v>2701.8199999999997</v>
+            <v>2666.8300000000017</v>
           </cell>
         </row>
         <row r="828">
@@ -46848,25 +46848,25 @@
             <v>35324.189999999995</v>
           </cell>
           <cell r="O828">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P828">
-            <v>549.29999999999995</v>
+            <v>549.29</v>
           </cell>
           <cell r="Q828">
             <v>14.66</v>
           </cell>
           <cell r="R828">
-            <v>35888.15</v>
+            <v>35923.14</v>
           </cell>
           <cell r="T828">
             <v>0</v>
           </cell>
           <cell r="U828">
-            <v>35888.15</v>
+            <v>35923.14</v>
           </cell>
           <cell r="V828">
-            <v>5374.2299999999959</v>
+            <v>5339.239999999998</v>
           </cell>
         </row>
         <row r="829">
@@ -46901,25 +46901,25 @@
             <v>35372.419999999991</v>
           </cell>
           <cell r="O829">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P829">
-            <v>549.29999999999995</v>
+            <v>549.29</v>
           </cell>
           <cell r="Q829">
             <v>14.66</v>
           </cell>
           <cell r="R829">
-            <v>35936.379999999997</v>
+            <v>35971.369999999995</v>
           </cell>
           <cell r="T829">
             <v>0</v>
           </cell>
           <cell r="U829">
-            <v>35936.379999999997</v>
+            <v>35971.369999999995</v>
           </cell>
           <cell r="V829">
-            <v>5326</v>
+            <v>5291.010000000002</v>
           </cell>
         </row>
         <row r="830">
@@ -46954,25 +46954,25 @@
             <v>35597.899999999994</v>
           </cell>
           <cell r="O830">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P830">
-            <v>549.29999999999995</v>
+            <v>549.29</v>
           </cell>
           <cell r="Q830">
             <v>14.66</v>
           </cell>
           <cell r="R830">
-            <v>36161.86</v>
+            <v>36196.85</v>
           </cell>
           <cell r="T830">
             <v>0</v>
           </cell>
           <cell r="U830">
-            <v>36161.86</v>
+            <v>36196.85</v>
           </cell>
           <cell r="V830">
-            <v>5100.5199999999968</v>
+            <v>5065.5299999999988</v>
           </cell>
         </row>
         <row r="831">
@@ -47007,25 +47007,25 @@
             <v>35883.49</v>
           </cell>
           <cell r="O831">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P831">
-            <v>531.29999999999995</v>
+            <v>531.29</v>
           </cell>
           <cell r="Q831">
             <v>14.66</v>
           </cell>
           <cell r="R831">
-            <v>36429.450000000004</v>
+            <v>36464.44</v>
           </cell>
           <cell r="T831">
             <v>0</v>
           </cell>
           <cell r="U831">
-            <v>36429.450000000004</v>
+            <v>36464.44</v>
           </cell>
           <cell r="V831">
-            <v>4832.929999999993</v>
+            <v>4797.9399999999951</v>
           </cell>
         </row>
         <row r="832">
@@ -47057,28 +47057,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N832">
-            <v>22576.87</v>
+            <v>35462.68</v>
           </cell>
           <cell r="O832">
-            <v>12885.81</v>
+            <v>35</v>
           </cell>
           <cell r="P832">
-            <v>549.29999999999995</v>
+            <v>549.29</v>
           </cell>
           <cell r="Q832">
             <v>14.66</v>
           </cell>
           <cell r="R832">
-            <v>36026.640000000007</v>
+            <v>36061.630000000005</v>
           </cell>
           <cell r="T832">
             <v>0</v>
           </cell>
           <cell r="U832">
-            <v>36026.640000000007</v>
+            <v>36061.630000000005</v>
           </cell>
           <cell r="V832">
-            <v>5235.7399999999907</v>
+            <v>5200.7499999999927</v>
           </cell>
         </row>
         <row r="833">
@@ -47110,28 +47110,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N833">
-            <v>25086.31</v>
+            <v>37972.120000000003</v>
           </cell>
           <cell r="O833">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P833">
-            <v>13435.09</v>
+            <v>549.29</v>
           </cell>
           <cell r="Q833">
             <v>14.66</v>
           </cell>
           <cell r="R833">
-            <v>38536.060000000005</v>
+            <v>38571.070000000007</v>
           </cell>
           <cell r="T833">
-            <v>2726.3199999999924</v>
+            <v>0</v>
           </cell>
           <cell r="U833">
-            <v>41262.379999999997</v>
+            <v>38571.070000000007</v>
           </cell>
           <cell r="V833">
-            <v>0</v>
+            <v>2691.3099999999904</v>
           </cell>
         </row>
         <row r="834">
@@ -47166,25 +47166,25 @@
             <v>23311.039999999997</v>
           </cell>
           <cell r="O834">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P834">
-            <v>13435.09</v>
+            <v>13435.1</v>
           </cell>
           <cell r="Q834">
-            <v>14.66</v>
+            <v>3359.33</v>
           </cell>
           <cell r="R834">
-            <v>36760.79</v>
+            <v>40140.47</v>
           </cell>
           <cell r="T834">
-            <v>4501.5899999999965</v>
+            <v>0</v>
           </cell>
           <cell r="U834">
-            <v>41262.379999999997</v>
+            <v>40140.47</v>
           </cell>
           <cell r="V834">
-            <v>0</v>
+            <v>1121.9099999999962</v>
           </cell>
         </row>
         <row r="835">
@@ -47216,28 +47216,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N835">
-            <v>23302.639999999996</v>
+            <v>25302.639999999996</v>
           </cell>
           <cell r="O835">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P835">
-            <v>13435.09</v>
+            <v>13435.1</v>
           </cell>
           <cell r="Q835">
-            <v>14.66</v>
+            <v>3359.33</v>
           </cell>
           <cell r="R835">
-            <v>36752.39</v>
+            <v>42132.07</v>
           </cell>
           <cell r="T835">
-            <v>4509.989999999998</v>
+            <v>0</v>
           </cell>
           <cell r="U835">
-            <v>41262.379999999997</v>
+            <v>42132.07</v>
           </cell>
           <cell r="V835">
-            <v>0</v>
+            <v>-869.69000000000233</v>
           </cell>
         </row>
         <row r="836">
@@ -47269,28 +47269,28 @@
             <v>41262.379999999997</v>
           </cell>
           <cell r="N836">
-            <v>23879.829999999998</v>
+            <v>25049.829999999998</v>
           </cell>
           <cell r="O836">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P836">
-            <v>13435.09</v>
+            <v>13435.1</v>
           </cell>
           <cell r="Q836">
-            <v>14.66</v>
+            <v>3359.33</v>
           </cell>
           <cell r="R836">
-            <v>37329.58</v>
+            <v>41879.26</v>
           </cell>
           <cell r="T836">
-            <v>3932.7999999999956</v>
+            <v>0</v>
           </cell>
           <cell r="U836">
-            <v>41262.379999999997</v>
+            <v>41879.26</v>
           </cell>
           <cell r="V836">
-            <v>0</v>
+            <v>-616.88000000000466</v>
           </cell>
         </row>
         <row r="837">
@@ -47325,7 +47325,7 @@
             <v>-455.04000000000013</v>
           </cell>
           <cell r="O837">
-            <v>0</v>
+            <v>35</v>
           </cell>
           <cell r="P837">
             <v>0</v>
@@ -47334,10 +47334,10 @@
             <v>0</v>
           </cell>
           <cell r="R837">
-            <v>-455.04000000000013</v>
+            <v>-420.04000000000013</v>
           </cell>
           <cell r="T837">
-            <v>455.04000000000013</v>
+            <v>420.04000000000013</v>
           </cell>
           <cell r="U837">
             <v>0</v>
@@ -47710,28 +47710,28 @@
             <v>523651.85000000015</v>
           </cell>
           <cell r="N845">
-            <v>64633.14</v>
+            <v>78628.340000000011</v>
           </cell>
           <cell r="O845">
-            <v>13070.71</v>
+            <v>1751.4</v>
           </cell>
           <cell r="P845">
-            <v>188651.67</v>
+            <v>188651.64</v>
           </cell>
           <cell r="Q845">
             <v>175</v>
           </cell>
           <cell r="R845">
-            <v>266530.52</v>
+            <v>269206.38</v>
           </cell>
           <cell r="T845">
-            <v>45311.9</v>
+            <v>45311.909999999996</v>
           </cell>
           <cell r="U845">
-            <v>311842.42000000004</v>
+            <v>314518.28999999998</v>
           </cell>
           <cell r="V845">
-            <v>211809.43000000011</v>
+            <v>209133.56000000017</v>
           </cell>
         </row>
         <row r="846">
@@ -47751,28 +47751,28 @@
             <v>523651.85000000015</v>
           </cell>
           <cell r="N846">
-            <v>64633.14</v>
+            <v>78628.340000000011</v>
           </cell>
           <cell r="O846">
-            <v>13070.71</v>
+            <v>1751.4</v>
           </cell>
           <cell r="P846">
-            <v>188651.67</v>
+            <v>188651.64</v>
           </cell>
           <cell r="Q846">
             <v>175</v>
           </cell>
           <cell r="R846">
-            <v>266530.52</v>
+            <v>269206.38</v>
           </cell>
           <cell r="T846">
-            <v>45311.9</v>
+            <v>45311.909999999996</v>
           </cell>
           <cell r="U846">
-            <v>311842.42000000004</v>
+            <v>314518.28999999998</v>
           </cell>
           <cell r="V846">
-            <v>211809.43000000011</v>
+            <v>209133.56000000017</v>
           </cell>
         </row>
         <row r="847">
@@ -47804,10 +47804,10 @@
             <v>19931.82</v>
           </cell>
           <cell r="N847">
-            <v>751.14</v>
+            <v>2982.27</v>
           </cell>
           <cell r="O847">
-            <v>2231.13</v>
+            <v>0</v>
           </cell>
           <cell r="P847">
             <v>11648.86</v>
@@ -47863,16 +47863,16 @@
             <v>0</v>
           </cell>
           <cell r="P848">
-            <v>14330.019999999999</v>
+            <v>14330.01</v>
           </cell>
           <cell r="Q848">
             <v>175</v>
           </cell>
           <cell r="R848">
-            <v>18485.75</v>
+            <v>18485.740000000002</v>
           </cell>
           <cell r="T848">
-            <v>5655.3300000000017</v>
+            <v>5655.34</v>
           </cell>
           <cell r="U848">
             <v>24141.08</v>
@@ -47916,22 +47916,22 @@
             <v>0</v>
           </cell>
           <cell r="P849">
-            <v>11952.64</v>
+            <v>11952.65</v>
           </cell>
           <cell r="Q849">
             <v>0</v>
           </cell>
           <cell r="R849">
-            <v>14920.22</v>
+            <v>14920.23</v>
           </cell>
           <cell r="T849">
             <v>1982.0000000000018</v>
           </cell>
           <cell r="U849">
-            <v>16902.22</v>
+            <v>16902.230000000003</v>
           </cell>
           <cell r="V849">
-            <v>14450.669999999998</v>
+            <v>14450.659999999996</v>
           </cell>
         </row>
         <row r="850">
@@ -47969,22 +47969,22 @@
             <v>0</v>
           </cell>
           <cell r="P850">
-            <v>10046.76</v>
+            <v>10046.75</v>
           </cell>
           <cell r="Q850">
             <v>0</v>
           </cell>
           <cell r="R850">
-            <v>14407.37</v>
+            <v>14407.36</v>
           </cell>
           <cell r="T850">
             <v>1981.9600000000009</v>
           </cell>
           <cell r="U850">
-            <v>16389.330000000002</v>
+            <v>16389.32</v>
           </cell>
           <cell r="V850">
-            <v>14963.559999999998</v>
+            <v>14963.57</v>
           </cell>
         </row>
         <row r="851">
@@ -48128,22 +48128,22 @@
             <v>0</v>
           </cell>
           <cell r="P853">
-            <v>13210.84</v>
+            <v>13210.829999999998</v>
           </cell>
           <cell r="Q853">
             <v>0</v>
           </cell>
           <cell r="R853">
-            <v>14406.97</v>
+            <v>14406.959999999997</v>
           </cell>
           <cell r="T853">
             <v>1982.0000000000018</v>
           </cell>
           <cell r="U853">
-            <v>16388.97</v>
+            <v>16388.96</v>
           </cell>
           <cell r="V853">
-            <v>14963.919999999998</v>
+            <v>14963.93</v>
           </cell>
         </row>
         <row r="854">
@@ -48181,22 +48181,22 @@
             <v>0</v>
           </cell>
           <cell r="P854">
-            <v>13210.84</v>
+            <v>13210.829999999998</v>
           </cell>
           <cell r="Q854">
             <v>0</v>
           </cell>
           <cell r="R854">
-            <v>14383.22</v>
+            <v>14383.209999999997</v>
           </cell>
           <cell r="T854">
             <v>1982.0000000000018</v>
           </cell>
           <cell r="U854">
-            <v>16365.220000000001</v>
+            <v>16365.21</v>
           </cell>
           <cell r="V854">
-            <v>14987.669999999998</v>
+            <v>14987.68</v>
           </cell>
         </row>
         <row r="855">
@@ -48234,22 +48234,22 @@
             <v>0</v>
           </cell>
           <cell r="P855">
-            <v>13210.84</v>
+            <v>13210.829999999998</v>
           </cell>
           <cell r="Q855">
             <v>0</v>
           </cell>
           <cell r="R855">
-            <v>14442.96</v>
+            <v>14442.949999999997</v>
           </cell>
           <cell r="T855">
             <v>1982</v>
           </cell>
           <cell r="U855">
-            <v>16424.96</v>
+            <v>16424.949999999997</v>
           </cell>
           <cell r="V855">
-            <v>14927.93</v>
+            <v>14927.940000000002</v>
           </cell>
         </row>
         <row r="856">
@@ -48287,22 +48287,22 @@
             <v>0</v>
           </cell>
           <cell r="P856">
-            <v>8023.38</v>
+            <v>8023.37</v>
           </cell>
           <cell r="Q856">
             <v>0</v>
           </cell>
           <cell r="R856">
-            <v>14382.66</v>
+            <v>14382.650000000001</v>
           </cell>
           <cell r="T856">
             <v>1981.9600000000009</v>
           </cell>
           <cell r="U856">
-            <v>16364.62</v>
+            <v>16364.610000000002</v>
           </cell>
           <cell r="V856">
-            <v>14988.269999999999</v>
+            <v>14988.279999999997</v>
           </cell>
         </row>
         <row r="857">
@@ -48334,28 +48334,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N857">
-            <v>53.14</v>
+            <v>80.490000000000009</v>
           </cell>
           <cell r="O857">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P857">
-            <v>14330.019999999999</v>
+            <v>14330.01</v>
           </cell>
           <cell r="Q857">
             <v>0</v>
           </cell>
           <cell r="R857">
-            <v>14758.439999999999</v>
+            <v>14660.7</v>
           </cell>
           <cell r="T857">
             <v>2357.2999999999993</v>
           </cell>
           <cell r="U857">
-            <v>17115.739999999998</v>
+            <v>17018</v>
           </cell>
           <cell r="V857">
-            <v>14237.150000000001</v>
+            <v>14334.89</v>
           </cell>
         </row>
         <row r="858">
@@ -48387,28 +48387,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N858">
-            <v>7119.2000000000007</v>
+            <v>7146.5500000000011</v>
           </cell>
           <cell r="O858">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P858">
-            <v>7263.869999999999</v>
+            <v>7263.8799999999992</v>
           </cell>
           <cell r="Q858">
             <v>0</v>
           </cell>
           <cell r="R858">
-            <v>14758.349999999999</v>
+            <v>14660.630000000001</v>
           </cell>
           <cell r="T858">
             <v>2357.3100000000013</v>
           </cell>
           <cell r="U858">
-            <v>17115.66</v>
+            <v>17017.940000000002</v>
           </cell>
           <cell r="V858">
-            <v>14237.23</v>
+            <v>14334.949999999997</v>
           </cell>
         </row>
         <row r="859">
@@ -48440,28 +48440,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N859">
-            <v>10526.490000000002</v>
+            <v>10553.840000000002</v>
           </cell>
           <cell r="O859">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P859">
-            <v>3856.2</v>
+            <v>3856.19</v>
           </cell>
           <cell r="Q859">
             <v>0</v>
           </cell>
           <cell r="R859">
-            <v>14757.970000000001</v>
+            <v>14660.230000000003</v>
           </cell>
           <cell r="T859">
             <v>2357.2999999999993</v>
           </cell>
           <cell r="U859">
-            <v>17115.27</v>
+            <v>17017.530000000002</v>
           </cell>
           <cell r="V859">
-            <v>14237.619999999999</v>
+            <v>14335.359999999997</v>
           </cell>
         </row>
         <row r="860">
@@ -48493,28 +48493,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N860">
-            <v>6983.4900000000007</v>
+            <v>7010.8400000000011</v>
           </cell>
           <cell r="O860">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P860">
-            <v>7400.01</v>
+            <v>7400.02</v>
           </cell>
           <cell r="Q860">
             <v>0</v>
           </cell>
           <cell r="R860">
-            <v>14758.78</v>
+            <v>14661.060000000001</v>
           </cell>
           <cell r="T860">
             <v>2356.9599999999973</v>
           </cell>
           <cell r="U860">
-            <v>17115.739999999998</v>
+            <v>17018.019999999997</v>
           </cell>
           <cell r="V860">
-            <v>14237.150000000001</v>
+            <v>14334.870000000003</v>
           </cell>
         </row>
         <row r="861">
@@ -48546,28 +48546,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N861">
-            <v>6983.56</v>
+            <v>7010.9100000000008</v>
           </cell>
           <cell r="O861">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P861">
-            <v>7400.01</v>
+            <v>7400.02</v>
           </cell>
           <cell r="Q861">
             <v>0</v>
           </cell>
           <cell r="R861">
-            <v>14758.85</v>
+            <v>14661.130000000001</v>
           </cell>
           <cell r="T861">
             <v>2356.8899999999976</v>
           </cell>
           <cell r="U861">
-            <v>17115.739999999998</v>
+            <v>17018.019999999997</v>
           </cell>
           <cell r="V861">
-            <v>14237.150000000001</v>
+            <v>14334.870000000003</v>
           </cell>
         </row>
         <row r="862">
@@ -48599,28 +48599,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N862">
-            <v>6983.4900000000007</v>
+            <v>7790.8400000000011</v>
           </cell>
           <cell r="O862">
-            <v>375.28</v>
+            <v>250.2</v>
           </cell>
           <cell r="P862">
-            <v>7400.01</v>
+            <v>7400.02</v>
           </cell>
           <cell r="Q862">
             <v>0</v>
           </cell>
           <cell r="R862">
-            <v>14758.78</v>
+            <v>15441.060000000001</v>
           </cell>
           <cell r="T862">
             <v>2356.9599999999973</v>
           </cell>
           <cell r="U862">
-            <v>17115.739999999998</v>
+            <v>17798.019999999997</v>
           </cell>
           <cell r="V862">
-            <v>14237.150000000001</v>
+            <v>13554.870000000003</v>
           </cell>
         </row>
         <row r="863">
@@ -48652,28 +48652,28 @@
             <v>31352.89</v>
           </cell>
           <cell r="N863">
-            <v>53.14</v>
+            <v>10873.11</v>
           </cell>
           <cell r="O863">
-            <v>8587.9000000000015</v>
+            <v>250.2</v>
           </cell>
           <cell r="P863">
-            <v>6117.4699999999993</v>
+            <v>6117.48</v>
           </cell>
           <cell r="Q863">
             <v>0</v>
           </cell>
           <cell r="R863">
-            <v>14758.51</v>
+            <v>17240.79</v>
           </cell>
           <cell r="T863">
             <v>2357.2299999999959</v>
           </cell>
           <cell r="U863">
-            <v>17115.739999999998</v>
+            <v>19598.019999999997</v>
           </cell>
           <cell r="V863">
-            <v>14237.150000000001</v>
+            <v>11754.870000000003</v>
           </cell>
         </row>
         <row r="864">
@@ -48711,22 +48711,22 @@
             <v>0</v>
           </cell>
           <cell r="P864">
-            <v>14330.019999999999</v>
+            <v>14330.01</v>
           </cell>
           <cell r="Q864">
             <v>0</v>
           </cell>
           <cell r="R864">
-            <v>14330.019999999999</v>
+            <v>14330.01</v>
           </cell>
           <cell r="T864">
             <v>2000.0100000000002</v>
           </cell>
           <cell r="U864">
-            <v>16330.029999999999</v>
+            <v>16330.02</v>
           </cell>
           <cell r="V864">
-            <v>-7044.4299999999985</v>
+            <v>-7044.42</v>
           </cell>
         </row>
         <row r="865">
@@ -48746,28 +48746,28 @@
             <v>332545.65000000002</v>
           </cell>
           <cell r="N865">
-            <v>493526.97999999986</v>
+            <v>573863.14999999991</v>
           </cell>
           <cell r="O865">
-            <v>76704.799999999988</v>
+            <v>109025.22</v>
           </cell>
           <cell r="P865">
-            <v>145093.53000000003</v>
+            <v>159953.03</v>
           </cell>
           <cell r="Q865">
-            <v>45257.88</v>
+            <v>6323.1100000000006</v>
           </cell>
           <cell r="R865">
-            <v>760583.18999999983</v>
+            <v>849164.50999999989</v>
           </cell>
           <cell r="T865">
-            <v>39429.739999999991</v>
+            <v>-40000</v>
           </cell>
           <cell r="U865">
-            <v>800012.92999999982</v>
+            <v>809164.50999999989</v>
           </cell>
           <cell r="V865">
-            <v>-467467.2799999998</v>
+            <v>-476618.85999999987</v>
           </cell>
         </row>
         <row r="866">
@@ -48787,10 +48787,10 @@
             <v>186326.13</v>
           </cell>
           <cell r="N866">
-            <v>437559.98999999987</v>
+            <v>496309.65999999986</v>
           </cell>
           <cell r="O866">
-            <v>38246.359999999993</v>
+            <v>40194.200000000004</v>
           </cell>
           <cell r="P866">
             <v>0</v>
@@ -48799,16 +48799,16 @@
             <v>0</v>
           </cell>
           <cell r="R866">
-            <v>475806.34999999986</v>
+            <v>536503.85999999987</v>
           </cell>
           <cell r="T866">
-            <v>20000</v>
+            <v>40000</v>
           </cell>
           <cell r="U866">
-            <v>495806.34999999986</v>
+            <v>576503.85999999987</v>
           </cell>
           <cell r="V866">
-            <v>-309480.21999999986</v>
+            <v>-390177.72999999986</v>
           </cell>
         </row>
         <row r="867">
@@ -48946,10 +48946,10 @@
             <v>146212.53</v>
           </cell>
           <cell r="N869">
-            <v>420410.16999999987</v>
+            <v>479159.83999999985</v>
           </cell>
           <cell r="O869">
-            <v>38246.359999999993</v>
+            <v>40194.200000000004</v>
           </cell>
           <cell r="P869">
             <v>0</v>
@@ -48958,16 +48958,16 @@
             <v>0</v>
           </cell>
           <cell r="R869">
-            <v>458656.52999999985</v>
+            <v>519354.03999999986</v>
           </cell>
           <cell r="T869">
-            <v>20000</v>
+            <v>40000</v>
           </cell>
           <cell r="U869">
-            <v>478656.52999999985</v>
+            <v>559354.0399999998</v>
           </cell>
           <cell r="V869">
-            <v>-332443.99999999988</v>
+            <v>-413141.50999999978</v>
           </cell>
         </row>
         <row r="870">
@@ -48987,28 +48987,28 @@
             <v>146219.52000000002</v>
           </cell>
           <cell r="N870">
-            <v>55966.990000000005</v>
+            <v>77553.490000000005</v>
           </cell>
           <cell r="O870">
-            <v>38458.44</v>
+            <v>68831.01999999999</v>
           </cell>
           <cell r="P870">
-            <v>145093.53000000003</v>
+            <v>159953.03</v>
           </cell>
           <cell r="Q870">
-            <v>45257.88</v>
+            <v>6323.1100000000006</v>
           </cell>
           <cell r="R870">
-            <v>284776.84000000003</v>
+            <v>312660.65000000002</v>
           </cell>
           <cell r="T870">
-            <v>19429.739999999991</v>
+            <v>-80000</v>
           </cell>
           <cell r="U870">
-            <v>304206.58</v>
+            <v>232660.65000000002</v>
           </cell>
           <cell r="V870">
-            <v>-157987.06</v>
+            <v>-86441.13</v>
           </cell>
         </row>
         <row r="871">
@@ -49040,28 +49040,28 @@
             <v>106219.52</v>
           </cell>
           <cell r="N871">
-            <v>16368.9</v>
+            <v>36325.4</v>
           </cell>
           <cell r="O871">
-            <v>36828.44</v>
+            <v>68831.01999999999</v>
           </cell>
           <cell r="P871">
-            <v>145093.53000000003</v>
+            <v>159953.03</v>
           </cell>
           <cell r="Q871">
-            <v>45257.88</v>
+            <v>6323.1100000000006</v>
           </cell>
           <cell r="R871">
-            <v>243548.75000000003</v>
+            <v>271432.55999999994</v>
           </cell>
           <cell r="T871">
-            <v>19429.739999999991</v>
+            <v>-80000</v>
           </cell>
           <cell r="U871">
-            <v>262978.49</v>
+            <v>191432.55999999994</v>
           </cell>
           <cell r="V871">
-            <v>-156758.96999999997</v>
+            <v>-85213.039999999935</v>
           </cell>
         </row>
         <row r="872">
@@ -49093,10 +49093,10 @@
             <v>40000</v>
           </cell>
           <cell r="N872">
-            <v>39598.090000000004</v>
+            <v>41228.090000000004</v>
           </cell>
           <cell r="O872">
-            <v>1630</v>
+            <v>0</v>
           </cell>
           <cell r="P872">
             <v>0</v>
@@ -49134,10 +49134,10 @@
             <v>355821.09</v>
           </cell>
           <cell r="N873">
-            <v>67359.26999999999</v>
+            <v>81509.98</v>
           </cell>
           <cell r="O873">
-            <v>14150.710000000001</v>
+            <v>5926.41</v>
           </cell>
           <cell r="P873">
             <v>0</v>
@@ -49146,10 +49146,10 @@
             <v>0</v>
           </cell>
           <cell r="R873">
-            <v>81509.98</v>
+            <v>87436.39</v>
           </cell>
           <cell r="T873">
-            <v>230451.89</v>
+            <v>224525.48</v>
           </cell>
           <cell r="U873">
             <v>311961.87</v>
@@ -49322,10 +49322,10 @@
             <v>191813.07</v>
           </cell>
           <cell r="N877">
-            <v>66734.76999999999</v>
+            <v>80885.48</v>
           </cell>
           <cell r="O877">
-            <v>14150.710000000001</v>
+            <v>5926.41</v>
           </cell>
           <cell r="P877">
             <v>0</v>
@@ -49334,10 +49334,10 @@
             <v>0</v>
           </cell>
           <cell r="R877">
-            <v>80885.48</v>
+            <v>86811.89</v>
           </cell>
           <cell r="T877">
-            <v>67068.37000000001</v>
+            <v>61141.96</v>
           </cell>
           <cell r="U877">
             <v>147953.85</v>
@@ -49375,10 +49375,10 @@
             <v>126999.44</v>
           </cell>
           <cell r="N878">
-            <v>26888.769999999997</v>
+            <v>41039.479999999996</v>
           </cell>
           <cell r="O878">
-            <v>14150.710000000001</v>
+            <v>5926.41</v>
           </cell>
           <cell r="P878">
             <v>0</v>
@@ -49387,10 +49387,10 @@
             <v>0</v>
           </cell>
           <cell r="R878">
-            <v>41039.479999999996</v>
+            <v>46965.89</v>
           </cell>
           <cell r="T878">
-            <v>11500.830000000002</v>
+            <v>5574.4199999999983</v>
           </cell>
           <cell r="U878">
             <v>52540.31</v>
@@ -49710,28 +49710,28 @@
             <v>461189.67000000004</v>
           </cell>
           <cell r="N885">
-            <v>132112.32000000001</v>
+            <v>173651.19999999998</v>
           </cell>
           <cell r="O885">
-            <v>41538.880000000005</v>
+            <v>41538.879999999997</v>
           </cell>
           <cell r="P885">
-            <v>41538.879999999997</v>
+            <v>0</v>
           </cell>
           <cell r="Q885">
             <v>0</v>
           </cell>
           <cell r="R885">
-            <v>215190.08000000002</v>
+            <v>215190.08</v>
           </cell>
           <cell r="T885">
-            <v>245999.59</v>
+            <v>14352.44</v>
           </cell>
           <cell r="U885">
-            <v>461189.67000000004</v>
+            <v>229542.52</v>
           </cell>
           <cell r="V885">
-            <v>0</v>
+            <v>231647.15000000005</v>
           </cell>
         </row>
         <row r="886">
@@ -49751,13 +49751,13 @@
             <v>356703.78</v>
           </cell>
           <cell r="N886">
-            <v>124616.65</v>
+            <v>162903.87</v>
           </cell>
           <cell r="O886">
-            <v>38287.22</v>
+            <v>425.12</v>
           </cell>
           <cell r="P886">
-            <v>425.12</v>
+            <v>0</v>
           </cell>
           <cell r="Q886">
             <v>0</v>
@@ -49766,13 +49766,13 @@
             <v>163328.99</v>
           </cell>
           <cell r="T886">
-            <v>193374.79</v>
+            <v>0</v>
           </cell>
           <cell r="U886">
-            <v>356703.78</v>
+            <v>163328.99</v>
           </cell>
           <cell r="V886">
-            <v>0</v>
+            <v>193374.79000000004</v>
           </cell>
         </row>
         <row r="887">
@@ -49804,10 +49804,10 @@
             <v>166326.19</v>
           </cell>
           <cell r="N887">
-            <v>90176.65</v>
+            <v>104319.31</v>
           </cell>
           <cell r="O887">
-            <v>14142.66</v>
+            <v>0</v>
           </cell>
           <cell r="P887">
             <v>0</v>
@@ -49819,13 +49819,13 @@
             <v>104319.31</v>
           </cell>
           <cell r="T887">
+            <v>0</v>
+          </cell>
+          <cell r="U887">
+            <v>104319.31</v>
+          </cell>
+          <cell r="V887">
             <v>62006.880000000005</v>
-          </cell>
-          <cell r="U887">
-            <v>166326.19</v>
-          </cell>
-          <cell r="V887">
-            <v>0</v>
           </cell>
         </row>
         <row r="888">
@@ -49857,10 +49857,10 @@
             <v>1386.05</v>
           </cell>
           <cell r="N888">
-            <v>0</v>
+            <v>869.34</v>
           </cell>
           <cell r="O888">
-            <v>869.34</v>
+            <v>0</v>
           </cell>
           <cell r="P888">
             <v>0</v>
@@ -49872,13 +49872,13 @@
             <v>869.34</v>
           </cell>
           <cell r="T888">
+            <v>0</v>
+          </cell>
+          <cell r="U888">
+            <v>869.34</v>
+          </cell>
+          <cell r="V888">
             <v>516.70999999999992</v>
-          </cell>
-          <cell r="U888">
-            <v>1386.05</v>
-          </cell>
-          <cell r="V888">
-            <v>0</v>
           </cell>
         </row>
         <row r="889">
@@ -49910,10 +49910,10 @@
             <v>2772.1</v>
           </cell>
           <cell r="N889">
-            <v>0</v>
+            <v>2904.02</v>
           </cell>
           <cell r="O889">
-            <v>2904.02</v>
+            <v>0</v>
           </cell>
           <cell r="P889">
             <v>0</v>
@@ -49925,13 +49925,13 @@
             <v>2904.02</v>
           </cell>
           <cell r="T889">
+            <v>0</v>
+          </cell>
+          <cell r="U889">
+            <v>2904.02</v>
+          </cell>
+          <cell r="V889">
             <v>-131.92000000000007</v>
-          </cell>
-          <cell r="U889">
-            <v>2772.1</v>
-          </cell>
-          <cell r="V889">
-            <v>0</v>
           </cell>
         </row>
         <row r="890">
@@ -49963,10 +49963,10 @@
             <v>129563.78</v>
           </cell>
           <cell r="N890">
-            <v>0</v>
+            <v>20371.2</v>
           </cell>
           <cell r="O890">
-            <v>20371.2</v>
+            <v>0</v>
           </cell>
           <cell r="P890">
             <v>0</v>
@@ -49978,13 +49978,13 @@
             <v>20371.2</v>
           </cell>
           <cell r="T890">
+            <v>0</v>
+          </cell>
+          <cell r="U890">
+            <v>20371.2</v>
+          </cell>
+          <cell r="V890">
             <v>109192.58</v>
-          </cell>
-          <cell r="U890">
-            <v>129563.78</v>
-          </cell>
-          <cell r="V890">
-            <v>0</v>
           </cell>
         </row>
         <row r="891">
@@ -50031,13 +50031,13 @@
             <v>0</v>
           </cell>
           <cell r="T891">
+            <v>0</v>
+          </cell>
+          <cell r="U891">
+            <v>0</v>
+          </cell>
+          <cell r="V891">
             <v>1079.7</v>
-          </cell>
-          <cell r="U891">
-            <v>1079.7</v>
-          </cell>
-          <cell r="V891">
-            <v>0</v>
           </cell>
         </row>
         <row r="892">
@@ -50072,10 +50072,10 @@
             <v>0</v>
           </cell>
           <cell r="O892">
-            <v>0</v>
+            <v>425.12</v>
           </cell>
           <cell r="P892">
-            <v>425.12</v>
+            <v>0</v>
           </cell>
           <cell r="Q892">
             <v>0</v>
@@ -50084,13 +50084,13 @@
             <v>425.12</v>
           </cell>
           <cell r="T892">
+            <v>0</v>
+          </cell>
+          <cell r="U892">
+            <v>425.12</v>
+          </cell>
+          <cell r="V892">
             <v>1734.2800000000002</v>
-          </cell>
-          <cell r="U892">
-            <v>2159.4</v>
-          </cell>
-          <cell r="V892">
-            <v>0</v>
           </cell>
         </row>
         <row r="893">
@@ -50137,13 +50137,13 @@
             <v>34440</v>
           </cell>
           <cell r="T893">
+            <v>0</v>
+          </cell>
+          <cell r="U893">
+            <v>34440</v>
+          </cell>
+          <cell r="V893">
             <v>18976.559999999998</v>
-          </cell>
-          <cell r="U893">
-            <v>53416.56</v>
-          </cell>
-          <cell r="V893">
-            <v>0</v>
           </cell>
         </row>
         <row r="894">
@@ -50163,13 +50163,13 @@
             <v>104485.88999999998</v>
           </cell>
           <cell r="N894">
-            <v>7495.67</v>
+            <v>10747.33</v>
           </cell>
           <cell r="O894">
-            <v>3251.66</v>
+            <v>41113.759999999995</v>
           </cell>
           <cell r="P894">
-            <v>41113.759999999995</v>
+            <v>0</v>
           </cell>
           <cell r="Q894">
             <v>0</v>
@@ -50178,13 +50178,13 @@
             <v>51861.09</v>
           </cell>
           <cell r="T894">
-            <v>52624.799999999996</v>
+            <v>14352.44</v>
           </cell>
           <cell r="U894">
-            <v>104485.88999999998</v>
+            <v>66213.53</v>
           </cell>
           <cell r="V894">
-            <v>0</v>
+            <v>38272.359999999986</v>
           </cell>
         </row>
         <row r="895">
@@ -50231,13 +50231,13 @@
             <v>7495.67</v>
           </cell>
           <cell r="T895">
+            <v>0</v>
+          </cell>
+          <cell r="U895">
+            <v>7495.67</v>
+          </cell>
+          <cell r="V895">
             <v>19674.059999999998</v>
-          </cell>
-          <cell r="U895">
-            <v>27169.729999999996</v>
-          </cell>
-          <cell r="V895">
-            <v>0</v>
           </cell>
         </row>
         <row r="896">
@@ -50378,10 +50378,10 @@
             <v>0</v>
           </cell>
           <cell r="O898">
-            <v>0</v>
+            <v>1017.63</v>
           </cell>
           <cell r="P898">
-            <v>1017.63</v>
+            <v>0</v>
           </cell>
           <cell r="Q898">
             <v>0</v>
@@ -50481,13 +50481,13 @@
             <v>16186.17</v>
           </cell>
           <cell r="N900">
-            <v>0</v>
+            <v>3251.66</v>
           </cell>
           <cell r="O900">
-            <v>3251.66</v>
+            <v>6947.27</v>
           </cell>
           <cell r="P900">
-            <v>6947.27</v>
+            <v>0</v>
           </cell>
           <cell r="Q900">
             <v>0</v>
@@ -50496,13 +50496,13 @@
             <v>10198.93</v>
           </cell>
           <cell r="T900">
+            <v>0</v>
+          </cell>
+          <cell r="U900">
+            <v>10198.93</v>
+          </cell>
+          <cell r="V900">
             <v>5987.24</v>
-          </cell>
-          <cell r="U900">
-            <v>16186.17</v>
-          </cell>
-          <cell r="V900">
-            <v>0</v>
           </cell>
         </row>
         <row r="901">
@@ -50537,10 +50537,10 @@
             <v>0</v>
           </cell>
           <cell r="O901">
-            <v>0</v>
+            <v>21141.599999999999</v>
           </cell>
           <cell r="P901">
-            <v>21141.599999999999</v>
+            <v>0</v>
           </cell>
           <cell r="Q901">
             <v>0</v>
@@ -50549,13 +50549,13 @@
             <v>21141.599999999999</v>
           </cell>
           <cell r="T901">
+            <v>0</v>
+          </cell>
+          <cell r="U901">
+            <v>21141.599999999999</v>
+          </cell>
+          <cell r="V901">
             <v>8887.2000000000007</v>
-          </cell>
-          <cell r="U901">
-            <v>30028.799999999999</v>
-          </cell>
-          <cell r="V901">
-            <v>0</v>
           </cell>
         </row>
         <row r="902">
@@ -50590,10 +50590,10 @@
             <v>0</v>
           </cell>
           <cell r="O902">
-            <v>0</v>
+            <v>91.12</v>
           </cell>
           <cell r="P902">
-            <v>91.12</v>
+            <v>0</v>
           </cell>
           <cell r="Q902">
             <v>0</v>
@@ -50643,10 +50643,10 @@
             <v>0</v>
           </cell>
           <cell r="O903">
-            <v>0</v>
+            <v>10934.4</v>
           </cell>
           <cell r="P903">
-            <v>10934.4</v>
+            <v>0</v>
           </cell>
           <cell r="Q903">
             <v>0</v>
@@ -50655,13 +50655,13 @@
             <v>10934.4</v>
           </cell>
           <cell r="T903">
+            <v>0</v>
+          </cell>
+          <cell r="U903">
+            <v>10934.4</v>
+          </cell>
+          <cell r="V903">
             <v>4080</v>
-          </cell>
-          <cell r="U903">
-            <v>15014.4</v>
-          </cell>
-          <cell r="V903">
-            <v>0</v>
           </cell>
         </row>
         <row r="904">
@@ -50696,10 +50696,10 @@
             <v>0</v>
           </cell>
           <cell r="O904">
-            <v>0</v>
+            <v>176.18</v>
           </cell>
           <cell r="P904">
-            <v>176.18</v>
+            <v>0</v>
           </cell>
           <cell r="Q904">
             <v>0</v>
@@ -50708,13 +50708,13 @@
             <v>176.18</v>
           </cell>
           <cell r="T904">
+            <v>0</v>
+          </cell>
+          <cell r="U904">
+            <v>176.18</v>
+          </cell>
+          <cell r="V904">
             <v>-51.06</v>
-          </cell>
-          <cell r="U904">
-            <v>125.12</v>
-          </cell>
-          <cell r="V904">
-            <v>0</v>
           </cell>
         </row>
         <row r="905">
@@ -50749,10 +50749,10 @@
             <v>0</v>
           </cell>
           <cell r="O905">
-            <v>0</v>
+            <v>805.56</v>
           </cell>
           <cell r="P905">
-            <v>805.56</v>
+            <v>0</v>
           </cell>
           <cell r="Q905">
             <v>0</v>
@@ -50761,13 +50761,13 @@
             <v>805.56</v>
           </cell>
           <cell r="T905">
+            <v>0</v>
+          </cell>
+          <cell r="U905">
+            <v>805.56</v>
+          </cell>
+          <cell r="V905">
             <v>-305.07999999999993</v>
-          </cell>
-          <cell r="U905">
-            <v>500.48</v>
-          </cell>
-          <cell r="V905">
-            <v>0</v>
           </cell>
         </row>
         <row r="906">
@@ -52168,7 +52168,7 @@
             <v>45748</v>
           </cell>
           <cell r="F48">
-            <v>564642.35999999964</v>
+            <v>564642.35999999952</v>
           </cell>
           <cell r="G48">
             <v>0</v>
@@ -52180,7 +52180,7 @@
             <v>0</v>
           </cell>
           <cell r="J48">
-            <v>564642.35999999964</v>
+            <v>564642.35999999952</v>
           </cell>
         </row>
         <row r="49">
@@ -52488,19 +52488,19 @@
             <v>46235</v>
           </cell>
           <cell r="F64">
-            <v>0</v>
+            <v>1446362.6999999979</v>
           </cell>
           <cell r="G64">
-            <v>374270.22999999981</v>
+            <v>0</v>
           </cell>
           <cell r="H64">
-            <v>116711.15000000007</v>
+            <v>11333.33</v>
           </cell>
           <cell r="I64">
-            <v>24294.039999999997</v>
+            <v>0</v>
           </cell>
           <cell r="J64">
-            <v>515275.42000000051</v>
+            <v>1457696.0299999979</v>
           </cell>
         </row>
         <row r="65">
@@ -52511,16 +52511,16 @@
             <v>0</v>
           </cell>
           <cell r="G65">
-            <v>28556.610000000022</v>
+            <v>392909.62000000005</v>
           </cell>
           <cell r="H65">
-            <v>250980.36000000007</v>
+            <v>143976.28999999998</v>
           </cell>
           <cell r="I65">
-            <v>15178.140000000001</v>
+            <v>13962.84</v>
           </cell>
           <cell r="J65">
-            <v>294715.10999999993</v>
+            <v>550848.75000000035</v>
           </cell>
         </row>
         <row r="66">
@@ -52531,16 +52531,16 @@
             <v>0</v>
           </cell>
           <cell r="G66">
-            <v>24354.770000000011</v>
+            <v>37302.500000000007</v>
           </cell>
           <cell r="H66">
-            <v>214225.75000000009</v>
+            <v>201573.16</v>
           </cell>
           <cell r="I66">
-            <v>24970.289999999997</v>
+            <v>12533.44</v>
           </cell>
           <cell r="J66">
-            <v>263550.80999999988</v>
+            <v>251409.09999999974</v>
           </cell>
         </row>
         <row r="67">
@@ -52551,16 +52551,16 @@
             <v>0</v>
           </cell>
           <cell r="G67">
-            <v>9720.86</v>
+            <v>18896.22</v>
           </cell>
           <cell r="H67">
-            <v>281010.50999999995</v>
+            <v>462662.68000000011</v>
           </cell>
           <cell r="I67">
-            <v>214.95000000000007</v>
+            <v>45025.200000000019</v>
           </cell>
           <cell r="J67">
-            <v>290946.31999999995</v>
+            <v>526584.09999999986</v>
           </cell>
         </row>
         <row r="68">
@@ -52574,13 +52574,13 @@
             <v>55761.840000000004</v>
           </cell>
           <cell r="H68">
-            <v>62354.84</v>
+            <v>50192.45</v>
           </cell>
           <cell r="I68">
-            <v>0</v>
+            <v>7314.9399999999978</v>
           </cell>
           <cell r="J68">
-            <v>118116.68000000001</v>
+            <v>113269.22999999998</v>
           </cell>
         </row>
         <row r="69">
@@ -52594,13 +52594,13 @@
             <v>287576</v>
           </cell>
           <cell r="H69">
-            <v>159653.63000000003</v>
+            <v>105433.04000000001</v>
           </cell>
           <cell r="I69">
             <v>0</v>
           </cell>
           <cell r="J69">
-            <v>447229.63000000006</v>
+            <v>393009.04</v>
           </cell>
         </row>
         <row r="70">
@@ -52614,13 +52614,13 @@
             <v>1226</v>
           </cell>
           <cell r="H70">
-            <v>85084.569999999978</v>
+            <v>100509.37999999999</v>
           </cell>
           <cell r="I70">
             <v>0</v>
           </cell>
           <cell r="J70">
-            <v>86310.569999999963</v>
+            <v>101735.37999999999</v>
           </cell>
         </row>
         <row r="71">
@@ -52634,13 +52634,13 @@
             <v>1226</v>
           </cell>
           <cell r="H71">
-            <v>191066.37000000011</v>
+            <v>188686.06999999995</v>
           </cell>
           <cell r="I71">
             <v>0</v>
           </cell>
           <cell r="J71">
-            <v>192292.37000000011</v>
+            <v>189912.06999999995</v>
           </cell>
         </row>
         <row r="72">
@@ -52654,13 +52654,13 @@
             <v>1226</v>
           </cell>
           <cell r="H72">
-            <v>17596.669999999998</v>
+            <v>17596.689999999999</v>
           </cell>
           <cell r="I72">
             <v>0</v>
           </cell>
           <cell r="J72">
-            <v>18822.669999999998</v>
+            <v>18822.689999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -53098,7 +53098,7 @@
       </c>
       <c r="D2" s="2">
         <f>VLOOKUP($C2,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>529117.84000000008</v>
+        <v>531321.84000000008</v>
       </c>
       <c r="E2" s="2">
         <f>VLOOKUP($C2,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
@@ -53106,7 +53106,7 @@
       </c>
       <c r="F2" s="2">
         <f>VLOOKUP($C2,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>12289.9</v>
+        <v>10085.9</v>
       </c>
       <c r="G2" s="2">
         <f>VLOOKUP($C2,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -53218,35 +53218,35 @@
       </c>
       <c r="D3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>796464.32000000007</v>
+        <v>901606.7300000001</v>
       </c>
       <c r="E3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>44749.82</v>
+        <v>96522.340000000011</v>
       </c>
       <c r="F3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>68303.25</v>
+        <v>136235.72</v>
       </c>
       <c r="G3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>656.45</v>
+        <v>36692.490000000005</v>
       </c>
       <c r="H3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>910173.84</v>
+        <v>1171057.28</v>
       </c>
       <c r="I3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>240674.02999999997</v>
+        <v>187540.56</v>
       </c>
       <c r="J3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>1150847.8699999999</v>
+        <v>1358597.84</v>
       </c>
       <c r="K3" s="2">
         <f>VLOOKUP($C3,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>0</v>
+        <v>-207749.9700000002</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="5">
@@ -53338,35 +53338,35 @@
       </c>
       <c r="D4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>447658.82000000007</v>
+        <v>458680.4800000001</v>
       </c>
       <c r="E4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>11472.399999999998</v>
+        <v>9336.2000000000007</v>
       </c>
       <c r="F4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>62490.37</v>
+        <v>57455.7</v>
       </c>
       <c r="G4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>52.300000000000004</v>
+        <v>270.5</v>
       </c>
       <c r="H4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>521673.89000000007</v>
+        <v>525742.88000000012</v>
       </c>
       <c r="I4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>86517.679999999978</v>
+        <v>82970.019999999975</v>
       </c>
       <c r="J4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>608191.57000000007</v>
+        <v>608712.90000000014</v>
       </c>
       <c r="K4" s="2">
         <f>VLOOKUP($C4,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-66391.570000000065</v>
+        <v>-66912.90000000014</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="5">
@@ -53458,7 +53458,7 @@
       </c>
       <c r="D5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>119523.54</v>
+        <v>166807.29999999999</v>
       </c>
       <c r="E5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
@@ -53466,7 +53466,7 @@
       </c>
       <c r="F5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>114451.87</v>
+        <v>60024.62000000001</v>
       </c>
       <c r="G5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -53474,7 +53474,7 @@
       </c>
       <c r="H5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>233975.40999999997</v>
+        <v>226831.91999999998</v>
       </c>
       <c r="I5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -53482,11 +53482,11 @@
       </c>
       <c r="J5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>233975.40999999997</v>
+        <v>226831.91999999998</v>
       </c>
       <c r="K5" s="2">
         <f>VLOOKUP($C5,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>27918.410000000033</v>
+        <v>35061.900000000023</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="5">
@@ -53578,35 +53578,35 @@
       </c>
       <c r="D6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>627501.06000000006</v>
+        <v>652166.56999999995</v>
       </c>
       <c r="E6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>16747.489999999998</v>
+        <v>13173.1</v>
       </c>
       <c r="F6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>139270</v>
+        <v>128970.00000000001</v>
       </c>
       <c r="G6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>2359.23</v>
+        <v>2390.7600000000002</v>
       </c>
       <c r="H6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>785877.78</v>
+        <v>796700.42999999993</v>
       </c>
       <c r="I6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>79675.130000000019</v>
+        <v>75366</v>
       </c>
       <c r="J6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>865552.91</v>
+        <v>872066.42999999993</v>
       </c>
       <c r="K6" s="2">
         <f>VLOOKUP($C6,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>56254.489999999991</v>
+        <v>49740.970000000088</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="5">
@@ -53698,27 +53698,27 @@
       </c>
       <c r="D7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>761608.56000000017</v>
+        <v>768178.99000000022</v>
       </c>
       <c r="E7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>12281.240000000002</v>
+        <v>11913.74</v>
       </c>
       <c r="F7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>146526.44999999998</v>
+        <v>152834.26999999999</v>
       </c>
       <c r="G7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>6869.08</v>
+        <v>11490.25</v>
       </c>
       <c r="H7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>927285.33000000007</v>
+        <v>944417.25000000023</v>
       </c>
       <c r="I7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>374979.93999999994</v>
+        <v>357848.0199999999</v>
       </c>
       <c r="J7" s="2">
         <f>VLOOKUP($C7,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
@@ -53819,11 +53819,11 @@
       </c>
       <c r="D8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>99537.17</v>
+        <v>105037.17</v>
       </c>
       <c r="E8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>5500</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -53839,15 +53839,15 @@
       </c>
       <c r="I8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>8382.36</v>
+        <v>18859.86</v>
       </c>
       <c r="J8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>139069.53</v>
+        <v>149547.03</v>
       </c>
       <c r="K8" s="2">
         <f>VLOOKUP($C8,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-52569.53</v>
+        <v>-63047.03</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" s="5">
@@ -53938,35 +53938,35 @@
       </c>
       <c r="D9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>112697.45999999999</v>
+        <v>137717.29999999999</v>
       </c>
       <c r="E9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>0</v>
+        <v>34510</v>
       </c>
       <c r="F9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>194181.90999999997</v>
+        <v>160631.90000000002</v>
       </c>
       <c r="G9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>3760.5</v>
+        <v>3972.86</v>
       </c>
       <c r="H9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>310639.87</v>
+        <v>336832.06</v>
       </c>
       <c r="I9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>221793.11000000007</v>
+        <v>238753.96000000002</v>
       </c>
       <c r="J9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>532432.9800000001</v>
+        <v>575586.02</v>
       </c>
       <c r="K9" s="2">
         <f>VLOOKUP($C9,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>0</v>
+        <v>-43153.040000000037</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" s="5">
@@ -54057,15 +54057,15 @@
       </c>
       <c r="D10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>1879230.2</v>
+        <v>1962204.1000000003</v>
       </c>
       <c r="E10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>58480.07</v>
+        <v>58536.83</v>
       </c>
       <c r="F10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>111879.58</v>
+        <v>97879.580000000016</v>
       </c>
       <c r="G10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -54073,19 +54073,19 @@
       </c>
       <c r="H10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>2049589.85</v>
+        <v>2118620.5100000002</v>
       </c>
       <c r="I10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>516907.43999999977</v>
+        <v>491626.20999999967</v>
       </c>
       <c r="J10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>2566497.29</v>
+        <v>2610246.7199999997</v>
       </c>
       <c r="K10" s="2">
         <f>VLOOKUP($C10,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>202393.71999999974</v>
+        <v>158644.29000000004</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="5">
@@ -54295,11 +54295,11 @@
       </c>
       <c r="D12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>343537.91</v>
+        <v>372223.73</v>
       </c>
       <c r="E12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>28100.98</v>
+        <v>9862.24</v>
       </c>
       <c r="F12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -54311,19 +54311,19 @@
       </c>
       <c r="H12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>386035.20999999996</v>
+        <v>396482.29</v>
       </c>
       <c r="I12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>147474.44</v>
+        <v>137067.35999999999</v>
       </c>
       <c r="J12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>533509.64999999991</v>
+        <v>533549.64999999991</v>
       </c>
       <c r="K12" s="2">
         <f>VLOOKUP($C12,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>89404.559999999939</v>
+        <v>89364.559999999939</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" s="5">
@@ -54412,11 +54412,11 @@
       </c>
       <c r="D13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>5652.78</v>
+        <v>46720.409999999996</v>
       </c>
       <c r="E13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>48723.82</v>
+        <v>11040.96</v>
       </c>
       <c r="F13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -54428,11 +54428,11 @@
       </c>
       <c r="H13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>54376.6</v>
+        <v>57761.369999999995</v>
       </c>
       <c r="I13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>305791.93</v>
+        <v>302407.15999999997</v>
       </c>
       <c r="J13" s="2">
         <f>VLOOKUP($C13,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
@@ -54648,35 +54648,35 @@
       </c>
       <c r="D15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>617578.93999999994</v>
+        <v>659128.20000000007</v>
       </c>
       <c r="E15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>285770.40000000002</v>
+        <v>286886.40000000002</v>
       </c>
       <c r="F15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>80295.999999999985</v>
+        <v>67378.709999999992</v>
       </c>
       <c r="G15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>281.10000000000002</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>983926.44</v>
+        <v>1013393.31</v>
       </c>
       <c r="I15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>40927.770000000004</v>
+        <v>30671.969999999998</v>
       </c>
       <c r="J15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>1024854.21</v>
+        <v>1044065.28</v>
       </c>
       <c r="K15" s="2">
         <f>VLOOKUP($C15,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>18889.830000000191</v>
+        <v>-321.23999999987427</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" s="5">
@@ -54822,6 +54822,12 @@
         <f>[1]RESUMO!J25</f>
         <v>33164.04</v>
       </c>
+      <c r="U16" s="4">
+        <v>46235</v>
+      </c>
+      <c r="V16" s="2">
+        <v>623822.48</v>
+      </c>
       <c r="X16" s="4">
         <v>45931</v>
       </c>
@@ -54832,7 +54838,18 @@
         <f t="shared" si="0"/>
         <v>10520153.699999997</v>
       </c>
-      <c r="AC16" s="2"/>
+      <c r="AB16" s="4">
+        <v>46235</v>
+      </c>
+      <c r="AC16" s="2">
+        <v>537115.20000000007</v>
+      </c>
+      <c r="AD16" s="2">
+        <v>126365.07</v>
+      </c>
+      <c r="AE16" s="2">
+        <v>326882.42999999988</v>
+      </c>
       <c r="AG16" s="4">
         <v>45901</v>
       </c>
@@ -54869,11 +54886,11 @@
       </c>
       <c r="D17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>541098.04</v>
+        <v>550896.84000000008</v>
       </c>
       <c r="E17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>8758.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="F17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -54885,7 +54902,7 @@
       </c>
       <c r="H17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>549856.84000000008</v>
+        <v>550896.84000000008</v>
       </c>
       <c r="I17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -54893,11 +54910,11 @@
       </c>
       <c r="J17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>595970.4800000001</v>
+        <v>597010.4800000001</v>
       </c>
       <c r="K17" s="2">
         <f>VLOOKUP($C17,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>170719.43999999983</v>
+        <v>169679.43999999983</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" s="5">
@@ -54971,11 +54988,11 @@
       </c>
       <c r="D18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>731519.75999999989</v>
+        <v>740758.89999999991</v>
       </c>
       <c r="E18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>3411.15</v>
+        <v>0</v>
       </c>
       <c r="F18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -54987,7 +55004,7 @@
       </c>
       <c r="H18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>738066.19</v>
+        <v>743894.17999999993</v>
       </c>
       <c r="I18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -54995,11 +55012,11 @@
       </c>
       <c r="J18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>738066.19</v>
+        <v>743894.17999999993</v>
       </c>
       <c r="K18" s="2">
         <f>VLOOKUP($C18,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-93697.589999999967</v>
+        <v>-99525.579999999958</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" s="5">
@@ -55072,15 +55089,15 @@
       </c>
       <c r="D19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>181892.92</v>
+        <v>190653.74000000002</v>
       </c>
       <c r="E19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>4432.91</v>
+        <v>0</v>
       </c>
       <c r="F19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>38401.549999999996</v>
+        <v>34073.61</v>
       </c>
       <c r="G19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -55088,7 +55105,7 @@
       </c>
       <c r="H19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>224727.38</v>
+        <v>224727.35000000003</v>
       </c>
       <c r="I19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -55096,11 +55113,11 @@
       </c>
       <c r="J19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>390725.5</v>
+        <v>390725.47000000003</v>
       </c>
       <c r="K19" s="2">
         <f>VLOOKUP($C19,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>327917.08999999973</v>
+        <v>327917.1199999997</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="5">
@@ -55275,23 +55292,23 @@
       </c>
       <c r="D21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>292479.10000000003</v>
+        <v>322514.71000000008</v>
       </c>
       <c r="E21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>11341.23</v>
+        <v>3121.4399999999991</v>
       </c>
       <c r="F21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>50559.19</v>
+        <v>33174.26</v>
       </c>
       <c r="G21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>2054.9899999999998</v>
+        <v>3317.4</v>
       </c>
       <c r="H21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>356434.51</v>
+        <v>362127.81000000011</v>
       </c>
       <c r="I21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -55299,11 +55316,11 @@
       </c>
       <c r="J21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>405739.67000000004</v>
+        <v>411432.97000000009</v>
       </c>
       <c r="K21" s="2">
         <f>VLOOKUP($C21,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>51353.649999999907</v>
+        <v>45660.34999999986</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="5">
@@ -55375,11 +55392,11 @@
       </c>
       <c r="D22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>5188602.8400000008</v>
+        <v>5190646.38</v>
       </c>
       <c r="E22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>2139.3000000000002</v>
+        <v>6904.3</v>
       </c>
       <c r="F22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -55387,11 +55404,11 @@
       </c>
       <c r="G22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>195.62</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>5218988.4000000004</v>
+        <v>5225601.3199999994</v>
       </c>
       <c r="I22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
@@ -55399,11 +55416,11 @@
       </c>
       <c r="J22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>5081988.4000000004</v>
+        <v>5088601.3199999994</v>
       </c>
       <c r="K22" s="2">
         <f>VLOOKUP($C22,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>98127.479999998584</v>
+        <v>91514.55999999959</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" s="5">
@@ -55475,35 +55492,35 @@
       </c>
       <c r="D23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>834611.95</v>
+        <v>866509.13</v>
       </c>
       <c r="E23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>15706.619999999999</v>
+        <v>1971.21</v>
       </c>
       <c r="F23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>66210.189999999988</v>
+        <v>53324.380000000005</v>
       </c>
       <c r="G23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>1786.65</v>
+        <v>12995.43</v>
       </c>
       <c r="H23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>918315.40999999992</v>
+        <v>934800.15</v>
       </c>
       <c r="I23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>172186.28999999998</v>
+        <v>156010.19</v>
       </c>
       <c r="J23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>1090501.7</v>
+        <v>1090810.3400000001</v>
       </c>
       <c r="K23" s="2">
         <f>VLOOKUP($C23,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>211036.7799999998</v>
+        <v>210728.13999999966</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="5">
@@ -55575,15 +55592,15 @@
       </c>
       <c r="D24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>64633.14</v>
+        <v>78628.340000000011</v>
       </c>
       <c r="E24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>13070.71</v>
+        <v>1751.4</v>
       </c>
       <c r="F24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>188651.67</v>
+        <v>188651.64</v>
       </c>
       <c r="G24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -55591,19 +55608,19 @@
       </c>
       <c r="H24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>266530.52</v>
+        <v>269206.38</v>
       </c>
       <c r="I24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>45311.9</v>
+        <v>45311.909999999996</v>
       </c>
       <c r="J24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>311842.42000000004</v>
+        <v>314518.28999999998</v>
       </c>
       <c r="K24" s="2">
         <f>VLOOKUP($C24,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>211809.43000000011</v>
+        <v>209133.56000000017</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" s="5">
@@ -55676,35 +55693,35 @@
       </c>
       <c r="D25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>493526.97999999986</v>
+        <v>573863.14999999991</v>
       </c>
       <c r="E25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>76704.799999999988</v>
+        <v>109025.22</v>
       </c>
       <c r="F25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>145093.53000000003</v>
+        <v>159953.03</v>
       </c>
       <c r="G25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
-        <v>45257.88</v>
+        <v>6323.1100000000006</v>
       </c>
       <c r="H25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>760583.18999999983</v>
+        <v>849164.50999999989</v>
       </c>
       <c r="I25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>39429.739999999991</v>
+        <v>-40000</v>
       </c>
       <c r="J25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>800012.92999999982</v>
+        <v>809164.50999999989</v>
       </c>
       <c r="K25" s="2">
         <f>VLOOKUP($C25,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>-467467.2799999998</v>
+        <v>-476618.85999999987</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="5">
@@ -55777,11 +55794,11 @@
       </c>
       <c r="D26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>67359.26999999999</v>
+        <v>81509.98</v>
       </c>
       <c r="E26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>14150.710000000001</v>
+        <v>5926.41</v>
       </c>
       <c r="F26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
@@ -55793,11 +55810,11 @@
       </c>
       <c r="H26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>81509.98</v>
+        <v>87436.39</v>
       </c>
       <c r="I26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>230451.89</v>
+        <v>224525.48</v>
       </c>
       <c r="J26" s="2">
         <f>VLOOKUP($C26,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
@@ -55832,6 +55849,16 @@
         <f>[1]RESUMO!J35</f>
         <v>144913.18000000005</v>
       </c>
+      <c r="X26" s="4">
+        <v>46235</v>
+      </c>
+      <c r="Y26" s="2">
+        <v>947074.47759999987</v>
+      </c>
+      <c r="Z26" s="13">
+        <f>Z25+Y26</f>
+        <v>19336051.921353843</v>
+      </c>
       <c r="AG26" s="4">
         <v>45931</v>
       </c>
@@ -55955,15 +55982,15 @@
       </c>
       <c r="D28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,3,0)</f>
-        <v>132112.32000000001</v>
+        <v>173651.19999999998</v>
       </c>
       <c r="E28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,4,0)</f>
-        <v>41538.880000000005</v>
+        <v>41538.879999999997</v>
       </c>
       <c r="F28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,5,0)</f>
-        <v>41538.879999999997</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,6,0)</f>
@@ -55971,19 +55998,19 @@
       </c>
       <c r="H28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,7,0)</f>
-        <v>215190.08000000002</v>
+        <v>215190.08</v>
       </c>
       <c r="I28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,9,0)</f>
-        <v>245999.59</v>
+        <v>14352.44</v>
       </c>
       <c r="J28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,10,0)</f>
-        <v>461189.67000000004</v>
+        <v>229542.52</v>
       </c>
       <c r="K28" s="2">
         <f>VLOOKUP($C28,'[1]MCC - OBRA'!$L$6:$V$918,11,0)</f>
-        <v>0</v>
+        <v>231647.15000000005</v>
       </c>
       <c r="L28" s="2"/>
       <c r="M28" s="5">
@@ -56226,7 +56253,7 @@
       </c>
       <c r="D31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,11,0)</f>
-        <v>1752027.23</v>
+        <v>1818331.6099999999</v>
       </c>
       <c r="E31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,12,0)</f>
@@ -56242,19 +56269,19 @@
       </c>
       <c r="H31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,15,0)</f>
-        <v>1752027.23</v>
+        <v>1818331.6099999999</v>
       </c>
       <c r="I31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,17,0)</f>
-        <v>517344.25500000035</v>
+        <v>463433.42400000058</v>
       </c>
       <c r="J31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,18,0)</f>
-        <v>2269371.4850000003</v>
+        <v>2281765.0340000005</v>
       </c>
       <c r="K31" s="2">
         <f>VLOOKUP($B31,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,19,0)</f>
-        <v>121694.51499999966</v>
+        <v>109300.96599999955</v>
       </c>
       <c r="M31" s="5">
         <f>[1]RESUMO!E40</f>
@@ -56314,15 +56341,15 @@
       </c>
       <c r="D32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,11,0)</f>
-        <v>4197678.5799999991</v>
+        <v>4458256.629999998</v>
       </c>
       <c r="E32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,12,0)</f>
-        <v>83164.98000000001</v>
+        <v>96431.510000000009</v>
       </c>
       <c r="F32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,13,0)</f>
-        <v>82233.159999999989</v>
+        <v>71973.159999999974</v>
       </c>
       <c r="G32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,14,0)</f>
@@ -56330,19 +56357,19 @@
       </c>
       <c r="H32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,15,0)</f>
-        <v>4363076.72</v>
+        <v>4626661.299999998</v>
       </c>
       <c r="I32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,17,0)</f>
-        <v>3371401.4500000007</v>
+        <v>3113420.4900000007</v>
       </c>
       <c r="J32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,18,0)</f>
-        <v>7734478.1699999999</v>
+        <v>7740081.7899999991</v>
       </c>
       <c r="K32" s="2">
         <f>VLOOKUP($B32,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,19,0)</f>
-        <v>-1364478.17</v>
+        <v>-1370081.7899999991</v>
       </c>
       <c r="M32" s="5">
         <f>[1]RESUMO!E41</f>
@@ -56490,7 +56517,7 @@
       </c>
       <c r="D34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,11,0)</f>
-        <v>1587120.41</v>
+        <v>2043120.41</v>
       </c>
       <c r="E34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,12,0)</f>
@@ -56506,19 +56533,19 @@
       </c>
       <c r="H34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,15,0)</f>
-        <v>1587120.41</v>
+        <v>2043120.41</v>
       </c>
       <c r="I34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,17,0)</f>
-        <v>-1496168.69</v>
+        <v>-2042368.69</v>
       </c>
       <c r="J34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,18,0)</f>
-        <v>90951.719999999972</v>
+        <v>751.71999999997206</v>
       </c>
       <c r="K34" s="2">
         <f>VLOOKUP($B34,'[1]MCC - INCORPORAÇÃO'!$D$7:$V$49,19,0)</f>
-        <v>-90951.719999999972</v>
+        <v>-751.71999999997206</v>
       </c>
       <c r="M34" s="5">
         <f>[1]RESUMO!E43</f>
@@ -56558,6 +56585,12 @@
       </c>
       <c r="AK34" s="2">
         <v>23400.240000000002</v>
+      </c>
+      <c r="AM34" s="4">
+        <v>46235</v>
+      </c>
+      <c r="AN34" s="2">
+        <v>163327.64000000001</v>
       </c>
     </row>
     <row r="35" spans="1:40" x14ac:dyDescent="0.3">
@@ -56743,7 +56776,7 @@
       </c>
       <c r="N39" s="2">
         <f>[1]RESUMO!F48</f>
-        <v>564642.35999999964</v>
+        <v>564642.35999999952</v>
       </c>
       <c r="O39" s="2">
         <f>[1]RESUMO!G48</f>
@@ -56759,7 +56792,7 @@
       </c>
       <c r="R39" s="2">
         <f>[1]RESUMO!J48</f>
-        <v>564642.35999999964</v>
+        <v>564642.35999999952</v>
       </c>
       <c r="AG39" s="4">
         <v>45962</v>
@@ -57408,23 +57441,23 @@
       </c>
       <c r="N55" s="9">
         <f>[1]RESUMO!F64</f>
-        <v>0</v>
+        <v>1446362.6999999979</v>
       </c>
       <c r="O55" s="9">
         <f>[1]RESUMO!G64</f>
-        <v>374270.22999999981</v>
+        <v>0</v>
       </c>
       <c r="P55" s="9">
         <f>[1]RESUMO!H64</f>
-        <v>116711.15000000007</v>
+        <v>11333.33</v>
       </c>
       <c r="Q55" s="9">
         <f>[1]RESUMO!I64</f>
-        <v>24294.039999999997</v>
+        <v>0</v>
       </c>
       <c r="R55" s="2">
         <f>[1]RESUMO!J64</f>
-        <v>515275.42000000051</v>
+        <v>1457696.0299999979</v>
       </c>
       <c r="AG55" s="4">
         <v>46023</v>
@@ -57453,19 +57486,19 @@
       </c>
       <c r="O56" s="9">
         <f>[1]RESUMO!G65</f>
-        <v>28556.610000000022</v>
+        <v>392909.62000000005</v>
       </c>
       <c r="P56" s="9">
         <f>[1]RESUMO!H65</f>
-        <v>250980.36000000007</v>
+        <v>143976.28999999998</v>
       </c>
       <c r="Q56" s="9">
         <f>[1]RESUMO!I65</f>
-        <v>15178.140000000001</v>
+        <v>13962.84</v>
       </c>
       <c r="R56" s="2">
         <f>[1]RESUMO!J65</f>
-        <v>294715.10999999993</v>
+        <v>550848.75000000035</v>
       </c>
       <c r="AG56" s="4">
         <v>46023</v>
@@ -57494,19 +57527,19 @@
       </c>
       <c r="O57" s="9">
         <f>[1]RESUMO!G66</f>
-        <v>24354.770000000011</v>
+        <v>37302.500000000007</v>
       </c>
       <c r="P57" s="9">
         <f>[1]RESUMO!H66</f>
-        <v>214225.75000000009</v>
+        <v>201573.16</v>
       </c>
       <c r="Q57" s="9">
         <f>[1]RESUMO!I66</f>
-        <v>24970.289999999997</v>
+        <v>12533.44</v>
       </c>
       <c r="R57" s="2">
         <f>[1]RESUMO!J66</f>
-        <v>263550.80999999988</v>
+        <v>251409.09999999974</v>
       </c>
       <c r="AG57" s="4"/>
       <c r="AH57" s="8"/>
@@ -57522,19 +57555,19 @@
       </c>
       <c r="O58" s="9">
         <f>[1]RESUMO!G67</f>
-        <v>9720.86</v>
+        <v>18896.22</v>
       </c>
       <c r="P58" s="9">
         <f>[1]RESUMO!H67</f>
-        <v>281010.50999999995</v>
+        <v>462662.68000000011</v>
       </c>
       <c r="Q58" s="9">
         <f>[1]RESUMO!I67</f>
-        <v>214.95000000000007</v>
+        <v>45025.200000000019</v>
       </c>
       <c r="R58" s="2">
         <f>[1]RESUMO!J67</f>
-        <v>290946.31999999995</v>
+        <v>526584.09999999986</v>
       </c>
       <c r="AG58" s="4"/>
     </row>
@@ -57553,15 +57586,15 @@
       </c>
       <c r="P59" s="9">
         <f>[1]RESUMO!H68</f>
-        <v>62354.84</v>
+        <v>50192.45</v>
       </c>
       <c r="Q59" s="9">
         <f>[1]RESUMO!I68</f>
-        <v>0</v>
+        <v>7314.9399999999978</v>
       </c>
       <c r="R59" s="2">
         <f>[1]RESUMO!J68</f>
-        <v>118116.68000000001</v>
+        <v>113269.22999999998</v>
       </c>
       <c r="AG59" s="4"/>
     </row>
@@ -57580,7 +57613,7 @@
       </c>
       <c r="P60" s="9">
         <f>[1]RESUMO!H69</f>
-        <v>159653.63000000003</v>
+        <v>105433.04000000001</v>
       </c>
       <c r="Q60" s="9">
         <f>[1]RESUMO!I69</f>
@@ -57588,7 +57621,7 @@
       </c>
       <c r="R60" s="2">
         <f>[1]RESUMO!J69</f>
-        <v>447229.63000000006</v>
+        <v>393009.04</v>
       </c>
       <c r="AG60" s="4"/>
     </row>
@@ -57607,7 +57640,7 @@
       </c>
       <c r="P61" s="9">
         <f>[1]RESUMO!H70</f>
-        <v>85084.569999999978</v>
+        <v>100509.37999999999</v>
       </c>
       <c r="Q61" s="9">
         <f>[1]RESUMO!I70</f>
@@ -57615,7 +57648,7 @@
       </c>
       <c r="R61" s="2">
         <f>[1]RESUMO!J70</f>
-        <v>86310.569999999963</v>
+        <v>101735.37999999999</v>
       </c>
       <c r="AG61" s="4"/>
     </row>
@@ -57634,7 +57667,7 @@
       </c>
       <c r="P62" s="9">
         <f>[1]RESUMO!H71</f>
-        <v>191066.37000000011</v>
+        <v>188686.06999999995</v>
       </c>
       <c r="Q62" s="9">
         <f>[1]RESUMO!I71</f>
@@ -57642,7 +57675,7 @@
       </c>
       <c r="R62" s="2">
         <f>[1]RESUMO!J71</f>
-        <v>192292.37000000011</v>
+        <v>189912.06999999995</v>
       </c>
     </row>
     <row r="63" spans="13:38" x14ac:dyDescent="0.3">
@@ -57660,7 +57693,7 @@
       </c>
       <c r="P63" s="9">
         <f>[1]RESUMO!H72</f>
-        <v>17596.669999999998</v>
+        <v>17596.689999999999</v>
       </c>
       <c r="Q63" s="9">
         <f>[1]RESUMO!I72</f>
@@ -57668,7 +57701,7 @@
       </c>
       <c r="R63" s="2">
         <f>[1]RESUMO!J72</f>
-        <v>18822.669999999998</v>
+        <v>18822.689999999999</v>
       </c>
     </row>
     <row r="64" spans="13:38" x14ac:dyDescent="0.3">
